--- a/InputData/trans/BHNVFEAL/BAU Historical New Veh Fuel Economy After Lifetime.xlsx
+++ b/InputData/trans/BHNVFEAL/BAU Historical New Veh Fuel Economy After Lifetime.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\United States\us-eps\InputData\trans\BHNVFEAL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29D056D9-250C-41EE-99AC-A85FBBA54DAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A986EBF-6A38-4458-9EF9-9AB3274F4F22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -1290,7 +1290,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1327,17 +1327,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="154" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="155" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="11" fontId="0" fillId="30" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="11" fontId="0" fillId="30" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="11" fontId="41" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="11" fontId="0" fillId="30" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="11" fontId="43" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="154" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="156">
     <cellStyle name="20% - Accent1 2" xfId="8" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -9012,6 +9008,7 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="31.140625" customWidth="1"/>
+    <col min="2" max="2" width="21.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:34" ht="30">
@@ -9430,7 +9427,7 @@
       <c r="A5" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="4">
+      <c r="B5" s="32">
         <f>Extrapolations!Q6</f>
         <v>4.3905417607014065E-4</v>
       </c>
@@ -17158,104 +17155,104 @@
       <c r="AJ15" s="4"/>
       <c r="AK15" s="4"/>
     </row>
-    <row r="16" spans="1:37" s="36" customFormat="1">
-      <c r="A16" s="36" t="s">
+    <row r="16" spans="1:37" s="31" customFormat="1">
+      <c r="A16" s="31" t="s">
         <v>16</v>
       </c>
-      <c r="B16" s="36" t="s">
+      <c r="B16" s="31" t="s">
         <v>22</v>
       </c>
-      <c r="C16" s="36" t="s">
+      <c r="C16" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="D16" s="36">
+      <c r="D16" s="31">
         <v>3.5120030000000001E-3</v>
       </c>
-      <c r="E16" s="36">
+      <c r="E16" s="31">
         <v>3.3663400000000002E-3</v>
       </c>
-      <c r="F16" s="36">
+      <c r="F16" s="31">
         <v>3.3698929999999997E-3</v>
       </c>
-      <c r="G16" s="36">
+      <c r="G16" s="31">
         <v>3.3734500000000001E-3</v>
       </c>
-      <c r="H16" s="36">
+      <c r="H16" s="31">
         <v>3.3770099999999997E-3</v>
       </c>
-      <c r="I16" s="36">
+      <c r="I16" s="31">
         <v>3.3805740000000003E-3</v>
       </c>
-      <c r="J16" s="36">
+      <c r="J16" s="31">
         <v>3.3841420000000001E-3</v>
       </c>
-      <c r="K16" s="36">
+      <c r="K16" s="31">
         <v>3.3877130000000001E-3</v>
       </c>
-      <c r="L16" s="36">
+      <c r="L16" s="31">
         <v>3.391289E-3</v>
       </c>
-      <c r="M16" s="36">
+      <c r="M16" s="31">
         <v>3.3948680000000001E-3</v>
       </c>
-      <c r="N16" s="36">
+      <c r="N16" s="31">
         <v>3.3984510000000002E-3</v>
       </c>
-      <c r="O16" s="36">
+      <c r="O16" s="31">
         <v>3.4020370000000001E-3</v>
       </c>
-      <c r="P16" s="36">
+      <c r="P16" s="31">
         <v>3.405628E-3</v>
       </c>
-      <c r="Q16" s="36">
+      <c r="Q16" s="31">
         <v>3.4092220000000004E-3</v>
       </c>
-      <c r="R16" s="36">
+      <c r="R16" s="31">
         <v>3.41282E-3</v>
       </c>
-      <c r="S16" s="36">
+      <c r="S16" s="31">
         <v>3.4164219999999997E-3</v>
       </c>
-      <c r="T16" s="36">
+      <c r="T16" s="31">
         <v>3.420027E-3</v>
       </c>
-      <c r="U16" s="36">
+      <c r="U16" s="31">
         <v>3.4236369999999998E-3</v>
       </c>
-      <c r="V16" s="36">
+      <c r="V16" s="31">
         <v>3.4272499999999997E-3</v>
       </c>
-      <c r="W16" s="36">
+      <c r="W16" s="31">
         <v>3.4308670000000002E-3</v>
       </c>
-      <c r="X16" s="36">
+      <c r="X16" s="31">
         <v>3.4344879999999999E-3</v>
       </c>
-      <c r="Y16" s="36">
+      <c r="Y16" s="31">
         <v>3.438113E-3</v>
       </c>
-      <c r="Z16" s="36">
+      <c r="Z16" s="31">
         <v>3.4417409999999999E-3</v>
       </c>
-      <c r="AA16" s="36">
+      <c r="AA16" s="31">
         <v>3.4453729999999998E-3</v>
       </c>
-      <c r="AB16" s="36">
+      <c r="AB16" s="31">
         <v>3.4490099999999997E-3</v>
       </c>
-      <c r="AC16" s="36">
+      <c r="AC16" s="31">
         <v>3.4526489999999999E-3</v>
       </c>
-      <c r="AD16" s="36">
+      <c r="AD16" s="31">
         <v>3.456293E-3</v>
       </c>
-      <c r="AE16" s="36">
+      <c r="AE16" s="31">
         <v>3.4599410000000002E-3</v>
       </c>
-      <c r="AF16" s="36">
+      <c r="AF16" s="31">
         <v>3.4635930000000001E-3</v>
       </c>
-      <c r="AG16" s="36">
+      <c r="AG16" s="31">
         <v>3.467248E-3</v>
       </c>
     </row>
@@ -18533,16 +18530,16 @@
         <v>7</v>
       </c>
       <c r="B4">
-        <v>1.2987877392438942E-3</v>
+        <v>1.3768785799698285E-3</v>
       </c>
       <c r="C4">
-        <v>4.0416928234185732E-4</v>
+        <v>4.2847034255362628E-4</v>
       </c>
       <c r="D4">
-        <v>4.0416928234185732E-4</v>
+        <v>4.2847034255362628E-4</v>
       </c>
       <c r="E4">
-        <v>4.0416928234185732E-4</v>
+        <v>4.2847034255362628E-4</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -18551,7 +18548,7 @@
         <v>0</v>
       </c>
       <c r="H4">
-        <v>1.2125078470255717E-3</v>
+        <v>1.2854110276608786E-3</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -18715,16 +18712,16 @@
         <v>7</v>
       </c>
       <c r="B12">
-        <v>4.6228905610524535E-4</v>
+        <v>5.4991909569712227E-4</v>
       </c>
       <c r="C12">
-        <v>1.4385956257126716E-4</v>
+        <v>1.7112912259502911E-4</v>
       </c>
       <c r="D12">
-        <v>1.4385956257126716E-4</v>
+        <v>1.7112912259502911E-4</v>
       </c>
       <c r="E12">
-        <v>1.4385956257126716E-4</v>
+        <v>1.7112912259502911E-4</v>
       </c>
       <c r="F12">
         <v>0</v>
@@ -18733,7 +18730,7 @@
         <v>0</v>
       </c>
       <c r="H12">
-        <v>4.3157868771380144E-4</v>
+        <v>5.1338736778508724E-4</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -19208,9 +19205,6 @@
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="15" max="15" width="11.42578125" customWidth="1"/>
-    <col min="28" max="39" width="9.140625" style="31"/>
-    <col min="40" max="40" width="8.7109375" style="31"/>
-    <col min="42" max="42" width="9.140625" style="31"/>
     <col min="43" max="43" width="9.140625" style="23"/>
   </cols>
   <sheetData>
@@ -19290,49 +19284,49 @@
       <c r="AA1">
         <v>2007</v>
       </c>
-      <c r="AB1" s="31">
+      <c r="AB1">
         <v>2008</v>
       </c>
-      <c r="AC1" s="31">
+      <c r="AC1">
         <v>2009</v>
       </c>
-      <c r="AD1" s="31">
+      <c r="AD1">
         <v>2010</v>
       </c>
-      <c r="AE1" s="31">
+      <c r="AE1">
         <v>2011</v>
       </c>
-      <c r="AF1" s="31">
+      <c r="AF1">
         <v>2012</v>
       </c>
-      <c r="AG1" s="31">
+      <c r="AG1">
         <v>2013</v>
       </c>
-      <c r="AH1" s="31">
+      <c r="AH1">
         <v>2014</v>
       </c>
-      <c r="AI1" s="31">
+      <c r="AI1">
         <v>2015</v>
       </c>
-      <c r="AJ1" s="31">
+      <c r="AJ1">
         <v>2016</v>
       </c>
-      <c r="AK1" s="31">
+      <c r="AK1">
         <v>2017</v>
       </c>
-      <c r="AL1" s="31">
+      <c r="AL1">
         <v>2018</v>
       </c>
-      <c r="AM1" s="31">
+      <c r="AM1">
         <v>2019</v>
       </c>
-      <c r="AN1" s="31">
+      <c r="AN1">
         <v>2020</v>
       </c>
       <c r="AO1">
         <v>2021</v>
       </c>
-      <c r="AP1" s="31">
+      <c r="AP1">
         <v>2022</v>
       </c>
       <c r="AQ1" s="23">
@@ -19455,55 +19449,55 @@
         <f>Calculations!C16</f>
         <v>3.142498616321923E-4</v>
       </c>
-      <c r="AB2" s="32">
+      <c r="AB2" s="26">
         <f t="shared" ref="AB2:AO2" si="0">($AR$2-$AA$2)/COUNT($AB$1:$AR$1)+AA2</f>
         <v>3.1779260113808729E-4</v>
       </c>
-      <c r="AC2" s="32">
+      <c r="AC2" s="26">
         <f t="shared" si="0"/>
         <v>3.2133534064398227E-4</v>
       </c>
-      <c r="AD2" s="32">
+      <c r="AD2" s="26">
         <f t="shared" si="0"/>
         <v>3.2487808014987726E-4</v>
       </c>
-      <c r="AE2" s="32">
+      <c r="AE2" s="26">
         <f t="shared" si="0"/>
         <v>3.2842081965577224E-4</v>
       </c>
-      <c r="AF2" s="32">
+      <c r="AF2" s="26">
         <f t="shared" si="0"/>
         <v>3.3196355916166722E-4</v>
       </c>
-      <c r="AG2" s="32">
+      <c r="AG2" s="26">
         <f t="shared" si="0"/>
         <v>3.3550629866756221E-4</v>
       </c>
-      <c r="AH2" s="32">
+      <c r="AH2" s="26">
         <f t="shared" si="0"/>
         <v>3.3904903817345719E-4</v>
       </c>
-      <c r="AI2" s="32">
+      <c r="AI2" s="26">
         <f t="shared" si="0"/>
         <v>3.4259177767935218E-4</v>
       </c>
-      <c r="AJ2" s="32">
+      <c r="AJ2" s="26">
         <f t="shared" si="0"/>
         <v>3.4613451718524716E-4</v>
       </c>
-      <c r="AK2" s="32">
+      <c r="AK2" s="26">
         <f t="shared" si="0"/>
         <v>3.4967725669114214E-4</v>
       </c>
-      <c r="AL2" s="32">
+      <c r="AL2" s="26">
         <f t="shared" si="0"/>
         <v>3.5321999619703713E-4</v>
       </c>
-      <c r="AM2" s="32">
+      <c r="AM2" s="26">
         <f t="shared" si="0"/>
         <v>3.5676273570293211E-4</v>
       </c>
-      <c r="AN2" s="32">
+      <c r="AN2" s="26">
         <f t="shared" si="0"/>
         <v>3.603054752088271E-4</v>
       </c>
@@ -19511,11 +19505,11 @@
         <f t="shared" si="0"/>
         <v>3.6384821471472208E-4</v>
       </c>
-      <c r="AP2" s="32">
+      <c r="AP2" s="26">
         <f>($AR$2-$AA$2)/COUNT($AB$1:$AR$1)+AO2</f>
         <v>3.6739095422061706E-4</v>
       </c>
-      <c r="AQ2" s="32">
+      <c r="AQ2" s="26">
         <f>($AR$2-$AA$2)/COUNT($AB$1:$AR$1)+AP2</f>
         <v>3.7093369372651205E-4</v>
       </c>
@@ -19661,71 +19655,71 @@
       <c r="X3" s="9"/>
       <c r="Y3" s="9"/>
       <c r="Z3" s="9"/>
-      <c r="AA3" s="30" cm="1">
+      <c r="AA3" s="4" cm="1">
         <f t="array" ref="AA3">TREND($AQ$3:$AU$3,$AQ$1:$AU$1,AA1)</f>
         <v>6.2736507518388511E-5</v>
       </c>
-      <c r="AB3" s="30" cm="1">
+      <c r="AB3" s="4" cm="1">
         <f t="array" ref="AB3">TREND($AQ$3:$AU$3,$AQ$1:$AU$1,AB1)</f>
         <v>6.3701994710036553E-5</v>
       </c>
-      <c r="AC3" s="30" cm="1">
+      <c r="AC3" s="4" cm="1">
         <f t="array" ref="AC3">TREND($AQ$3:$AU$3,$AQ$1:$AU$1,AC1)</f>
         <v>6.4667481901684379E-5</v>
       </c>
-      <c r="AD3" s="30" cm="1">
+      <c r="AD3" s="4" cm="1">
         <f t="array" ref="AD3">TREND($AQ$3:$AU$3,$AQ$1:$AU$1,AD1)</f>
         <v>6.5632969093332421E-5</v>
       </c>
-      <c r="AE3" s="30" cm="1">
+      <c r="AE3" s="4" cm="1">
         <f t="array" ref="AE3">TREND($AQ$3:$AU$3,$AQ$1:$AU$1,AE1)</f>
         <v>6.6598456284980246E-5</v>
       </c>
-      <c r="AF3" s="30" cm="1">
+      <c r="AF3" s="4" cm="1">
         <f t="array" ref="AF3">TREND($AQ$3:$AU$3,$AQ$1:$AU$1,AF1)</f>
         <v>6.7563943476628288E-5</v>
       </c>
-      <c r="AG3" s="30" cm="1">
+      <c r="AG3" s="4" cm="1">
         <f t="array" ref="AG3">TREND($AQ$3:$AU$3,$AQ$1:$AU$1,AG1)</f>
         <v>6.8529430668276114E-5</v>
       </c>
-      <c r="AH3" s="30" cm="1">
+      <c r="AH3" s="4" cm="1">
         <f t="array" ref="AH3">TREND($AQ$3:$AU$3,$AQ$1:$AU$1,AH1)</f>
         <v>6.9494917859924156E-5</v>
       </c>
-      <c r="AI3" s="30" cm="1">
+      <c r="AI3" s="4" cm="1">
         <f t="array" ref="AI3">TREND($AQ$3:$AU$3,$AQ$1:$AU$1,AI1)</f>
         <v>7.0460405051572198E-5</v>
       </c>
-      <c r="AJ3" s="30" cm="1">
+      <c r="AJ3" s="4" cm="1">
         <f t="array" ref="AJ3">TREND($AQ$3:$AU$3,$AQ$1:$AU$1,AJ1)</f>
         <v>7.1425892243220023E-5</v>
       </c>
-      <c r="AK3" s="30" cm="1">
+      <c r="AK3" s="4" cm="1">
         <f t="array" ref="AK3">TREND($AQ$3:$AU$3,$AQ$1:$AU$1,AK1)</f>
         <v>7.2391379434868066E-5</v>
       </c>
-      <c r="AL3" s="30" cm="1">
+      <c r="AL3" s="4" cm="1">
         <f t="array" ref="AL3">TREND($AQ$3:$AU$3,$AQ$1:$AU$1,AL1)</f>
         <v>7.3356866626515891E-5</v>
       </c>
-      <c r="AM3" s="30" cm="1">
+      <c r="AM3" s="4" cm="1">
         <f t="array" ref="AM3">TREND($AQ$3:$AU$3,$AQ$1:$AU$1,AM1)</f>
         <v>7.4322353818163933E-5</v>
       </c>
-      <c r="AN3" s="30" cm="1">
+      <c r="AN3" s="4" cm="1">
         <f t="array" ref="AN3">TREND($AQ$3:$AU$3,$AQ$1:$AU$1,AN1)</f>
         <v>7.5287841009811758E-5</v>
       </c>
-      <c r="AO3" s="30" cm="1">
+      <c r="AO3" s="4" cm="1">
         <f t="array" ref="AO3">TREND($AQ$3:$AU$3,$AQ$1:$AU$1,AO1)</f>
         <v>7.6253328201459801E-5</v>
       </c>
-      <c r="AP3" s="30" cm="1">
+      <c r="AP3" s="4" cm="1">
         <f t="array" ref="AP3">TREND($AR$3:$AV$3,$AR$1:$AV$1,AP1)</f>
         <v>7.6915445435660028E-5</v>
       </c>
-      <c r="AQ3" s="30" cm="1">
+      <c r="AQ3" s="4" cm="1">
         <f t="array" ref="AQ3">TREND($AR$3:$AV$3,$AR$1:$AV$1,AQ1)</f>
         <v>7.8010948323356793E-5</v>
       </c>
@@ -19920,67 +19914,67 @@
         <f t="shared" si="1"/>
         <v>9.9033214307749757E-4</v>
       </c>
-      <c r="AB4" s="30">
+      <c r="AB4" s="4">
         <f t="shared" si="1"/>
         <v>9.9152077795891806E-4</v>
       </c>
-      <c r="AC4" s="30">
+      <c r="AC4" s="4">
         <f t="shared" si="1"/>
         <v>9.9270941284033856E-4</v>
       </c>
-      <c r="AD4" s="30">
+      <c r="AD4" s="4">
         <f t="shared" si="1"/>
         <v>9.9389804772175906E-4</v>
       </c>
-      <c r="AE4" s="30">
+      <c r="AE4" s="4">
         <f t="shared" si="1"/>
         <v>9.9508668260317955E-4</v>
       </c>
-      <c r="AF4" s="30">
+      <c r="AF4" s="4">
         <f t="shared" si="1"/>
         <v>9.9627531748460005E-4</v>
       </c>
-      <c r="AG4" s="30">
+      <c r="AG4" s="4">
         <f>AG5/AH5*AH4</f>
         <v>9.9746395236602055E-4</v>
       </c>
-      <c r="AH4" s="30">
+      <c r="AH4" s="4">
         <f t="shared" si="1"/>
         <v>9.9865258724744104E-4</v>
       </c>
-      <c r="AI4" s="30">
+      <c r="AI4" s="4">
         <f t="shared" si="1"/>
         <v>9.9984122212886154E-4</v>
       </c>
-      <c r="AJ4" s="30">
+      <c r="AJ4" s="4">
         <f>AJ5/AK5*AK4</f>
         <v>1.001029857010282E-3</v>
       </c>
-      <c r="AK4" s="33">
+      <c r="AK4" s="19">
         <f>AK5/AL5*AL4</f>
         <v>1.0022184918917025E-3</v>
       </c>
-      <c r="AL4" s="33">
+      <c r="AL4" s="19">
         <f>AL5/AM5*AM4</f>
         <v>1.003407126773123E-3</v>
       </c>
-      <c r="AM4" s="33">
+      <c r="AM4" s="19">
         <f>AM5/AN5*AN4</f>
         <v>1.0045957616545435E-3</v>
       </c>
-      <c r="AN4" s="33">
+      <c r="AN4" s="19">
         <f t="shared" ref="AN4:AQ4" si="2">AN5/AO5*AO4</f>
         <v>1.005784396535964E-3</v>
       </c>
-      <c r="AO4" s="33">
+      <c r="AO4" s="19">
         <f t="shared" si="2"/>
         <v>1.0069730314173845E-3</v>
       </c>
-      <c r="AP4" s="33">
+      <c r="AP4" s="19">
         <f t="shared" si="2"/>
         <v>1.008161666298805E-3</v>
       </c>
-      <c r="AQ4" s="33">
+      <c r="AQ4" s="19">
         <f t="shared" si="2"/>
         <v>1.0105389360616456E-3</v>
       </c>
@@ -20160,7 +20154,7 @@
         <v>7.8134709903309753E-4</v>
       </c>
       <c r="X5" s="4">
-        <f t="shared" ref="X5:AP5" si="4">($AQ$5-$V$5)/COUNT($V$1:$AQ$1)+W5</f>
+        <f t="shared" ref="X5:AN5" si="4">($AQ$5-$V$5)/COUNT($V$1:$AQ$1)+W5</f>
         <v>7.8228942606352163E-4</v>
       </c>
       <c r="Y5" s="4">
@@ -20231,7 +20225,7 @@
         <f>($AQ$5-$V$5)/COUNT($V$1:$AQ$1)+AN5</f>
         <v>7.9830898558073125E-4</v>
       </c>
-      <c r="AP5" s="30">
+      <c r="AP5" s="4">
         <f>($AQ$5-$V$5)/COUNT($V$1:$AQ$1)+AO5</f>
         <v>7.9925131261115534E-4</v>
       </c>
@@ -20370,111 +20364,111 @@
       <c r="M6" s="9"/>
       <c r="N6" s="9"/>
       <c r="O6" s="9"/>
-      <c r="P6" s="30">
+      <c r="P6" s="4">
         <f t="shared" ref="P6:AM6" si="5">TREND($AQ6:$BR6,$AQ$1:$BR$1,P$1)</f>
         <v>4.3905417607014065E-4</v>
       </c>
-      <c r="Q6" s="30">
+      <c r="Q6" s="4">
+        <f>TREND($AQ6:$BR6,$AQ$1:$BR$1,Q$1)</f>
+        <v>4.3905417607014065E-4</v>
+      </c>
+      <c r="R6" s="4">
         <f t="shared" si="5"/>
         <v>4.3905417607014065E-4</v>
       </c>
-      <c r="R6" s="30">
+      <c r="S6" s="4">
         <f t="shared" si="5"/>
         <v>4.3905417607014065E-4</v>
       </c>
-      <c r="S6" s="30">
+      <c r="T6" s="4">
         <f t="shared" si="5"/>
         <v>4.3905417607014065E-4</v>
       </c>
-      <c r="T6" s="30">
+      <c r="U6" s="4">
         <f t="shared" si="5"/>
         <v>4.3905417607014065E-4</v>
       </c>
-      <c r="U6" s="30">
+      <c r="V6" s="4">
         <f t="shared" si="5"/>
         <v>4.3905417607014065E-4</v>
       </c>
-      <c r="V6" s="30">
+      <c r="W6" s="4">
         <f t="shared" si="5"/>
         <v>4.3905417607014065E-4</v>
       </c>
-      <c r="W6" s="30">
+      <c r="X6" s="4">
         <f t="shared" si="5"/>
         <v>4.3905417607014065E-4</v>
       </c>
-      <c r="X6" s="30">
+      <c r="Y6" s="4">
         <f t="shared" si="5"/>
         <v>4.3905417607014065E-4</v>
       </c>
-      <c r="Y6" s="30">
+      <c r="Z6" s="4">
         <f t="shared" si="5"/>
         <v>4.3905417607014065E-4</v>
       </c>
-      <c r="Z6" s="30">
+      <c r="AA6" s="4">
         <f t="shared" si="5"/>
         <v>4.3905417607014065E-4</v>
       </c>
-      <c r="AA6" s="30">
+      <c r="AB6" s="4">
         <f t="shared" si="5"/>
         <v>4.3905417607014065E-4</v>
       </c>
-      <c r="AB6" s="30">
+      <c r="AC6" s="4">
         <f t="shared" si="5"/>
         <v>4.3905417607014065E-4</v>
       </c>
-      <c r="AC6" s="30">
+      <c r="AD6" s="4">
         <f t="shared" si="5"/>
         <v>4.3905417607014065E-4</v>
       </c>
-      <c r="AD6" s="30">
+      <c r="AE6" s="4">
         <f t="shared" si="5"/>
         <v>4.3905417607014065E-4</v>
       </c>
-      <c r="AE6" s="30">
+      <c r="AF6" s="4">
         <f t="shared" si="5"/>
         <v>4.3905417607014065E-4</v>
       </c>
-      <c r="AF6" s="30">
+      <c r="AG6" s="4">
         <f t="shared" si="5"/>
         <v>4.3905417607014065E-4</v>
       </c>
-      <c r="AG6" s="30">
+      <c r="AH6" s="4">
         <f t="shared" si="5"/>
         <v>4.3905417607014065E-4</v>
       </c>
-      <c r="AH6" s="30">
+      <c r="AI6" s="4">
         <f t="shared" si="5"/>
         <v>4.3905417607014065E-4</v>
       </c>
-      <c r="AI6" s="30">
+      <c r="AJ6" s="4">
         <f t="shared" si="5"/>
         <v>4.3905417607014065E-4</v>
       </c>
-      <c r="AJ6" s="30">
+      <c r="AK6" s="4">
         <f t="shared" si="5"/>
         <v>4.3905417607014065E-4</v>
       </c>
-      <c r="AK6" s="30">
+      <c r="AL6" s="4">
         <f t="shared" si="5"/>
         <v>4.3905417607014065E-4</v>
       </c>
-      <c r="AL6" s="30">
+      <c r="AM6" s="4">
         <f t="shared" si="5"/>
         <v>4.3905417607014065E-4</v>
       </c>
-      <c r="AM6" s="30">
-        <f t="shared" si="5"/>
-        <v>4.3905417607014065E-4</v>
-      </c>
-      <c r="AN6" s="30">
+      <c r="AN6" s="4">
         <f>TREND($AQ6:$BR6,$AQ$1:$BR$1,AN$1)</f>
         <v>4.3905417607014065E-4</v>
       </c>
-      <c r="AO6" s="30">
+      <c r="AO6" s="4">
         <f t="shared" ref="AO6:AP6" si="6">TREND($AQ6:$BR6,$AQ$1:$BR$1,AO$1)</f>
         <v>4.3905417607014065E-4</v>
       </c>
-      <c r="AP6" s="30">
+      <c r="AP6" s="4">
         <f t="shared" si="6"/>
         <v>4.3905417607014065E-4</v>
       </c>
@@ -20934,55 +20928,55 @@
         <f t="shared" si="8"/>
         <v>7.1745362435245036E-5</v>
       </c>
-      <c r="AB8" s="30">
+      <c r="AB8" s="4">
         <f t="shared" si="8"/>
         <v>7.1745362435245036E-5</v>
       </c>
-      <c r="AC8" s="30">
+      <c r="AC8" s="4">
         <f t="shared" si="8"/>
         <v>7.1745362435245036E-5</v>
       </c>
-      <c r="AD8" s="30">
+      <c r="AD8" s="4">
         <f t="shared" si="8"/>
         <v>7.1745362435245036E-5</v>
       </c>
-      <c r="AE8" s="30">
+      <c r="AE8" s="4">
         <f t="shared" si="8"/>
         <v>7.1745362435245036E-5</v>
       </c>
-      <c r="AF8" s="30">
+      <c r="AF8" s="4">
         <f t="shared" si="8"/>
         <v>7.1745362435245036E-5</v>
       </c>
-      <c r="AG8" s="30">
+      <c r="AG8" s="4">
         <f t="shared" si="8"/>
         <v>7.1745362435245036E-5</v>
       </c>
-      <c r="AH8" s="30">
+      <c r="AH8" s="4">
         <f t="shared" si="8"/>
         <v>7.1745362435245036E-5</v>
       </c>
-      <c r="AI8" s="30">
+      <c r="AI8" s="4">
         <f t="shared" si="8"/>
         <v>7.1745362435245036E-5</v>
       </c>
-      <c r="AJ8" s="30">
+      <c r="AJ8" s="4">
         <f t="shared" si="8"/>
         <v>7.1745362435245036E-5</v>
       </c>
-      <c r="AK8" s="30">
+      <c r="AK8" s="4">
         <f t="shared" si="8"/>
         <v>7.1745362435245036E-5</v>
       </c>
-      <c r="AL8" s="30">
+      <c r="AL8" s="4">
         <f t="shared" si="8"/>
         <v>7.1745362435245036E-5</v>
       </c>
-      <c r="AM8" s="30">
+      <c r="AM8" s="4">
         <f t="shared" si="8"/>
         <v>7.1745362435245036E-5</v>
       </c>
-      <c r="AN8" s="30">
+      <c r="AN8" s="4">
         <f t="shared" si="8"/>
         <v>7.1745362435245036E-5</v>
       </c>
@@ -20990,7 +20984,7 @@
         <f t="shared" si="8"/>
         <v>7.1745362435245036E-5</v>
       </c>
-      <c r="AP8" s="30">
+      <c r="AP8" s="4">
         <f>AO8</f>
         <v>7.1745362435245036E-5</v>
       </c>
@@ -21207,55 +21201,55 @@
         <f t="shared" si="9"/>
         <v>7.5686214263268839E-4</v>
       </c>
-      <c r="AB9" s="30">
+      <c r="AB9" s="4">
         <f t="shared" si="9"/>
         <v>7.5686214263268839E-4</v>
       </c>
-      <c r="AC9" s="30">
+      <c r="AC9" s="4">
         <f t="shared" si="9"/>
         <v>7.5686214263268839E-4</v>
       </c>
-      <c r="AD9" s="30">
+      <c r="AD9" s="4">
         <f t="shared" si="9"/>
         <v>7.5686214263268839E-4</v>
       </c>
-      <c r="AE9" s="30">
+      <c r="AE9" s="4">
         <f t="shared" si="9"/>
         <v>7.5686214263268839E-4</v>
       </c>
-      <c r="AF9" s="30">
+      <c r="AF9" s="4">
         <f t="shared" si="9"/>
         <v>7.5686214263268839E-4</v>
       </c>
-      <c r="AG9" s="30">
+      <c r="AG9" s="4">
         <f t="shared" si="9"/>
         <v>7.5686214263268839E-4</v>
       </c>
-      <c r="AH9" s="30">
+      <c r="AH9" s="4">
         <f t="shared" si="9"/>
         <v>7.5686214263268839E-4</v>
       </c>
-      <c r="AI9" s="30">
+      <c r="AI9" s="4">
         <f t="shared" si="9"/>
         <v>7.5686214263268839E-4</v>
       </c>
-      <c r="AJ9" s="30">
+      <c r="AJ9" s="4">
         <f t="shared" si="9"/>
         <v>7.5686214263268839E-4</v>
       </c>
-      <c r="AK9" s="30">
+      <c r="AK9" s="4">
         <f t="shared" si="9"/>
         <v>7.5686214263268839E-4</v>
       </c>
-      <c r="AL9" s="30">
+      <c r="AL9" s="4">
         <f t="shared" si="9"/>
         <v>7.5686214263268839E-4</v>
       </c>
-      <c r="AM9" s="30">
+      <c r="AM9" s="4">
         <f t="shared" si="9"/>
         <v>7.5686214263268839E-4</v>
       </c>
-      <c r="AN9" s="30">
+      <c r="AN9" s="4">
         <f t="shared" si="9"/>
         <v>7.5686214263268839E-4</v>
       </c>
@@ -21263,7 +21257,7 @@
         <f t="shared" si="9"/>
         <v>7.5686214263268839E-4</v>
       </c>
-      <c r="AP9" s="30">
+      <c r="AP9" s="4">
         <f t="shared" si="9"/>
         <v>7.5686214263268839E-4</v>
       </c>
@@ -21936,151 +21930,151 @@
       <c r="D12" s="9"/>
       <c r="E12" s="9"/>
       <c r="F12" s="9"/>
-      <c r="G12" s="30">
-        <f t="shared" ref="G12:AN12" si="11">TREND($AR12:$BR12,$AR$1:$BR$1,G$1)</f>
+      <c r="G12" s="4">
+        <f t="shared" ref="G12" si="11">TREND($AR12:$BR12,$AR$1:$BR$1,G$1)</f>
         <v>5.2112239143541636E-3</v>
       </c>
-      <c r="H12" s="30">
+      <c r="H12" s="4">
         <f t="shared" si="10"/>
         <v>5.2112239143541636E-3</v>
       </c>
-      <c r="I12" s="30">
+      <c r="I12" s="4">
         <f t="shared" si="10"/>
         <v>5.2112239143541636E-3</v>
       </c>
-      <c r="J12" s="30">
+      <c r="J12" s="4">
         <f t="shared" si="10"/>
         <v>5.2112239143541636E-3</v>
       </c>
-      <c r="K12" s="30">
+      <c r="K12" s="4">
         <f t="shared" si="10"/>
         <v>5.2112239143541636E-3</v>
       </c>
-      <c r="L12" s="30">
+      <c r="L12" s="4">
         <f t="shared" si="10"/>
         <v>5.2112239143541636E-3</v>
       </c>
-      <c r="M12" s="30">
+      <c r="M12" s="4">
         <f t="shared" si="10"/>
         <v>5.2112239143541636E-3</v>
       </c>
-      <c r="N12" s="30">
+      <c r="N12" s="4">
         <f t="shared" si="10"/>
         <v>5.2112239143541636E-3</v>
       </c>
-      <c r="O12" s="30">
+      <c r="O12" s="4">
         <f t="shared" si="10"/>
         <v>5.2112239143541636E-3</v>
       </c>
-      <c r="P12" s="30">
+      <c r="P12" s="4">
         <f t="shared" si="10"/>
         <v>5.2112239143541636E-3</v>
       </c>
-      <c r="Q12" s="30">
+      <c r="Q12" s="4">
         <f t="shared" si="10"/>
         <v>5.2112239143541636E-3</v>
       </c>
-      <c r="R12" s="30">
+      <c r="R12" s="4">
         <f t="shared" si="10"/>
         <v>5.2112239143541636E-3</v>
       </c>
-      <c r="S12" s="30">
+      <c r="S12" s="4">
         <f t="shared" si="10"/>
         <v>5.2112239143541636E-3</v>
       </c>
-      <c r="T12" s="30">
+      <c r="T12" s="4">
         <f t="shared" si="10"/>
         <v>5.2112239143541636E-3</v>
       </c>
-      <c r="U12" s="30">
+      <c r="U12" s="4">
         <f t="shared" si="10"/>
         <v>5.2112239143541636E-3</v>
       </c>
-      <c r="V12" s="30">
+      <c r="V12" s="4">
         <f t="shared" si="10"/>
         <v>5.2112239143541636E-3</v>
       </c>
-      <c r="W12" s="30">
+      <c r="W12" s="4">
         <f t="shared" si="10"/>
         <v>5.2112239143541636E-3</v>
       </c>
-      <c r="X12" s="30">
+      <c r="X12" s="4">
         <f t="shared" si="10"/>
         <v>5.2112239143541636E-3</v>
       </c>
-      <c r="Y12" s="30">
+      <c r="Y12" s="4">
         <f t="shared" si="10"/>
         <v>5.2112239143541636E-3</v>
       </c>
-      <c r="Z12" s="30">
+      <c r="Z12" s="4">
         <f t="shared" si="10"/>
         <v>5.2112239143541636E-3</v>
       </c>
-      <c r="AA12" s="30">
+      <c r="AA12" s="4">
         <f t="shared" si="10"/>
         <v>5.2112239143541636E-3</v>
       </c>
-      <c r="AB12" s="30">
+      <c r="AB12" s="4">
         <f t="shared" si="10"/>
         <v>5.2112239143541636E-3</v>
       </c>
-      <c r="AC12" s="30">
+      <c r="AC12" s="4">
         <f t="shared" si="10"/>
         <v>5.2112239143541636E-3</v>
       </c>
-      <c r="AD12" s="30">
+      <c r="AD12" s="4">
         <f t="shared" si="10"/>
         <v>5.2112239143541636E-3</v>
       </c>
-      <c r="AE12" s="30">
+      <c r="AE12" s="4">
         <f t="shared" si="10"/>
         <v>5.2112239143541636E-3</v>
       </c>
-      <c r="AF12" s="30">
+      <c r="AF12" s="4">
         <f t="shared" si="10"/>
         <v>5.2112239143541636E-3</v>
       </c>
-      <c r="AG12" s="30">
+      <c r="AG12" s="4">
         <f t="shared" si="10"/>
         <v>5.2112239143541636E-3</v>
       </c>
-      <c r="AH12" s="30">
+      <c r="AH12" s="4">
         <f t="shared" si="10"/>
         <v>5.2112239143541636E-3</v>
       </c>
-      <c r="AI12" s="30">
+      <c r="AI12" s="4">
         <f t="shared" si="10"/>
         <v>5.2112239143541636E-3</v>
       </c>
-      <c r="AJ12" s="30">
+      <c r="AJ12" s="4">
         <f t="shared" si="10"/>
         <v>5.2112239143541636E-3</v>
       </c>
-      <c r="AK12" s="30">
+      <c r="AK12" s="4">
         <f t="shared" si="10"/>
         <v>5.2112239143541636E-3</v>
       </c>
-      <c r="AL12" s="30">
+      <c r="AL12" s="4">
         <f t="shared" si="10"/>
         <v>5.2112239143541636E-3</v>
       </c>
-      <c r="AM12" s="30">
+      <c r="AM12" s="4">
         <f t="shared" si="10"/>
         <v>5.2112239143541636E-3</v>
       </c>
-      <c r="AN12" s="30">
+      <c r="AN12" s="4">
         <f t="shared" si="10"/>
         <v>5.2112239143541636E-3</v>
       </c>
-      <c r="AO12" s="30">
+      <c r="AO12" s="4">
         <f>TREND($AR12:$BR12,$AR$1:$BR$1,AO$1)</f>
         <v>5.2112239143541636E-3</v>
       </c>
-      <c r="AP12" s="30">
+      <c r="AP12" s="4">
         <f t="shared" si="10"/>
         <v>5.2112239143541636E-3</v>
       </c>
-      <c r="AQ12" s="30">
+      <c r="AQ12" s="4">
         <f t="shared" si="10"/>
         <v>5.2112239143541636E-3</v>
       </c>
@@ -22464,55 +22458,55 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AB14" s="31">
+      <c r="AB14">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AC14" s="31">
+      <c r="AC14">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AD14" s="31">
+      <c r="AD14">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AE14" s="31">
+      <c r="AE14">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AF14" s="31">
+      <c r="AF14">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AG14" s="31">
+      <c r="AG14">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AH14" s="31">
+      <c r="AH14">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AI14" s="31">
+      <c r="AI14">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AJ14" s="31">
+      <c r="AJ14">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AK14" s="34">
+      <c r="AK14" s="30">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AL14" s="34">
+      <c r="AL14" s="30">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AM14" s="34">
+      <c r="AM14" s="30">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AN14" s="34">
+      <c r="AN14" s="30">
         <f>$AO14</f>
         <v>0</v>
       </c>
@@ -22520,7 +22514,7 @@
         <f>BNVFE!D20</f>
         <v>0</v>
       </c>
-      <c r="AP14" s="35">
+      <c r="AP14" s="11">
         <f>BNVFE!E20</f>
         <v>0</v>
       </c>
@@ -22641,7 +22635,7 @@
     <row r="15" spans="1:72">
       <c r="E15" s="21"/>
       <c r="X15" s="4"/>
-      <c r="AH15" s="30"/>
+      <c r="AH15" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/InputData/trans/BHNVFEAL/BAU Historical New Veh Fuel Economy After Lifetime.xlsx
+++ b/InputData/trans/BHNVFEAL/BAU Historical New Veh Fuel Economy After Lifetime.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\United States\us-eps\InputData\trans\BHNVFEAL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A986EBF-6A38-4458-9EF9-9AB3274F4F22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51991E45-905E-42B8-9F2E-7BCF8D3BD7AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="10260" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -1290,7 +1290,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1333,7 +1333,6 @@
     <xf numFmtId="0" fontId="41" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="154" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="156">
     <cellStyle name="20% - Accent1 2" xfId="8" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -2232,196 +2231,196 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="70"/>
                 <c:pt idx="4" formatCode="0.00E+00">
-                  <c:v>5.2112239143541636E-3</c:v>
+                  <c:v>4.1199493300773313E-3</c:v>
                 </c:pt>
                 <c:pt idx="5" formatCode="0.00E+00">
-                  <c:v>5.2112239143541636E-3</c:v>
+                  <c:v>4.139779079772081E-3</c:v>
                 </c:pt>
                 <c:pt idx="6" formatCode="0.00E+00">
-                  <c:v>5.2112239143541636E-3</c:v>
+                  <c:v>4.1596088294668307E-3</c:v>
                 </c:pt>
                 <c:pt idx="7" formatCode="0.00E+00">
-                  <c:v>5.2112239143541636E-3</c:v>
+                  <c:v>4.1794385791615804E-3</c:v>
                 </c:pt>
                 <c:pt idx="8" formatCode="0.00E+00">
-                  <c:v>5.2112239143541636E-3</c:v>
+                  <c:v>4.1992683288563301E-3</c:v>
                 </c:pt>
                 <c:pt idx="9" formatCode="0.00E+00">
-                  <c:v>5.2112239143541636E-3</c:v>
+                  <c:v>4.2190980785510798E-3</c:v>
                 </c:pt>
                 <c:pt idx="10" formatCode="0.00E+00">
-                  <c:v>5.2112239143541636E-3</c:v>
+                  <c:v>4.2389278282458295E-3</c:v>
                 </c:pt>
                 <c:pt idx="11" formatCode="0.00E+00">
-                  <c:v>5.2112239143541636E-3</c:v>
+                  <c:v>4.2587575779405792E-3</c:v>
                 </c:pt>
                 <c:pt idx="12" formatCode="0.00E+00">
-                  <c:v>5.2112239143541636E-3</c:v>
+                  <c:v>4.278587327635329E-3</c:v>
                 </c:pt>
                 <c:pt idx="13" formatCode="0.00E+00">
-                  <c:v>5.2112239143541636E-3</c:v>
+                  <c:v>4.2984170773300787E-3</c:v>
                 </c:pt>
                 <c:pt idx="14" formatCode="0.00E+00">
-                  <c:v>5.2112239143541636E-3</c:v>
+                  <c:v>4.3182468270248284E-3</c:v>
                 </c:pt>
                 <c:pt idx="15" formatCode="0.00E+00">
-                  <c:v>5.2112239143541636E-3</c:v>
+                  <c:v>4.3380765767195781E-3</c:v>
                 </c:pt>
                 <c:pt idx="16" formatCode="0.00E+00">
-                  <c:v>5.2112239143541636E-3</c:v>
+                  <c:v>4.3579063264143278E-3</c:v>
                 </c:pt>
                 <c:pt idx="17" formatCode="0.00E+00">
-                  <c:v>5.2112239143541636E-3</c:v>
+                  <c:v>4.3777360761090775E-3</c:v>
                 </c:pt>
                 <c:pt idx="18" formatCode="0.00E+00">
-                  <c:v>5.2112239143541636E-3</c:v>
+                  <c:v>4.3975658258038272E-3</c:v>
                 </c:pt>
                 <c:pt idx="19" formatCode="0.00E+00">
-                  <c:v>5.2112239143541636E-3</c:v>
+                  <c:v>4.4173955754985769E-3</c:v>
                 </c:pt>
                 <c:pt idx="20" formatCode="0.00E+00">
-                  <c:v>5.2112239143541636E-3</c:v>
+                  <c:v>4.4372253251933266E-3</c:v>
                 </c:pt>
                 <c:pt idx="21" formatCode="0.00E+00">
-                  <c:v>5.2112239143541636E-3</c:v>
+                  <c:v>4.4570550748880763E-3</c:v>
                 </c:pt>
                 <c:pt idx="22" formatCode="0.00E+00">
-                  <c:v>5.2112239143541636E-3</c:v>
+                  <c:v>4.4768848245828261E-3</c:v>
                 </c:pt>
                 <c:pt idx="23" formatCode="0.00E+00">
-                  <c:v>5.2112239143541636E-3</c:v>
+                  <c:v>4.4967145742775758E-3</c:v>
                 </c:pt>
                 <c:pt idx="24" formatCode="0.00E+00">
-                  <c:v>5.2112239143541636E-3</c:v>
+                  <c:v>4.5165443239723255E-3</c:v>
                 </c:pt>
                 <c:pt idx="25" formatCode="0.00E+00">
-                  <c:v>5.2112239143541636E-3</c:v>
+                  <c:v>4.5363740736670752E-3</c:v>
                 </c:pt>
                 <c:pt idx="26" formatCode="0.00E+00">
-                  <c:v>5.2112239143541636E-3</c:v>
+                  <c:v>4.5562038233618249E-3</c:v>
                 </c:pt>
                 <c:pt idx="27" formatCode="0.00E+00">
-                  <c:v>5.2112239143541636E-3</c:v>
+                  <c:v>4.5760335730565746E-3</c:v>
                 </c:pt>
                 <c:pt idx="28" formatCode="0.00E+00">
-                  <c:v>5.2112239143541636E-3</c:v>
+                  <c:v>4.5958633227513243E-3</c:v>
                 </c:pt>
                 <c:pt idx="29" formatCode="0.00E+00">
-                  <c:v>5.2112239143541636E-3</c:v>
+                  <c:v>4.615693072446074E-3</c:v>
                 </c:pt>
                 <c:pt idx="30" formatCode="0.00E+00">
-                  <c:v>5.2112239143541636E-3</c:v>
+                  <c:v>4.6355228221408237E-3</c:v>
                 </c:pt>
                 <c:pt idx="31" formatCode="0.00E+00">
-                  <c:v>5.2112239143541636E-3</c:v>
+                  <c:v>4.6553525718355734E-3</c:v>
                 </c:pt>
                 <c:pt idx="32" formatCode="0.00E+00">
-                  <c:v>5.2112239143541636E-3</c:v>
+                  <c:v>4.6751823215303231E-3</c:v>
                 </c:pt>
                 <c:pt idx="33" formatCode="0.00E+00">
-                  <c:v>5.2112239143541636E-3</c:v>
+                  <c:v>4.6950120712250729E-3</c:v>
                 </c:pt>
                 <c:pt idx="34" formatCode="0.00E+00">
-                  <c:v>5.2112239143541636E-3</c:v>
+                  <c:v>4.7148418209198226E-3</c:v>
                 </c:pt>
                 <c:pt idx="35" formatCode="0.00E+00">
-                  <c:v>5.2112239143541636E-3</c:v>
+                  <c:v>4.7346715706145723E-3</c:v>
                 </c:pt>
                 <c:pt idx="36" formatCode="0.00E+00">
-                  <c:v>5.2112239143541636E-3</c:v>
+                  <c:v>4.754501320309322E-3</c:v>
                 </c:pt>
                 <c:pt idx="37" formatCode="0.00E+00">
-                  <c:v>5.2112239143541636E-3</c:v>
+                  <c:v>4.7743310700040717E-3</c:v>
                 </c:pt>
                 <c:pt idx="38" formatCode="0.00E+00">
-                  <c:v>5.2112239143541636E-3</c:v>
+                  <c:v>4.7941608196988214E-3</c:v>
                 </c:pt>
                 <c:pt idx="39" formatCode="0.00E+00">
-                  <c:v>5.2112239143541636E-3</c:v>
+                  <c:v>4.8139905693935711E-3</c:v>
                 </c:pt>
                 <c:pt idx="40" formatCode="0.00E+00">
-                  <c:v>5.2112239143541636E-3</c:v>
+                  <c:v>4.8338203190883208E-3</c:v>
                 </c:pt>
                 <c:pt idx="41" formatCode="0.00E+00">
-                  <c:v>5.2112239143541636E-3</c:v>
+                  <c:v>4.8577789999999996E-3</c:v>
                 </c:pt>
                 <c:pt idx="42" formatCode="0.00E+00">
-                  <c:v>5.2112239143541636E-3</c:v>
+                  <c:v>4.8766649999999996E-3</c:v>
                 </c:pt>
                 <c:pt idx="43" formatCode="0.00E+00">
-                  <c:v>5.2112239143541636E-3</c:v>
+                  <c:v>4.8956239999999995E-3</c:v>
                 </c:pt>
                 <c:pt idx="44" formatCode="0.00E+00">
-                  <c:v>5.2112239143541636E-3</c:v>
+                  <c:v>4.9146570000000002E-3</c:v>
                 </c:pt>
                 <c:pt idx="45" formatCode="0.00E+00">
-                  <c:v>5.2112239143541636E-3</c:v>
+                  <c:v>4.9337640000000002E-3</c:v>
                 </c:pt>
                 <c:pt idx="46" formatCode="0.00E+00">
-                  <c:v>5.2112239143541636E-3</c:v>
+                  <c:v>4.9529449999999994E-3</c:v>
                 </c:pt>
                 <c:pt idx="47" formatCode="0.00E+00">
-                  <c:v>5.2112239143541636E-3</c:v>
+                  <c:v>4.9721999999999995E-3</c:v>
                 </c:pt>
                 <c:pt idx="48" formatCode="0.00E+00">
-                  <c:v>5.2112239143541636E-3</c:v>
+                  <c:v>4.9915310000000004E-3</c:v>
                 </c:pt>
                 <c:pt idx="49" formatCode="0.00E+00">
-                  <c:v>5.2112239143541636E-3</c:v>
+                  <c:v>5.010937E-3</c:v>
                 </c:pt>
                 <c:pt idx="50" formatCode="0.00E+00">
-                  <c:v>5.2112239143541636E-3</c:v>
+                  <c:v>5.030418E-3</c:v>
                 </c:pt>
                 <c:pt idx="51" formatCode="0.00E+00">
-                  <c:v>5.2112239143541636E-3</c:v>
+                  <c:v>5.049975E-3</c:v>
                 </c:pt>
                 <c:pt idx="52" formatCode="0.00E+00">
-                  <c:v>5.2112239143541636E-3</c:v>
+                  <c:v>5.0696079999999998E-3</c:v>
                 </c:pt>
                 <c:pt idx="53" formatCode="0.00E+00">
-                  <c:v>5.2112239143541636E-3</c:v>
+                  <c:v>5.0893170000000003E-3</c:v>
                 </c:pt>
                 <c:pt idx="54" formatCode="0.00E+00">
-                  <c:v>5.2112239143541636E-3</c:v>
+                  <c:v>5.1091030000000003E-3</c:v>
                 </c:pt>
                 <c:pt idx="55" formatCode="0.00E+00">
-                  <c:v>5.2112239143541636E-3</c:v>
+                  <c:v>5.1289660000000004E-3</c:v>
                 </c:pt>
                 <c:pt idx="56" formatCode="0.00E+00">
-                  <c:v>5.2112239143541636E-3</c:v>
+                  <c:v>5.148906E-3</c:v>
                 </c:pt>
                 <c:pt idx="57" formatCode="0.00E+00">
-                  <c:v>5.2112239143541636E-3</c:v>
+                  <c:v>5.1689230000000006E-3</c:v>
                 </c:pt>
                 <c:pt idx="58" formatCode="0.00E+00">
-                  <c:v>5.2112239143541636E-3</c:v>
+                  <c:v>5.1890190000000004E-3</c:v>
                 </c:pt>
                 <c:pt idx="59" formatCode="0.00E+00">
-                  <c:v>5.2112239143541636E-3</c:v>
+                  <c:v>5.2091919999999996E-3</c:v>
                 </c:pt>
                 <c:pt idx="60" formatCode="0.00E+00">
-                  <c:v>5.2112239143541636E-3</c:v>
+                  <c:v>5.2294450000000001E-3</c:v>
                 </c:pt>
                 <c:pt idx="61" formatCode="0.00E+00">
-                  <c:v>5.2112239143541636E-3</c:v>
+                  <c:v>5.2497749999999999E-3</c:v>
                 </c:pt>
                 <c:pt idx="62" formatCode="0.00E+00">
-                  <c:v>5.2112239143541636E-3</c:v>
+                  <c:v>5.2701849999999993E-3</c:v>
                 </c:pt>
                 <c:pt idx="63" formatCode="0.00E+00">
-                  <c:v>5.2112239143541636E-3</c:v>
+                  <c:v>5.2906740000000004E-3</c:v>
                 </c:pt>
                 <c:pt idx="64" formatCode="0.00E+00">
-                  <c:v>5.2112239143541636E-3</c:v>
+                  <c:v>5.3112430000000002E-3</c:v>
                 </c:pt>
                 <c:pt idx="65" formatCode="0.00E+00">
-                  <c:v>5.2112239143541636E-3</c:v>
+                  <c:v>5.3318919999999995E-3</c:v>
                 </c:pt>
                 <c:pt idx="66" formatCode="0.00E+00">
-                  <c:v>5.2112239143541636E-3</c:v>
+                  <c:v>5.3526210000000001E-3</c:v>
                 </c:pt>
                 <c:pt idx="67" formatCode="0.00E+00">
-                  <c:v>5.2112239143541636E-3</c:v>
+                  <c:v>5.3734300000000002E-3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3231,136 +3230,136 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="70"/>
                 <c:pt idx="24" formatCode="0.00E+00">
-                  <c:v>6.2736507518388511E-5</c:v>
+                  <c:v>6.7936644557507406E-5</c:v>
                 </c:pt>
                 <c:pt idx="25" formatCode="0.00E+00">
-                  <c:v>6.3701994710036553E-5</c:v>
+                  <c:v>6.8982159565568642E-5</c:v>
                 </c:pt>
                 <c:pt idx="26" formatCode="0.00E+00">
-                  <c:v>6.4667481901684379E-5</c:v>
+                  <c:v>7.0027674573629444E-5</c:v>
                 </c:pt>
                 <c:pt idx="27" formatCode="0.00E+00">
-                  <c:v>6.5632969093332421E-5</c:v>
+                  <c:v>7.107318958169068E-5</c:v>
                 </c:pt>
                 <c:pt idx="28" formatCode="0.00E+00">
-                  <c:v>6.6598456284980246E-5</c:v>
+                  <c:v>7.2118704589751916E-5</c:v>
                 </c:pt>
                 <c:pt idx="29" formatCode="0.00E+00">
-                  <c:v>6.7563943476628288E-5</c:v>
+                  <c:v>7.3164219597812719E-5</c:v>
                 </c:pt>
                 <c:pt idx="30" formatCode="0.00E+00">
-                  <c:v>6.8529430668276114E-5</c:v>
+                  <c:v>7.4209734605873955E-5</c:v>
                 </c:pt>
                 <c:pt idx="31" formatCode="0.00E+00">
-                  <c:v>6.9494917859924156E-5</c:v>
+                  <c:v>7.5255249613935191E-5</c:v>
                 </c:pt>
                 <c:pt idx="32" formatCode="0.00E+00">
-                  <c:v>7.0460405051572198E-5</c:v>
+                  <c:v>7.6300764621996427E-5</c:v>
                 </c:pt>
                 <c:pt idx="33" formatCode="0.00E+00">
-                  <c:v>7.1425892243220023E-5</c:v>
+                  <c:v>7.7346279630057229E-5</c:v>
                 </c:pt>
                 <c:pt idx="34" formatCode="0.00E+00">
-                  <c:v>7.2391379434868066E-5</c:v>
+                  <c:v>7.8391794638118465E-5</c:v>
                 </c:pt>
                 <c:pt idx="35" formatCode="0.00E+00">
-                  <c:v>7.3356866626515891E-5</c:v>
+                  <c:v>7.9437309646179701E-5</c:v>
                 </c:pt>
                 <c:pt idx="36" formatCode="0.00E+00">
-                  <c:v>7.4322353818163933E-5</c:v>
+                  <c:v>8.0482824654240937E-5</c:v>
                 </c:pt>
                 <c:pt idx="37" formatCode="0.00E+00">
-                  <c:v>7.5287841009811758E-5</c:v>
+                  <c:v>8.152833966230174E-5</c:v>
                 </c:pt>
                 <c:pt idx="38" formatCode="0.00E+00">
-                  <c:v>7.6253328201459801E-5</c:v>
+                  <c:v>8.2573854670362976E-5</c:v>
                 </c:pt>
                 <c:pt idx="39" formatCode="0.00E+00">
-                  <c:v>7.6915445435660028E-5</c:v>
+                  <c:v>8.3290853830414978E-5</c:v>
                 </c:pt>
                 <c:pt idx="40" formatCode="0.00E+00">
-                  <c:v>7.8010948323356793E-5</c:v>
+                  <c:v>8.4477161344765576E-5</c:v>
                 </c:pt>
                 <c:pt idx="41" formatCode="0.00E+00">
-                  <c:v>7.9492494824774367E-5</c:v>
+                  <c:v>8.6081511061439429E-5</c:v>
                 </c:pt>
                 <c:pt idx="42" formatCode="0.00E+00">
-                  <c:v>7.9975948644702701E-5</c:v>
+                  <c:v>8.6605037659008062E-5</c:v>
                 </c:pt>
                 <c:pt idx="43" formatCode="0.00E+00">
-                  <c:v>8.1024722706877106E-5</c:v>
+                  <c:v>8.774074306406576E-5</c:v>
                 </c:pt>
                 <c:pt idx="44" formatCode="0.00E+00">
-                  <c:v>8.2072270340545126E-5</c:v>
+                  <c:v>8.8875120383758021E-5</c:v>
                 </c:pt>
                 <c:pt idx="45" formatCode="0.00E+00">
-                  <c:v>8.3921848415336979E-5</c:v>
+                  <c:v>9.0878007270817581E-5</c:v>
                 </c:pt>
                 <c:pt idx="46" formatCode="0.00E+00">
-                  <c:v>8.424008288356597E-5</c:v>
+                  <c:v>9.1222619727092481E-5</c:v>
                 </c:pt>
                 <c:pt idx="47" formatCode="0.00E+00">
-                  <c:v>8.5145457355772448E-5</c:v>
+                  <c:v>9.2203039360616137E-5</c:v>
                 </c:pt>
                 <c:pt idx="48" formatCode="0.00E+00">
-                  <c:v>8.6269511754863824E-5</c:v>
+                  <c:v>9.3420264979240058E-5</c:v>
                 </c:pt>
                 <c:pt idx="49" formatCode="0.00E+00">
-                  <c:v>8.7316787399673934E-5</c:v>
+                  <c:v>9.4554347765317116E-5</c:v>
                 </c:pt>
                 <c:pt idx="50" formatCode="0.00E+00">
-                  <c:v>8.7981217262129169E-5</c:v>
+                  <c:v>9.5273851243985993E-5</c:v>
                 </c:pt>
                 <c:pt idx="51" formatCode="0.00E+00">
-                  <c:v>8.8870744349267236E-5</c:v>
+                  <c:v>9.6237109925949779E-5</c:v>
                 </c:pt>
                 <c:pt idx="52" formatCode="0.00E+00">
-                  <c:v>8.9949247005972088E-5</c:v>
+                  <c:v>9.7405008085110293E-5</c:v>
                 </c:pt>
                 <c:pt idx="53" formatCode="0.00E+00">
-                  <c:v>9.0831024253729272E-5</c:v>
+                  <c:v>9.83598745548802E-5</c:v>
                 </c:pt>
                 <c:pt idx="54" formatCode="0.00E+00">
-                  <c:v>9.1579110752047641E-5</c:v>
+                  <c:v>9.9169968845188442E-5</c:v>
                 </c:pt>
                 <c:pt idx="55" formatCode="0.00E+00">
-                  <c:v>9.2403640539502613E-5</c:v>
+                  <c:v>1.0006284269668531E-4</c:v>
                 </c:pt>
                 <c:pt idx="56" formatCode="0.00E+00">
-                  <c:v>9.319851514165077E-5</c:v>
+                  <c:v>1.009236032880858E-4</c:v>
                 </c:pt>
                 <c:pt idx="57" formatCode="0.00E+00">
-                  <c:v>9.3891059740218658E-5</c:v>
+                  <c:v>1.0167355189208385E-4</c:v>
                 </c:pt>
                 <c:pt idx="58" formatCode="0.00E+00">
-                  <c:v>9.5047122599296139E-5</c:v>
+                  <c:v>1.0292543910496804E-4</c:v>
                 </c:pt>
                 <c:pt idx="59" formatCode="0.00E+00">
-                  <c:v>9.6059950070461278E-5</c:v>
+                  <c:v>1.0402221835884117E-4</c:v>
                 </c:pt>
                 <c:pt idx="60" formatCode="0.00E+00">
-                  <c:v>9.7048480369583043E-5</c:v>
+                  <c:v>1.0509268648373766E-4</c:v>
                 </c:pt>
                 <c:pt idx="61" formatCode="0.00E+00">
-                  <c:v>9.7649579603605602E-5</c:v>
+                  <c:v>1.0574360995112404E-4</c:v>
                 </c:pt>
                 <c:pt idx="62" formatCode="0.00E+00">
-                  <c:v>9.8224460923876486E-5</c:v>
+                  <c:v>1.0636614234036401E-4</c:v>
                 </c:pt>
                 <c:pt idx="63" formatCode="0.00E+00">
-                  <c:v>9.8795624738493866E-5</c:v>
+                  <c:v>1.069846490853625E-4</c:v>
                 </c:pt>
                 <c:pt idx="64" formatCode="0.00E+00">
-                  <c:v>9.9479244599585216E-5</c:v>
+                  <c:v>1.077249331934921E-4</c:v>
                 </c:pt>
                 <c:pt idx="65" formatCode="0.00E+00">
-                  <c:v>9.9975448040260604E-5</c:v>
+                  <c:v>1.0826226620916075E-4</c:v>
                 </c:pt>
                 <c:pt idx="66" formatCode="0.00E+00">
-                  <c:v>1.0044050579002983E-4</c:v>
+                  <c:v>1.08765871913312E-4</c:v>
                 </c:pt>
                 <c:pt idx="67" formatCode="0.00E+00">
-                  <c:v>1.0101640935179317E-4</c:v>
+                  <c:v>1.0938951127614153E-4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4710,169 +4709,169 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="70"/>
                 <c:pt idx="13" formatCode="0.00E+00">
-                  <c:v>4.3905417607014065E-4</c:v>
+                  <c:v>3.4763021843211422E-4</c:v>
                 </c:pt>
                 <c:pt idx="14" formatCode="0.00E+00">
-                  <c:v>4.3905417607014065E-4</c:v>
+                  <c:v>3.5180176772518779E-4</c:v>
                 </c:pt>
                 <c:pt idx="15" formatCode="0.00E+00">
-                  <c:v>4.3905417607014065E-4</c:v>
+                  <c:v>3.5597331701826135E-4</c:v>
                 </c:pt>
                 <c:pt idx="16" formatCode="0.00E+00">
-                  <c:v>4.3905417607014065E-4</c:v>
+                  <c:v>3.6014486631133318E-4</c:v>
                 </c:pt>
                 <c:pt idx="17" formatCode="0.00E+00">
-                  <c:v>4.3905417607014065E-4</c:v>
+                  <c:v>3.6431641560440674E-4</c:v>
                 </c:pt>
                 <c:pt idx="18" formatCode="0.00E+00">
-                  <c:v>4.3905417607014065E-4</c:v>
+                  <c:v>3.684879648974803E-4</c:v>
                 </c:pt>
                 <c:pt idx="19" formatCode="0.00E+00">
-                  <c:v>4.3905417607014065E-4</c:v>
+                  <c:v>3.7265951419055386E-4</c:v>
                 </c:pt>
                 <c:pt idx="20" formatCode="0.00E+00">
-                  <c:v>4.3905417607014065E-4</c:v>
+                  <c:v>3.7683106348362569E-4</c:v>
                 </c:pt>
                 <c:pt idx="21" formatCode="0.00E+00">
-                  <c:v>4.3905417607014065E-4</c:v>
+                  <c:v>3.8100261277669925E-4</c:v>
                 </c:pt>
                 <c:pt idx="22" formatCode="0.00E+00">
-                  <c:v>4.3905417607014065E-4</c:v>
+                  <c:v>3.8517416206977281E-4</c:v>
                 </c:pt>
                 <c:pt idx="23" formatCode="0.00E+00">
-                  <c:v>4.3905417607014065E-4</c:v>
+                  <c:v>3.8934571136284464E-4</c:v>
                 </c:pt>
                 <c:pt idx="24" formatCode="0.00E+00">
-                  <c:v>4.3905417607014065E-4</c:v>
+                  <c:v>3.935172606559182E-4</c:v>
                 </c:pt>
                 <c:pt idx="25" formatCode="0.00E+00">
-                  <c:v>4.3905417607014065E-4</c:v>
+                  <c:v>3.9768880994899176E-4</c:v>
                 </c:pt>
                 <c:pt idx="26" formatCode="0.00E+00">
-                  <c:v>4.3905417607014065E-4</c:v>
+                  <c:v>4.0186035924206359E-4</c:v>
                 </c:pt>
                 <c:pt idx="27" formatCode="0.00E+00">
-                  <c:v>4.3905417607014065E-4</c:v>
+                  <c:v>4.0603190853513715E-4</c:v>
                 </c:pt>
                 <c:pt idx="28" formatCode="0.00E+00">
-                  <c:v>4.3905417607014065E-4</c:v>
+                  <c:v>4.1020345782821072E-4</c:v>
                 </c:pt>
                 <c:pt idx="29" formatCode="0.00E+00">
-                  <c:v>4.3905417607014065E-4</c:v>
+                  <c:v>4.1437500712128254E-4</c:v>
                 </c:pt>
                 <c:pt idx="30" formatCode="0.00E+00">
-                  <c:v>4.3905417607014065E-4</c:v>
+                  <c:v>4.1854655641435611E-4</c:v>
                 </c:pt>
                 <c:pt idx="31" formatCode="0.00E+00">
-                  <c:v>4.3905417607014065E-4</c:v>
+                  <c:v>4.2271810570742967E-4</c:v>
                 </c:pt>
                 <c:pt idx="32" formatCode="0.00E+00">
-                  <c:v>4.3905417607014065E-4</c:v>
+                  <c:v>4.2688965500050149E-4</c:v>
                 </c:pt>
                 <c:pt idx="33" formatCode="0.00E+00">
-                  <c:v>4.3905417607014065E-4</c:v>
+                  <c:v>4.3106120429357506E-4</c:v>
                 </c:pt>
                 <c:pt idx="34" formatCode="0.00E+00">
-                  <c:v>4.3905417607014065E-4</c:v>
+                  <c:v>4.3523275358664862E-4</c:v>
                 </c:pt>
                 <c:pt idx="35" formatCode="0.00E+00">
-                  <c:v>4.3905417607014065E-4</c:v>
+                  <c:v>4.3940430287972045E-4</c:v>
                 </c:pt>
                 <c:pt idx="36" formatCode="0.00E+00">
-                  <c:v>4.3905417607014065E-4</c:v>
+                  <c:v>4.4357585217279401E-4</c:v>
                 </c:pt>
                 <c:pt idx="37" formatCode="0.00E+00">
-                  <c:v>4.3905417607014065E-4</c:v>
+                  <c:v>4.4774740146586757E-4</c:v>
                 </c:pt>
                 <c:pt idx="38" formatCode="0.00E+00">
-                  <c:v>4.3905417607014065E-4</c:v>
+                  <c:v>4.5191895075894113E-4</c:v>
                 </c:pt>
                 <c:pt idx="39" formatCode="0.00E+00">
-                  <c:v>4.3905417607014065E-4</c:v>
+                  <c:v>4.5609050005201296E-4</c:v>
                 </c:pt>
                 <c:pt idx="40" formatCode="0.00E+00">
-                  <c:v>4.390541760701407E-4</c:v>
+                  <c:v>4.6292253798248397E-4</c:v>
                 </c:pt>
                 <c:pt idx="41" formatCode="0.00E+00">
-                  <c:v>4.390541760701407E-4</c:v>
+                  <c:v>4.6724180152163598E-4</c:v>
                 </c:pt>
                 <c:pt idx="42" formatCode="0.00E+00">
-                  <c:v>4.390541760701407E-4</c:v>
+                  <c:v>4.6965127581020212E-4</c:v>
                 </c:pt>
                 <c:pt idx="43" formatCode="0.00E+00">
-                  <c:v>4.390541760701407E-4</c:v>
+                  <c:v>4.7322813533235715E-4</c:v>
                 </c:pt>
                 <c:pt idx="44" formatCode="0.00E+00">
-                  <c:v>4.390541760701407E-4</c:v>
+                  <c:v>4.7696949985651614E-4</c:v>
                 </c:pt>
                 <c:pt idx="45" formatCode="0.00E+00">
-                  <c:v>4.390541760701407E-4</c:v>
+                  <c:v>4.8083975908889043E-4</c:v>
                 </c:pt>
                 <c:pt idx="46" formatCode="0.00E+00">
-                  <c:v>4.390541760701407E-4</c:v>
+                  <c:v>4.847773340732441E-4</c:v>
                 </c:pt>
                 <c:pt idx="47" formatCode="0.00E+00">
-                  <c:v>4.390541760701407E-4</c:v>
+                  <c:v>4.8876510978465549E-4</c:v>
                 </c:pt>
                 <c:pt idx="48" formatCode="0.00E+00">
-                  <c:v>4.390541760701407E-4</c:v>
+                  <c:v>4.9280339238632709E-4</c:v>
                 </c:pt>
                 <c:pt idx="49" formatCode="0.00E+00">
-                  <c:v>4.390541760701407E-4</c:v>
+                  <c:v>4.9685871974595585E-4</c:v>
                 </c:pt>
                 <c:pt idx="50" formatCode="0.00E+00">
-                  <c:v>4.390541760701407E-4</c:v>
+                  <c:v>5.0093827917019513E-4</c:v>
                 </c:pt>
                 <c:pt idx="51" formatCode="0.00E+00">
-                  <c:v>4.390541760701407E-4</c:v>
+                  <c:v>5.0505403110021464E-4</c:v>
                 </c:pt>
                 <c:pt idx="52" formatCode="0.00E+00">
-                  <c:v>4.390541760701407E-4</c:v>
+                  <c:v>5.091914152171586E-4</c:v>
                 </c:pt>
                 <c:pt idx="53" formatCode="0.00E+00">
-                  <c:v>4.390541760701407E-4</c:v>
+                  <c:v>5.1335993261843963E-4</c:v>
                 </c:pt>
                 <c:pt idx="54" formatCode="0.00E+00">
-                  <c:v>4.390541760701407E-4</c:v>
+                  <c:v>5.1755601976514434E-4</c:v>
                 </c:pt>
                 <c:pt idx="55" formatCode="0.00E+00">
-                  <c:v>4.390541760701407E-4</c:v>
+                  <c:v>5.2177673046383325E-4</c:v>
                 </c:pt>
                 <c:pt idx="56" formatCode="0.00E+00">
-                  <c:v>4.390541760701407E-4</c:v>
+                  <c:v>5.2602994967173547E-4</c:v>
                 </c:pt>
                 <c:pt idx="57" formatCode="0.00E+00">
-                  <c:v>4.390541760701407E-4</c:v>
+                  <c:v>5.3031732866251667E-4</c:v>
                 </c:pt>
                 <c:pt idx="58" formatCode="0.00E+00">
-                  <c:v>4.390541760701407E-4</c:v>
+                  <c:v>5.346381346521186E-4</c:v>
                 </c:pt>
                 <c:pt idx="59" formatCode="0.00E+00">
-                  <c:v>4.390541760701407E-4</c:v>
+                  <c:v>5.3898042225657822E-4</c:v>
                 </c:pt>
                 <c:pt idx="60" formatCode="0.00E+00">
-                  <c:v>4.390541760701407E-4</c:v>
+                  <c:v>5.4335778311445497E-4</c:v>
                 </c:pt>
                 <c:pt idx="61" formatCode="0.00E+00">
-                  <c:v>4.390541760701407E-4</c:v>
+                  <c:v>5.4777558261039474E-4</c:v>
                 </c:pt>
                 <c:pt idx="62" formatCode="0.00E+00">
-                  <c:v>4.390541760701407E-4</c:v>
+                  <c:v>5.5222750675573099E-4</c:v>
                 </c:pt>
                 <c:pt idx="63" formatCode="0.00E+00">
-                  <c:v>4.390541760701407E-4</c:v>
+                  <c:v>5.5671423312476443E-4</c:v>
                 </c:pt>
                 <c:pt idx="64" formatCode="0.00E+00">
-                  <c:v>4.390541760701407E-4</c:v>
+                  <c:v>5.6121623753950501E-4</c:v>
                 </c:pt>
                 <c:pt idx="65" formatCode="0.00E+00">
-                  <c:v>4.390541760701407E-4</c:v>
+                  <c:v>5.6574653946465893E-4</c:v>
                 </c:pt>
                 <c:pt idx="66" formatCode="0.00E+00">
-                  <c:v>4.390541760701407E-4</c:v>
+                  <c:v>5.7031870042437182E-4</c:v>
                 </c:pt>
                 <c:pt idx="67" formatCode="0.00E+00">
-                  <c:v>4.390541760701407E-4</c:v>
+                  <c:v>5.7492662224994018E-4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5206,169 +5205,169 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="70"/>
                 <c:pt idx="13" formatCode="0.00E+00">
-                  <c:v>1.5492656753114542E-4</c:v>
+                  <c:v>1.8429395373095432E-4</c:v>
                 </c:pt>
                 <c:pt idx="14" formatCode="0.00E+00">
-                  <c:v>1.5492656753114542E-4</c:v>
+                  <c:v>1.8429395373095432E-4</c:v>
                 </c:pt>
                 <c:pt idx="15" formatCode="0.00E+00">
-                  <c:v>1.5492656753114542E-4</c:v>
+                  <c:v>1.8429395373095432E-4</c:v>
                 </c:pt>
                 <c:pt idx="16" formatCode="0.00E+00">
-                  <c:v>1.5492656753114542E-4</c:v>
+                  <c:v>1.8429395373095432E-4</c:v>
                 </c:pt>
                 <c:pt idx="17" formatCode="0.00E+00">
-                  <c:v>1.5492656753114542E-4</c:v>
+                  <c:v>1.8429395373095432E-4</c:v>
                 </c:pt>
                 <c:pt idx="18" formatCode="0.00E+00">
-                  <c:v>1.5492656753114542E-4</c:v>
+                  <c:v>1.8429395373095432E-4</c:v>
                 </c:pt>
                 <c:pt idx="19" formatCode="0.00E+00">
-                  <c:v>1.5492656753114542E-4</c:v>
+                  <c:v>1.8429395373095432E-4</c:v>
                 </c:pt>
                 <c:pt idx="20" formatCode="0.00E+00">
-                  <c:v>1.5492656753114542E-4</c:v>
+                  <c:v>1.8429395373095432E-4</c:v>
                 </c:pt>
                 <c:pt idx="21" formatCode="0.00E+00">
-                  <c:v>1.5492656753114542E-4</c:v>
+                  <c:v>1.8429395373095432E-4</c:v>
                 </c:pt>
                 <c:pt idx="22" formatCode="0.00E+00">
-                  <c:v>1.5492656753114542E-4</c:v>
+                  <c:v>1.8429395373095432E-4</c:v>
                 </c:pt>
                 <c:pt idx="23" formatCode="0.00E+00">
-                  <c:v>1.5492656753114542E-4</c:v>
+                  <c:v>1.8429395373095432E-4</c:v>
                 </c:pt>
                 <c:pt idx="24" formatCode="0.00E+00">
-                  <c:v>1.5492656753114542E-4</c:v>
+                  <c:v>1.8429395373095432E-4</c:v>
                 </c:pt>
                 <c:pt idx="25" formatCode="0.00E+00">
-                  <c:v>1.5492656753114542E-4</c:v>
+                  <c:v>1.8429395373095432E-4</c:v>
                 </c:pt>
                 <c:pt idx="26" formatCode="0.00E+00">
-                  <c:v>1.5492656753114542E-4</c:v>
+                  <c:v>1.8429395373095432E-4</c:v>
                 </c:pt>
                 <c:pt idx="27" formatCode="0.00E+00">
-                  <c:v>1.5492656753114542E-4</c:v>
+                  <c:v>1.8429395373095432E-4</c:v>
                 </c:pt>
                 <c:pt idx="28" formatCode="0.00E+00">
-                  <c:v>1.5492656753114542E-4</c:v>
+                  <c:v>1.8429395373095432E-4</c:v>
                 </c:pt>
                 <c:pt idx="29" formatCode="0.00E+00">
-                  <c:v>1.5492656753114542E-4</c:v>
+                  <c:v>1.8429395373095432E-4</c:v>
                 </c:pt>
                 <c:pt idx="30" formatCode="0.00E+00">
-                  <c:v>1.5492656753114542E-4</c:v>
+                  <c:v>1.8429395373095432E-4</c:v>
                 </c:pt>
                 <c:pt idx="31" formatCode="0.00E+00">
-                  <c:v>1.5492656753114542E-4</c:v>
+                  <c:v>1.8429395373095432E-4</c:v>
                 </c:pt>
                 <c:pt idx="32" formatCode="0.00E+00">
-                  <c:v>1.5492656753114542E-4</c:v>
+                  <c:v>1.8429395373095432E-4</c:v>
                 </c:pt>
                 <c:pt idx="33" formatCode="0.00E+00">
-                  <c:v>1.5492656753114542E-4</c:v>
+                  <c:v>1.8429395373095432E-4</c:v>
                 </c:pt>
                 <c:pt idx="34" formatCode="0.00E+00">
-                  <c:v>1.5492656753114542E-4</c:v>
+                  <c:v>1.8429395373095432E-4</c:v>
                 </c:pt>
                 <c:pt idx="35" formatCode="0.00E+00">
-                  <c:v>1.5492656753114542E-4</c:v>
+                  <c:v>1.8429395373095432E-4</c:v>
                 </c:pt>
                 <c:pt idx="36" formatCode="0.00E+00">
-                  <c:v>1.5492656753114542E-4</c:v>
+                  <c:v>1.8429395373095432E-4</c:v>
                 </c:pt>
                 <c:pt idx="37" formatCode="0.00E+00">
-                  <c:v>1.5492656753114542E-4</c:v>
+                  <c:v>1.8429395373095432E-4</c:v>
                 </c:pt>
                 <c:pt idx="38" formatCode="0.00E+00">
-                  <c:v>1.5492656753114542E-4</c:v>
+                  <c:v>1.8429395373095432E-4</c:v>
                 </c:pt>
                 <c:pt idx="39" formatCode="0.00E+00">
-                  <c:v>1.5492656753114542E-4</c:v>
+                  <c:v>1.8429395373095432E-4</c:v>
                 </c:pt>
                 <c:pt idx="40" formatCode="0.00E+00">
-                  <c:v>1.5492656753114542E-4</c:v>
+                  <c:v>1.8429395373095432E-4</c:v>
                 </c:pt>
                 <c:pt idx="41" formatCode="0.00E+00">
-                  <c:v>1.5492656753114542E-4</c:v>
+                  <c:v>1.8429395373095432E-4</c:v>
                 </c:pt>
                 <c:pt idx="42" formatCode="0.00E+00">
-                  <c:v>1.5492656753114542E-4</c:v>
+                  <c:v>1.8429395373095432E-4</c:v>
                 </c:pt>
                 <c:pt idx="43" formatCode="0.00E+00">
-                  <c:v>1.5492656753114542E-4</c:v>
+                  <c:v>1.8429395373095432E-4</c:v>
                 </c:pt>
                 <c:pt idx="44" formatCode="0.00E+00">
-                  <c:v>1.5492656753114542E-4</c:v>
+                  <c:v>1.8429395373095432E-4</c:v>
                 </c:pt>
                 <c:pt idx="45" formatCode="0.00E+00">
-                  <c:v>1.5492656753114542E-4</c:v>
+                  <c:v>1.8429395373095432E-4</c:v>
                 </c:pt>
                 <c:pt idx="46" formatCode="0.00E+00">
-                  <c:v>1.5492656753114542E-4</c:v>
+                  <c:v>1.8429395373095432E-4</c:v>
                 </c:pt>
                 <c:pt idx="47" formatCode="0.00E+00">
-                  <c:v>1.5492656753114542E-4</c:v>
+                  <c:v>1.8429395373095432E-4</c:v>
                 </c:pt>
                 <c:pt idx="48" formatCode="0.00E+00">
-                  <c:v>1.5492656753114542E-4</c:v>
+                  <c:v>1.8429395373095432E-4</c:v>
                 </c:pt>
                 <c:pt idx="49" formatCode="0.00E+00">
-                  <c:v>1.5492656753114542E-4</c:v>
+                  <c:v>1.8429395373095432E-4</c:v>
                 </c:pt>
                 <c:pt idx="50" formatCode="0.00E+00">
-                  <c:v>1.5492656753114542E-4</c:v>
+                  <c:v>1.8429395373095432E-4</c:v>
                 </c:pt>
                 <c:pt idx="51" formatCode="0.00E+00">
-                  <c:v>1.5492656753114542E-4</c:v>
+                  <c:v>1.8429395373095432E-4</c:v>
                 </c:pt>
                 <c:pt idx="52" formatCode="0.00E+00">
-                  <c:v>1.5492656753114542E-4</c:v>
+                  <c:v>1.8429395373095432E-4</c:v>
                 </c:pt>
                 <c:pt idx="53" formatCode="0.00E+00">
-                  <c:v>1.5492656753114542E-4</c:v>
+                  <c:v>1.8429395373095432E-4</c:v>
                 </c:pt>
                 <c:pt idx="54" formatCode="0.00E+00">
-                  <c:v>1.5492656753114542E-4</c:v>
+                  <c:v>1.8429395373095432E-4</c:v>
                 </c:pt>
                 <c:pt idx="55" formatCode="0.00E+00">
-                  <c:v>1.5492656753114542E-4</c:v>
+                  <c:v>1.8429395373095432E-4</c:v>
                 </c:pt>
                 <c:pt idx="56" formatCode="0.00E+00">
-                  <c:v>1.5492656753114542E-4</c:v>
+                  <c:v>1.8429395373095432E-4</c:v>
                 </c:pt>
                 <c:pt idx="57" formatCode="0.00E+00">
-                  <c:v>1.5492656753114542E-4</c:v>
+                  <c:v>1.8429395373095432E-4</c:v>
                 </c:pt>
                 <c:pt idx="58" formatCode="0.00E+00">
-                  <c:v>1.5492656753114542E-4</c:v>
+                  <c:v>1.8429395373095432E-4</c:v>
                 </c:pt>
                 <c:pt idx="59" formatCode="0.00E+00">
-                  <c:v>1.5492656753114542E-4</c:v>
+                  <c:v>1.8429395373095432E-4</c:v>
                 </c:pt>
                 <c:pt idx="60" formatCode="0.00E+00">
-                  <c:v>1.5492656753114542E-4</c:v>
+                  <c:v>1.8429395373095432E-4</c:v>
                 </c:pt>
                 <c:pt idx="61" formatCode="0.00E+00">
-                  <c:v>1.5492656753114542E-4</c:v>
+                  <c:v>1.8429395373095432E-4</c:v>
                 </c:pt>
                 <c:pt idx="62" formatCode="0.00E+00">
-                  <c:v>1.5492656753114542E-4</c:v>
+                  <c:v>1.8429395373095432E-4</c:v>
                 </c:pt>
                 <c:pt idx="63" formatCode="0.00E+00">
-                  <c:v>1.5492656753114542E-4</c:v>
+                  <c:v>1.8429395373095432E-4</c:v>
                 </c:pt>
                 <c:pt idx="64" formatCode="0.00E+00">
-                  <c:v>1.5492656753114542E-4</c:v>
+                  <c:v>1.8429395373095432E-4</c:v>
                 </c:pt>
                 <c:pt idx="65" formatCode="0.00E+00">
-                  <c:v>1.5492656753114542E-4</c:v>
+                  <c:v>1.8429395373095432E-4</c:v>
                 </c:pt>
                 <c:pt idx="66" formatCode="0.00E+00">
-                  <c:v>1.5492656753114542E-4</c:v>
+                  <c:v>1.8429395373095432E-4</c:v>
                 </c:pt>
                 <c:pt idx="67" formatCode="0.00E+00">
-                  <c:v>1.5492656753114542E-4</c:v>
+                  <c:v>1.8429395373095432E-4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5702,199 +5701,199 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="70"/>
                 <c:pt idx="3" formatCode="0.00E+00">
-                  <c:v>7.1745362435245036E-5</c:v>
+                  <c:v>5.0586266198922429E-5</c:v>
                 </c:pt>
                 <c:pt idx="4" formatCode="0.00E+00">
-                  <c:v>7.1745362435245036E-5</c:v>
+                  <c:v>5.0586266198922429E-5</c:v>
                 </c:pt>
                 <c:pt idx="5" formatCode="0.00E+00">
-                  <c:v>7.1745362435245036E-5</c:v>
+                  <c:v>5.0586266198922429E-5</c:v>
                 </c:pt>
                 <c:pt idx="6" formatCode="0.00E+00">
-                  <c:v>7.1745362435245036E-5</c:v>
+                  <c:v>5.0586266198922429E-5</c:v>
                 </c:pt>
                 <c:pt idx="7" formatCode="0.00E+00">
-                  <c:v>7.1745362435245036E-5</c:v>
+                  <c:v>5.0586266198922429E-5</c:v>
                 </c:pt>
                 <c:pt idx="8" formatCode="0.00E+00">
-                  <c:v>7.1745362435245036E-5</c:v>
+                  <c:v>5.0586266198922429E-5</c:v>
                 </c:pt>
                 <c:pt idx="9" formatCode="0.00E+00">
-                  <c:v>7.1745362435245036E-5</c:v>
+                  <c:v>5.0586266198922429E-5</c:v>
                 </c:pt>
                 <c:pt idx="10" formatCode="0.00E+00">
-                  <c:v>7.1745362435245036E-5</c:v>
+                  <c:v>5.0586266198922429E-5</c:v>
                 </c:pt>
                 <c:pt idx="11" formatCode="0.00E+00">
-                  <c:v>7.1745362435245036E-5</c:v>
+                  <c:v>5.0586266198922429E-5</c:v>
                 </c:pt>
                 <c:pt idx="12" formatCode="0.00E+00">
-                  <c:v>7.1745362435245036E-5</c:v>
+                  <c:v>5.0586266198922429E-5</c:v>
                 </c:pt>
                 <c:pt idx="13" formatCode="0.00E+00">
-                  <c:v>7.1745362435245036E-5</c:v>
+                  <c:v>5.0586266198922429E-5</c:v>
                 </c:pt>
                 <c:pt idx="14" formatCode="0.00E+00">
-                  <c:v>7.1745362435245036E-5</c:v>
+                  <c:v>5.0586266198922429E-5</c:v>
                 </c:pt>
                 <c:pt idx="15" formatCode="0.00E+00">
-                  <c:v>7.1745362435245036E-5</c:v>
+                  <c:v>5.0586266198922429E-5</c:v>
                 </c:pt>
                 <c:pt idx="16" formatCode="0.00E+00">
-                  <c:v>7.1745362435245036E-5</c:v>
+                  <c:v>5.0586266198922429E-5</c:v>
                 </c:pt>
                 <c:pt idx="17" formatCode="0.00E+00">
-                  <c:v>7.1745362435245036E-5</c:v>
+                  <c:v>5.0586266198922429E-5</c:v>
                 </c:pt>
                 <c:pt idx="18" formatCode="0.00E+00">
-                  <c:v>7.1745362435245036E-5</c:v>
+                  <c:v>5.0586266198922429E-5</c:v>
                 </c:pt>
                 <c:pt idx="19" formatCode="0.00E+00">
-                  <c:v>7.1745362435245036E-5</c:v>
+                  <c:v>5.0586266198922429E-5</c:v>
                 </c:pt>
                 <c:pt idx="20" formatCode="0.00E+00">
-                  <c:v>7.1745362435245036E-5</c:v>
+                  <c:v>5.0586266198922429E-5</c:v>
                 </c:pt>
                 <c:pt idx="21" formatCode="0.00E+00">
-                  <c:v>7.1745362435245036E-5</c:v>
+                  <c:v>5.0586266198922429E-5</c:v>
                 </c:pt>
                 <c:pt idx="22" formatCode="0.00E+00">
-                  <c:v>7.1745362435245036E-5</c:v>
+                  <c:v>5.0586266198922429E-5</c:v>
                 </c:pt>
                 <c:pt idx="23" formatCode="0.00E+00">
-                  <c:v>7.1745362435245036E-5</c:v>
+                  <c:v>5.0586266198922429E-5</c:v>
                 </c:pt>
                 <c:pt idx="24" formatCode="0.00E+00">
-                  <c:v>7.1745362435245036E-5</c:v>
+                  <c:v>5.0586266198922429E-5</c:v>
                 </c:pt>
                 <c:pt idx="25" formatCode="0.00E+00">
-                  <c:v>7.1745362435245036E-5</c:v>
+                  <c:v>5.0586266198922429E-5</c:v>
                 </c:pt>
                 <c:pt idx="26" formatCode="0.00E+00">
-                  <c:v>7.1745362435245036E-5</c:v>
+                  <c:v>5.0586266198922429E-5</c:v>
                 </c:pt>
                 <c:pt idx="27" formatCode="0.00E+00">
-                  <c:v>7.1745362435245036E-5</c:v>
+                  <c:v>5.0586266198922429E-5</c:v>
                 </c:pt>
                 <c:pt idx="28" formatCode="0.00E+00">
-                  <c:v>7.1745362435245036E-5</c:v>
+                  <c:v>5.0586266198922429E-5</c:v>
                 </c:pt>
                 <c:pt idx="29" formatCode="0.00E+00">
-                  <c:v>7.1745362435245036E-5</c:v>
+                  <c:v>5.0586266198922429E-5</c:v>
                 </c:pt>
                 <c:pt idx="30" formatCode="0.00E+00">
-                  <c:v>7.1745362435245036E-5</c:v>
+                  <c:v>5.0586266198922429E-5</c:v>
                 </c:pt>
                 <c:pt idx="31" formatCode="0.00E+00">
-                  <c:v>7.1745362435245036E-5</c:v>
+                  <c:v>5.0586266198922429E-5</c:v>
                 </c:pt>
                 <c:pt idx="32" formatCode="0.00E+00">
-                  <c:v>7.1745362435245036E-5</c:v>
+                  <c:v>5.0586266198922429E-5</c:v>
                 </c:pt>
                 <c:pt idx="33" formatCode="0.00E+00">
-                  <c:v>7.1745362435245036E-5</c:v>
+                  <c:v>5.0586266198922429E-5</c:v>
                 </c:pt>
                 <c:pt idx="34" formatCode="0.00E+00">
-                  <c:v>7.1745362435245036E-5</c:v>
+                  <c:v>5.0586266198922429E-5</c:v>
                 </c:pt>
                 <c:pt idx="35" formatCode="0.00E+00">
-                  <c:v>7.1745362435245036E-5</c:v>
+                  <c:v>5.0586266198922429E-5</c:v>
                 </c:pt>
                 <c:pt idx="36" formatCode="0.00E+00">
-                  <c:v>7.1745362435245036E-5</c:v>
+                  <c:v>5.0586266198922429E-5</c:v>
                 </c:pt>
                 <c:pt idx="37" formatCode="0.00E+00">
-                  <c:v>7.1745362435245036E-5</c:v>
+                  <c:v>5.0586266198922429E-5</c:v>
                 </c:pt>
                 <c:pt idx="38" formatCode="0.00E+00">
-                  <c:v>7.1745362435245036E-5</c:v>
+                  <c:v>5.0586266198922429E-5</c:v>
                 </c:pt>
                 <c:pt idx="39" formatCode="0.00E+00">
-                  <c:v>7.1745362435245036E-5</c:v>
+                  <c:v>5.0586266198922429E-5</c:v>
                 </c:pt>
                 <c:pt idx="40" formatCode="0.00E+00">
-                  <c:v>7.1745362435245036E-5</c:v>
+                  <c:v>5.0586266198922429E-5</c:v>
                 </c:pt>
                 <c:pt idx="41" formatCode="0.00E+00">
-                  <c:v>7.1745362435245036E-5</c:v>
+                  <c:v>5.0586266198922429E-5</c:v>
                 </c:pt>
                 <c:pt idx="42" formatCode="0.00E+00">
-                  <c:v>7.1745362435245036E-5</c:v>
+                  <c:v>5.0586266198922429E-5</c:v>
                 </c:pt>
                 <c:pt idx="43" formatCode="0.00E+00">
-                  <c:v>7.1745362435245036E-5</c:v>
+                  <c:v>5.0586266198922429E-5</c:v>
                 </c:pt>
                 <c:pt idx="44" formatCode="0.00E+00">
-                  <c:v>7.1745362435245036E-5</c:v>
+                  <c:v>5.0586266198922429E-5</c:v>
                 </c:pt>
                 <c:pt idx="45" formatCode="0.00E+00">
-                  <c:v>7.1745362435245036E-5</c:v>
+                  <c:v>5.0586266198922429E-5</c:v>
                 </c:pt>
                 <c:pt idx="46" formatCode="0.00E+00">
-                  <c:v>7.1745362435245036E-5</c:v>
+                  <c:v>5.0586266198922429E-5</c:v>
                 </c:pt>
                 <c:pt idx="47" formatCode="0.00E+00">
-                  <c:v>7.1745362435245036E-5</c:v>
+                  <c:v>5.0586266198922429E-5</c:v>
                 </c:pt>
                 <c:pt idx="48" formatCode="0.00E+00">
-                  <c:v>7.1745362435245036E-5</c:v>
+                  <c:v>5.0586266198922429E-5</c:v>
                 </c:pt>
                 <c:pt idx="49" formatCode="0.00E+00">
-                  <c:v>7.1745362435245036E-5</c:v>
+                  <c:v>5.0586266198922429E-5</c:v>
                 </c:pt>
                 <c:pt idx="50" formatCode="0.00E+00">
-                  <c:v>7.1745362435245036E-5</c:v>
+                  <c:v>5.0586266198922429E-5</c:v>
                 </c:pt>
                 <c:pt idx="51" formatCode="0.00E+00">
-                  <c:v>7.1745362435245036E-5</c:v>
+                  <c:v>5.0586266198922429E-5</c:v>
                 </c:pt>
                 <c:pt idx="52" formatCode="0.00E+00">
-                  <c:v>7.1745362435245036E-5</c:v>
+                  <c:v>5.0586266198922429E-5</c:v>
                 </c:pt>
                 <c:pt idx="53" formatCode="0.00E+00">
-                  <c:v>7.1745362435245036E-5</c:v>
+                  <c:v>5.0586266198922429E-5</c:v>
                 </c:pt>
                 <c:pt idx="54" formatCode="0.00E+00">
-                  <c:v>7.1745362435245036E-5</c:v>
+                  <c:v>5.0586266198922429E-5</c:v>
                 </c:pt>
                 <c:pt idx="55" formatCode="0.00E+00">
-                  <c:v>7.1745362435245036E-5</c:v>
+                  <c:v>5.0586266198922429E-5</c:v>
                 </c:pt>
                 <c:pt idx="56" formatCode="0.00E+00">
-                  <c:v>7.1745362435245036E-5</c:v>
+                  <c:v>5.0586266198922429E-5</c:v>
                 </c:pt>
                 <c:pt idx="57" formatCode="0.00E+00">
-                  <c:v>7.1745362435245036E-5</c:v>
+                  <c:v>5.0586266198922429E-5</c:v>
                 </c:pt>
                 <c:pt idx="58" formatCode="0.00E+00">
-                  <c:v>7.1745362435245036E-5</c:v>
+                  <c:v>5.0586266198922429E-5</c:v>
                 </c:pt>
                 <c:pt idx="59" formatCode="0.00E+00">
-                  <c:v>7.1745362435245036E-5</c:v>
+                  <c:v>5.0586266198922429E-5</c:v>
                 </c:pt>
                 <c:pt idx="60" formatCode="0.00E+00">
-                  <c:v>7.1745362435245036E-5</c:v>
+                  <c:v>5.0586266198922429E-5</c:v>
                 </c:pt>
                 <c:pt idx="61" formatCode="0.00E+00">
-                  <c:v>7.1745362435245036E-5</c:v>
+                  <c:v>5.0586266198922429E-5</c:v>
                 </c:pt>
                 <c:pt idx="62" formatCode="0.00E+00">
-                  <c:v>7.1745362435245036E-5</c:v>
+                  <c:v>5.0586266198922429E-5</c:v>
                 </c:pt>
                 <c:pt idx="63" formatCode="0.00E+00">
-                  <c:v>7.1745362435245036E-5</c:v>
+                  <c:v>5.0586266198922429E-5</c:v>
                 </c:pt>
                 <c:pt idx="64" formatCode="0.00E+00">
-                  <c:v>7.1745362435245036E-5</c:v>
+                  <c:v>5.0586266198922429E-5</c:v>
                 </c:pt>
                 <c:pt idx="65" formatCode="0.00E+00">
-                  <c:v>7.1745362435245036E-5</c:v>
+                  <c:v>5.0586266198922429E-5</c:v>
                 </c:pt>
                 <c:pt idx="66" formatCode="0.00E+00">
-                  <c:v>7.1745362435245036E-5</c:v>
+                  <c:v>5.0586266198922429E-5</c:v>
                 </c:pt>
                 <c:pt idx="67" formatCode="0.00E+00">
-                  <c:v>7.1745362435245036E-5</c:v>
+                  <c:v>5.0586266198922429E-5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9112,123 +9111,123 @@
       </c>
       <c r="B2" s="4">
         <f>B$5/(1-'Other Values'!$B$3)</f>
-        <v>1.4108894605736162E-3</v>
+        <v>1.1305060590411976E-3</v>
       </c>
       <c r="C2" s="4">
         <f>C$5/(1-'Other Values'!$B$3)</f>
-        <v>1.4108894605736162E-3</v>
+        <v>1.1439112269057679E-3</v>
       </c>
       <c r="D2" s="4">
         <f>D$5/(1-'Other Values'!$B$3)</f>
-        <v>1.4108894605736162E-3</v>
+        <v>1.1573163947703326E-3</v>
       </c>
       <c r="E2" s="4">
         <f>E$5/(1-'Other Values'!$B$3)</f>
-        <v>1.4108894605736162E-3</v>
+        <v>1.1707215626349026E-3</v>
       </c>
       <c r="F2" s="4">
         <f>F$5/(1-'Other Values'!$B$3)</f>
-        <v>1.4108894605736162E-3</v>
+        <v>1.1841267304994729E-3</v>
       </c>
       <c r="G2" s="4">
         <f>G$5/(1-'Other Values'!$B$3)</f>
-        <v>1.4108894605736162E-3</v>
+        <v>1.1975318983640433E-3</v>
       </c>
       <c r="H2" s="4">
         <f>H$5/(1-'Other Values'!$B$3)</f>
-        <v>1.4108894605736162E-3</v>
+        <v>1.2109370662286079E-3</v>
       </c>
       <c r="I2" s="4">
         <f>I$5/(1-'Other Values'!$B$3)</f>
-        <v>1.4108894605736162E-3</v>
+        <v>1.224342234093178E-3</v>
       </c>
       <c r="J2" s="4">
         <f>J$5/(1-'Other Values'!$B$3)</f>
-        <v>1.4108894605736162E-3</v>
+        <v>1.2377474019577483E-3</v>
       </c>
       <c r="K2" s="4">
         <f>K$5/(1-'Other Values'!$B$3)</f>
-        <v>1.4108894605736162E-3</v>
+        <v>1.251152569822313E-3</v>
       </c>
       <c r="L2" s="4">
         <f>L$5/(1-'Other Values'!$B$3)</f>
-        <v>1.4108894605736162E-3</v>
+        <v>1.2645577376868833E-3</v>
       </c>
       <c r="M2" s="4">
         <f>M$5/(1-'Other Values'!$B$3)</f>
-        <v>1.4108894605736162E-3</v>
+        <v>1.2779629055514534E-3</v>
       </c>
       <c r="N2" s="4">
         <f>N$5/(1-'Other Values'!$B$3)</f>
-        <v>1.4108894605736162E-3</v>
+        <v>1.291368073416018E-3</v>
       </c>
       <c r="O2" s="4">
         <f>O$5/(1-'Other Values'!$B$3)</f>
-        <v>1.4108894605736162E-3</v>
+        <v>1.3047732412805883E-3</v>
       </c>
       <c r="P2" s="4">
         <f>P$5/(1-'Other Values'!$B$3)</f>
-        <v>1.4108894605736162E-3</v>
+        <v>1.3181784091451584E-3</v>
       </c>
       <c r="Q2" s="4">
         <f>Q$5/(1-'Other Values'!$B$3)</f>
-        <v>1.4108894605736162E-3</v>
+        <v>1.3315835770097231E-3</v>
       </c>
       <c r="R2" s="4">
         <f>R$5/(1-'Other Values'!$B$3)</f>
-        <v>1.4108894605736162E-3</v>
+        <v>1.3449887448742934E-3</v>
       </c>
       <c r="S2" s="4">
         <f>S$5/(1-'Other Values'!$B$3)</f>
-        <v>1.4108894605736162E-3</v>
+        <v>1.3583939127388637E-3</v>
       </c>
       <c r="T2" s="4">
         <f>T$5/(1-'Other Values'!$B$3)</f>
-        <v>1.4108894605736162E-3</v>
+        <v>1.3717990806034284E-3</v>
       </c>
       <c r="U2" s="4">
         <f>U$5/(1-'Other Values'!$B$3)</f>
-        <v>1.4108894605736162E-3</v>
+        <v>1.3852042484679985E-3</v>
       </c>
       <c r="V2" s="4">
         <f>V$5/(1-'Other Values'!$B$3)</f>
-        <v>1.4108894605736162E-3</v>
+        <v>1.3986094163325688E-3</v>
       </c>
       <c r="W2" s="4">
         <f>W$5/(1-'Other Values'!$B$3)</f>
-        <v>1.4108894605736162E-3</v>
+        <v>1.4120145841971334E-3</v>
       </c>
       <c r="X2" s="4">
         <f>X$5/(1-'Other Values'!$B$3)</f>
-        <v>1.4108894605736162E-3</v>
+        <v>1.4254197520617035E-3</v>
       </c>
       <c r="Y2" s="4">
         <f>Y$5/(1-'Other Values'!$B$3)</f>
-        <v>1.4108894605736162E-3</v>
+        <v>1.4388249199262738E-3</v>
       </c>
       <c r="Z2" s="4">
         <f>Z$5/(1-'Other Values'!$B$3)</f>
-        <v>1.4108894605736162E-3</v>
+        <v>1.4522300877908441E-3</v>
       </c>
       <c r="AA2" s="4">
         <f>AA$5/(1-'Other Values'!$B$3)</f>
-        <v>1.4108894605736162E-3</v>
+        <v>1.4656352556554088E-3</v>
       </c>
       <c r="AB2" s="4">
         <f>AB$5/(1-'Other Values'!$B$3)</f>
-        <v>1.4108894605736164E-3</v>
+        <v>1.4875898362873916E-3</v>
       </c>
       <c r="AC2" s="4">
         <f>AC$5/(1-'Other Values'!$B$3)</f>
-        <v>1.4108894605736164E-3</v>
+        <v>1.5014696801357644E-3</v>
       </c>
       <c r="AD2" s="4">
         <f>AD$5/(1-'Other Values'!$B$3)</f>
-        <v>1.4108894605736164E-3</v>
+        <v>1.5092124646588251E-3</v>
       </c>
       <c r="AE2" s="4">
         <f>AE$5/(1-'Other Values'!$B$3)</f>
-        <v>1.4108894605736164E-3</v>
+        <v>1.5207066120256291E-3</v>
       </c>
       <c r="AG2" s="4"/>
       <c r="AH2" s="4"/>
@@ -9427,125 +9426,125 @@
       <c r="A5" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="32">
+      <c r="B5">
         <f>Extrapolations!Q6</f>
-        <v>4.3905417607014065E-4</v>
+        <v>3.5180176772518779E-4</v>
       </c>
       <c r="C5" s="4">
         <f>Extrapolations!R6</f>
-        <v>4.3905417607014065E-4</v>
+        <v>3.5597331701826135E-4</v>
       </c>
       <c r="D5" s="4">
         <f>Extrapolations!S6</f>
-        <v>4.3905417607014065E-4</v>
+        <v>3.6014486631133318E-4</v>
       </c>
       <c r="E5" s="4">
         <f>Extrapolations!T6</f>
-        <v>4.3905417607014065E-4</v>
+        <v>3.6431641560440674E-4</v>
       </c>
       <c r="F5" s="4">
         <f>Extrapolations!U6</f>
-        <v>4.3905417607014065E-4</v>
+        <v>3.684879648974803E-4</v>
       </c>
       <c r="G5" s="4">
         <f>Extrapolations!V6</f>
-        <v>4.3905417607014065E-4</v>
+        <v>3.7265951419055386E-4</v>
       </c>
       <c r="H5" s="4">
         <f>Extrapolations!W6</f>
-        <v>4.3905417607014065E-4</v>
+        <v>3.7683106348362569E-4</v>
       </c>
       <c r="I5" s="4">
         <f>Extrapolations!X6</f>
-        <v>4.3905417607014065E-4</v>
+        <v>3.8100261277669925E-4</v>
       </c>
       <c r="J5" s="4">
         <f>Extrapolations!Y6</f>
-        <v>4.3905417607014065E-4</v>
+        <v>3.8517416206977281E-4</v>
       </c>
       <c r="K5" s="4">
         <f>Extrapolations!Z6</f>
-        <v>4.3905417607014065E-4</v>
+        <v>3.8934571136284464E-4</v>
       </c>
       <c r="L5" s="4">
         <f>Extrapolations!AA6</f>
-        <v>4.3905417607014065E-4</v>
+        <v>3.935172606559182E-4</v>
       </c>
       <c r="M5" s="4">
         <f>Extrapolations!AB6</f>
-        <v>4.3905417607014065E-4</v>
+        <v>3.9768880994899176E-4</v>
       </c>
       <c r="N5" s="4">
         <f>Extrapolations!AC6</f>
-        <v>4.3905417607014065E-4</v>
+        <v>4.0186035924206359E-4</v>
       </c>
       <c r="O5" s="4">
         <f>Extrapolations!AD6</f>
-        <v>4.3905417607014065E-4</v>
+        <v>4.0603190853513715E-4</v>
       </c>
       <c r="P5" s="4">
         <f>Extrapolations!AE6</f>
-        <v>4.3905417607014065E-4</v>
+        <v>4.1020345782821072E-4</v>
       </c>
       <c r="Q5" s="4">
         <f>Extrapolations!AF6</f>
-        <v>4.3905417607014065E-4</v>
+        <v>4.1437500712128254E-4</v>
       </c>
       <c r="R5" s="4">
         <f>Extrapolations!AG6</f>
-        <v>4.3905417607014065E-4</v>
+        <v>4.1854655641435611E-4</v>
       </c>
       <c r="S5" s="4">
         <f>Extrapolations!AH6</f>
-        <v>4.3905417607014065E-4</v>
+        <v>4.2271810570742967E-4</v>
       </c>
       <c r="T5" s="4">
         <f>Extrapolations!AI6</f>
-        <v>4.3905417607014065E-4</v>
+        <v>4.2688965500050149E-4</v>
       </c>
       <c r="U5" s="4">
         <f>Extrapolations!AJ6</f>
-        <v>4.3905417607014065E-4</v>
+        <v>4.3106120429357506E-4</v>
       </c>
       <c r="V5" s="4">
         <f>Extrapolations!AK6</f>
-        <v>4.3905417607014065E-4</v>
+        <v>4.3523275358664862E-4</v>
       </c>
       <c r="W5" s="4">
         <f>Extrapolations!AL6</f>
-        <v>4.3905417607014065E-4</v>
+        <v>4.3940430287972045E-4</v>
       </c>
       <c r="X5" s="4">
         <f>Extrapolations!AM6</f>
-        <v>4.3905417607014065E-4</v>
+        <v>4.4357585217279401E-4</v>
       </c>
       <c r="Y5" s="4">
         <f>Extrapolations!AN6</f>
-        <v>4.3905417607014065E-4</v>
+        <v>4.4774740146586757E-4</v>
       </c>
       <c r="Z5" s="4">
         <f>Extrapolations!AO6</f>
-        <v>4.3905417607014065E-4</v>
+        <v>4.5191895075894113E-4</v>
       </c>
       <c r="AA5" s="4">
         <f>Extrapolations!AP6</f>
-        <v>4.3905417607014065E-4</v>
+        <v>4.5609050005201296E-4</v>
       </c>
       <c r="AB5" s="4">
         <f>Extrapolations!AQ6</f>
-        <v>4.390541760701407E-4</v>
+        <v>4.6292253798248397E-4</v>
       </c>
       <c r="AC5" s="4">
         <f>Extrapolations!AR6</f>
-        <v>4.390541760701407E-4</v>
+        <v>4.6724180152163598E-4</v>
       </c>
       <c r="AD5" s="4">
         <f>Extrapolations!AS6</f>
-        <v>4.390541760701407E-4</v>
+        <v>4.6965127581020212E-4</v>
       </c>
       <c r="AE5" s="4">
         <f>Extrapolations!AT6</f>
-        <v>4.390541760701407E-4</v>
+        <v>4.7322813533235715E-4</v>
       </c>
       <c r="AG5" s="4"/>
       <c r="AH5" s="4"/>
@@ -9746,123 +9745,123 @@
       </c>
       <c r="B8" s="4">
         <f>B$5*Calculations!$B$27</f>
-        <v>1.3171625282104218E-3</v>
+        <v>1.0554053031755631E-3</v>
       </c>
       <c r="C8" s="4">
         <f>C$5*Calculations!$B$27</f>
-        <v>1.3171625282104218E-3</v>
+        <v>1.0679199510547838E-3</v>
       </c>
       <c r="D8" s="4">
         <f>D$5*Calculations!$B$27</f>
-        <v>1.3171625282104218E-3</v>
+        <v>1.0804345989339993E-3</v>
       </c>
       <c r="E8" s="4">
         <f>E$5*Calculations!$B$27</f>
-        <v>1.3171625282104218E-3</v>
+        <v>1.09294924681322E-3</v>
       </c>
       <c r="F8" s="4">
         <f>F$5*Calculations!$B$27</f>
-        <v>1.3171625282104218E-3</v>
+        <v>1.1054638946924407E-3</v>
       </c>
       <c r="G8" s="4">
         <f>G$5*Calculations!$B$27</f>
-        <v>1.3171625282104218E-3</v>
+        <v>1.1179785425716614E-3</v>
       </c>
       <c r="H8" s="4">
         <f>H$5*Calculations!$B$27</f>
-        <v>1.3171625282104218E-3</v>
+        <v>1.1304931904508768E-3</v>
       </c>
       <c r="I8" s="4">
         <f>I$5*Calculations!$B$27</f>
-        <v>1.3171625282104218E-3</v>
+        <v>1.1430078383300975E-3</v>
       </c>
       <c r="J8" s="4">
         <f>J$5*Calculations!$B$27</f>
-        <v>1.3171625282104218E-3</v>
+        <v>1.1555224862093182E-3</v>
       </c>
       <c r="K8" s="4">
         <f>K$5*Calculations!$B$27</f>
-        <v>1.3171625282104218E-3</v>
+        <v>1.1680371340885337E-3</v>
       </c>
       <c r="L8" s="4">
         <f>L$5*Calculations!$B$27</f>
-        <v>1.3171625282104218E-3</v>
+        <v>1.1805517819677544E-3</v>
       </c>
       <c r="M8" s="4">
         <f>M$5*Calculations!$B$27</f>
-        <v>1.3171625282104218E-3</v>
+        <v>1.1930664298469751E-3</v>
       </c>
       <c r="N8" s="4">
         <f>N$5*Calculations!$B$27</f>
-        <v>1.3171625282104218E-3</v>
+        <v>1.2055810777261906E-3</v>
       </c>
       <c r="O8" s="4">
         <f>O$5*Calculations!$B$27</f>
-        <v>1.3171625282104218E-3</v>
+        <v>1.2180957256054112E-3</v>
       </c>
       <c r="P8" s="4">
         <f>P$5*Calculations!$B$27</f>
-        <v>1.3171625282104218E-3</v>
+        <v>1.2306103734846319E-3</v>
       </c>
       <c r="Q8" s="4">
         <f>Q$5*Calculations!$B$27</f>
-        <v>1.3171625282104218E-3</v>
+        <v>1.2431250213638474E-3</v>
       </c>
       <c r="R8" s="4">
         <f>R$5*Calculations!$B$27</f>
-        <v>1.3171625282104218E-3</v>
+        <v>1.2556396692430681E-3</v>
       </c>
       <c r="S8" s="4">
         <f>S$5*Calculations!$B$27</f>
-        <v>1.3171625282104218E-3</v>
+        <v>1.2681543171222888E-3</v>
       </c>
       <c r="T8" s="4">
         <f>T$5*Calculations!$B$27</f>
-        <v>1.3171625282104218E-3</v>
+        <v>1.2806689650015043E-3</v>
       </c>
       <c r="U8" s="4">
         <f>U$5*Calculations!$B$27</f>
-        <v>1.3171625282104218E-3</v>
+        <v>1.293183612880725E-3</v>
       </c>
       <c r="V8" s="4">
         <f>V$5*Calculations!$B$27</f>
-        <v>1.3171625282104218E-3</v>
+        <v>1.3056982607599456E-3</v>
       </c>
       <c r="W8" s="4">
         <f>W$5*Calculations!$B$27</f>
-        <v>1.3171625282104218E-3</v>
+        <v>1.3182129086391611E-3</v>
       </c>
       <c r="X8" s="4">
         <f>X$5*Calculations!$B$27</f>
-        <v>1.3171625282104218E-3</v>
+        <v>1.3307275565183818E-3</v>
       </c>
       <c r="Y8" s="4">
         <f>Y$5*Calculations!$B$27</f>
-        <v>1.3171625282104218E-3</v>
+        <v>1.3432422043976025E-3</v>
       </c>
       <c r="Z8" s="4">
         <f>Z$5*Calculations!$B$27</f>
-        <v>1.3171625282104218E-3</v>
+        <v>1.3557568522768232E-3</v>
       </c>
       <c r="AA8" s="4">
         <f>AA$5*Calculations!$B$27</f>
-        <v>1.3171625282104218E-3</v>
+        <v>1.3682715001560387E-3</v>
       </c>
       <c r="AB8" s="4">
         <f>AB$5*Calculations!$B$27</f>
-        <v>1.317162528210422E-3</v>
+        <v>1.3887676139474516E-3</v>
       </c>
       <c r="AC8" s="4">
         <f>AC$5*Calculations!$B$27</f>
-        <v>1.317162528210422E-3</v>
+        <v>1.4017254045649078E-3</v>
       </c>
       <c r="AD8" s="4">
         <f>AD$5*Calculations!$B$27</f>
-        <v>1.317162528210422E-3</v>
+        <v>1.4089538274306061E-3</v>
       </c>
       <c r="AE8" s="4">
         <f>AE$5*Calculations!$B$27</f>
-        <v>1.317162528210422E-3</v>
+        <v>1.4196844059970713E-3</v>
       </c>
       <c r="AG8" s="4"/>
       <c r="AH8" s="4"/>
@@ -9984,123 +9983,123 @@
       </c>
       <c r="B2" s="4">
         <f>B$5/(1-'Other Values'!$B$3)</f>
-        <v>4.9785259588925983E-4</v>
+        <v>5.9222394669788123E-4</v>
       </c>
       <c r="C2" s="4">
         <f>C$5/(1-'Other Values'!$B$3)</f>
-        <v>4.9785259588925983E-4</v>
+        <v>5.9222394669788123E-4</v>
       </c>
       <c r="D2" s="4">
         <f>D$5/(1-'Other Values'!$B$3)</f>
-        <v>4.9785259588925983E-4</v>
+        <v>5.9222394669788123E-4</v>
       </c>
       <c r="E2" s="4">
         <f>E$5/(1-'Other Values'!$B$3)</f>
-        <v>4.9785259588925983E-4</v>
+        <v>5.9222394669788123E-4</v>
       </c>
       <c r="F2" s="4">
         <f>F$5/(1-'Other Values'!$B$3)</f>
-        <v>4.9785259588925983E-4</v>
+        <v>5.9222394669788123E-4</v>
       </c>
       <c r="G2" s="4">
         <f>G$5/(1-'Other Values'!$B$3)</f>
-        <v>4.9785259588925983E-4</v>
+        <v>5.9222394669788123E-4</v>
       </c>
       <c r="H2" s="4">
         <f>H$5/(1-'Other Values'!$B$3)</f>
-        <v>4.9785259588925983E-4</v>
+        <v>5.9222394669788123E-4</v>
       </c>
       <c r="I2" s="4">
         <f>I$5/(1-'Other Values'!$B$3)</f>
-        <v>4.9785259588925983E-4</v>
+        <v>5.9222394669788123E-4</v>
       </c>
       <c r="J2" s="4">
         <f>J$5/(1-'Other Values'!$B$3)</f>
-        <v>4.9785259588925983E-4</v>
+        <v>5.9222394669788123E-4</v>
       </c>
       <c r="K2" s="4">
         <f>K$5/(1-'Other Values'!$B$3)</f>
-        <v>4.9785259588925983E-4</v>
+        <v>5.9222394669788123E-4</v>
       </c>
       <c r="L2" s="4">
         <f>L$5/(1-'Other Values'!$B$3)</f>
-        <v>4.9785259588925983E-4</v>
+        <v>5.9222394669788123E-4</v>
       </c>
       <c r="M2" s="4">
         <f>M$5/(1-'Other Values'!$B$3)</f>
-        <v>4.9785259588925983E-4</v>
+        <v>5.9222394669788123E-4</v>
       </c>
       <c r="N2" s="4">
         <f>N$5/(1-'Other Values'!$B$3)</f>
-        <v>4.9785259588925983E-4</v>
+        <v>5.9222394669788123E-4</v>
       </c>
       <c r="O2" s="4">
         <f>O$5/(1-'Other Values'!$B$3)</f>
-        <v>4.9785259588925983E-4</v>
+        <v>5.9222394669788123E-4</v>
       </c>
       <c r="P2" s="4">
         <f>P$5/(1-'Other Values'!$B$3)</f>
-        <v>4.9785259588925983E-4</v>
+        <v>5.9222394669788123E-4</v>
       </c>
       <c r="Q2" s="4">
         <f>Q$5/(1-'Other Values'!$B$3)</f>
-        <v>4.9785259588925983E-4</v>
+        <v>5.9222394669788123E-4</v>
       </c>
       <c r="R2" s="4">
         <f>R$5/(1-'Other Values'!$B$3)</f>
-        <v>4.9785259588925983E-4</v>
+        <v>5.9222394669788123E-4</v>
       </c>
       <c r="S2" s="4">
         <f>S$5/(1-'Other Values'!$B$3)</f>
-        <v>4.9785259588925983E-4</v>
+        <v>5.9222394669788123E-4</v>
       </c>
       <c r="T2" s="4">
         <f>T$5/(1-'Other Values'!$B$3)</f>
-        <v>4.9785259588925983E-4</v>
+        <v>5.9222394669788123E-4</v>
       </c>
       <c r="U2" s="4">
         <f>U$5/(1-'Other Values'!$B$3)</f>
-        <v>4.9785259588925983E-4</v>
+        <v>5.9222394669788123E-4</v>
       </c>
       <c r="V2" s="4">
         <f>V$5/(1-'Other Values'!$B$3)</f>
-        <v>4.9785259588925983E-4</v>
+        <v>5.9222394669788123E-4</v>
       </c>
       <c r="W2" s="4">
         <f>W$5/(1-'Other Values'!$B$3)</f>
-        <v>4.9785259588925983E-4</v>
+        <v>5.9222394669788123E-4</v>
       </c>
       <c r="X2" s="4">
         <f>X$5/(1-'Other Values'!$B$3)</f>
-        <v>4.9785259588925983E-4</v>
+        <v>5.9222394669788123E-4</v>
       </c>
       <c r="Y2" s="4">
         <f>Y$5/(1-'Other Values'!$B$3)</f>
-        <v>4.9785259588925983E-4</v>
+        <v>5.9222394669788123E-4</v>
       </c>
       <c r="Z2" s="4">
         <f>Z$5/(1-'Other Values'!$B$3)</f>
-        <v>4.9785259588925983E-4</v>
+        <v>5.9222394669788123E-4</v>
       </c>
       <c r="AA2" s="4">
         <f>AA$5/(1-'Other Values'!$B$3)</f>
-        <v>4.9785259588925983E-4</v>
+        <v>5.9222394669788123E-4</v>
       </c>
       <c r="AB2" s="4">
         <f>AB$5/(1-'Other Values'!$B$3)</f>
-        <v>4.9785259588925983E-4</v>
+        <v>5.9222394669788123E-4</v>
       </c>
       <c r="AC2" s="4">
         <f>AC$5/(1-'Other Values'!$B$3)</f>
-        <v>4.9785259588925983E-4</v>
+        <v>5.9222394669788123E-4</v>
       </c>
       <c r="AD2" s="4">
         <f>AD$5/(1-'Other Values'!$B$3)</f>
-        <v>4.9785259588925983E-4</v>
+        <v>5.9222394669788123E-4</v>
       </c>
       <c r="AE2" s="4">
         <f>AE$5/(1-'Other Values'!$B$3)</f>
-        <v>4.9785259588925983E-4</v>
+        <v>5.9222394669788123E-4</v>
       </c>
       <c r="AG2" s="4"/>
       <c r="AH2" s="4"/>
@@ -10301,123 +10300,123 @@
       </c>
       <c r="B5" s="4">
         <f>Extrapolations!Q7</f>
-        <v>1.5492656753114542E-4</v>
+        <v>1.8429395373095432E-4</v>
       </c>
       <c r="C5" s="4">
         <f>Extrapolations!R7</f>
-        <v>1.5492656753114542E-4</v>
+        <v>1.8429395373095432E-4</v>
       </c>
       <c r="D5" s="4">
         <f>Extrapolations!S7</f>
-        <v>1.5492656753114542E-4</v>
+        <v>1.8429395373095432E-4</v>
       </c>
       <c r="E5" s="4">
         <f>Extrapolations!T7</f>
-        <v>1.5492656753114542E-4</v>
+        <v>1.8429395373095432E-4</v>
       </c>
       <c r="F5" s="4">
         <f>Extrapolations!U7</f>
-        <v>1.5492656753114542E-4</v>
+        <v>1.8429395373095432E-4</v>
       </c>
       <c r="G5" s="4">
         <f>Extrapolations!V7</f>
-        <v>1.5492656753114542E-4</v>
+        <v>1.8429395373095432E-4</v>
       </c>
       <c r="H5" s="4">
         <f>Extrapolations!W7</f>
-        <v>1.5492656753114542E-4</v>
+        <v>1.8429395373095432E-4</v>
       </c>
       <c r="I5" s="4">
         <f>Extrapolations!X7</f>
-        <v>1.5492656753114542E-4</v>
+        <v>1.8429395373095432E-4</v>
       </c>
       <c r="J5" s="4">
         <f>Extrapolations!Y7</f>
-        <v>1.5492656753114542E-4</v>
+        <v>1.8429395373095432E-4</v>
       </c>
       <c r="K5" s="4">
         <f>Extrapolations!Z7</f>
-        <v>1.5492656753114542E-4</v>
+        <v>1.8429395373095432E-4</v>
       </c>
       <c r="L5" s="4">
         <f>Extrapolations!AA7</f>
-        <v>1.5492656753114542E-4</v>
+        <v>1.8429395373095432E-4</v>
       </c>
       <c r="M5" s="4">
         <f>Extrapolations!AB7</f>
-        <v>1.5492656753114542E-4</v>
+        <v>1.8429395373095432E-4</v>
       </c>
       <c r="N5" s="4">
         <f>Extrapolations!AC7</f>
-        <v>1.5492656753114542E-4</v>
+        <v>1.8429395373095432E-4</v>
       </c>
       <c r="O5" s="4">
         <f>Extrapolations!AD7</f>
-        <v>1.5492656753114542E-4</v>
+        <v>1.8429395373095432E-4</v>
       </c>
       <c r="P5" s="4">
         <f>Extrapolations!AE7</f>
-        <v>1.5492656753114542E-4</v>
+        <v>1.8429395373095432E-4</v>
       </c>
       <c r="Q5" s="4">
         <f>Extrapolations!AF7</f>
-        <v>1.5492656753114542E-4</v>
+        <v>1.8429395373095432E-4</v>
       </c>
       <c r="R5" s="4">
         <f>Extrapolations!AG7</f>
-        <v>1.5492656753114542E-4</v>
+        <v>1.8429395373095432E-4</v>
       </c>
       <c r="S5" s="4">
         <f>Extrapolations!AH7</f>
-        <v>1.5492656753114542E-4</v>
+        <v>1.8429395373095432E-4</v>
       </c>
       <c r="T5" s="4">
         <f>Extrapolations!AI7</f>
-        <v>1.5492656753114542E-4</v>
+        <v>1.8429395373095432E-4</v>
       </c>
       <c r="U5" s="4">
         <f>Extrapolations!AJ7</f>
-        <v>1.5492656753114542E-4</v>
+        <v>1.8429395373095432E-4</v>
       </c>
       <c r="V5" s="4">
         <f>Extrapolations!AK7</f>
-        <v>1.5492656753114542E-4</v>
+        <v>1.8429395373095432E-4</v>
       </c>
       <c r="W5" s="4">
         <f>Extrapolations!AL7</f>
-        <v>1.5492656753114542E-4</v>
+        <v>1.8429395373095432E-4</v>
       </c>
       <c r="X5" s="4">
         <f>Extrapolations!AM7</f>
-        <v>1.5492656753114542E-4</v>
+        <v>1.8429395373095432E-4</v>
       </c>
       <c r="Y5" s="4">
         <f>Extrapolations!AN7</f>
-        <v>1.5492656753114542E-4</v>
+        <v>1.8429395373095432E-4</v>
       </c>
       <c r="Z5" s="4">
         <f>Extrapolations!AO7</f>
-        <v>1.5492656753114542E-4</v>
+        <v>1.8429395373095432E-4</v>
       </c>
       <c r="AA5" s="4">
         <f>Extrapolations!AP7</f>
-        <v>1.5492656753114542E-4</v>
+        <v>1.8429395373095432E-4</v>
       </c>
       <c r="AB5" s="4">
         <f>Extrapolations!AQ7</f>
-        <v>1.5492656753114542E-4</v>
+        <v>1.8429395373095432E-4</v>
       </c>
       <c r="AC5" s="4">
         <f>Extrapolations!AR7</f>
-        <v>1.5492656753114542E-4</v>
+        <v>1.8429395373095432E-4</v>
       </c>
       <c r="AD5" s="4">
         <f>Extrapolations!AS7</f>
-        <v>1.5492656753114542E-4</v>
+        <v>1.8429395373095432E-4</v>
       </c>
       <c r="AE5" s="4">
         <f>Extrapolations!AT7</f>
-        <v>1.5492656753114542E-4</v>
+        <v>1.8429395373095432E-4</v>
       </c>
       <c r="AG5" s="4"/>
       <c r="AH5" s="4"/>
@@ -10618,123 +10617,123 @@
       </c>
       <c r="B8" s="4">
         <f>B$5*Calculations!$B$27</f>
-        <v>4.6477970259343619E-4</v>
+        <v>5.5288186119286287E-4</v>
       </c>
       <c r="C8" s="4">
         <f>C$5*Calculations!$B$27</f>
-        <v>4.6477970259343619E-4</v>
+        <v>5.5288186119286287E-4</v>
       </c>
       <c r="D8" s="4">
         <f>D$5*Calculations!$B$27</f>
-        <v>4.6477970259343619E-4</v>
+        <v>5.5288186119286287E-4</v>
       </c>
       <c r="E8" s="4">
         <f>E$5*Calculations!$B$27</f>
-        <v>4.6477970259343619E-4</v>
+        <v>5.5288186119286287E-4</v>
       </c>
       <c r="F8" s="4">
         <f>F$5*Calculations!$B$27</f>
-        <v>4.6477970259343619E-4</v>
+        <v>5.5288186119286287E-4</v>
       </c>
       <c r="G8" s="4">
         <f>G$5*Calculations!$B$27</f>
-        <v>4.6477970259343619E-4</v>
+        <v>5.5288186119286287E-4</v>
       </c>
       <c r="H8" s="4">
         <f>H$5*Calculations!$B$27</f>
-        <v>4.6477970259343619E-4</v>
+        <v>5.5288186119286287E-4</v>
       </c>
       <c r="I8" s="4">
         <f>I$5*Calculations!$B$27</f>
-        <v>4.6477970259343619E-4</v>
+        <v>5.5288186119286287E-4</v>
       </c>
       <c r="J8" s="4">
         <f>J$5*Calculations!$B$27</f>
-        <v>4.6477970259343619E-4</v>
+        <v>5.5288186119286287E-4</v>
       </c>
       <c r="K8" s="4">
         <f>K$5*Calculations!$B$27</f>
-        <v>4.6477970259343619E-4</v>
+        <v>5.5288186119286287E-4</v>
       </c>
       <c r="L8" s="4">
         <f>L$5*Calculations!$B$27</f>
-        <v>4.6477970259343619E-4</v>
+        <v>5.5288186119286287E-4</v>
       </c>
       <c r="M8" s="4">
         <f>M$5*Calculations!$B$27</f>
-        <v>4.6477970259343619E-4</v>
+        <v>5.5288186119286287E-4</v>
       </c>
       <c r="N8" s="4">
         <f>N$5*Calculations!$B$27</f>
-        <v>4.6477970259343619E-4</v>
+        <v>5.5288186119286287E-4</v>
       </c>
       <c r="O8" s="4">
         <f>O$5*Calculations!$B$27</f>
-        <v>4.6477970259343619E-4</v>
+        <v>5.5288186119286287E-4</v>
       </c>
       <c r="P8" s="4">
         <f>P$5*Calculations!$B$27</f>
-        <v>4.6477970259343619E-4</v>
+        <v>5.5288186119286287E-4</v>
       </c>
       <c r="Q8" s="4">
         <f>Q$5*Calculations!$B$27</f>
-        <v>4.6477970259343619E-4</v>
+        <v>5.5288186119286287E-4</v>
       </c>
       <c r="R8" s="4">
         <f>R$5*Calculations!$B$27</f>
-        <v>4.6477970259343619E-4</v>
+        <v>5.5288186119286287E-4</v>
       </c>
       <c r="S8" s="4">
         <f>S$5*Calculations!$B$27</f>
-        <v>4.6477970259343619E-4</v>
+        <v>5.5288186119286287E-4</v>
       </c>
       <c r="T8" s="4">
         <f>T$5*Calculations!$B$27</f>
-        <v>4.6477970259343619E-4</v>
+        <v>5.5288186119286287E-4</v>
       </c>
       <c r="U8" s="4">
         <f>U$5*Calculations!$B$27</f>
-        <v>4.6477970259343619E-4</v>
+        <v>5.5288186119286287E-4</v>
       </c>
       <c r="V8" s="4">
         <f>V$5*Calculations!$B$27</f>
-        <v>4.6477970259343619E-4</v>
+        <v>5.5288186119286287E-4</v>
       </c>
       <c r="W8" s="4">
         <f>W$5*Calculations!$B$27</f>
-        <v>4.6477970259343619E-4</v>
+        <v>5.5288186119286287E-4</v>
       </c>
       <c r="X8" s="4">
         <f>X$5*Calculations!$B$27</f>
-        <v>4.6477970259343619E-4</v>
+        <v>5.5288186119286287E-4</v>
       </c>
       <c r="Y8" s="4">
         <f>Y$5*Calculations!$B$27</f>
-        <v>4.6477970259343619E-4</v>
+        <v>5.5288186119286287E-4</v>
       </c>
       <c r="Z8" s="4">
         <f>Z$5*Calculations!$B$27</f>
-        <v>4.6477970259343619E-4</v>
+        <v>5.5288186119286287E-4</v>
       </c>
       <c r="AA8" s="4">
         <f>AA$5*Calculations!$B$27</f>
-        <v>4.6477970259343619E-4</v>
+        <v>5.5288186119286287E-4</v>
       </c>
       <c r="AB8" s="4">
         <f>AB$5*Calculations!$B$27</f>
-        <v>4.6477970259343619E-4</v>
+        <v>5.5288186119286287E-4</v>
       </c>
       <c r="AC8" s="4">
         <f>AC$5*Calculations!$B$27</f>
-        <v>4.6477970259343619E-4</v>
+        <v>5.5288186119286287E-4</v>
       </c>
       <c r="AD8" s="4">
         <f>AD$5*Calculations!$B$27</f>
-        <v>4.6477970259343619E-4</v>
+        <v>5.5288186119286287E-4</v>
       </c>
       <c r="AE8" s="4">
         <f>AE$5*Calculations!$B$27</f>
-        <v>4.6477970259343619E-4</v>
+        <v>5.5288186119286287E-4</v>
       </c>
       <c r="AG8" s="4"/>
       <c r="AH8" s="4"/>
@@ -10858,123 +10857,123 @@
       </c>
       <c r="B2" s="4">
         <f>Extrapolations!G9</f>
-        <v>7.5686214263268839E-4</v>
+        <v>6.7428486606874269E-4</v>
       </c>
       <c r="C2" s="4">
         <f>Extrapolations!H9</f>
-        <v>7.5686214263268839E-4</v>
+        <v>6.7428486606874269E-4</v>
       </c>
       <c r="D2" s="4">
         <f>Extrapolations!I9</f>
-        <v>7.5686214263268839E-4</v>
+        <v>6.7428486606874269E-4</v>
       </c>
       <c r="E2" s="4">
         <f>Extrapolations!J9</f>
-        <v>7.5686214263268839E-4</v>
+        <v>6.7428486606874269E-4</v>
       </c>
       <c r="F2" s="4">
         <f>Extrapolations!K9</f>
-        <v>7.5686214263268839E-4</v>
+        <v>6.7428486606874269E-4</v>
       </c>
       <c r="G2" s="4">
         <f>Extrapolations!L9</f>
-        <v>7.5686214263268839E-4</v>
+        <v>6.7428486606874269E-4</v>
       </c>
       <c r="H2" s="4">
         <f>Extrapolations!M9</f>
-        <v>7.5686214263268839E-4</v>
+        <v>6.7428486606874269E-4</v>
       </c>
       <c r="I2" s="4">
         <f>Extrapolations!N9</f>
-        <v>7.5686214263268839E-4</v>
+        <v>6.7428486606874269E-4</v>
       </c>
       <c r="J2" s="4">
         <f>Extrapolations!O9</f>
-        <v>7.5686214263268839E-4</v>
+        <v>6.7428486606874269E-4</v>
       </c>
       <c r="K2" s="4">
         <f>Extrapolations!P9</f>
-        <v>7.5686214263268839E-4</v>
+        <v>6.7428486606874269E-4</v>
       </c>
       <c r="L2" s="4">
         <f>Extrapolations!Q9</f>
-        <v>7.5686214263268839E-4</v>
+        <v>6.7428486606874269E-4</v>
       </c>
       <c r="M2" s="4">
         <f>Extrapolations!R9</f>
-        <v>7.5686214263268839E-4</v>
+        <v>6.7428486606874269E-4</v>
       </c>
       <c r="N2" s="4">
         <f>Extrapolations!S9</f>
-        <v>7.5686214263268839E-4</v>
+        <v>6.7428486606874269E-4</v>
       </c>
       <c r="O2" s="4">
         <f>Extrapolations!T9</f>
-        <v>7.5686214263268839E-4</v>
+        <v>6.7428486606874269E-4</v>
       </c>
       <c r="P2" s="4">
         <f>Extrapolations!U9</f>
-        <v>7.5686214263268839E-4</v>
+        <v>6.7428486606874269E-4</v>
       </c>
       <c r="Q2" s="4">
         <f>Extrapolations!V9</f>
-        <v>7.5686214263268839E-4</v>
+        <v>6.7428486606874269E-4</v>
       </c>
       <c r="R2" s="4">
         <f>Extrapolations!W9</f>
-        <v>7.5686214263268839E-4</v>
+        <v>6.7428486606874269E-4</v>
       </c>
       <c r="S2" s="4">
         <f>Extrapolations!X9</f>
-        <v>7.5686214263268839E-4</v>
+        <v>6.7428486606874269E-4</v>
       </c>
       <c r="T2" s="4">
         <f>Extrapolations!Y9</f>
-        <v>7.5686214263268839E-4</v>
+        <v>6.7428486606874269E-4</v>
       </c>
       <c r="U2" s="4">
         <f>Extrapolations!Z9</f>
-        <v>7.5686214263268839E-4</v>
+        <v>6.7428486606874269E-4</v>
       </c>
       <c r="V2" s="4">
         <f>Extrapolations!AA9</f>
-        <v>7.5686214263268839E-4</v>
+        <v>6.7428486606874269E-4</v>
       </c>
       <c r="W2" s="4">
         <f>Extrapolations!AB9</f>
-        <v>7.5686214263268839E-4</v>
+        <v>6.7428486606874269E-4</v>
       </c>
       <c r="X2" s="4">
         <f>Extrapolations!AC9</f>
-        <v>7.5686214263268839E-4</v>
+        <v>6.7428486606874269E-4</v>
       </c>
       <c r="Y2" s="4">
         <f>Extrapolations!AD9</f>
-        <v>7.5686214263268839E-4</v>
+        <v>6.7428486606874269E-4</v>
       </c>
       <c r="Z2" s="4">
         <f>Extrapolations!AE9</f>
-        <v>7.5686214263268839E-4</v>
+        <v>6.7428486606874269E-4</v>
       </c>
       <c r="AA2" s="4">
         <f>Extrapolations!AF9</f>
-        <v>7.5686214263268839E-4</v>
+        <v>6.7428486606874269E-4</v>
       </c>
       <c r="AB2" s="4">
         <f>Extrapolations!AG9</f>
-        <v>7.5686214263268839E-4</v>
+        <v>6.7428486606874269E-4</v>
       </c>
       <c r="AC2" s="4">
         <f>Extrapolations!AH9</f>
-        <v>7.5686214263268839E-4</v>
+        <v>6.7428486606874269E-4</v>
       </c>
       <c r="AD2" s="4">
         <f>Extrapolations!AI9</f>
-        <v>7.5686214263268839E-4</v>
+        <v>6.7428486606874269E-4</v>
       </c>
       <c r="AE2" s="4">
         <f>Extrapolations!AJ9</f>
-        <v>7.5686214263268839E-4</v>
+        <v>6.7428486606874269E-4</v>
       </c>
     </row>
     <row r="3" spans="1:32">
@@ -11173,123 +11172,123 @@
       </c>
       <c r="B5" s="24">
         <f>Extrapolations!G8</f>
-        <v>7.1745362435245036E-5</v>
+        <v>5.0586266198922429E-5</v>
       </c>
       <c r="C5" s="24">
         <f>Extrapolations!H8</f>
-        <v>7.1745362435245036E-5</v>
+        <v>5.0586266198922429E-5</v>
       </c>
       <c r="D5" s="24">
         <f>Extrapolations!I8</f>
-        <v>7.1745362435245036E-5</v>
+        <v>5.0586266198922429E-5</v>
       </c>
       <c r="E5" s="24">
         <f>Extrapolations!J8</f>
-        <v>7.1745362435245036E-5</v>
+        <v>5.0586266198922429E-5</v>
       </c>
       <c r="F5" s="24">
         <f>Extrapolations!K8</f>
-        <v>7.1745362435245036E-5</v>
+        <v>5.0586266198922429E-5</v>
       </c>
       <c r="G5" s="24">
         <f>Extrapolations!L8</f>
-        <v>7.1745362435245036E-5</v>
+        <v>5.0586266198922429E-5</v>
       </c>
       <c r="H5" s="24">
         <f>Extrapolations!M8</f>
-        <v>7.1745362435245036E-5</v>
+        <v>5.0586266198922429E-5</v>
       </c>
       <c r="I5" s="24">
         <f>Extrapolations!N8</f>
-        <v>7.1745362435245036E-5</v>
+        <v>5.0586266198922429E-5</v>
       </c>
       <c r="J5" s="24">
         <f>Extrapolations!O8</f>
-        <v>7.1745362435245036E-5</v>
+        <v>5.0586266198922429E-5</v>
       </c>
       <c r="K5" s="24">
         <f>Extrapolations!P8</f>
-        <v>7.1745362435245036E-5</v>
+        <v>5.0586266198922429E-5</v>
       </c>
       <c r="L5" s="24">
         <f>Extrapolations!Q8</f>
-        <v>7.1745362435245036E-5</v>
+        <v>5.0586266198922429E-5</v>
       </c>
       <c r="M5" s="24">
         <f>Extrapolations!R8</f>
-        <v>7.1745362435245036E-5</v>
+        <v>5.0586266198922429E-5</v>
       </c>
       <c r="N5" s="24">
         <f>Extrapolations!S8</f>
-        <v>7.1745362435245036E-5</v>
+        <v>5.0586266198922429E-5</v>
       </c>
       <c r="O5" s="24">
         <f>Extrapolations!T8</f>
-        <v>7.1745362435245036E-5</v>
+        <v>5.0586266198922429E-5</v>
       </c>
       <c r="P5" s="24">
         <f>Extrapolations!U8</f>
-        <v>7.1745362435245036E-5</v>
+        <v>5.0586266198922429E-5</v>
       </c>
       <c r="Q5" s="24">
         <f>Extrapolations!V8</f>
-        <v>7.1745362435245036E-5</v>
+        <v>5.0586266198922429E-5</v>
       </c>
       <c r="R5" s="24">
         <f>Extrapolations!W8</f>
-        <v>7.1745362435245036E-5</v>
+        <v>5.0586266198922429E-5</v>
       </c>
       <c r="S5" s="24">
         <f>Extrapolations!X8</f>
-        <v>7.1745362435245036E-5</v>
+        <v>5.0586266198922429E-5</v>
       </c>
       <c r="T5" s="24">
         <f>Extrapolations!Y8</f>
-        <v>7.1745362435245036E-5</v>
+        <v>5.0586266198922429E-5</v>
       </c>
       <c r="U5" s="24">
         <f>Extrapolations!Z8</f>
-        <v>7.1745362435245036E-5</v>
+        <v>5.0586266198922429E-5</v>
       </c>
       <c r="V5" s="24">
         <f>Extrapolations!AA8</f>
-        <v>7.1745362435245036E-5</v>
+        <v>5.0586266198922429E-5</v>
       </c>
       <c r="W5" s="24">
         <f>Extrapolations!AB8</f>
-        <v>7.1745362435245036E-5</v>
+        <v>5.0586266198922429E-5</v>
       </c>
       <c r="X5" s="24">
         <f>Extrapolations!AC8</f>
-        <v>7.1745362435245036E-5</v>
+        <v>5.0586266198922429E-5</v>
       </c>
       <c r="Y5" s="24">
         <f>Extrapolations!AD8</f>
-        <v>7.1745362435245036E-5</v>
+        <v>5.0586266198922429E-5</v>
       </c>
       <c r="Z5" s="24">
         <f>Extrapolations!AE8</f>
-        <v>7.1745362435245036E-5</v>
+        <v>5.0586266198922429E-5</v>
       </c>
       <c r="AA5" s="24">
         <f>Extrapolations!AF8</f>
-        <v>7.1745362435245036E-5</v>
+        <v>5.0586266198922429E-5</v>
       </c>
       <c r="AB5" s="24">
         <f>Extrapolations!AG8</f>
-        <v>7.1745362435245036E-5</v>
+        <v>5.0586266198922429E-5</v>
       </c>
       <c r="AC5" s="24">
         <f>Extrapolations!AH8</f>
-        <v>7.1745362435245036E-5</v>
+        <v>5.0586266198922429E-5</v>
       </c>
       <c r="AD5" s="24">
         <f>Extrapolations!AI8</f>
-        <v>7.1745362435245036E-5</v>
+        <v>5.0586266198922429E-5</v>
       </c>
       <c r="AE5" s="24">
         <f>Extrapolations!AJ8</f>
-        <v>7.1745362435245036E-5</v>
+        <v>5.0586266198922429E-5</v>
       </c>
     </row>
     <row r="6" spans="1:32">
@@ -11488,123 +11487,123 @@
       </c>
       <c r="B8" s="4">
         <f>B$5*Calculations!$B$27</f>
-        <v>2.1523608730573507E-4</v>
+        <v>1.5175879859676727E-4</v>
       </c>
       <c r="C8" s="4">
         <f>C$5*Calculations!$B$27</f>
-        <v>2.1523608730573507E-4</v>
+        <v>1.5175879859676727E-4</v>
       </c>
       <c r="D8" s="4">
         <f>D$5*Calculations!$B$27</f>
-        <v>2.1523608730573507E-4</v>
+        <v>1.5175879859676727E-4</v>
       </c>
       <c r="E8" s="4">
         <f>E$5*Calculations!$B$27</f>
-        <v>2.1523608730573507E-4</v>
+        <v>1.5175879859676727E-4</v>
       </c>
       <c r="F8" s="4">
         <f>F$5*Calculations!$B$27</f>
-        <v>2.1523608730573507E-4</v>
+        <v>1.5175879859676727E-4</v>
       </c>
       <c r="G8" s="4">
         <f>G$5*Calculations!$B$27</f>
-        <v>2.1523608730573507E-4</v>
+        <v>1.5175879859676727E-4</v>
       </c>
       <c r="H8" s="4">
         <f>H$5*Calculations!$B$27</f>
-        <v>2.1523608730573507E-4</v>
+        <v>1.5175879859676727E-4</v>
       </c>
       <c r="I8" s="4">
         <f>I$5*Calculations!$B$27</f>
-        <v>2.1523608730573507E-4</v>
+        <v>1.5175879859676727E-4</v>
       </c>
       <c r="J8" s="4">
         <f>J$5*Calculations!$B$27</f>
-        <v>2.1523608730573507E-4</v>
+        <v>1.5175879859676727E-4</v>
       </c>
       <c r="K8" s="4">
         <f>K$5*Calculations!$B$27</f>
-        <v>2.1523608730573507E-4</v>
+        <v>1.5175879859676727E-4</v>
       </c>
       <c r="L8" s="4">
         <f>L$5*Calculations!$B$27</f>
-        <v>2.1523608730573507E-4</v>
+        <v>1.5175879859676727E-4</v>
       </c>
       <c r="M8" s="4">
         <f>M$5*Calculations!$B$27</f>
-        <v>2.1523608730573507E-4</v>
+        <v>1.5175879859676727E-4</v>
       </c>
       <c r="N8" s="4">
         <f>N$5*Calculations!$B$27</f>
-        <v>2.1523608730573507E-4</v>
+        <v>1.5175879859676727E-4</v>
       </c>
       <c r="O8" s="4">
         <f>O$5*Calculations!$B$27</f>
-        <v>2.1523608730573507E-4</v>
+        <v>1.5175879859676727E-4</v>
       </c>
       <c r="P8" s="4">
         <f>P$5*Calculations!$B$27</f>
-        <v>2.1523608730573507E-4</v>
+        <v>1.5175879859676727E-4</v>
       </c>
       <c r="Q8" s="4">
         <f>Q$5*Calculations!$B$27</f>
-        <v>2.1523608730573507E-4</v>
+        <v>1.5175879859676727E-4</v>
       </c>
       <c r="R8" s="4">
         <f>R$5*Calculations!$B$27</f>
-        <v>2.1523608730573507E-4</v>
+        <v>1.5175879859676727E-4</v>
       </c>
       <c r="S8" s="4">
         <f>S$5*Calculations!$B$27</f>
-        <v>2.1523608730573507E-4</v>
+        <v>1.5175879859676727E-4</v>
       </c>
       <c r="T8" s="4">
         <f>T$5*Calculations!$B$27</f>
-        <v>2.1523608730573507E-4</v>
+        <v>1.5175879859676727E-4</v>
       </c>
       <c r="U8" s="4">
         <f>U$5*Calculations!$B$27</f>
-        <v>2.1523608730573507E-4</v>
+        <v>1.5175879859676727E-4</v>
       </c>
       <c r="V8" s="4">
         <f>V$5*Calculations!$B$27</f>
-        <v>2.1523608730573507E-4</v>
+        <v>1.5175879859676727E-4</v>
       </c>
       <c r="W8" s="4">
         <f>W$5*Calculations!$B$27</f>
-        <v>2.1523608730573507E-4</v>
+        <v>1.5175879859676727E-4</v>
       </c>
       <c r="X8" s="4">
         <f>X$5*Calculations!$B$27</f>
-        <v>2.1523608730573507E-4</v>
+        <v>1.5175879859676727E-4</v>
       </c>
       <c r="Y8" s="4">
         <f>Y$5*Calculations!$B$27</f>
-        <v>2.1523608730573507E-4</v>
+        <v>1.5175879859676727E-4</v>
       </c>
       <c r="Z8" s="4">
         <f>Z$5*Calculations!$B$27</f>
-        <v>2.1523608730573507E-4</v>
+        <v>1.5175879859676727E-4</v>
       </c>
       <c r="AA8" s="4">
         <f>AA$5*Calculations!$B$27</f>
-        <v>2.1523608730573507E-4</v>
+        <v>1.5175879859676727E-4</v>
       </c>
       <c r="AB8" s="4">
         <f>AB$5*Calculations!$B$27</f>
-        <v>2.1523608730573507E-4</v>
+        <v>1.5175879859676727E-4</v>
       </c>
       <c r="AC8" s="4">
         <f>AC$5*Calculations!$B$27</f>
-        <v>2.1523608730573507E-4</v>
+        <v>1.5175879859676727E-4</v>
       </c>
       <c r="AD8" s="4">
         <f>AD$5*Calculations!$B$27</f>
-        <v>2.1523608730573507E-4</v>
+        <v>1.5175879859676727E-4</v>
       </c>
       <c r="AE8" s="4">
         <f>AE$5*Calculations!$B$27</f>
-        <v>2.1523608730573507E-4</v>
+        <v>1.5175879859676727E-4</v>
       </c>
     </row>
     <row r="13" spans="1:32">
@@ -13615,123 +13614,123 @@
       </c>
       <c r="B2" s="4">
         <f>B$5/(1-'Other Values'!$B$3)</f>
-        <v>1.6746135894347786E-2</v>
+        <v>1.3303075089805058E-2</v>
       </c>
       <c r="C2" s="4">
         <f>C$5/(1-'Other Values'!$B$3)</f>
-        <v>1.6746135894347786E-2</v>
+        <v>1.3366797487575091E-2</v>
       </c>
       <c r="D2" s="4">
         <f>D$5/(1-'Other Values'!$B$3)</f>
-        <v>1.6746135894347786E-2</v>
+        <v>1.3430519885345124E-2</v>
       </c>
       <c r="E2" s="4">
         <f>E$5/(1-'Other Values'!$B$3)</f>
-        <v>1.6746135894347786E-2</v>
+        <v>1.3494242283115156E-2</v>
       </c>
       <c r="F2" s="4">
         <f>F$5/(1-'Other Values'!$B$3)</f>
-        <v>1.6746135894347786E-2</v>
+        <v>1.3557964680885187E-2</v>
       </c>
       <c r="G2" s="4">
         <f>G$5/(1-'Other Values'!$B$3)</f>
-        <v>1.6746135894347786E-2</v>
+        <v>1.362168707865522E-2</v>
       </c>
       <c r="H2" s="4">
         <f>H$5/(1-'Other Values'!$B$3)</f>
-        <v>1.6746135894347786E-2</v>
+        <v>1.3685409476425252E-2</v>
       </c>
       <c r="I2" s="4">
         <f>I$5/(1-'Other Values'!$B$3)</f>
-        <v>1.6746135894347786E-2</v>
+        <v>1.3749131874195285E-2</v>
       </c>
       <c r="J2" s="4">
         <f>J$5/(1-'Other Values'!$B$3)</f>
-        <v>1.6746135894347786E-2</v>
+        <v>1.3812854271965316E-2</v>
       </c>
       <c r="K2" s="4">
         <f>K$5/(1-'Other Values'!$B$3)</f>
-        <v>1.6746135894347786E-2</v>
+        <v>1.3876576669735349E-2</v>
       </c>
       <c r="L2" s="4">
         <f>L$5/(1-'Other Values'!$B$3)</f>
-        <v>1.6746135894347786E-2</v>
+        <v>1.3940299067505381E-2</v>
       </c>
       <c r="M2" s="4">
         <f>M$5/(1-'Other Values'!$B$3)</f>
-        <v>1.6746135894347786E-2</v>
+        <v>1.4004021465275414E-2</v>
       </c>
       <c r="N2" s="4">
         <f>N$5/(1-'Other Values'!$B$3)</f>
-        <v>1.6746135894347786E-2</v>
+        <v>1.4067743863045445E-2</v>
       </c>
       <c r="O2" s="4">
         <f>O$5/(1-'Other Values'!$B$3)</f>
-        <v>1.6746135894347786E-2</v>
+        <v>1.4131466260815477E-2</v>
       </c>
       <c r="P2" s="4">
         <f>P$5/(1-'Other Values'!$B$3)</f>
-        <v>1.6746135894347786E-2</v>
+        <v>1.419518865858551E-2</v>
       </c>
       <c r="Q2" s="4">
         <f>Q$5/(1-'Other Values'!$B$3)</f>
-        <v>1.6746135894347786E-2</v>
+        <v>1.4258911056355543E-2</v>
       </c>
       <c r="R2" s="4">
         <f>R$5/(1-'Other Values'!$B$3)</f>
-        <v>1.6746135894347786E-2</v>
+        <v>1.4322633454125573E-2</v>
       </c>
       <c r="S2" s="4">
         <f>S$5/(1-'Other Values'!$B$3)</f>
-        <v>1.6746135894347786E-2</v>
+        <v>1.4386355851895606E-2</v>
       </c>
       <c r="T2" s="4">
         <f>T$5/(1-'Other Values'!$B$3)</f>
-        <v>1.6746135894347786E-2</v>
+        <v>1.4450078249665639E-2</v>
       </c>
       <c r="U2" s="4">
         <f>U$5/(1-'Other Values'!$B$3)</f>
-        <v>1.6746135894347786E-2</v>
+        <v>1.4513800647435671E-2</v>
       </c>
       <c r="V2" s="4">
         <f>V$5/(1-'Other Values'!$B$3)</f>
-        <v>1.6746135894347786E-2</v>
+        <v>1.4577523045205702E-2</v>
       </c>
       <c r="W2" s="4">
         <f>W$5/(1-'Other Values'!$B$3)</f>
-        <v>1.6746135894347786E-2</v>
+        <v>1.4641245442975735E-2</v>
       </c>
       <c r="X2" s="4">
         <f>X$5/(1-'Other Values'!$B$3)</f>
-        <v>1.6746135894347786E-2</v>
+        <v>1.4704967840745767E-2</v>
       </c>
       <c r="Y2" s="4">
         <f>Y$5/(1-'Other Values'!$B$3)</f>
-        <v>1.6746135894347786E-2</v>
+        <v>1.47686902385158E-2</v>
       </c>
       <c r="Z2" s="4">
         <f>Z$5/(1-'Other Values'!$B$3)</f>
-        <v>1.6746135894347786E-2</v>
+        <v>1.4832412636285831E-2</v>
       </c>
       <c r="AA2" s="4">
         <f>AA$5/(1-'Other Values'!$B$3)</f>
-        <v>1.6746135894347786E-2</v>
+        <v>1.4896135034055864E-2</v>
       </c>
       <c r="AB2" s="4">
         <f>AB$5/(1-'Other Values'!$B$3)</f>
-        <v>1.6746135894347786E-2</v>
+        <v>1.4959857431825896E-2</v>
       </c>
       <c r="AC2" s="4">
         <f>AC$5/(1-'Other Values'!$B$3)</f>
-        <v>1.6746135894347786E-2</v>
+        <v>1.5023579829595929E-2</v>
       </c>
       <c r="AD2" s="4">
         <f>AD$5/(1-'Other Values'!$B$3)</f>
-        <v>1.6746135894347786E-2</v>
+        <v>1.508730222736596E-2</v>
       </c>
       <c r="AE2" s="4">
         <f>AE$5/(1-'Other Values'!$B$3)</f>
-        <v>1.6746135894347786E-2</v>
+        <v>1.5151024625135992E-2</v>
       </c>
       <c r="AG2" s="4"/>
       <c r="AH2" s="4"/>
@@ -13932,123 +13931,123 @@
       </c>
       <c r="B5" s="4">
         <f>Extrapolations!H12</f>
-        <v>5.2112239143541636E-3</v>
+        <v>4.139779079772081E-3</v>
       </c>
       <c r="C5" s="4">
         <f>Extrapolations!I12</f>
-        <v>5.2112239143541636E-3</v>
+        <v>4.1596088294668307E-3</v>
       </c>
       <c r="D5" s="4">
         <f>Extrapolations!J12</f>
-        <v>5.2112239143541636E-3</v>
+        <v>4.1794385791615804E-3</v>
       </c>
       <c r="E5" s="4">
         <f>Extrapolations!K12</f>
-        <v>5.2112239143541636E-3</v>
+        <v>4.1992683288563301E-3</v>
       </c>
       <c r="F5" s="4">
         <f>Extrapolations!L12</f>
-        <v>5.2112239143541636E-3</v>
+        <v>4.2190980785510798E-3</v>
       </c>
       <c r="G5" s="4">
         <f>Extrapolations!M12</f>
-        <v>5.2112239143541636E-3</v>
+        <v>4.2389278282458295E-3</v>
       </c>
       <c r="H5" s="4">
         <f>Extrapolations!N12</f>
-        <v>5.2112239143541636E-3</v>
+        <v>4.2587575779405792E-3</v>
       </c>
       <c r="I5" s="4">
         <f>Extrapolations!O12</f>
-        <v>5.2112239143541636E-3</v>
+        <v>4.278587327635329E-3</v>
       </c>
       <c r="J5" s="4">
         <f>Extrapolations!P12</f>
-        <v>5.2112239143541636E-3</v>
+        <v>4.2984170773300787E-3</v>
       </c>
       <c r="K5" s="4">
         <f>Extrapolations!Q12</f>
-        <v>5.2112239143541636E-3</v>
+        <v>4.3182468270248284E-3</v>
       </c>
       <c r="L5" s="4">
         <f>Extrapolations!R12</f>
-        <v>5.2112239143541636E-3</v>
+        <v>4.3380765767195781E-3</v>
       </c>
       <c r="M5" s="4">
         <f>Extrapolations!S12</f>
-        <v>5.2112239143541636E-3</v>
+        <v>4.3579063264143278E-3</v>
       </c>
       <c r="N5" s="4">
         <f>Extrapolations!T12</f>
-        <v>5.2112239143541636E-3</v>
+        <v>4.3777360761090775E-3</v>
       </c>
       <c r="O5" s="4">
         <f>Extrapolations!U12</f>
-        <v>5.2112239143541636E-3</v>
+        <v>4.3975658258038272E-3</v>
       </c>
       <c r="P5" s="4">
         <f>Extrapolations!V12</f>
-        <v>5.2112239143541636E-3</v>
+        <v>4.4173955754985769E-3</v>
       </c>
       <c r="Q5" s="4">
         <f>Extrapolations!W12</f>
-        <v>5.2112239143541636E-3</v>
+        <v>4.4372253251933266E-3</v>
       </c>
       <c r="R5" s="4">
         <f>Extrapolations!X12</f>
-        <v>5.2112239143541636E-3</v>
+        <v>4.4570550748880763E-3</v>
       </c>
       <c r="S5" s="4">
         <f>Extrapolations!Y12</f>
-        <v>5.2112239143541636E-3</v>
+        <v>4.4768848245828261E-3</v>
       </c>
       <c r="T5" s="4">
         <f>Extrapolations!Z12</f>
-        <v>5.2112239143541636E-3</v>
+        <v>4.4967145742775758E-3</v>
       </c>
       <c r="U5" s="4">
         <f>Extrapolations!AA12</f>
-        <v>5.2112239143541636E-3</v>
+        <v>4.5165443239723255E-3</v>
       </c>
       <c r="V5" s="4">
         <f>Extrapolations!AB12</f>
-        <v>5.2112239143541636E-3</v>
+        <v>4.5363740736670752E-3</v>
       </c>
       <c r="W5" s="4">
         <f>Extrapolations!AC12</f>
-        <v>5.2112239143541636E-3</v>
+        <v>4.5562038233618249E-3</v>
       </c>
       <c r="X5" s="4">
         <f>Extrapolations!AD12</f>
-        <v>5.2112239143541636E-3</v>
+        <v>4.5760335730565746E-3</v>
       </c>
       <c r="Y5" s="4">
         <f>Extrapolations!AE12</f>
-        <v>5.2112239143541636E-3</v>
+        <v>4.5958633227513243E-3</v>
       </c>
       <c r="Z5" s="4">
         <f>Extrapolations!AF12</f>
-        <v>5.2112239143541636E-3</v>
+        <v>4.615693072446074E-3</v>
       </c>
       <c r="AA5" s="4">
         <f>Extrapolations!AG12</f>
-        <v>5.2112239143541636E-3</v>
+        <v>4.6355228221408237E-3</v>
       </c>
       <c r="AB5" s="4">
         <f>Extrapolations!AH12</f>
-        <v>5.2112239143541636E-3</v>
+        <v>4.6553525718355734E-3</v>
       </c>
       <c r="AC5" s="4">
         <f>Extrapolations!AI12</f>
-        <v>5.2112239143541636E-3</v>
+        <v>4.6751823215303231E-3</v>
       </c>
       <c r="AD5" s="4">
         <f>Extrapolations!AJ12</f>
-        <v>5.2112239143541636E-3</v>
+        <v>4.6950120712250729E-3</v>
       </c>
       <c r="AE5" s="4">
         <f>Extrapolations!AK12</f>
-        <v>5.2112239143541636E-3</v>
+        <v>4.7148418209198226E-3</v>
       </c>
       <c r="AG5" s="4"/>
       <c r="AH5" s="4"/>
@@ -14249,123 +14248,123 @@
       </c>
       <c r="B8" s="4">
         <f>B$5*Calculations!$B$27</f>
-        <v>1.5633671743062488E-2</v>
+        <v>1.2419337239316241E-2</v>
       </c>
       <c r="C8" s="4">
         <f>C$5*Calculations!$B$27</f>
-        <v>1.5633671743062488E-2</v>
+        <v>1.247882648840049E-2</v>
       </c>
       <c r="D8" s="4">
         <f>D$5*Calculations!$B$27</f>
-        <v>1.5633671743062488E-2</v>
+        <v>1.2538315737484739E-2</v>
       </c>
       <c r="E8" s="4">
         <f>E$5*Calculations!$B$27</f>
-        <v>1.5633671743062488E-2</v>
+        <v>1.2597804986568989E-2</v>
       </c>
       <c r="F8" s="4">
         <f>F$5*Calculations!$B$27</f>
-        <v>1.5633671743062488E-2</v>
+        <v>1.2657294235653238E-2</v>
       </c>
       <c r="G8" s="4">
         <f>G$5*Calculations!$B$27</f>
-        <v>1.5633671743062488E-2</v>
+        <v>1.2716783484737487E-2</v>
       </c>
       <c r="H8" s="4">
         <f>H$5*Calculations!$B$27</f>
-        <v>1.5633671743062488E-2</v>
+        <v>1.2776272733821736E-2</v>
       </c>
       <c r="I8" s="4">
         <f>I$5*Calculations!$B$27</f>
-        <v>1.5633671743062488E-2</v>
+        <v>1.2835761982905985E-2</v>
       </c>
       <c r="J8" s="4">
         <f>J$5*Calculations!$B$27</f>
-        <v>1.5633671743062488E-2</v>
+        <v>1.2895251231990234E-2</v>
       </c>
       <c r="K8" s="4">
         <f>K$5*Calculations!$B$27</f>
-        <v>1.5633671743062488E-2</v>
+        <v>1.2954740481074483E-2</v>
       </c>
       <c r="L8" s="4">
         <f>L$5*Calculations!$B$27</f>
-        <v>1.5633671743062488E-2</v>
+        <v>1.3014229730158733E-2</v>
       </c>
       <c r="M8" s="4">
         <f>M$5*Calculations!$B$27</f>
-        <v>1.5633671743062488E-2</v>
+        <v>1.3073718979242982E-2</v>
       </c>
       <c r="N8" s="4">
         <f>N$5*Calculations!$B$27</f>
-        <v>1.5633671743062488E-2</v>
+        <v>1.3133208228327231E-2</v>
       </c>
       <c r="O8" s="4">
         <f>O$5*Calculations!$B$27</f>
-        <v>1.5633671743062488E-2</v>
+        <v>1.319269747741148E-2</v>
       </c>
       <c r="P8" s="4">
         <f>P$5*Calculations!$B$27</f>
-        <v>1.5633671743062488E-2</v>
+        <v>1.3252186726495729E-2</v>
       </c>
       <c r="Q8" s="4">
         <f>Q$5*Calculations!$B$27</f>
-        <v>1.5633671743062488E-2</v>
+        <v>1.3311675975579978E-2</v>
       </c>
       <c r="R8" s="4">
         <f>R$5*Calculations!$B$27</f>
-        <v>1.5633671743062488E-2</v>
+        <v>1.3371165224664227E-2</v>
       </c>
       <c r="S8" s="4">
         <f>S$5*Calculations!$B$27</f>
-        <v>1.5633671743062488E-2</v>
+        <v>1.3430654473748476E-2</v>
       </c>
       <c r="T8" s="4">
         <f>T$5*Calculations!$B$27</f>
-        <v>1.5633671743062488E-2</v>
+        <v>1.3490143722832726E-2</v>
       </c>
       <c r="U8" s="4">
         <f>U$5*Calculations!$B$27</f>
-        <v>1.5633671743062488E-2</v>
+        <v>1.3549632971916975E-2</v>
       </c>
       <c r="V8" s="4">
         <f>V$5*Calculations!$B$27</f>
-        <v>1.5633671743062488E-2</v>
+        <v>1.3609122221001224E-2</v>
       </c>
       <c r="W8" s="4">
         <f>W$5*Calculations!$B$27</f>
-        <v>1.5633671743062488E-2</v>
+        <v>1.3668611470085473E-2</v>
       </c>
       <c r="X8" s="4">
         <f>X$5*Calculations!$B$27</f>
-        <v>1.5633671743062488E-2</v>
+        <v>1.3728100719169722E-2</v>
       </c>
       <c r="Y8" s="4">
         <f>Y$5*Calculations!$B$27</f>
-        <v>1.5633671743062488E-2</v>
+        <v>1.3787589968253971E-2</v>
       </c>
       <c r="Z8" s="4">
         <f>Z$5*Calculations!$B$27</f>
-        <v>1.5633671743062488E-2</v>
+        <v>1.384707921733822E-2</v>
       </c>
       <c r="AA8" s="4">
         <f>AA$5*Calculations!$B$27</f>
-        <v>1.5633671743062488E-2</v>
+        <v>1.3906568466422469E-2</v>
       </c>
       <c r="AB8" s="4">
         <f>AB$5*Calculations!$B$27</f>
-        <v>1.5633671743062488E-2</v>
+        <v>1.3966057715506719E-2</v>
       </c>
       <c r="AC8" s="4">
         <f>AC$5*Calculations!$B$27</f>
-        <v>1.5633671743062488E-2</v>
+        <v>1.4025546964590968E-2</v>
       </c>
       <c r="AD8" s="4">
         <f>AD$5*Calculations!$B$27</f>
-        <v>1.5633671743062488E-2</v>
+        <v>1.4085036213675217E-2</v>
       </c>
       <c r="AE8" s="4">
         <f>AE$5*Calculations!$B$27</f>
-        <v>1.5633671743062488E-2</v>
+        <v>1.4144525462759466E-2</v>
       </c>
       <c r="AG8" s="4"/>
       <c r="AH8" s="4"/>
@@ -16437,88 +16436,88 @@
         <v>1.0877081887028839E-4</v>
       </c>
       <c r="F9" s="4">
-        <v>9.2955581997260681E-5</v>
+        <v>1.0066053377187421E-4</v>
       </c>
       <c r="G9" s="4">
-        <v>7.9492494824774367E-5</v>
+        <v>8.6081511061439429E-5</v>
       </c>
       <c r="H9" s="4">
-        <v>7.9975948644702701E-5</v>
+        <v>8.6605037659008062E-5</v>
       </c>
       <c r="I9" s="4">
-        <v>8.1024722706877106E-5</v>
+        <v>8.774074306406576E-5</v>
       </c>
       <c r="J9" s="4">
-        <v>8.2072270340545126E-5</v>
+        <v>8.8875120383758021E-5</v>
       </c>
       <c r="K9" s="4">
-        <v>8.3921848415336979E-5</v>
+        <v>9.0878007270817581E-5</v>
       </c>
       <c r="L9" s="4">
-        <v>8.424008288356597E-5</v>
+        <v>9.1222619727092481E-5</v>
       </c>
       <c r="M9" s="4">
-        <v>8.5145457355772448E-5</v>
+        <v>9.2203039360616137E-5</v>
       </c>
       <c r="N9" s="4">
-        <v>8.6269511754863824E-5</v>
+        <v>9.3420264979240058E-5</v>
       </c>
       <c r="O9" s="4">
-        <v>8.7316787399673934E-5</v>
+        <v>9.4554347765317116E-5</v>
       </c>
       <c r="P9" s="4">
-        <v>8.7981217262129169E-5</v>
+        <v>9.5273851243985993E-5</v>
       </c>
       <c r="Q9" s="4">
-        <v>8.8870744349267236E-5</v>
+        <v>9.6237109925949779E-5</v>
       </c>
       <c r="R9" s="4">
-        <v>8.9949247005972088E-5</v>
+        <v>9.7405008085110293E-5</v>
       </c>
       <c r="S9" s="4">
-        <v>9.0831024253729272E-5</v>
+        <v>9.83598745548802E-5</v>
       </c>
       <c r="T9" s="4">
-        <v>9.1579110752047641E-5</v>
+        <v>9.9169968845188442E-5</v>
       </c>
       <c r="U9" s="4">
-        <v>9.2403640539502613E-5</v>
+        <v>1.0006284269668531E-4</v>
       </c>
       <c r="V9" s="4">
-        <v>9.319851514165077E-5</v>
+        <v>1.009236032880858E-4</v>
       </c>
       <c r="W9" s="4">
-        <v>9.3891059740218658E-5</v>
+        <v>1.0167355189208385E-4</v>
       </c>
       <c r="X9" s="4">
-        <v>9.5047122599296139E-5</v>
+        <v>1.0292543910496804E-4</v>
       </c>
       <c r="Y9" s="4">
-        <v>9.6059950070461278E-5</v>
+        <v>1.0402221835884117E-4</v>
       </c>
       <c r="Z9" s="4">
-        <v>9.7048480369583043E-5</v>
+        <v>1.0509268648373766E-4</v>
       </c>
       <c r="AA9" s="4">
-        <v>9.7649579603605602E-5</v>
+        <v>1.0574360995112404E-4</v>
       </c>
       <c r="AB9" s="4">
-        <v>9.8224460923876486E-5</v>
+        <v>1.0636614234036401E-4</v>
       </c>
       <c r="AC9" s="4">
-        <v>9.8795624738493866E-5</v>
+        <v>1.069846490853625E-4</v>
       </c>
       <c r="AD9" s="4">
-        <v>9.9479244599585216E-5</v>
+        <v>1.077249331934921E-4</v>
       </c>
       <c r="AE9" s="4">
-        <v>9.9975448040260604E-5</v>
+        <v>1.0826226620916075E-4</v>
       </c>
       <c r="AF9" s="4">
-        <v>1.0044050579002983E-4</v>
+        <v>1.08765871913312E-4</v>
       </c>
       <c r="AG9" s="4">
-        <v>1.0101640935179317E-4</v>
+        <v>1.0938951127614153E-4</v>
       </c>
       <c r="AH9" s="4"/>
       <c r="AI9" s="4"/>
@@ -16752,88 +16751,88 @@
         <v>5.7245968727451246E-4</v>
       </c>
       <c r="F12" s="4">
-        <v>4.390541760701407E-4</v>
+        <v>4.6292253798248397E-4</v>
       </c>
       <c r="G12" s="4">
-        <v>4.390541760701407E-4</v>
+        <v>4.6724180152163598E-4</v>
       </c>
       <c r="H12" s="4">
-        <v>4.390541760701407E-4</v>
+        <v>4.6965127581020212E-4</v>
       </c>
       <c r="I12" s="4">
-        <v>4.390541760701407E-4</v>
+        <v>4.7322813533235715E-4</v>
       </c>
       <c r="J12" s="4">
-        <v>4.390541760701407E-4</v>
+        <v>4.7696949985651614E-4</v>
       </c>
       <c r="K12" s="4">
-        <v>4.390541760701407E-4</v>
+        <v>4.8083975908889043E-4</v>
       </c>
       <c r="L12" s="4">
-        <v>4.390541760701407E-4</v>
+        <v>4.847773340732441E-4</v>
       </c>
       <c r="M12" s="4">
-        <v>4.390541760701407E-4</v>
+        <v>4.8876510978465549E-4</v>
       </c>
       <c r="N12" s="4">
-        <v>4.390541760701407E-4</v>
+        <v>4.9280339238632709E-4</v>
       </c>
       <c r="O12" s="4">
-        <v>4.390541760701407E-4</v>
+        <v>4.9685871974595585E-4</v>
       </c>
       <c r="P12" s="4">
-        <v>4.390541760701407E-4</v>
+        <v>5.0093827917019513E-4</v>
       </c>
       <c r="Q12" s="4">
-        <v>4.390541760701407E-4</v>
+        <v>5.0505403110021464E-4</v>
       </c>
       <c r="R12" s="4">
-        <v>4.390541760701407E-4</v>
+        <v>5.091914152171586E-4</v>
       </c>
       <c r="S12" s="4">
-        <v>4.390541760701407E-4</v>
+        <v>5.1335993261843963E-4</v>
       </c>
       <c r="T12" s="4">
-        <v>4.390541760701407E-4</v>
+        <v>5.1755601976514434E-4</v>
       </c>
       <c r="U12" s="4">
-        <v>4.390541760701407E-4</v>
+        <v>5.2177673046383325E-4</v>
       </c>
       <c r="V12" s="4">
-        <v>4.390541760701407E-4</v>
+        <v>5.2602994967173547E-4</v>
       </c>
       <c r="W12" s="4">
-        <v>4.390541760701407E-4</v>
+        <v>5.3031732866251667E-4</v>
       </c>
       <c r="X12" s="4">
-        <v>4.390541760701407E-4</v>
+        <v>5.346381346521186E-4</v>
       </c>
       <c r="Y12" s="4">
-        <v>4.390541760701407E-4</v>
+        <v>5.3898042225657822E-4</v>
       </c>
       <c r="Z12" s="4">
-        <v>4.390541760701407E-4</v>
+        <v>5.4335778311445497E-4</v>
       </c>
       <c r="AA12" s="4">
-        <v>4.390541760701407E-4</v>
+        <v>5.4777558261039474E-4</v>
       </c>
       <c r="AB12" s="4">
-        <v>4.390541760701407E-4</v>
+        <v>5.5222750675573099E-4</v>
       </c>
       <c r="AC12" s="4">
-        <v>4.390541760701407E-4</v>
+        <v>5.5671423312476443E-4</v>
       </c>
       <c r="AD12" s="4">
-        <v>4.390541760701407E-4</v>
+        <v>5.6121623753950501E-4</v>
       </c>
       <c r="AE12" s="4">
-        <v>4.390541760701407E-4</v>
+        <v>5.6574653946465893E-4</v>
       </c>
       <c r="AF12" s="4">
-        <v>4.390541760701407E-4</v>
+        <v>5.7031870042437182E-4</v>
       </c>
       <c r="AG12" s="4">
-        <v>4.390541760701407E-4</v>
+        <v>5.7492662224994018E-4</v>
       </c>
       <c r="AH12" s="4"/>
       <c r="AI12" s="4"/>
@@ -16857,88 +16856,88 @@
         <v>4.7951937565239972E-5</v>
       </c>
       <c r="F13" s="4">
-        <v>1.5492656753114542E-4</v>
+        <v>1.8429395373095432E-4</v>
       </c>
       <c r="G13" s="4">
-        <v>1.5492656753114542E-4</v>
+        <v>1.8429395373095432E-4</v>
       </c>
       <c r="H13" s="4">
-        <v>1.5492656753114542E-4</v>
+        <v>1.8429395373095432E-4</v>
       </c>
       <c r="I13" s="4">
-        <v>1.5492656753114542E-4</v>
+        <v>1.8429395373095432E-4</v>
       </c>
       <c r="J13" s="4">
-        <v>1.5492656753114542E-4</v>
+        <v>1.8429395373095432E-4</v>
       </c>
       <c r="K13" s="4">
-        <v>1.5492656753114542E-4</v>
+        <v>1.8429395373095432E-4</v>
       </c>
       <c r="L13" s="4">
-        <v>1.5492656753114542E-4</v>
+        <v>1.8429395373095432E-4</v>
       </c>
       <c r="M13" s="4">
-        <v>1.5492656753114542E-4</v>
+        <v>1.8429395373095432E-4</v>
       </c>
       <c r="N13" s="4">
-        <v>1.5492656753114542E-4</v>
+        <v>1.8429395373095432E-4</v>
       </c>
       <c r="O13" s="4">
-        <v>1.5492656753114542E-4</v>
+        <v>1.8429395373095432E-4</v>
       </c>
       <c r="P13" s="4">
-        <v>1.5492656753114542E-4</v>
+        <v>1.8429395373095432E-4</v>
       </c>
       <c r="Q13" s="4">
-        <v>1.5492656753114542E-4</v>
+        <v>1.8429395373095432E-4</v>
       </c>
       <c r="R13" s="4">
-        <v>1.5492656753114542E-4</v>
+        <v>1.8429395373095432E-4</v>
       </c>
       <c r="S13" s="4">
-        <v>1.5492656753114542E-4</v>
+        <v>1.8429395373095432E-4</v>
       </c>
       <c r="T13" s="4">
-        <v>1.5492656753114542E-4</v>
+        <v>1.8429395373095432E-4</v>
       </c>
       <c r="U13" s="4">
-        <v>1.5492656753114542E-4</v>
+        <v>1.8429395373095432E-4</v>
       </c>
       <c r="V13" s="4">
-        <v>1.5492656753114542E-4</v>
+        <v>1.8429395373095432E-4</v>
       </c>
       <c r="W13" s="4">
-        <v>1.5492656753114542E-4</v>
+        <v>1.8429395373095432E-4</v>
       </c>
       <c r="X13" s="4">
-        <v>1.5492656753114542E-4</v>
+        <v>1.8429395373095432E-4</v>
       </c>
       <c r="Y13" s="4">
-        <v>1.5492656753114542E-4</v>
+        <v>1.8429395373095432E-4</v>
       </c>
       <c r="Z13" s="4">
-        <v>1.5492656753114542E-4</v>
+        <v>1.8429395373095432E-4</v>
       </c>
       <c r="AA13" s="4">
-        <v>1.5492656753114542E-4</v>
+        <v>1.8429395373095432E-4</v>
       </c>
       <c r="AB13" s="4">
-        <v>1.5492656753114542E-4</v>
+        <v>1.8429395373095432E-4</v>
       </c>
       <c r="AC13" s="4">
-        <v>1.5492656753114542E-4</v>
+        <v>1.8429395373095432E-4</v>
       </c>
       <c r="AD13" s="4">
-        <v>1.5492656753114542E-4</v>
+        <v>1.8429395373095432E-4</v>
       </c>
       <c r="AE13" s="4">
-        <v>1.5492656753114542E-4</v>
+        <v>1.8429395373095432E-4</v>
       </c>
       <c r="AF13" s="4">
-        <v>1.5492656753114542E-4</v>
+        <v>1.8429395373095432E-4</v>
       </c>
       <c r="AG13" s="4">
-        <v>1.5492656753114542E-4</v>
+        <v>1.8429395373095432E-4</v>
       </c>
       <c r="AH13" s="4"/>
       <c r="AI13" s="4"/>
@@ -16962,88 +16961,88 @@
         <v>7.1745362435245036E-5</v>
       </c>
       <c r="F14" s="4">
-        <v>7.1745362435245036E-5</v>
+        <v>5.0586266198922429E-5</v>
       </c>
       <c r="G14" s="4">
-        <v>7.1745362435245036E-5</v>
+        <v>5.0586266198922429E-5</v>
       </c>
       <c r="H14" s="4">
-        <v>7.1745362435245036E-5</v>
+        <v>5.3101596884754634E-5</v>
       </c>
       <c r="I14" s="4">
-        <v>7.1745362435245036E-5</v>
+        <v>5.5476684979521999E-5</v>
       </c>
       <c r="J14" s="4">
-        <v>7.1745362435245036E-5</v>
+        <v>5.7582399958914863E-5</v>
       </c>
       <c r="K14" s="4">
-        <v>7.1745362435245036E-5</v>
+        <v>5.9286666683388943E-5</v>
       </c>
       <c r="L14" s="4">
-        <v>7.1745362435245036E-5</v>
+        <v>6.0610395754023679E-5</v>
       </c>
       <c r="M14" s="4">
-        <v>7.1745362435245036E-5</v>
+        <v>6.1478539640264247E-5</v>
       </c>
       <c r="N14" s="4">
-        <v>7.1745362435245036E-5</v>
+        <v>6.2186018569269444E-5</v>
       </c>
       <c r="O14" s="4">
-        <v>7.1745362435245036E-5</v>
+        <v>6.2719039327693317E-5</v>
       </c>
       <c r="P14" s="4">
-        <v>7.1745362435245036E-5</v>
+        <v>6.3153887297853718E-5</v>
       </c>
       <c r="Q14" s="4">
-        <v>7.1745362435245036E-5</v>
+        <v>6.3628880192573051E-5</v>
       </c>
       <c r="R14" s="4">
-        <v>7.1745362435245036E-5</v>
+        <v>6.3761431096533459E-5</v>
       </c>
       <c r="S14" s="4">
-        <v>7.1745362435245036E-5</v>
+        <v>6.3729513130366037E-5</v>
       </c>
       <c r="T14" s="4">
-        <v>7.1745362435245036E-5</v>
+        <v>6.3732591582412674E-5</v>
       </c>
       <c r="U14" s="4">
-        <v>7.1745362435245036E-5</v>
+        <v>6.3745932608772252E-5</v>
       </c>
       <c r="V14" s="4">
-        <v>7.1745362435245036E-5</v>
+        <v>6.3747499557147288E-5</v>
       </c>
       <c r="W14" s="4">
-        <v>7.1745362435245036E-5</v>
+        <v>6.3758927758343791E-5</v>
       </c>
       <c r="X14" s="4">
-        <v>7.1745362435245036E-5</v>
+        <v>6.3766114056474239E-5</v>
       </c>
       <c r="Y14" s="4">
-        <v>7.1745362435245036E-5</v>
+        <v>6.377291869318759E-5</v>
       </c>
       <c r="Z14" s="4">
-        <v>7.1745362435245036E-5</v>
+        <v>6.3770415255279687E-5</v>
       </c>
       <c r="AA14" s="4">
-        <v>7.1745362435245036E-5</v>
+        <v>6.3757191437674787E-5</v>
       </c>
       <c r="AB14" s="4">
-        <v>7.1745362435245036E-5</v>
+        <v>6.3739981586323922E-5</v>
       </c>
       <c r="AC14" s="4">
-        <v>7.1745362435245036E-5</v>
+        <v>6.3714202878978367E-5</v>
       </c>
       <c r="AD14" s="4">
-        <v>7.1745362435245036E-5</v>
+        <v>6.3705931242018896E-5</v>
       </c>
       <c r="AE14" s="4">
-        <v>7.1745362435245036E-5</v>
+        <v>6.3710650453125008E-5</v>
       </c>
       <c r="AF14" s="4">
-        <v>7.1745362435245036E-5</v>
+        <v>6.371634382274241E-5</v>
       </c>
       <c r="AG14" s="4">
-        <v>7.1745362435245036E-5</v>
+        <v>6.3734281954707259E-5</v>
       </c>
       <c r="AH14" s="4"/>
       <c r="AI14" s="4"/>
@@ -17067,88 +17066,88 @@
         <v>7.5686214263268839E-4</v>
       </c>
       <c r="F15" s="4">
-        <v>7.5686214263268839E-4</v>
+        <v>6.7428486606874269E-4</v>
       </c>
       <c r="G15" s="4">
-        <v>7.5686214263268839E-4</v>
+        <v>6.7428486606874269E-4</v>
       </c>
       <c r="H15" s="4">
-        <v>7.5686214263268839E-4</v>
+        <v>7.0781272930232322E-4</v>
       </c>
       <c r="I15" s="4">
-        <v>7.5686214263268839E-4</v>
+        <v>7.394712421402561E-4</v>
       </c>
       <c r="J15" s="4">
-        <v>7.5686214263268839E-4</v>
+        <v>7.6753917143307089E-4</v>
       </c>
       <c r="K15" s="4">
-        <v>7.5686214263268839E-4</v>
+        <v>7.9025603406014298E-4</v>
       </c>
       <c r="L15" s="4">
-        <v>7.5686214263268839E-4</v>
+        <v>8.0790055590712715E-4</v>
       </c>
       <c r="M15" s="4">
-        <v>7.5686214263268839E-4</v>
+        <v>8.1947239799090967E-4</v>
       </c>
       <c r="N15" s="4">
-        <v>7.5686214263268839E-4</v>
+        <v>8.289026716745779E-4</v>
       </c>
       <c r="O15" s="4">
-        <v>7.5686214263268839E-4</v>
+        <v>8.3600752162124896E-4</v>
       </c>
       <c r="P15" s="4">
-        <v>7.5686214263268839E-4</v>
+        <v>8.4180378664240824E-4</v>
       </c>
       <c r="Q15" s="4">
-        <v>7.5686214263268839E-4</v>
+        <v>8.4813515965064684E-4</v>
       </c>
       <c r="R15" s="4">
-        <v>7.5686214263268839E-4</v>
+        <v>8.4990198442820152E-4</v>
       </c>
       <c r="S15" s="4">
-        <v>7.5686214263268839E-4</v>
+        <v>8.4947653690737148E-4</v>
       </c>
       <c r="T15" s="4">
-        <v>7.5686214263268839E-4</v>
+        <v>8.4951757084369322E-4</v>
       </c>
       <c r="U15" s="4">
-        <v>7.5686214263268839E-4</v>
+        <v>8.4969539879677265E-4</v>
       </c>
       <c r="V15" s="4">
-        <v>7.5686214263268839E-4</v>
+        <v>8.4971628528740723E-4</v>
       </c>
       <c r="W15" s="4">
-        <v>7.5686214263268839E-4</v>
+        <v>8.4986861641781495E-4</v>
       </c>
       <c r="X15" s="4">
-        <v>7.5686214263268839E-4</v>
+        <v>8.4996440550122682E-4</v>
       </c>
       <c r="Y15" s="4">
-        <v>7.5686214263268839E-4</v>
+        <v>8.5005510726476202E-4</v>
       </c>
       <c r="Z15" s="4">
-        <v>7.5686214263268839E-4</v>
+        <v>8.5002173792519053E-4</v>
       </c>
       <c r="AA15" s="4">
-        <v>7.5686214263268839E-4</v>
+        <v>8.4984547229515633E-4</v>
       </c>
       <c r="AB15" s="4">
-        <v>7.5686214263268839E-4</v>
+        <v>8.4961607520410507E-4</v>
       </c>
       <c r="AC15" s="4">
-        <v>7.5686214263268839E-4</v>
+        <v>8.4927246035493688E-4</v>
       </c>
       <c r="AD15" s="4">
-        <v>7.5686214263268839E-4</v>
+        <v>8.4916220434992835E-4</v>
       </c>
       <c r="AE15" s="4">
-        <v>7.5686214263268839E-4</v>
+        <v>8.4922510862944409E-4</v>
       </c>
       <c r="AF15" s="4">
-        <v>7.5686214263268839E-4</v>
+        <v>8.4930099786299329E-4</v>
       </c>
       <c r="AG15" s="4">
-        <v>7.5686214263268839E-4</v>
+        <v>8.4954010250182699E-4</v>
       </c>
       <c r="AH15" s="4"/>
       <c r="AI15" s="4"/>
@@ -17378,88 +17377,88 @@
         <v>5.2454271866069326E-3</v>
       </c>
       <c r="F18" s="4">
-        <v>5.2112239143541636E-3</v>
+        <v>4.8577789999999996E-3</v>
       </c>
       <c r="G18" s="4">
-        <v>5.2112239143541636E-3</v>
+        <v>4.8577789999999996E-3</v>
       </c>
       <c r="H18" s="4">
-        <v>5.2112239143541636E-3</v>
+        <v>4.8766649999999996E-3</v>
       </c>
       <c r="I18" s="4">
-        <v>5.2112239143541636E-3</v>
+        <v>4.8956239999999995E-3</v>
       </c>
       <c r="J18" s="4">
-        <v>5.2112239143541636E-3</v>
+        <v>4.9146570000000002E-3</v>
       </c>
       <c r="K18" s="4">
-        <v>5.2112239143541636E-3</v>
+        <v>4.9337640000000002E-3</v>
       </c>
       <c r="L18" s="4">
-        <v>5.2112239143541636E-3</v>
+        <v>4.9529449999999994E-3</v>
       </c>
       <c r="M18" s="4">
-        <v>5.2112239143541636E-3</v>
+        <v>4.9721999999999995E-3</v>
       </c>
       <c r="N18" s="4">
-        <v>5.2112239143541636E-3</v>
+        <v>4.9915310000000004E-3</v>
       </c>
       <c r="O18" s="4">
-        <v>5.2112239143541636E-3</v>
+        <v>5.010937E-3</v>
       </c>
       <c r="P18" s="4">
-        <v>5.2112239143541636E-3</v>
+        <v>5.030418E-3</v>
       </c>
       <c r="Q18" s="4">
-        <v>5.2112239143541636E-3</v>
+        <v>5.049975E-3</v>
       </c>
       <c r="R18" s="4">
-        <v>5.2112239143541636E-3</v>
+        <v>5.0696079999999998E-3</v>
       </c>
       <c r="S18" s="4">
-        <v>5.2112239143541636E-3</v>
+        <v>5.0893170000000003E-3</v>
       </c>
       <c r="T18" s="4">
-        <v>5.2112239143541636E-3</v>
+        <v>5.1091030000000003E-3</v>
       </c>
       <c r="U18" s="4">
-        <v>5.2112239143541636E-3</v>
+        <v>5.1289660000000004E-3</v>
       </c>
       <c r="V18" s="4">
-        <v>5.2112239143541636E-3</v>
+        <v>5.148906E-3</v>
       </c>
       <c r="W18" s="4">
-        <v>5.2112239143541636E-3</v>
+        <v>5.1689230000000006E-3</v>
       </c>
       <c r="X18" s="4">
-        <v>5.2112239143541636E-3</v>
+        <v>5.1890190000000004E-3</v>
       </c>
       <c r="Y18" s="4">
-        <v>5.2112239143541636E-3</v>
+        <v>5.2091919999999996E-3</v>
       </c>
       <c r="Z18" s="4">
-        <v>5.2112239143541636E-3</v>
+        <v>5.2294450000000001E-3</v>
       </c>
       <c r="AA18" s="4">
-        <v>5.2112239143541636E-3</v>
+        <v>5.2497749999999999E-3</v>
       </c>
       <c r="AB18" s="4">
-        <v>5.2112239143541636E-3</v>
+        <v>5.2701849999999993E-3</v>
       </c>
       <c r="AC18" s="4">
-        <v>5.2112239143541636E-3</v>
+        <v>5.2906740000000004E-3</v>
       </c>
       <c r="AD18" s="4">
-        <v>5.2112239143541636E-3</v>
+        <v>5.3112430000000002E-3</v>
       </c>
       <c r="AE18" s="4">
-        <v>5.2112239143541636E-3</v>
+        <v>5.3318919999999995E-3</v>
       </c>
       <c r="AF18" s="4">
-        <v>5.2112239143541636E-3</v>
+        <v>5.3526210000000001E-3</v>
       </c>
       <c r="AG18" s="4">
-        <v>5.2112239143541636E-3</v>
+        <v>5.3734300000000002E-3</v>
       </c>
       <c r="AH18" s="4"/>
       <c r="AI18" s="4"/>
@@ -18556,16 +18555,16 @@
         <v>16</v>
       </c>
       <c r="B5">
-        <v>7.5686214263268839E-4</v>
+        <v>6.7428486606874269E-4</v>
       </c>
       <c r="C5">
-        <v>7.1745362435245036E-5</v>
+        <v>5.0586266198922429E-5</v>
       </c>
       <c r="D5">
-        <v>7.1745362435245036E-5</v>
+        <v>5.0586266198922429E-5</v>
       </c>
       <c r="E5">
-        <v>7.1745362435245036E-5</v>
+        <v>5.0586266198922429E-5</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -18574,7 +18573,7 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>2.1523608730573507E-4</v>
+        <v>1.5175879859676727E-4</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -18666,10 +18665,10 @@
         <v>7.0204850469879831E-5</v>
       </c>
       <c r="D10">
-        <v>9.2955581997260681E-5</v>
+        <v>1.0066053377187421E-4</v>
       </c>
       <c r="E10">
-        <v>1.0087912753938768E-4</v>
+        <v>7.8079341843850301E-5</v>
       </c>
       <c r="F10">
         <v>1.7525323807361898E-4</v>
@@ -19657,179 +19656,179 @@
       <c r="Z3" s="9"/>
       <c r="AA3" s="4" cm="1">
         <f t="array" ref="AA3">TREND($AQ$3:$AU$3,$AQ$1:$AU$1,AA1)</f>
-        <v>6.2736507518388511E-5</v>
+        <v>6.7936644557507406E-5</v>
       </c>
       <c r="AB3" s="4" cm="1">
         <f t="array" ref="AB3">TREND($AQ$3:$AU$3,$AQ$1:$AU$1,AB1)</f>
-        <v>6.3701994710036553E-5</v>
+        <v>6.8982159565568642E-5</v>
       </c>
       <c r="AC3" s="4" cm="1">
         <f t="array" ref="AC3">TREND($AQ$3:$AU$3,$AQ$1:$AU$1,AC1)</f>
-        <v>6.4667481901684379E-5</v>
+        <v>7.0027674573629444E-5</v>
       </c>
       <c r="AD3" s="4" cm="1">
         <f t="array" ref="AD3">TREND($AQ$3:$AU$3,$AQ$1:$AU$1,AD1)</f>
-        <v>6.5632969093332421E-5</v>
+        <v>7.107318958169068E-5</v>
       </c>
       <c r="AE3" s="4" cm="1">
         <f t="array" ref="AE3">TREND($AQ$3:$AU$3,$AQ$1:$AU$1,AE1)</f>
-        <v>6.6598456284980246E-5</v>
+        <v>7.2118704589751916E-5</v>
       </c>
       <c r="AF3" s="4" cm="1">
         <f t="array" ref="AF3">TREND($AQ$3:$AU$3,$AQ$1:$AU$1,AF1)</f>
-        <v>6.7563943476628288E-5</v>
+        <v>7.3164219597812719E-5</v>
       </c>
       <c r="AG3" s="4" cm="1">
         <f t="array" ref="AG3">TREND($AQ$3:$AU$3,$AQ$1:$AU$1,AG1)</f>
-        <v>6.8529430668276114E-5</v>
+        <v>7.4209734605873955E-5</v>
       </c>
       <c r="AH3" s="4" cm="1">
         <f t="array" ref="AH3">TREND($AQ$3:$AU$3,$AQ$1:$AU$1,AH1)</f>
-        <v>6.9494917859924156E-5</v>
+        <v>7.5255249613935191E-5</v>
       </c>
       <c r="AI3" s="4" cm="1">
         <f t="array" ref="AI3">TREND($AQ$3:$AU$3,$AQ$1:$AU$1,AI1)</f>
-        <v>7.0460405051572198E-5</v>
+        <v>7.6300764621996427E-5</v>
       </c>
       <c r="AJ3" s="4" cm="1">
         <f t="array" ref="AJ3">TREND($AQ$3:$AU$3,$AQ$1:$AU$1,AJ1)</f>
-        <v>7.1425892243220023E-5</v>
+        <v>7.7346279630057229E-5</v>
       </c>
       <c r="AK3" s="4" cm="1">
         <f t="array" ref="AK3">TREND($AQ$3:$AU$3,$AQ$1:$AU$1,AK1)</f>
-        <v>7.2391379434868066E-5</v>
+        <v>7.8391794638118465E-5</v>
       </c>
       <c r="AL3" s="4" cm="1">
         <f t="array" ref="AL3">TREND($AQ$3:$AU$3,$AQ$1:$AU$1,AL1)</f>
-        <v>7.3356866626515891E-5</v>
+        <v>7.9437309646179701E-5</v>
       </c>
       <c r="AM3" s="4" cm="1">
         <f t="array" ref="AM3">TREND($AQ$3:$AU$3,$AQ$1:$AU$1,AM1)</f>
-        <v>7.4322353818163933E-5</v>
+        <v>8.0482824654240937E-5</v>
       </c>
       <c r="AN3" s="4" cm="1">
         <f t="array" ref="AN3">TREND($AQ$3:$AU$3,$AQ$1:$AU$1,AN1)</f>
-        <v>7.5287841009811758E-5</v>
+        <v>8.152833966230174E-5</v>
       </c>
       <c r="AO3" s="4" cm="1">
         <f t="array" ref="AO3">TREND($AQ$3:$AU$3,$AQ$1:$AU$1,AO1)</f>
-        <v>7.6253328201459801E-5</v>
+        <v>8.2573854670362976E-5</v>
       </c>
       <c r="AP3" s="4" cm="1">
         <f t="array" ref="AP3">TREND($AR$3:$AV$3,$AR$1:$AV$1,AP1)</f>
-        <v>7.6915445435660028E-5</v>
+        <v>8.3290853830414978E-5</v>
       </c>
       <c r="AQ3" s="4" cm="1">
         <f t="array" ref="AQ3">TREND($AR$3:$AV$3,$AR$1:$AV$1,AQ1)</f>
-        <v>7.8010948323356793E-5</v>
+        <v>8.4477161344765576E-5</v>
       </c>
       <c r="AR3" s="10">
         <f>BNVFE!G9</f>
-        <v>7.9492494824774367E-5</v>
+        <v>8.6081511061439429E-5</v>
       </c>
       <c r="AS3" s="10">
         <f>BNVFE!H9</f>
-        <v>7.9975948644702701E-5</v>
+        <v>8.6605037659008062E-5</v>
       </c>
       <c r="AT3" s="10">
         <f>BNVFE!I9</f>
-        <v>8.1024722706877106E-5</v>
+        <v>8.774074306406576E-5</v>
       </c>
       <c r="AU3" s="10">
         <f>BNVFE!J9</f>
-        <v>8.2072270340545126E-5</v>
+        <v>8.8875120383758021E-5</v>
       </c>
       <c r="AV3" s="10">
         <f>BNVFE!K9</f>
-        <v>8.3921848415336979E-5</v>
+        <v>9.0878007270817581E-5</v>
       </c>
       <c r="AW3" s="10">
         <f>BNVFE!L9</f>
-        <v>8.424008288356597E-5</v>
+        <v>9.1222619727092481E-5</v>
       </c>
       <c r="AX3" s="10">
         <f>BNVFE!M9</f>
-        <v>8.5145457355772448E-5</v>
+        <v>9.2203039360616137E-5</v>
       </c>
       <c r="AY3" s="10">
         <f>BNVFE!N9</f>
-        <v>8.6269511754863824E-5</v>
+        <v>9.3420264979240058E-5</v>
       </c>
       <c r="AZ3" s="10">
         <f>BNVFE!O9</f>
-        <v>8.7316787399673934E-5</v>
+        <v>9.4554347765317116E-5</v>
       </c>
       <c r="BA3" s="10">
         <f>BNVFE!P9</f>
-        <v>8.7981217262129169E-5</v>
+        <v>9.5273851243985993E-5</v>
       </c>
       <c r="BB3" s="10">
         <f>BNVFE!Q9</f>
-        <v>8.8870744349267236E-5</v>
+        <v>9.6237109925949779E-5</v>
       </c>
       <c r="BC3" s="10">
         <f>BNVFE!R9</f>
-        <v>8.9949247005972088E-5</v>
+        <v>9.7405008085110293E-5</v>
       </c>
       <c r="BD3" s="10">
         <f>BNVFE!S9</f>
-        <v>9.0831024253729272E-5</v>
+        <v>9.83598745548802E-5</v>
       </c>
       <c r="BE3" s="10">
         <f>BNVFE!T9</f>
-        <v>9.1579110752047641E-5</v>
+        <v>9.9169968845188442E-5</v>
       </c>
       <c r="BF3" s="10">
         <f>BNVFE!U9</f>
-        <v>9.2403640539502613E-5</v>
+        <v>1.0006284269668531E-4</v>
       </c>
       <c r="BG3" s="10">
         <f>BNVFE!V9</f>
-        <v>9.319851514165077E-5</v>
+        <v>1.009236032880858E-4</v>
       </c>
       <c r="BH3" s="10">
         <f>BNVFE!W9</f>
-        <v>9.3891059740218658E-5</v>
+        <v>1.0167355189208385E-4</v>
       </c>
       <c r="BI3" s="10">
         <f>BNVFE!X9</f>
-        <v>9.5047122599296139E-5</v>
+        <v>1.0292543910496804E-4</v>
       </c>
       <c r="BJ3" s="10">
         <f>BNVFE!Y9</f>
-        <v>9.6059950070461278E-5</v>
+        <v>1.0402221835884117E-4</v>
       </c>
       <c r="BK3" s="10">
         <f>BNVFE!Z9</f>
-        <v>9.7048480369583043E-5</v>
+        <v>1.0509268648373766E-4</v>
       </c>
       <c r="BL3" s="10">
         <f>BNVFE!AA9</f>
-        <v>9.7649579603605602E-5</v>
+        <v>1.0574360995112404E-4</v>
       </c>
       <c r="BM3" s="10">
         <f>BNVFE!AB9</f>
-        <v>9.8224460923876486E-5</v>
+        <v>1.0636614234036401E-4</v>
       </c>
       <c r="BN3" s="10">
         <f>BNVFE!AC9</f>
-        <v>9.8795624738493866E-5</v>
+        <v>1.069846490853625E-4</v>
       </c>
       <c r="BO3" s="10">
         <f>BNVFE!AD9</f>
-        <v>9.9479244599585216E-5</v>
+        <v>1.077249331934921E-4</v>
       </c>
       <c r="BP3" s="10">
         <f>BNVFE!AE9</f>
-        <v>9.9975448040260604E-5</v>
+        <v>1.0826226620916075E-4</v>
       </c>
       <c r="BQ3" s="10">
         <f>BNVFE!AF9</f>
-        <v>1.0044050579002983E-4</v>
+        <v>1.08765871913312E-4</v>
       </c>
       <c r="BR3" s="10">
         <f>BNVFE!AG9</f>
-        <v>1.0101640935179317E-4</v>
+        <v>1.0938951127614153E-4</v>
       </c>
       <c r="BS3" s="10"/>
       <c r="BT3" s="4"/>
@@ -20366,223 +20365,223 @@
       <c r="O6" s="9"/>
       <c r="P6" s="4">
         <f t="shared" ref="P6:AM6" si="5">TREND($AQ6:$BR6,$AQ$1:$BR$1,P$1)</f>
-        <v>4.3905417607014065E-4</v>
+        <v>3.4763021843211422E-4</v>
       </c>
       <c r="Q6" s="4">
         <f>TREND($AQ6:$BR6,$AQ$1:$BR$1,Q$1)</f>
-        <v>4.3905417607014065E-4</v>
+        <v>3.5180176772518779E-4</v>
       </c>
       <c r="R6" s="4">
         <f t="shared" si="5"/>
-        <v>4.3905417607014065E-4</v>
+        <v>3.5597331701826135E-4</v>
       </c>
       <c r="S6" s="4">
         <f t="shared" si="5"/>
-        <v>4.3905417607014065E-4</v>
+        <v>3.6014486631133318E-4</v>
       </c>
       <c r="T6" s="4">
         <f t="shared" si="5"/>
-        <v>4.3905417607014065E-4</v>
+        <v>3.6431641560440674E-4</v>
       </c>
       <c r="U6" s="4">
         <f t="shared" si="5"/>
-        <v>4.3905417607014065E-4</v>
+        <v>3.684879648974803E-4</v>
       </c>
       <c r="V6" s="4">
         <f t="shared" si="5"/>
-        <v>4.3905417607014065E-4</v>
+        <v>3.7265951419055386E-4</v>
       </c>
       <c r="W6" s="4">
         <f t="shared" si="5"/>
-        <v>4.3905417607014065E-4</v>
+        <v>3.7683106348362569E-4</v>
       </c>
       <c r="X6" s="4">
         <f t="shared" si="5"/>
-        <v>4.3905417607014065E-4</v>
+        <v>3.8100261277669925E-4</v>
       </c>
       <c r="Y6" s="4">
         <f t="shared" si="5"/>
-        <v>4.3905417607014065E-4</v>
+        <v>3.8517416206977281E-4</v>
       </c>
       <c r="Z6" s="4">
         <f t="shared" si="5"/>
-        <v>4.3905417607014065E-4</v>
+        <v>3.8934571136284464E-4</v>
       </c>
       <c r="AA6" s="4">
         <f t="shared" si="5"/>
-        <v>4.3905417607014065E-4</v>
+        <v>3.935172606559182E-4</v>
       </c>
       <c r="AB6" s="4">
         <f t="shared" si="5"/>
-        <v>4.3905417607014065E-4</v>
+        <v>3.9768880994899176E-4</v>
       </c>
       <c r="AC6" s="4">
         <f t="shared" si="5"/>
-        <v>4.3905417607014065E-4</v>
+        <v>4.0186035924206359E-4</v>
       </c>
       <c r="AD6" s="4">
         <f t="shared" si="5"/>
-        <v>4.3905417607014065E-4</v>
+        <v>4.0603190853513715E-4</v>
       </c>
       <c r="AE6" s="4">
         <f t="shared" si="5"/>
-        <v>4.3905417607014065E-4</v>
+        <v>4.1020345782821072E-4</v>
       </c>
       <c r="AF6" s="4">
         <f t="shared" si="5"/>
-        <v>4.3905417607014065E-4</v>
+        <v>4.1437500712128254E-4</v>
       </c>
       <c r="AG6" s="4">
         <f t="shared" si="5"/>
-        <v>4.3905417607014065E-4</v>
+        <v>4.1854655641435611E-4</v>
       </c>
       <c r="AH6" s="4">
         <f t="shared" si="5"/>
-        <v>4.3905417607014065E-4</v>
+        <v>4.2271810570742967E-4</v>
       </c>
       <c r="AI6" s="4">
         <f t="shared" si="5"/>
-        <v>4.3905417607014065E-4</v>
+        <v>4.2688965500050149E-4</v>
       </c>
       <c r="AJ6" s="4">
         <f t="shared" si="5"/>
-        <v>4.3905417607014065E-4</v>
+        <v>4.3106120429357506E-4</v>
       </c>
       <c r="AK6" s="4">
         <f t="shared" si="5"/>
-        <v>4.3905417607014065E-4</v>
+        <v>4.3523275358664862E-4</v>
       </c>
       <c r="AL6" s="4">
         <f t="shared" si="5"/>
-        <v>4.3905417607014065E-4</v>
+        <v>4.3940430287972045E-4</v>
       </c>
       <c r="AM6" s="4">
         <f t="shared" si="5"/>
-        <v>4.3905417607014065E-4</v>
+        <v>4.4357585217279401E-4</v>
       </c>
       <c r="AN6" s="4">
         <f>TREND($AQ6:$BR6,$AQ$1:$BR$1,AN$1)</f>
-        <v>4.3905417607014065E-4</v>
+        <v>4.4774740146586757E-4</v>
       </c>
       <c r="AO6" s="4">
         <f t="shared" ref="AO6:AP6" si="6">TREND($AQ6:$BR6,$AQ$1:$BR$1,AO$1)</f>
-        <v>4.3905417607014065E-4</v>
+        <v>4.5191895075894113E-4</v>
       </c>
       <c r="AP6" s="4">
         <f t="shared" si="6"/>
-        <v>4.3905417607014065E-4</v>
+        <v>4.5609050005201296E-4</v>
       </c>
       <c r="AQ6" s="28">
         <f>BNVFE!F12</f>
-        <v>4.390541760701407E-4</v>
+        <v>4.6292253798248397E-4</v>
       </c>
       <c r="AR6" s="10">
         <f>BNVFE!G12</f>
-        <v>4.390541760701407E-4</v>
+        <v>4.6724180152163598E-4</v>
       </c>
       <c r="AS6" s="10">
         <f>BNVFE!H12</f>
-        <v>4.390541760701407E-4</v>
+        <v>4.6965127581020212E-4</v>
       </c>
       <c r="AT6" s="10">
         <f>BNVFE!I12</f>
-        <v>4.390541760701407E-4</v>
+        <v>4.7322813533235715E-4</v>
       </c>
       <c r="AU6" s="10">
         <f>BNVFE!J12</f>
-        <v>4.390541760701407E-4</v>
+        <v>4.7696949985651614E-4</v>
       </c>
       <c r="AV6" s="10">
         <f>BNVFE!K12</f>
-        <v>4.390541760701407E-4</v>
+        <v>4.8083975908889043E-4</v>
       </c>
       <c r="AW6" s="10">
         <f>BNVFE!L12</f>
-        <v>4.390541760701407E-4</v>
+        <v>4.847773340732441E-4</v>
       </c>
       <c r="AX6" s="10">
         <f>BNVFE!M12</f>
-        <v>4.390541760701407E-4</v>
+        <v>4.8876510978465549E-4</v>
       </c>
       <c r="AY6" s="10">
         <f>BNVFE!N12</f>
-        <v>4.390541760701407E-4</v>
+        <v>4.9280339238632709E-4</v>
       </c>
       <c r="AZ6" s="10">
         <f>BNVFE!O12</f>
-        <v>4.390541760701407E-4</v>
+        <v>4.9685871974595585E-4</v>
       </c>
       <c r="BA6" s="10">
         <f>BNVFE!P12</f>
-        <v>4.390541760701407E-4</v>
+        <v>5.0093827917019513E-4</v>
       </c>
       <c r="BB6" s="10">
         <f>BNVFE!Q12</f>
-        <v>4.390541760701407E-4</v>
+        <v>5.0505403110021464E-4</v>
       </c>
       <c r="BC6" s="10">
         <f>BNVFE!R12</f>
-        <v>4.390541760701407E-4</v>
+        <v>5.091914152171586E-4</v>
       </c>
       <c r="BD6" s="10">
         <f>BNVFE!S12</f>
-        <v>4.390541760701407E-4</v>
+        <v>5.1335993261843963E-4</v>
       </c>
       <c r="BE6" s="10">
         <f>BNVFE!T12</f>
-        <v>4.390541760701407E-4</v>
+        <v>5.1755601976514434E-4</v>
       </c>
       <c r="BF6" s="10">
         <f>BNVFE!U12</f>
-        <v>4.390541760701407E-4</v>
+        <v>5.2177673046383325E-4</v>
       </c>
       <c r="BG6" s="10">
         <f>BNVFE!V12</f>
-        <v>4.390541760701407E-4</v>
+        <v>5.2602994967173547E-4</v>
       </c>
       <c r="BH6" s="10">
         <f>BNVFE!W12</f>
-        <v>4.390541760701407E-4</v>
+        <v>5.3031732866251667E-4</v>
       </c>
       <c r="BI6" s="10">
         <f>BNVFE!X12</f>
-        <v>4.390541760701407E-4</v>
+        <v>5.346381346521186E-4</v>
       </c>
       <c r="BJ6" s="10">
         <f>BNVFE!Y12</f>
-        <v>4.390541760701407E-4</v>
+        <v>5.3898042225657822E-4</v>
       </c>
       <c r="BK6" s="10">
         <f>BNVFE!Z12</f>
-        <v>4.390541760701407E-4</v>
+        <v>5.4335778311445497E-4</v>
       </c>
       <c r="BL6" s="10">
         <f>BNVFE!AA12</f>
-        <v>4.390541760701407E-4</v>
+        <v>5.4777558261039474E-4</v>
       </c>
       <c r="BM6" s="10">
         <f>BNVFE!AB12</f>
-        <v>4.390541760701407E-4</v>
+        <v>5.5222750675573099E-4</v>
       </c>
       <c r="BN6" s="10">
         <f>BNVFE!AC12</f>
-        <v>4.390541760701407E-4</v>
+        <v>5.5671423312476443E-4</v>
       </c>
       <c r="BO6" s="10">
         <f>BNVFE!AD12</f>
-        <v>4.390541760701407E-4</v>
+        <v>5.6121623753950501E-4</v>
       </c>
       <c r="BP6" s="10">
         <f>BNVFE!AE12</f>
-        <v>4.390541760701407E-4</v>
+        <v>5.6574653946465893E-4</v>
       </c>
       <c r="BQ6" s="10">
         <f>BNVFE!AF12</f>
-        <v>4.390541760701407E-4</v>
+        <v>5.7031870042437182E-4</v>
       </c>
       <c r="BR6" s="10">
         <f>BNVFE!AG12</f>
-        <v>4.390541760701407E-4</v>
+        <v>5.7492662224994018E-4</v>
       </c>
       <c r="BS6" s="10"/>
       <c r="BT6" s="4"/>
@@ -20609,223 +20608,223 @@
       <c r="O7" s="9"/>
       <c r="P7" s="28">
         <f t="shared" ref="P7:AP7" si="7">Q7</f>
-        <v>1.5492656753114542E-4</v>
+        <v>1.8429395373095432E-4</v>
       </c>
       <c r="Q7" s="28">
         <f t="shared" si="7"/>
-        <v>1.5492656753114542E-4</v>
+        <v>1.8429395373095432E-4</v>
       </c>
       <c r="R7" s="28">
         <f t="shared" si="7"/>
-        <v>1.5492656753114542E-4</v>
+        <v>1.8429395373095432E-4</v>
       </c>
       <c r="S7" s="28">
         <f t="shared" si="7"/>
-        <v>1.5492656753114542E-4</v>
+        <v>1.8429395373095432E-4</v>
       </c>
       <c r="T7" s="28">
         <f t="shared" si="7"/>
-        <v>1.5492656753114542E-4</v>
+        <v>1.8429395373095432E-4</v>
       </c>
       <c r="U7" s="28">
         <f t="shared" si="7"/>
-        <v>1.5492656753114542E-4</v>
+        <v>1.8429395373095432E-4</v>
       </c>
       <c r="V7" s="28">
         <f t="shared" si="7"/>
-        <v>1.5492656753114542E-4</v>
+        <v>1.8429395373095432E-4</v>
       </c>
       <c r="W7" s="28">
         <f t="shared" si="7"/>
-        <v>1.5492656753114542E-4</v>
+        <v>1.8429395373095432E-4</v>
       </c>
       <c r="X7" s="28">
         <f t="shared" si="7"/>
-        <v>1.5492656753114542E-4</v>
+        <v>1.8429395373095432E-4</v>
       </c>
       <c r="Y7" s="28">
         <f t="shared" si="7"/>
-        <v>1.5492656753114542E-4</v>
+        <v>1.8429395373095432E-4</v>
       </c>
       <c r="Z7" s="28">
         <f t="shared" si="7"/>
-        <v>1.5492656753114542E-4</v>
+        <v>1.8429395373095432E-4</v>
       </c>
       <c r="AA7" s="28">
         <f t="shared" si="7"/>
-        <v>1.5492656753114542E-4</v>
+        <v>1.8429395373095432E-4</v>
       </c>
       <c r="AB7" s="28">
         <f t="shared" si="7"/>
-        <v>1.5492656753114542E-4</v>
+        <v>1.8429395373095432E-4</v>
       </c>
       <c r="AC7" s="28">
         <f t="shared" si="7"/>
-        <v>1.5492656753114542E-4</v>
+        <v>1.8429395373095432E-4</v>
       </c>
       <c r="AD7" s="28">
         <f t="shared" si="7"/>
-        <v>1.5492656753114542E-4</v>
+        <v>1.8429395373095432E-4</v>
       </c>
       <c r="AE7" s="28">
         <f t="shared" si="7"/>
-        <v>1.5492656753114542E-4</v>
+        <v>1.8429395373095432E-4</v>
       </c>
       <c r="AF7" s="28">
         <f t="shared" si="7"/>
-        <v>1.5492656753114542E-4</v>
+        <v>1.8429395373095432E-4</v>
       </c>
       <c r="AG7" s="28">
         <f t="shared" si="7"/>
-        <v>1.5492656753114542E-4</v>
+        <v>1.8429395373095432E-4</v>
       </c>
       <c r="AH7" s="28">
         <f t="shared" si="7"/>
-        <v>1.5492656753114542E-4</v>
+        <v>1.8429395373095432E-4</v>
       </c>
       <c r="AI7" s="28">
         <f t="shared" si="7"/>
-        <v>1.5492656753114542E-4</v>
+        <v>1.8429395373095432E-4</v>
       </c>
       <c r="AJ7" s="28">
         <f t="shared" si="7"/>
-        <v>1.5492656753114542E-4</v>
+        <v>1.8429395373095432E-4</v>
       </c>
       <c r="AK7" s="28">
         <f t="shared" si="7"/>
-        <v>1.5492656753114542E-4</v>
+        <v>1.8429395373095432E-4</v>
       </c>
       <c r="AL7" s="28">
         <f t="shared" si="7"/>
-        <v>1.5492656753114542E-4</v>
+        <v>1.8429395373095432E-4</v>
       </c>
       <c r="AM7" s="28">
         <f t="shared" si="7"/>
-        <v>1.5492656753114542E-4</v>
+        <v>1.8429395373095432E-4</v>
       </c>
       <c r="AN7" s="28">
         <f t="shared" si="7"/>
-        <v>1.5492656753114542E-4</v>
+        <v>1.8429395373095432E-4</v>
       </c>
       <c r="AO7" s="28">
         <f t="shared" si="7"/>
-        <v>1.5492656753114542E-4</v>
+        <v>1.8429395373095432E-4</v>
       </c>
       <c r="AP7" s="28">
         <f t="shared" si="7"/>
-        <v>1.5492656753114542E-4</v>
+        <v>1.8429395373095432E-4</v>
       </c>
       <c r="AQ7" s="28">
         <f>AR7</f>
-        <v>1.5492656753114542E-4</v>
+        <v>1.8429395373095432E-4</v>
       </c>
       <c r="AR7" s="10">
         <f>BNVFE!G13</f>
-        <v>1.5492656753114542E-4</v>
+        <v>1.8429395373095432E-4</v>
       </c>
       <c r="AS7" s="10">
         <f>BNVFE!H13</f>
-        <v>1.5492656753114542E-4</v>
+        <v>1.8429395373095432E-4</v>
       </c>
       <c r="AT7" s="10">
         <f>BNVFE!I13</f>
-        <v>1.5492656753114542E-4</v>
+        <v>1.8429395373095432E-4</v>
       </c>
       <c r="AU7" s="10">
         <f>BNVFE!J13</f>
-        <v>1.5492656753114542E-4</v>
+        <v>1.8429395373095432E-4</v>
       </c>
       <c r="AV7" s="10">
         <f>BNVFE!K13</f>
-        <v>1.5492656753114542E-4</v>
+        <v>1.8429395373095432E-4</v>
       </c>
       <c r="AW7" s="10">
         <f>BNVFE!L13</f>
-        <v>1.5492656753114542E-4</v>
+        <v>1.8429395373095432E-4</v>
       </c>
       <c r="AX7" s="10">
         <f>BNVFE!M13</f>
-        <v>1.5492656753114542E-4</v>
+        <v>1.8429395373095432E-4</v>
       </c>
       <c r="AY7" s="10">
         <f>BNVFE!N13</f>
-        <v>1.5492656753114542E-4</v>
+        <v>1.8429395373095432E-4</v>
       </c>
       <c r="AZ7" s="10">
         <f>BNVFE!O13</f>
-        <v>1.5492656753114542E-4</v>
+        <v>1.8429395373095432E-4</v>
       </c>
       <c r="BA7" s="10">
         <f>BNVFE!P13</f>
-        <v>1.5492656753114542E-4</v>
+        <v>1.8429395373095432E-4</v>
       </c>
       <c r="BB7" s="10">
         <f>BNVFE!Q13</f>
-        <v>1.5492656753114542E-4</v>
+        <v>1.8429395373095432E-4</v>
       </c>
       <c r="BC7" s="10">
         <f>BNVFE!R13</f>
-        <v>1.5492656753114542E-4</v>
+        <v>1.8429395373095432E-4</v>
       </c>
       <c r="BD7" s="10">
         <f>BNVFE!S13</f>
-        <v>1.5492656753114542E-4</v>
+        <v>1.8429395373095432E-4</v>
       </c>
       <c r="BE7" s="10">
         <f>BNVFE!T13</f>
-        <v>1.5492656753114542E-4</v>
+        <v>1.8429395373095432E-4</v>
       </c>
       <c r="BF7" s="10">
         <f>BNVFE!U13</f>
-        <v>1.5492656753114542E-4</v>
+        <v>1.8429395373095432E-4</v>
       </c>
       <c r="BG7" s="10">
         <f>BNVFE!V13</f>
-        <v>1.5492656753114542E-4</v>
+        <v>1.8429395373095432E-4</v>
       </c>
       <c r="BH7" s="10">
         <f>BNVFE!W13</f>
-        <v>1.5492656753114542E-4</v>
+        <v>1.8429395373095432E-4</v>
       </c>
       <c r="BI7" s="10">
         <f>BNVFE!X13</f>
-        <v>1.5492656753114542E-4</v>
+        <v>1.8429395373095432E-4</v>
       </c>
       <c r="BJ7" s="10">
         <f>BNVFE!Y13</f>
-        <v>1.5492656753114542E-4</v>
+        <v>1.8429395373095432E-4</v>
       </c>
       <c r="BK7" s="10">
         <f>BNVFE!Z13</f>
-        <v>1.5492656753114542E-4</v>
+        <v>1.8429395373095432E-4</v>
       </c>
       <c r="BL7" s="10">
         <f>BNVFE!AA13</f>
-        <v>1.5492656753114542E-4</v>
+        <v>1.8429395373095432E-4</v>
       </c>
       <c r="BM7" s="10">
         <f>BNVFE!AB13</f>
-        <v>1.5492656753114542E-4</v>
+        <v>1.8429395373095432E-4</v>
       </c>
       <c r="BN7" s="10">
         <f>BNVFE!AC13</f>
-        <v>1.5492656753114542E-4</v>
+        <v>1.8429395373095432E-4</v>
       </c>
       <c r="BO7" s="10">
         <f>BNVFE!AD13</f>
-        <v>1.5492656753114542E-4</v>
+        <v>1.8429395373095432E-4</v>
       </c>
       <c r="BP7" s="10">
         <f>BNVFE!AE13</f>
-        <v>1.5492656753114542E-4</v>
+        <v>1.8429395373095432E-4</v>
       </c>
       <c r="BQ7" s="10">
         <f>BNVFE!AF13</f>
-        <v>1.5492656753114542E-4</v>
+        <v>1.8429395373095432E-4</v>
       </c>
       <c r="BR7" s="10">
         <f>BNVFE!AG13</f>
-        <v>1.5492656753114542E-4</v>
+        <v>1.8429395373095432E-4</v>
       </c>
       <c r="BS7" s="10"/>
       <c r="BT7" s="4"/>
@@ -20842,263 +20841,263 @@
       <c r="E8" s="9"/>
       <c r="F8" s="4">
         <f>SYFAFE!$E$5</f>
-        <v>7.1745362435245036E-5</v>
+        <v>5.0586266198922429E-5</v>
       </c>
       <c r="G8" s="4">
         <f>F8</f>
-        <v>7.1745362435245036E-5</v>
+        <v>5.0586266198922429E-5</v>
       </c>
       <c r="H8" s="4">
         <f t="shared" ref="H8:BR8" si="8">G8</f>
-        <v>7.1745362435245036E-5</v>
+        <v>5.0586266198922429E-5</v>
       </c>
       <c r="I8" s="4">
         <f t="shared" si="8"/>
-        <v>7.1745362435245036E-5</v>
+        <v>5.0586266198922429E-5</v>
       </c>
       <c r="J8" s="4">
         <f t="shared" si="8"/>
-        <v>7.1745362435245036E-5</v>
+        <v>5.0586266198922429E-5</v>
       </c>
       <c r="K8" s="4">
         <f t="shared" si="8"/>
-        <v>7.1745362435245036E-5</v>
+        <v>5.0586266198922429E-5</v>
       </c>
       <c r="L8" s="4">
         <f t="shared" si="8"/>
-        <v>7.1745362435245036E-5</v>
+        <v>5.0586266198922429E-5</v>
       </c>
       <c r="M8" s="4">
         <f t="shared" si="8"/>
-        <v>7.1745362435245036E-5</v>
+        <v>5.0586266198922429E-5</v>
       </c>
       <c r="N8" s="4">
         <f t="shared" si="8"/>
-        <v>7.1745362435245036E-5</v>
+        <v>5.0586266198922429E-5</v>
       </c>
       <c r="O8" s="4">
         <f t="shared" si="8"/>
-        <v>7.1745362435245036E-5</v>
+        <v>5.0586266198922429E-5</v>
       </c>
       <c r="P8" s="4">
         <f t="shared" si="8"/>
-        <v>7.1745362435245036E-5</v>
+        <v>5.0586266198922429E-5</v>
       </c>
       <c r="Q8" s="4">
         <f t="shared" si="8"/>
-        <v>7.1745362435245036E-5</v>
+        <v>5.0586266198922429E-5</v>
       </c>
       <c r="R8" s="4">
         <f t="shared" si="8"/>
-        <v>7.1745362435245036E-5</v>
+        <v>5.0586266198922429E-5</v>
       </c>
       <c r="S8" s="4">
         <f t="shared" si="8"/>
-        <v>7.1745362435245036E-5</v>
+        <v>5.0586266198922429E-5</v>
       </c>
       <c r="T8" s="4">
         <f t="shared" si="8"/>
-        <v>7.1745362435245036E-5</v>
+        <v>5.0586266198922429E-5</v>
       </c>
       <c r="U8" s="4">
         <f t="shared" si="8"/>
-        <v>7.1745362435245036E-5</v>
+        <v>5.0586266198922429E-5</v>
       </c>
       <c r="V8" s="4">
         <f t="shared" si="8"/>
-        <v>7.1745362435245036E-5</v>
+        <v>5.0586266198922429E-5</v>
       </c>
       <c r="W8" s="4">
         <f t="shared" si="8"/>
-        <v>7.1745362435245036E-5</v>
+        <v>5.0586266198922429E-5</v>
       </c>
       <c r="X8" s="4">
         <f t="shared" si="8"/>
-        <v>7.1745362435245036E-5</v>
+        <v>5.0586266198922429E-5</v>
       </c>
       <c r="Y8" s="4">
         <f t="shared" si="8"/>
-        <v>7.1745362435245036E-5</v>
+        <v>5.0586266198922429E-5</v>
       </c>
       <c r="Z8" s="4">
         <f t="shared" si="8"/>
-        <v>7.1745362435245036E-5</v>
+        <v>5.0586266198922429E-5</v>
       </c>
       <c r="AA8" s="4">
         <f t="shared" si="8"/>
-        <v>7.1745362435245036E-5</v>
+        <v>5.0586266198922429E-5</v>
       </c>
       <c r="AB8" s="4">
         <f t="shared" si="8"/>
-        <v>7.1745362435245036E-5</v>
+        <v>5.0586266198922429E-5</v>
       </c>
       <c r="AC8" s="4">
         <f t="shared" si="8"/>
-        <v>7.1745362435245036E-5</v>
+        <v>5.0586266198922429E-5</v>
       </c>
       <c r="AD8" s="4">
         <f t="shared" si="8"/>
-        <v>7.1745362435245036E-5</v>
+        <v>5.0586266198922429E-5</v>
       </c>
       <c r="AE8" s="4">
         <f t="shared" si="8"/>
-        <v>7.1745362435245036E-5</v>
+        <v>5.0586266198922429E-5</v>
       </c>
       <c r="AF8" s="4">
         <f t="shared" si="8"/>
-        <v>7.1745362435245036E-5</v>
+        <v>5.0586266198922429E-5</v>
       </c>
       <c r="AG8" s="4">
         <f t="shared" si="8"/>
-        <v>7.1745362435245036E-5</v>
+        <v>5.0586266198922429E-5</v>
       </c>
       <c r="AH8" s="4">
         <f t="shared" si="8"/>
-        <v>7.1745362435245036E-5</v>
+        <v>5.0586266198922429E-5</v>
       </c>
       <c r="AI8" s="4">
         <f t="shared" si="8"/>
-        <v>7.1745362435245036E-5</v>
+        <v>5.0586266198922429E-5</v>
       </c>
       <c r="AJ8" s="4">
         <f t="shared" si="8"/>
-        <v>7.1745362435245036E-5</v>
+        <v>5.0586266198922429E-5</v>
       </c>
       <c r="AK8" s="4">
         <f t="shared" si="8"/>
-        <v>7.1745362435245036E-5</v>
+        <v>5.0586266198922429E-5</v>
       </c>
       <c r="AL8" s="4">
         <f t="shared" si="8"/>
-        <v>7.1745362435245036E-5</v>
+        <v>5.0586266198922429E-5</v>
       </c>
       <c r="AM8" s="4">
         <f t="shared" si="8"/>
-        <v>7.1745362435245036E-5</v>
+        <v>5.0586266198922429E-5</v>
       </c>
       <c r="AN8" s="4">
         <f t="shared" si="8"/>
-        <v>7.1745362435245036E-5</v>
+        <v>5.0586266198922429E-5</v>
       </c>
       <c r="AO8" s="4">
         <f t="shared" si="8"/>
-        <v>7.1745362435245036E-5</v>
+        <v>5.0586266198922429E-5</v>
       </c>
       <c r="AP8" s="4">
         <f>AO8</f>
-        <v>7.1745362435245036E-5</v>
+        <v>5.0586266198922429E-5</v>
       </c>
       <c r="AQ8" s="27">
         <f>AP8</f>
-        <v>7.1745362435245036E-5</v>
+        <v>5.0586266198922429E-5</v>
       </c>
       <c r="AR8" s="4">
         <f t="shared" si="8"/>
-        <v>7.1745362435245036E-5</v>
+        <v>5.0586266198922429E-5</v>
       </c>
       <c r="AS8" s="4">
         <f t="shared" si="8"/>
-        <v>7.1745362435245036E-5</v>
+        <v>5.0586266198922429E-5</v>
       </c>
       <c r="AT8" s="4">
         <f t="shared" si="8"/>
-        <v>7.1745362435245036E-5</v>
+        <v>5.0586266198922429E-5</v>
       </c>
       <c r="AU8" s="4">
         <f t="shared" si="8"/>
-        <v>7.1745362435245036E-5</v>
+        <v>5.0586266198922429E-5</v>
       </c>
       <c r="AV8" s="4">
         <f t="shared" si="8"/>
-        <v>7.1745362435245036E-5</v>
+        <v>5.0586266198922429E-5</v>
       </c>
       <c r="AW8" s="4">
         <f t="shared" si="8"/>
-        <v>7.1745362435245036E-5</v>
+        <v>5.0586266198922429E-5</v>
       </c>
       <c r="AX8" s="4">
         <f t="shared" si="8"/>
-        <v>7.1745362435245036E-5</v>
+        <v>5.0586266198922429E-5</v>
       </c>
       <c r="AY8" s="4">
         <f t="shared" si="8"/>
-        <v>7.1745362435245036E-5</v>
+        <v>5.0586266198922429E-5</v>
       </c>
       <c r="AZ8" s="4">
         <f t="shared" si="8"/>
-        <v>7.1745362435245036E-5</v>
+        <v>5.0586266198922429E-5</v>
       </c>
       <c r="BA8" s="4">
         <f t="shared" si="8"/>
-        <v>7.1745362435245036E-5</v>
+        <v>5.0586266198922429E-5</v>
       </c>
       <c r="BB8" s="4">
         <f t="shared" si="8"/>
-        <v>7.1745362435245036E-5</v>
+        <v>5.0586266198922429E-5</v>
       </c>
       <c r="BC8" s="4">
         <f t="shared" si="8"/>
-        <v>7.1745362435245036E-5</v>
+        <v>5.0586266198922429E-5</v>
       </c>
       <c r="BD8" s="4">
         <f t="shared" si="8"/>
-        <v>7.1745362435245036E-5</v>
+        <v>5.0586266198922429E-5</v>
       </c>
       <c r="BE8" s="4">
         <f t="shared" si="8"/>
-        <v>7.1745362435245036E-5</v>
+        <v>5.0586266198922429E-5</v>
       </c>
       <c r="BF8" s="4">
         <f t="shared" si="8"/>
-        <v>7.1745362435245036E-5</v>
+        <v>5.0586266198922429E-5</v>
       </c>
       <c r="BG8" s="4">
         <f t="shared" si="8"/>
-        <v>7.1745362435245036E-5</v>
+        <v>5.0586266198922429E-5</v>
       </c>
       <c r="BH8" s="4">
         <f t="shared" si="8"/>
-        <v>7.1745362435245036E-5</v>
+        <v>5.0586266198922429E-5</v>
       </c>
       <c r="BI8" s="4">
         <f t="shared" si="8"/>
-        <v>7.1745362435245036E-5</v>
+        <v>5.0586266198922429E-5</v>
       </c>
       <c r="BJ8" s="4">
         <f t="shared" si="8"/>
-        <v>7.1745362435245036E-5</v>
+        <v>5.0586266198922429E-5</v>
       </c>
       <c r="BK8" s="4">
         <f t="shared" si="8"/>
-        <v>7.1745362435245036E-5</v>
+        <v>5.0586266198922429E-5</v>
       </c>
       <c r="BL8" s="4">
         <f t="shared" si="8"/>
-        <v>7.1745362435245036E-5</v>
+        <v>5.0586266198922429E-5</v>
       </c>
       <c r="BM8" s="4">
         <f t="shared" si="8"/>
-        <v>7.1745362435245036E-5</v>
+        <v>5.0586266198922429E-5</v>
       </c>
       <c r="BN8" s="4">
         <f t="shared" si="8"/>
-        <v>7.1745362435245036E-5</v>
+        <v>5.0586266198922429E-5</v>
       </c>
       <c r="BO8" s="4">
         <f t="shared" si="8"/>
-        <v>7.1745362435245036E-5</v>
+        <v>5.0586266198922429E-5</v>
       </c>
       <c r="BP8" s="4">
         <f t="shared" si="8"/>
-        <v>7.1745362435245036E-5</v>
+        <v>5.0586266198922429E-5</v>
       </c>
       <c r="BQ8" s="4">
         <f t="shared" si="8"/>
-        <v>7.1745362435245036E-5</v>
+        <v>5.0586266198922429E-5</v>
       </c>
       <c r="BR8" s="4">
         <f t="shared" si="8"/>
-        <v>7.1745362435245036E-5</v>
+        <v>5.0586266198922429E-5</v>
       </c>
       <c r="BS8" s="10"/>
       <c r="BT8" s="4"/>
@@ -21115,263 +21114,263 @@
       <c r="E9" s="9"/>
       <c r="F9" s="19">
         <f>SYFAFE!$B$5</f>
-        <v>7.5686214263268839E-4</v>
+        <v>6.7428486606874269E-4</v>
       </c>
       <c r="G9" s="4">
         <f>F9</f>
-        <v>7.5686214263268839E-4</v>
+        <v>6.7428486606874269E-4</v>
       </c>
       <c r="H9" s="4">
         <f t="shared" ref="H9:BR9" si="9">G9</f>
-        <v>7.5686214263268839E-4</v>
+        <v>6.7428486606874269E-4</v>
       </c>
       <c r="I9" s="4">
         <f t="shared" si="9"/>
-        <v>7.5686214263268839E-4</v>
+        <v>6.7428486606874269E-4</v>
       </c>
       <c r="J9" s="4">
         <f t="shared" si="9"/>
-        <v>7.5686214263268839E-4</v>
+        <v>6.7428486606874269E-4</v>
       </c>
       <c r="K9" s="4">
         <f t="shared" si="9"/>
-        <v>7.5686214263268839E-4</v>
+        <v>6.7428486606874269E-4</v>
       </c>
       <c r="L9" s="4">
         <f t="shared" si="9"/>
-        <v>7.5686214263268839E-4</v>
+        <v>6.7428486606874269E-4</v>
       </c>
       <c r="M9" s="4">
         <f t="shared" si="9"/>
-        <v>7.5686214263268839E-4</v>
+        <v>6.7428486606874269E-4</v>
       </c>
       <c r="N9" s="4">
         <f t="shared" si="9"/>
-        <v>7.5686214263268839E-4</v>
+        <v>6.7428486606874269E-4</v>
       </c>
       <c r="O9" s="4">
         <f t="shared" si="9"/>
-        <v>7.5686214263268839E-4</v>
+        <v>6.7428486606874269E-4</v>
       </c>
       <c r="P9" s="4">
         <f t="shared" si="9"/>
-        <v>7.5686214263268839E-4</v>
+        <v>6.7428486606874269E-4</v>
       </c>
       <c r="Q9" s="4">
         <f t="shared" si="9"/>
-        <v>7.5686214263268839E-4</v>
+        <v>6.7428486606874269E-4</v>
       </c>
       <c r="R9" s="4">
         <f t="shared" si="9"/>
-        <v>7.5686214263268839E-4</v>
+        <v>6.7428486606874269E-4</v>
       </c>
       <c r="S9" s="4">
         <f t="shared" si="9"/>
-        <v>7.5686214263268839E-4</v>
+        <v>6.7428486606874269E-4</v>
       </c>
       <c r="T9" s="4">
         <f t="shared" si="9"/>
-        <v>7.5686214263268839E-4</v>
+        <v>6.7428486606874269E-4</v>
       </c>
       <c r="U9" s="4">
         <f t="shared" si="9"/>
-        <v>7.5686214263268839E-4</v>
+        <v>6.7428486606874269E-4</v>
       </c>
       <c r="V9" s="4">
         <f t="shared" si="9"/>
-        <v>7.5686214263268839E-4</v>
+        <v>6.7428486606874269E-4</v>
       </c>
       <c r="W9" s="4">
         <f t="shared" si="9"/>
-        <v>7.5686214263268839E-4</v>
+        <v>6.7428486606874269E-4</v>
       </c>
       <c r="X9" s="4">
         <f t="shared" si="9"/>
-        <v>7.5686214263268839E-4</v>
+        <v>6.7428486606874269E-4</v>
       </c>
       <c r="Y9" s="4">
         <f t="shared" si="9"/>
-        <v>7.5686214263268839E-4</v>
+        <v>6.7428486606874269E-4</v>
       </c>
       <c r="Z9" s="4">
         <f t="shared" si="9"/>
-        <v>7.5686214263268839E-4</v>
+        <v>6.7428486606874269E-4</v>
       </c>
       <c r="AA9" s="4">
         <f t="shared" si="9"/>
-        <v>7.5686214263268839E-4</v>
+        <v>6.7428486606874269E-4</v>
       </c>
       <c r="AB9" s="4">
         <f t="shared" si="9"/>
-        <v>7.5686214263268839E-4</v>
+        <v>6.7428486606874269E-4</v>
       </c>
       <c r="AC9" s="4">
         <f t="shared" si="9"/>
-        <v>7.5686214263268839E-4</v>
+        <v>6.7428486606874269E-4</v>
       </c>
       <c r="AD9" s="4">
         <f t="shared" si="9"/>
-        <v>7.5686214263268839E-4</v>
+        <v>6.7428486606874269E-4</v>
       </c>
       <c r="AE9" s="4">
         <f t="shared" si="9"/>
-        <v>7.5686214263268839E-4</v>
+        <v>6.7428486606874269E-4</v>
       </c>
       <c r="AF9" s="4">
         <f t="shared" si="9"/>
-        <v>7.5686214263268839E-4</v>
+        <v>6.7428486606874269E-4</v>
       </c>
       <c r="AG9" s="4">
         <f t="shared" si="9"/>
-        <v>7.5686214263268839E-4</v>
+        <v>6.7428486606874269E-4</v>
       </c>
       <c r="AH9" s="4">
         <f t="shared" si="9"/>
-        <v>7.5686214263268839E-4</v>
+        <v>6.7428486606874269E-4</v>
       </c>
       <c r="AI9" s="4">
         <f t="shared" si="9"/>
-        <v>7.5686214263268839E-4</v>
+        <v>6.7428486606874269E-4</v>
       </c>
       <c r="AJ9" s="4">
         <f t="shared" si="9"/>
-        <v>7.5686214263268839E-4</v>
+        <v>6.7428486606874269E-4</v>
       </c>
       <c r="AK9" s="4">
         <f t="shared" si="9"/>
-        <v>7.5686214263268839E-4</v>
+        <v>6.7428486606874269E-4</v>
       </c>
       <c r="AL9" s="4">
         <f t="shared" si="9"/>
-        <v>7.5686214263268839E-4</v>
+        <v>6.7428486606874269E-4</v>
       </c>
       <c r="AM9" s="4">
         <f t="shared" si="9"/>
-        <v>7.5686214263268839E-4</v>
+        <v>6.7428486606874269E-4</v>
       </c>
       <c r="AN9" s="4">
         <f t="shared" si="9"/>
-        <v>7.5686214263268839E-4</v>
+        <v>6.7428486606874269E-4</v>
       </c>
       <c r="AO9" s="4">
         <f t="shared" si="9"/>
-        <v>7.5686214263268839E-4</v>
+        <v>6.7428486606874269E-4</v>
       </c>
       <c r="AP9" s="4">
         <f t="shared" si="9"/>
-        <v>7.5686214263268839E-4</v>
+        <v>6.7428486606874269E-4</v>
       </c>
       <c r="AQ9" s="27">
         <f t="shared" si="9"/>
-        <v>7.5686214263268839E-4</v>
+        <v>6.7428486606874269E-4</v>
       </c>
       <c r="AR9" s="4">
         <f t="shared" si="9"/>
-        <v>7.5686214263268839E-4</v>
+        <v>6.7428486606874269E-4</v>
       </c>
       <c r="AS9" s="4">
         <f t="shared" si="9"/>
-        <v>7.5686214263268839E-4</v>
+        <v>6.7428486606874269E-4</v>
       </c>
       <c r="AT9" s="4">
         <f t="shared" si="9"/>
-        <v>7.5686214263268839E-4</v>
+        <v>6.7428486606874269E-4</v>
       </c>
       <c r="AU9" s="4">
         <f t="shared" si="9"/>
-        <v>7.5686214263268839E-4</v>
+        <v>6.7428486606874269E-4</v>
       </c>
       <c r="AV9" s="4">
         <f t="shared" si="9"/>
-        <v>7.5686214263268839E-4</v>
+        <v>6.7428486606874269E-4</v>
       </c>
       <c r="AW9" s="4">
         <f t="shared" si="9"/>
-        <v>7.5686214263268839E-4</v>
+        <v>6.7428486606874269E-4</v>
       </c>
       <c r="AX9" s="4">
         <f t="shared" si="9"/>
-        <v>7.5686214263268839E-4</v>
+        <v>6.7428486606874269E-4</v>
       </c>
       <c r="AY9" s="4">
         <f t="shared" si="9"/>
-        <v>7.5686214263268839E-4</v>
+        <v>6.7428486606874269E-4</v>
       </c>
       <c r="AZ9" s="4">
         <f t="shared" si="9"/>
-        <v>7.5686214263268839E-4</v>
+        <v>6.7428486606874269E-4</v>
       </c>
       <c r="BA9" s="4">
         <f t="shared" si="9"/>
-        <v>7.5686214263268839E-4</v>
+        <v>6.7428486606874269E-4</v>
       </c>
       <c r="BB9" s="4">
         <f t="shared" si="9"/>
-        <v>7.5686214263268839E-4</v>
+        <v>6.7428486606874269E-4</v>
       </c>
       <c r="BC9" s="4">
         <f t="shared" si="9"/>
-        <v>7.5686214263268839E-4</v>
+        <v>6.7428486606874269E-4</v>
       </c>
       <c r="BD9" s="4">
         <f t="shared" si="9"/>
-        <v>7.5686214263268839E-4</v>
+        <v>6.7428486606874269E-4</v>
       </c>
       <c r="BE9" s="4">
         <f t="shared" si="9"/>
-        <v>7.5686214263268839E-4</v>
+        <v>6.7428486606874269E-4</v>
       </c>
       <c r="BF9" s="4">
         <f t="shared" si="9"/>
-        <v>7.5686214263268839E-4</v>
+        <v>6.7428486606874269E-4</v>
       </c>
       <c r="BG9" s="4">
         <f t="shared" si="9"/>
-        <v>7.5686214263268839E-4</v>
+        <v>6.7428486606874269E-4</v>
       </c>
       <c r="BH9" s="4">
         <f t="shared" si="9"/>
-        <v>7.5686214263268839E-4</v>
+        <v>6.7428486606874269E-4</v>
       </c>
       <c r="BI9" s="4">
         <f t="shared" si="9"/>
-        <v>7.5686214263268839E-4</v>
+        <v>6.7428486606874269E-4</v>
       </c>
       <c r="BJ9" s="4">
         <f t="shared" si="9"/>
-        <v>7.5686214263268839E-4</v>
+        <v>6.7428486606874269E-4</v>
       </c>
       <c r="BK9" s="4">
         <f t="shared" si="9"/>
-        <v>7.5686214263268839E-4</v>
+        <v>6.7428486606874269E-4</v>
       </c>
       <c r="BL9" s="4">
         <f t="shared" si="9"/>
-        <v>7.5686214263268839E-4</v>
+        <v>6.7428486606874269E-4</v>
       </c>
       <c r="BM9" s="4">
         <f t="shared" si="9"/>
-        <v>7.5686214263268839E-4</v>
+        <v>6.7428486606874269E-4</v>
       </c>
       <c r="BN9" s="4">
         <f t="shared" si="9"/>
-        <v>7.5686214263268839E-4</v>
+        <v>6.7428486606874269E-4</v>
       </c>
       <c r="BO9" s="4">
         <f t="shared" si="9"/>
-        <v>7.5686214263268839E-4</v>
+        <v>6.7428486606874269E-4</v>
       </c>
       <c r="BP9" s="4">
         <f t="shared" si="9"/>
-        <v>7.5686214263268839E-4</v>
+        <v>6.7428486606874269E-4</v>
       </c>
       <c r="BQ9" s="4">
         <f t="shared" si="9"/>
-        <v>7.5686214263268839E-4</v>
+        <v>6.7428486606874269E-4</v>
       </c>
       <c r="BR9" s="4">
         <f t="shared" si="9"/>
-        <v>7.5686214263268839E-4</v>
+        <v>6.7428486606874269E-4</v>
       </c>
       <c r="BS9" s="10"/>
       <c r="BT9" s="4"/>
@@ -21932,259 +21931,259 @@
       <c r="F12" s="9"/>
       <c r="G12" s="4">
         <f t="shared" ref="G12" si="11">TREND($AR12:$BR12,$AR$1:$BR$1,G$1)</f>
-        <v>5.2112239143541636E-3</v>
+        <v>4.1199493300773313E-3</v>
       </c>
       <c r="H12" s="4">
         <f t="shared" si="10"/>
-        <v>5.2112239143541636E-3</v>
+        <v>4.139779079772081E-3</v>
       </c>
       <c r="I12" s="4">
         <f t="shared" si="10"/>
-        <v>5.2112239143541636E-3</v>
+        <v>4.1596088294668307E-3</v>
       </c>
       <c r="J12" s="4">
         <f t="shared" si="10"/>
-        <v>5.2112239143541636E-3</v>
+        <v>4.1794385791615804E-3</v>
       </c>
       <c r="K12" s="4">
         <f t="shared" si="10"/>
-        <v>5.2112239143541636E-3</v>
+        <v>4.1992683288563301E-3</v>
       </c>
       <c r="L12" s="4">
         <f t="shared" si="10"/>
-        <v>5.2112239143541636E-3</v>
+        <v>4.2190980785510798E-3</v>
       </c>
       <c r="M12" s="4">
         <f t="shared" si="10"/>
-        <v>5.2112239143541636E-3</v>
+        <v>4.2389278282458295E-3</v>
       </c>
       <c r="N12" s="4">
         <f t="shared" si="10"/>
-        <v>5.2112239143541636E-3</v>
+        <v>4.2587575779405792E-3</v>
       </c>
       <c r="O12" s="4">
         <f t="shared" si="10"/>
-        <v>5.2112239143541636E-3</v>
+        <v>4.278587327635329E-3</v>
       </c>
       <c r="P12" s="4">
         <f t="shared" si="10"/>
-        <v>5.2112239143541636E-3</v>
+        <v>4.2984170773300787E-3</v>
       </c>
       <c r="Q12" s="4">
         <f t="shared" si="10"/>
-        <v>5.2112239143541636E-3</v>
+        <v>4.3182468270248284E-3</v>
       </c>
       <c r="R12" s="4">
         <f t="shared" si="10"/>
-        <v>5.2112239143541636E-3</v>
+        <v>4.3380765767195781E-3</v>
       </c>
       <c r="S12" s="4">
         <f t="shared" si="10"/>
-        <v>5.2112239143541636E-3</v>
+        <v>4.3579063264143278E-3</v>
       </c>
       <c r="T12" s="4">
         <f t="shared" si="10"/>
-        <v>5.2112239143541636E-3</v>
+        <v>4.3777360761090775E-3</v>
       </c>
       <c r="U12" s="4">
         <f t="shared" si="10"/>
-        <v>5.2112239143541636E-3</v>
+        <v>4.3975658258038272E-3</v>
       </c>
       <c r="V12" s="4">
         <f t="shared" si="10"/>
-        <v>5.2112239143541636E-3</v>
+        <v>4.4173955754985769E-3</v>
       </c>
       <c r="W12" s="4">
         <f t="shared" si="10"/>
-        <v>5.2112239143541636E-3</v>
+        <v>4.4372253251933266E-3</v>
       </c>
       <c r="X12" s="4">
         <f t="shared" si="10"/>
-        <v>5.2112239143541636E-3</v>
+        <v>4.4570550748880763E-3</v>
       </c>
       <c r="Y12" s="4">
         <f t="shared" si="10"/>
-        <v>5.2112239143541636E-3</v>
+        <v>4.4768848245828261E-3</v>
       </c>
       <c r="Z12" s="4">
         <f t="shared" si="10"/>
-        <v>5.2112239143541636E-3</v>
+        <v>4.4967145742775758E-3</v>
       </c>
       <c r="AA12" s="4">
         <f t="shared" si="10"/>
-        <v>5.2112239143541636E-3</v>
+        <v>4.5165443239723255E-3</v>
       </c>
       <c r="AB12" s="4">
         <f t="shared" si="10"/>
-        <v>5.2112239143541636E-3</v>
+        <v>4.5363740736670752E-3</v>
       </c>
       <c r="AC12" s="4">
         <f t="shared" si="10"/>
-        <v>5.2112239143541636E-3</v>
+        <v>4.5562038233618249E-3</v>
       </c>
       <c r="AD12" s="4">
         <f t="shared" si="10"/>
-        <v>5.2112239143541636E-3</v>
+        <v>4.5760335730565746E-3</v>
       </c>
       <c r="AE12" s="4">
         <f t="shared" si="10"/>
-        <v>5.2112239143541636E-3</v>
+        <v>4.5958633227513243E-3</v>
       </c>
       <c r="AF12" s="4">
         <f t="shared" si="10"/>
-        <v>5.2112239143541636E-3</v>
+        <v>4.615693072446074E-3</v>
       </c>
       <c r="AG12" s="4">
         <f t="shared" si="10"/>
-        <v>5.2112239143541636E-3</v>
+        <v>4.6355228221408237E-3</v>
       </c>
       <c r="AH12" s="4">
         <f t="shared" si="10"/>
-        <v>5.2112239143541636E-3</v>
+        <v>4.6553525718355734E-3</v>
       </c>
       <c r="AI12" s="4">
         <f t="shared" si="10"/>
-        <v>5.2112239143541636E-3</v>
+        <v>4.6751823215303231E-3</v>
       </c>
       <c r="AJ12" s="4">
         <f t="shared" si="10"/>
-        <v>5.2112239143541636E-3</v>
+        <v>4.6950120712250729E-3</v>
       </c>
       <c r="AK12" s="4">
         <f t="shared" si="10"/>
-        <v>5.2112239143541636E-3</v>
+        <v>4.7148418209198226E-3</v>
       </c>
       <c r="AL12" s="4">
         <f t="shared" si="10"/>
-        <v>5.2112239143541636E-3</v>
+        <v>4.7346715706145723E-3</v>
       </c>
       <c r="AM12" s="4">
         <f t="shared" si="10"/>
-        <v>5.2112239143541636E-3</v>
+        <v>4.754501320309322E-3</v>
       </c>
       <c r="AN12" s="4">
         <f t="shared" si="10"/>
-        <v>5.2112239143541636E-3</v>
+        <v>4.7743310700040717E-3</v>
       </c>
       <c r="AO12" s="4">
         <f>TREND($AR12:$BR12,$AR$1:$BR$1,AO$1)</f>
-        <v>5.2112239143541636E-3</v>
+        <v>4.7941608196988214E-3</v>
       </c>
       <c r="AP12" s="4">
         <f t="shared" si="10"/>
-        <v>5.2112239143541636E-3</v>
+        <v>4.8139905693935711E-3</v>
       </c>
       <c r="AQ12" s="4">
         <f t="shared" si="10"/>
-        <v>5.2112239143541636E-3</v>
+        <v>4.8338203190883208E-3</v>
       </c>
       <c r="AR12" s="10">
         <f>BNVFE!G18</f>
-        <v>5.2112239143541636E-3</v>
+        <v>4.8577789999999996E-3</v>
       </c>
       <c r="AS12" s="10">
         <f>BNVFE!H18</f>
-        <v>5.2112239143541636E-3</v>
+        <v>4.8766649999999996E-3</v>
       </c>
       <c r="AT12" s="10">
         <f>BNVFE!I18</f>
-        <v>5.2112239143541636E-3</v>
+        <v>4.8956239999999995E-3</v>
       </c>
       <c r="AU12" s="10">
         <f>BNVFE!J18</f>
-        <v>5.2112239143541636E-3</v>
+        <v>4.9146570000000002E-3</v>
       </c>
       <c r="AV12" s="10">
         <f>BNVFE!K18</f>
-        <v>5.2112239143541636E-3</v>
+        <v>4.9337640000000002E-3</v>
       </c>
       <c r="AW12" s="10">
         <f>BNVFE!L18</f>
-        <v>5.2112239143541636E-3</v>
+        <v>4.9529449999999994E-3</v>
       </c>
       <c r="AX12" s="10">
         <f>BNVFE!M18</f>
-        <v>5.2112239143541636E-3</v>
+        <v>4.9721999999999995E-3</v>
       </c>
       <c r="AY12" s="10">
         <f>BNVFE!N18</f>
-        <v>5.2112239143541636E-3</v>
+        <v>4.9915310000000004E-3</v>
       </c>
       <c r="AZ12" s="10">
         <f>BNVFE!O18</f>
-        <v>5.2112239143541636E-3</v>
+        <v>5.010937E-3</v>
       </c>
       <c r="BA12" s="10">
         <f>BNVFE!P18</f>
-        <v>5.2112239143541636E-3</v>
+        <v>5.030418E-3</v>
       </c>
       <c r="BB12" s="10">
         <f>BNVFE!Q18</f>
-        <v>5.2112239143541636E-3</v>
+        <v>5.049975E-3</v>
       </c>
       <c r="BC12" s="10">
         <f>BNVFE!R18</f>
-        <v>5.2112239143541636E-3</v>
+        <v>5.0696079999999998E-3</v>
       </c>
       <c r="BD12" s="10">
         <f>BNVFE!S18</f>
-        <v>5.2112239143541636E-3</v>
+        <v>5.0893170000000003E-3</v>
       </c>
       <c r="BE12" s="10">
         <f>BNVFE!T18</f>
-        <v>5.2112239143541636E-3</v>
+        <v>5.1091030000000003E-3</v>
       </c>
       <c r="BF12" s="10">
         <f>BNVFE!U18</f>
-        <v>5.2112239143541636E-3</v>
+        <v>5.1289660000000004E-3</v>
       </c>
       <c r="BG12" s="10">
         <f>BNVFE!V18</f>
-        <v>5.2112239143541636E-3</v>
+        <v>5.148906E-3</v>
       </c>
       <c r="BH12" s="10">
         <f>BNVFE!W18</f>
-        <v>5.2112239143541636E-3</v>
+        <v>5.1689230000000006E-3</v>
       </c>
       <c r="BI12" s="10">
         <f>BNVFE!X18</f>
-        <v>5.2112239143541636E-3</v>
+        <v>5.1890190000000004E-3</v>
       </c>
       <c r="BJ12" s="10">
         <f>BNVFE!Y18</f>
-        <v>5.2112239143541636E-3</v>
+        <v>5.2091919999999996E-3</v>
       </c>
       <c r="BK12" s="10">
         <f>BNVFE!Z18</f>
-        <v>5.2112239143541636E-3</v>
+        <v>5.2294450000000001E-3</v>
       </c>
       <c r="BL12" s="10">
         <f>BNVFE!AA18</f>
-        <v>5.2112239143541636E-3</v>
+        <v>5.2497749999999999E-3</v>
       </c>
       <c r="BM12" s="10">
         <f>BNVFE!AB18</f>
-        <v>5.2112239143541636E-3</v>
+        <v>5.2701849999999993E-3</v>
       </c>
       <c r="BN12" s="10">
         <f>BNVFE!AC18</f>
-        <v>5.2112239143541636E-3</v>
+        <v>5.2906740000000004E-3</v>
       </c>
       <c r="BO12" s="10">
         <f>BNVFE!AD18</f>
-        <v>5.2112239143541636E-3</v>
+        <v>5.3112430000000002E-3</v>
       </c>
       <c r="BP12" s="10">
         <f>BNVFE!AE18</f>
-        <v>5.2112239143541636E-3</v>
+        <v>5.3318919999999995E-3</v>
       </c>
       <c r="BQ12" s="10">
         <f>BNVFE!AF18</f>
-        <v>5.2112239143541636E-3</v>
+        <v>5.3526210000000001E-3</v>
       </c>
       <c r="BR12" s="10">
         <f>BNVFE!AG18</f>
-        <v>5.2112239143541636E-3</v>
+        <v>5.3734300000000002E-3</v>
       </c>
       <c r="BS12" s="10"/>
       <c r="BT12" s="4"/>
@@ -24041,123 +24040,123 @@
         <v>4</v>
       </c>
       <c r="B4" s="4">
-        <v>9.2955581997260681E-5</v>
+        <v>1.0066053377187421E-4</v>
       </c>
       <c r="C4" s="4">
         <f t="shared" si="1"/>
-        <v>9.2955581997260681E-5</v>
+        <v>1.0066053377187421E-4</v>
       </c>
       <c r="D4" s="4">
         <f t="shared" si="0"/>
-        <v>9.2955581997260681E-5</v>
+        <v>1.0066053377187421E-4</v>
       </c>
       <c r="E4" s="4">
         <f t="shared" si="0"/>
-        <v>9.2955581997260681E-5</v>
+        <v>1.0066053377187421E-4</v>
       </c>
       <c r="F4" s="4">
         <f t="shared" si="0"/>
-        <v>9.2955581997260681E-5</v>
+        <v>1.0066053377187421E-4</v>
       </c>
       <c r="G4" s="4">
         <f t="shared" si="0"/>
-        <v>9.2955581997260681E-5</v>
+        <v>1.0066053377187421E-4</v>
       </c>
       <c r="H4" s="4">
         <f t="shared" si="0"/>
-        <v>9.2955581997260681E-5</v>
+        <v>1.0066053377187421E-4</v>
       </c>
       <c r="I4" s="4">
         <f t="shared" si="0"/>
-        <v>9.2955581997260681E-5</v>
+        <v>1.0066053377187421E-4</v>
       </c>
       <c r="J4" s="4">
         <f t="shared" si="0"/>
-        <v>9.2955581997260681E-5</v>
+        <v>1.0066053377187421E-4</v>
       </c>
       <c r="K4" s="4">
         <f t="shared" si="0"/>
-        <v>9.2955581997260681E-5</v>
+        <v>1.0066053377187421E-4</v>
       </c>
       <c r="L4" s="4">
         <f t="shared" si="0"/>
-        <v>9.2955581997260681E-5</v>
+        <v>1.0066053377187421E-4</v>
       </c>
       <c r="M4" s="4">
         <f t="shared" si="0"/>
-        <v>9.2955581997260681E-5</v>
+        <v>1.0066053377187421E-4</v>
       </c>
       <c r="N4" s="4">
         <f t="shared" si="0"/>
-        <v>9.2955581997260681E-5</v>
+        <v>1.0066053377187421E-4</v>
       </c>
       <c r="O4" s="4">
         <f t="shared" si="0"/>
-        <v>9.2955581997260681E-5</v>
+        <v>1.0066053377187421E-4</v>
       </c>
       <c r="P4" s="4">
         <f t="shared" si="0"/>
-        <v>9.2955581997260681E-5</v>
+        <v>1.0066053377187421E-4</v>
       </c>
       <c r="Q4" s="4">
         <f t="shared" si="0"/>
-        <v>9.2955581997260681E-5</v>
+        <v>1.0066053377187421E-4</v>
       </c>
       <c r="R4" s="4">
         <f t="shared" si="0"/>
-        <v>9.2955581997260681E-5</v>
+        <v>1.0066053377187421E-4</v>
       </c>
       <c r="S4" s="4">
         <f t="shared" si="0"/>
-        <v>9.2955581997260681E-5</v>
+        <v>1.0066053377187421E-4</v>
       </c>
       <c r="T4" s="4">
         <f t="shared" si="0"/>
-        <v>9.2955581997260681E-5</v>
+        <v>1.0066053377187421E-4</v>
       </c>
       <c r="U4" s="4">
         <f t="shared" si="0"/>
-        <v>9.2955581997260681E-5</v>
+        <v>1.0066053377187421E-4</v>
       </c>
       <c r="V4" s="4">
         <f t="shared" si="0"/>
-        <v>9.2955581997260681E-5</v>
+        <v>1.0066053377187421E-4</v>
       </c>
       <c r="W4" s="4">
         <f t="shared" si="0"/>
-        <v>9.2955581997260681E-5</v>
+        <v>1.0066053377187421E-4</v>
       </c>
       <c r="X4" s="4">
         <f t="shared" si="0"/>
-        <v>9.2955581997260681E-5</v>
+        <v>1.0066053377187421E-4</v>
       </c>
       <c r="Y4" s="4">
         <f t="shared" si="0"/>
-        <v>9.2955581997260681E-5</v>
+        <v>1.0066053377187421E-4</v>
       </c>
       <c r="Z4" s="4">
         <f t="shared" si="0"/>
-        <v>9.2955581997260681E-5</v>
+        <v>1.0066053377187421E-4</v>
       </c>
       <c r="AA4" s="4">
         <f t="shared" si="0"/>
-        <v>9.2955581997260681E-5</v>
+        <v>1.0066053377187421E-4</v>
       </c>
       <c r="AB4" s="4">
         <f t="shared" si="0"/>
-        <v>9.2955581997260681E-5</v>
+        <v>1.0066053377187421E-4</v>
       </c>
       <c r="AC4" s="4">
         <f t="shared" si="0"/>
-        <v>9.2955581997260681E-5</v>
+        <v>1.0066053377187421E-4</v>
       </c>
       <c r="AD4" s="4">
         <f t="shared" si="0"/>
-        <v>9.2955581997260681E-5</v>
+        <v>1.0066053377187421E-4</v>
       </c>
       <c r="AE4" s="4">
         <f t="shared" si="0"/>
-        <v>9.2955581997260681E-5</v>
+        <v>1.0066053377187421E-4</v>
       </c>
       <c r="AG4" s="4"/>
       <c r="AH4" s="4"/>
@@ -24167,123 +24166,123 @@
         <v>5</v>
       </c>
       <c r="B5" s="4">
-        <v>1.0087912753938768E-4</v>
+        <v>7.8079341843850301E-5</v>
       </c>
       <c r="C5" s="4">
         <f t="shared" si="1"/>
-        <v>1.0087912753938768E-4</v>
+        <v>7.8079341843850301E-5</v>
       </c>
       <c r="D5" s="4">
         <f t="shared" si="0"/>
-        <v>1.0087912753938768E-4</v>
+        <v>7.8079341843850301E-5</v>
       </c>
       <c r="E5" s="4">
         <f t="shared" si="0"/>
-        <v>1.0087912753938768E-4</v>
+        <v>7.8079341843850301E-5</v>
       </c>
       <c r="F5" s="4">
         <f t="shared" si="0"/>
-        <v>1.0087912753938768E-4</v>
+        <v>7.8079341843850301E-5</v>
       </c>
       <c r="G5" s="4">
         <f t="shared" si="0"/>
-        <v>1.0087912753938768E-4</v>
+        <v>7.8079341843850301E-5</v>
       </c>
       <c r="H5" s="4">
         <f t="shared" si="0"/>
-        <v>1.0087912753938768E-4</v>
+        <v>7.8079341843850301E-5</v>
       </c>
       <c r="I5" s="4">
         <f t="shared" si="0"/>
-        <v>1.0087912753938768E-4</v>
+        <v>7.8079341843850301E-5</v>
       </c>
       <c r="J5" s="4">
         <f t="shared" si="0"/>
-        <v>1.0087912753938768E-4</v>
+        <v>7.8079341843850301E-5</v>
       </c>
       <c r="K5" s="4">
         <f t="shared" si="0"/>
-        <v>1.0087912753938768E-4</v>
+        <v>7.8079341843850301E-5</v>
       </c>
       <c r="L5" s="4">
         <f t="shared" si="0"/>
-        <v>1.0087912753938768E-4</v>
+        <v>7.8079341843850301E-5</v>
       </c>
       <c r="M5" s="4">
         <f t="shared" si="0"/>
-        <v>1.0087912753938768E-4</v>
+        <v>7.8079341843850301E-5</v>
       </c>
       <c r="N5" s="4">
         <f t="shared" si="0"/>
-        <v>1.0087912753938768E-4</v>
+        <v>7.8079341843850301E-5</v>
       </c>
       <c r="O5" s="4">
         <f t="shared" si="0"/>
-        <v>1.0087912753938768E-4</v>
+        <v>7.8079341843850301E-5</v>
       </c>
       <c r="P5" s="4">
         <f t="shared" si="0"/>
-        <v>1.0087912753938768E-4</v>
+        <v>7.8079341843850301E-5</v>
       </c>
       <c r="Q5" s="4">
         <f t="shared" si="0"/>
-        <v>1.0087912753938768E-4</v>
+        <v>7.8079341843850301E-5</v>
       </c>
       <c r="R5" s="4">
         <f t="shared" si="0"/>
-        <v>1.0087912753938768E-4</v>
+        <v>7.8079341843850301E-5</v>
       </c>
       <c r="S5" s="4">
         <f t="shared" si="0"/>
-        <v>1.0087912753938768E-4</v>
+        <v>7.8079341843850301E-5</v>
       </c>
       <c r="T5" s="4">
         <f t="shared" si="0"/>
-        <v>1.0087912753938768E-4</v>
+        <v>7.8079341843850301E-5</v>
       </c>
       <c r="U5" s="4">
         <f t="shared" si="0"/>
-        <v>1.0087912753938768E-4</v>
+        <v>7.8079341843850301E-5</v>
       </c>
       <c r="V5" s="4">
         <f t="shared" si="0"/>
-        <v>1.0087912753938768E-4</v>
+        <v>7.8079341843850301E-5</v>
       </c>
       <c r="W5" s="4">
         <f t="shared" si="0"/>
-        <v>1.0087912753938768E-4</v>
+        <v>7.8079341843850301E-5</v>
       </c>
       <c r="X5" s="4">
         <f t="shared" si="0"/>
-        <v>1.0087912753938768E-4</v>
+        <v>7.8079341843850301E-5</v>
       </c>
       <c r="Y5" s="4">
         <f t="shared" si="0"/>
-        <v>1.0087912753938768E-4</v>
+        <v>7.8079341843850301E-5</v>
       </c>
       <c r="Z5" s="4">
         <f t="shared" si="0"/>
-        <v>1.0087912753938768E-4</v>
+        <v>7.8079341843850301E-5</v>
       </c>
       <c r="AA5" s="4">
         <f t="shared" si="0"/>
-        <v>1.0087912753938768E-4</v>
+        <v>7.8079341843850301E-5</v>
       </c>
       <c r="AB5" s="4">
         <f t="shared" si="0"/>
-        <v>1.0087912753938768E-4</v>
+        <v>7.8079341843850301E-5</v>
       </c>
       <c r="AC5" s="4">
         <f t="shared" si="0"/>
-        <v>1.0087912753938768E-4</v>
+        <v>7.8079341843850301E-5</v>
       </c>
       <c r="AD5" s="4">
         <f t="shared" si="0"/>
-        <v>1.0087912753938768E-4</v>
+        <v>7.8079341843850301E-5</v>
       </c>
       <c r="AE5" s="4">
         <f t="shared" si="0"/>
-        <v>1.0087912753938768E-4</v>
+        <v>7.8079341843850301E-5</v>
       </c>
       <c r="AG5" s="4"/>
       <c r="AH5" s="4"/>

--- a/InputData/trans/BHNVFEAL/BAU Historical New Veh Fuel Economy After Lifetime.xlsx
+++ b/InputData/trans/BHNVFEAL/BAU Historical New Veh Fuel Economy After Lifetime.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\United States\us-eps\InputData\trans\BHNVFEAL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51991E45-905E-42B8-9F2E-7BCF8D3BD7AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28AC5378-ED77-42E3-8839-619BE7FF2F86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="10260" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -18763,16 +18763,16 @@
         <v>17</v>
       </c>
       <c r="B14">
-        <v>1.5549894526873581E-2</v>
+        <v>1.5610349625283874E-2</v>
       </c>
       <c r="C14">
-        <v>4.8389660000000001E-3</v>
+        <v>4.8577789999999996E-3</v>
       </c>
       <c r="D14">
-        <v>4.8389660000000001E-3</v>
+        <v>4.8577789999999996E-3</v>
       </c>
       <c r="E14">
-        <v>4.8389660000000001E-3</v>
+        <v>4.8577789999999996E-3</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -18781,7 +18781,7 @@
         <v>0</v>
       </c>
       <c r="H14">
-        <v>1.4516897999999999E-2</v>
+        <v>1.4573336999999997E-2</v>
       </c>
     </row>
     <row r="15" spans="1:8">

--- a/InputData/trans/BHNVFEAL/BAU Historical New Veh Fuel Economy After Lifetime.xlsx
+++ b/InputData/trans/BHNVFEAL/BAU Historical New Veh Fuel Economy After Lifetime.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\United States\us-eps\InputData\trans\BHNVFEAL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28AC5378-ED77-42E3-8839-619BE7FF2F86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D77C2360-6206-45AD-A5B2-FB9CD1B26A33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3693,181 +3693,181 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="68"/>
                 <c:pt idx="9" formatCode="0.00E+00">
-                  <c:v>9.8438896867039508E-4</c:v>
+                  <c:v>1.0506747874471361E-3</c:v>
                 </c:pt>
                 <c:pt idx="10" formatCode="0.00E+00">
-                  <c:v>9.8438896867039508E-4</c:v>
+                  <c:v>1.0506747874471361E-3</c:v>
                 </c:pt>
                 <c:pt idx="11" formatCode="0.00E+00">
-                  <c:v>9.8438896867039508E-4</c:v>
+                  <c:v>1.0506747874471361E-3</c:v>
                 </c:pt>
                 <c:pt idx="12" formatCode="0.00E+00">
-                  <c:v>9.8438896867039508E-4</c:v>
+                  <c:v>1.0506747874471361E-3</c:v>
                 </c:pt>
                 <c:pt idx="13" formatCode="0.00E+00">
-                  <c:v>9.8438896867039508E-4</c:v>
+                  <c:v>1.0506747874471361E-3</c:v>
                 </c:pt>
                 <c:pt idx="14" formatCode="0.00E+00">
-                  <c:v>9.8438896867039508E-4</c:v>
+                  <c:v>1.0506747874471361E-3</c:v>
                 </c:pt>
                 <c:pt idx="15" formatCode="0.00E+00">
-                  <c:v>9.8438896867039508E-4</c:v>
+                  <c:v>1.0506747874471361E-3</c:v>
                 </c:pt>
                 <c:pt idx="16" formatCode="0.00E+00">
-                  <c:v>9.8438896867039508E-4</c:v>
+                  <c:v>1.0506747874471361E-3</c:v>
                 </c:pt>
                 <c:pt idx="17" formatCode="0.00E+00">
-                  <c:v>9.8438896867039508E-4</c:v>
+                  <c:v>1.0506747874471361E-3</c:v>
                 </c:pt>
                 <c:pt idx="18" formatCode="0.00E+00">
-                  <c:v>9.8438896867039508E-4</c:v>
+                  <c:v>1.0506747874471361E-3</c:v>
                 </c:pt>
                 <c:pt idx="19" formatCode="0.00E+00">
-                  <c:v>9.8438896867039508E-4</c:v>
+                  <c:v>1.0506747874471361E-3</c:v>
                 </c:pt>
                 <c:pt idx="20" formatCode="0.00E+00">
-                  <c:v>9.8557760355181558E-4</c:v>
+                  <c:v>1.0488504305659774E-3</c:v>
                 </c:pt>
                 <c:pt idx="21" formatCode="0.00E+00">
-                  <c:v>9.8676623843323608E-4</c:v>
+                  <c:v>1.0470260736848186E-3</c:v>
                 </c:pt>
                 <c:pt idx="22" formatCode="0.00E+00">
-                  <c:v>9.8795487331465657E-4</c:v>
+                  <c:v>1.04520171680366E-3</c:v>
                 </c:pt>
                 <c:pt idx="23" formatCode="0.00E+00">
-                  <c:v>9.8914350819607707E-4</c:v>
+                  <c:v>1.0433773599225014E-3</c:v>
                 </c:pt>
                 <c:pt idx="24" formatCode="0.00E+00">
-                  <c:v>9.9033214307749757E-4</c:v>
+                  <c:v>1.0415530030413428E-3</c:v>
                 </c:pt>
                 <c:pt idx="25" formatCode="0.00E+00">
-                  <c:v>9.9152077795891806E-4</c:v>
+                  <c:v>1.0397286461601841E-3</c:v>
                 </c:pt>
                 <c:pt idx="26" formatCode="0.00E+00">
-                  <c:v>9.9270941284033856E-4</c:v>
+                  <c:v>1.0379042892790255E-3</c:v>
                 </c:pt>
                 <c:pt idx="27" formatCode="0.00E+00">
-                  <c:v>9.9389804772175906E-4</c:v>
+                  <c:v>1.0360799323978669E-3</c:v>
                 </c:pt>
                 <c:pt idx="28" formatCode="0.00E+00">
-                  <c:v>9.9508668260317955E-4</c:v>
+                  <c:v>1.0342555755167083E-3</c:v>
                 </c:pt>
                 <c:pt idx="29" formatCode="0.00E+00">
-                  <c:v>9.9627531748460005E-4</c:v>
+                  <c:v>1.0324312186355497E-3</c:v>
                 </c:pt>
                 <c:pt idx="30" formatCode="0.00E+00">
-                  <c:v>9.9746395236602055E-4</c:v>
+                  <c:v>1.030606861754391E-3</c:v>
                 </c:pt>
                 <c:pt idx="31" formatCode="0.00E+00">
-                  <c:v>9.9865258724744104E-4</c:v>
+                  <c:v>1.0287825048732324E-3</c:v>
                 </c:pt>
                 <c:pt idx="32" formatCode="0.00E+00">
-                  <c:v>9.9984122212886154E-4</c:v>
+                  <c:v>1.0269581479920738E-3</c:v>
                 </c:pt>
                 <c:pt idx="33" formatCode="0.00E+00">
-                  <c:v>1.001029857010282E-3</c:v>
+                  <c:v>1.0251337911109152E-3</c:v>
                 </c:pt>
                 <c:pt idx="34" formatCode="0.00E+00">
-                  <c:v>1.0022184918917025E-3</c:v>
+                  <c:v>1.0233094342297566E-3</c:v>
                 </c:pt>
                 <c:pt idx="35" formatCode="0.00E+00">
-                  <c:v>1.003407126773123E-3</c:v>
+                  <c:v>1.0214850773485979E-3</c:v>
                 </c:pt>
                 <c:pt idx="36" formatCode="0.00E+00">
-                  <c:v>1.0045957616545435E-3</c:v>
+                  <c:v>1.0196607204674393E-3</c:v>
                 </c:pt>
                 <c:pt idx="37" formatCode="0.00E+00">
-                  <c:v>1.005784396535964E-3</c:v>
+                  <c:v>1.0178363635862807E-3</c:v>
                 </c:pt>
                 <c:pt idx="38" formatCode="0.00E+00">
-                  <c:v>1.0069730314173845E-3</c:v>
+                  <c:v>1.0160120067051221E-3</c:v>
                 </c:pt>
                 <c:pt idx="39" formatCode="0.00E+00">
-                  <c:v>1.008161666298805E-3</c:v>
+                  <c:v>1.0141876498239635E-3</c:v>
                 </c:pt>
                 <c:pt idx="40" formatCode="0.00E+00">
                   <c:v>1.0105389360616456E-3</c:v>
                 </c:pt>
                 <c:pt idx="41" formatCode="0.00E+00">
-                  <c:v>1.0071619859986915E-3</c:v>
+                  <c:v>1.0754660288918199E-3</c:v>
                 </c:pt>
                 <c:pt idx="42" formatCode="0.00E+00">
-                  <c:v>1.0297946332597221E-3</c:v>
+                  <c:v>1.0997832463414735E-3</c:v>
                 </c:pt>
                 <c:pt idx="43" formatCode="0.00E+00">
-                  <c:v>1.0542694402792506E-3</c:v>
+                  <c:v>1.1259180725970582E-3</c:v>
                 </c:pt>
                 <c:pt idx="44" formatCode="0.00E+00">
-                  <c:v>1.0790300186124084E-3</c:v>
+                  <c:v>1.1522254447480843E-3</c:v>
                 </c:pt>
                 <c:pt idx="45" formatCode="0.00E+00">
-                  <c:v>1.1024390235193078E-3</c:v>
+                  <c:v>1.1772174874709175E-3</c:v>
                 </c:pt>
                 <c:pt idx="46" formatCode="0.00E+00">
-                  <c:v>1.1250162796311157E-3</c:v>
+                  <c:v>1.2013234498187955E-3</c:v>
                 </c:pt>
                 <c:pt idx="47" formatCode="0.00E+00">
-                  <c:v>1.1437364311026228E-3</c:v>
+                  <c:v>1.2212854897622565E-3</c:v>
                 </c:pt>
                 <c:pt idx="48" formatCode="0.00E+00">
-                  <c:v>1.1601755544794832E-3</c:v>
+                  <c:v>1.238809319858962E-3</c:v>
                 </c:pt>
                 <c:pt idx="49" formatCode="0.00E+00">
-                  <c:v>1.1731175422229271E-3</c:v>
+                  <c:v>1.25258619281297E-3</c:v>
                 </c:pt>
                 <c:pt idx="50" formatCode="0.00E+00">
-                  <c:v>1.1829709958873008E-3</c:v>
+                  <c:v>1.2631583509478295E-3</c:v>
                 </c:pt>
                 <c:pt idx="51" formatCode="0.00E+00">
-                  <c:v>1.1904376346468411E-3</c:v>
+                  <c:v>1.271115521969759E-3</c:v>
                 </c:pt>
                 <c:pt idx="52" formatCode="0.00E+00">
-                  <c:v>1.1951266350083583E-3</c:v>
+                  <c:v>1.2761007035628495E-3</c:v>
                 </c:pt>
                 <c:pt idx="53" formatCode="0.00E+00">
-                  <c:v>1.1954817554531098E-3</c:v>
+                  <c:v>1.2764716537304337E-3</c:v>
                 </c:pt>
                 <c:pt idx="54" formatCode="0.00E+00">
-                  <c:v>1.1956768733474535E-3</c:v>
+                  <c:v>1.2767311778020512E-3</c:v>
                 </c:pt>
                 <c:pt idx="55" formatCode="0.00E+00">
-                  <c:v>1.1953490811620006E-3</c:v>
+                  <c:v>1.276353645502216E-3</c:v>
                 </c:pt>
                 <c:pt idx="56" formatCode="0.00E+00">
-                  <c:v>1.195614135891968E-3</c:v>
+                  <c:v>1.2766760132650891E-3</c:v>
                 </c:pt>
                 <c:pt idx="57" formatCode="0.00E+00">
-                  <c:v>1.1955621240436263E-3</c:v>
+                  <c:v>1.2766818118101673E-3</c:v>
                 </c:pt>
                 <c:pt idx="58" formatCode="0.00E+00">
-                  <c:v>1.1954516355974314E-3</c:v>
+                  <c:v>1.2766739759384397E-3</c:v>
                 </c:pt>
                 <c:pt idx="59" formatCode="0.00E+00">
-                  <c:v>1.1954450239217949E-3</c:v>
+                  <c:v>1.2766888640947222E-3</c:v>
                 </c:pt>
                 <c:pt idx="60" formatCode="0.00E+00">
-                  <c:v>1.1950872588067892E-3</c:v>
+                  <c:v>1.2763212049932639E-3</c:v>
                 </c:pt>
                 <c:pt idx="61" formatCode="0.00E+00">
-                  <c:v>1.1949745664687152E-3</c:v>
+                  <c:v>1.276284062961275E-3</c:v>
                 </c:pt>
                 <c:pt idx="62" formatCode="0.00E+00">
-                  <c:v>1.1948443899217356E-3</c:v>
+                  <c:v>1.2762870405925318E-3</c:v>
                 </c:pt>
                 <c:pt idx="63" formatCode="0.00E+00">
-                  <c:v>1.1946410441643772E-3</c:v>
+                  <c:v>1.2761892489133713E-3</c:v>
                 </c:pt>
                 <c:pt idx="64" formatCode="0.00E+00">
-                  <c:v>1.1944371107025177E-3</c:v>
+                  <c:v>1.2761347112461472E-3</c:v>
                 </c:pt>
                 <c:pt idx="65" formatCode="0.00E+00">
-                  <c:v>1.193589934664274E-3</c:v>
+                  <c:v>1.2753821541254299E-3</c:v>
                 </c:pt>
                 <c:pt idx="66" formatCode="0.00E+00">
-                  <c:v>1.1933357524675759E-3</c:v>
+                  <c:v>1.2752958028189919E-3</c:v>
                 </c:pt>
                 <c:pt idx="67" formatCode="0.00E+00">
-                  <c:v>1.1931159509841881E-3</c:v>
+                  <c:v>1.2752821684021858E-3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4234,148 +4234,148 @@
                   <c:v>7.8040477200267344E-4</c:v>
                 </c:pt>
                 <c:pt idx="20" formatCode="0.00E+00">
-                  <c:v>7.8134709903309753E-4</c:v>
+                  <c:v>7.7904970301948082E-4</c:v>
                 </c:pt>
                 <c:pt idx="21" formatCode="0.00E+00">
-                  <c:v>7.8228942606352163E-4</c:v>
+                  <c:v>7.7769463403628821E-4</c:v>
                 </c:pt>
                 <c:pt idx="22" formatCode="0.00E+00">
-                  <c:v>7.8323175309394572E-4</c:v>
+                  <c:v>7.7633956505309559E-4</c:v>
                 </c:pt>
                 <c:pt idx="23" formatCode="0.00E+00">
-                  <c:v>7.8417408012436982E-4</c:v>
+                  <c:v>7.7498449606990298E-4</c:v>
                 </c:pt>
                 <c:pt idx="24" formatCode="0.00E+00">
-                  <c:v>7.8511640715479391E-4</c:v>
+                  <c:v>7.7362942708671036E-4</c:v>
                 </c:pt>
                 <c:pt idx="25" formatCode="0.00E+00">
-                  <c:v>7.8605873418521801E-4</c:v>
+                  <c:v>7.7227435810351774E-4</c:v>
                 </c:pt>
                 <c:pt idx="26" formatCode="0.00E+00">
-                  <c:v>7.870010612156421E-4</c:v>
+                  <c:v>7.7091928912032513E-4</c:v>
                 </c:pt>
                 <c:pt idx="27" formatCode="0.00E+00">
-                  <c:v>7.879433882460662E-4</c:v>
+                  <c:v>7.6956422013713251E-4</c:v>
                 </c:pt>
                 <c:pt idx="28" formatCode="0.00E+00">
-                  <c:v>7.8888571527649029E-4</c:v>
+                  <c:v>7.682091511539399E-4</c:v>
                 </c:pt>
                 <c:pt idx="29" formatCode="0.00E+00">
-                  <c:v>7.8982804230691439E-4</c:v>
+                  <c:v>7.6685408217074728E-4</c:v>
                 </c:pt>
                 <c:pt idx="30" formatCode="0.00E+00">
-                  <c:v>7.9077036933733848E-4</c:v>
+                  <c:v>7.6549901318755467E-4</c:v>
                 </c:pt>
                 <c:pt idx="31" formatCode="0.00E+00">
-                  <c:v>7.9171269636776258E-4</c:v>
+                  <c:v>7.6414394420436205E-4</c:v>
                 </c:pt>
                 <c:pt idx="32" formatCode="0.00E+00">
-                  <c:v>7.9265502339818667E-4</c:v>
+                  <c:v>7.6278887522116944E-4</c:v>
                 </c:pt>
                 <c:pt idx="33" formatCode="0.00E+00">
-                  <c:v>7.9359735042861077E-4</c:v>
+                  <c:v>7.6143380623797682E-4</c:v>
                 </c:pt>
                 <c:pt idx="34" formatCode="0.00E+00">
-                  <c:v>7.9453967745903486E-4</c:v>
+                  <c:v>7.6007873725478421E-4</c:v>
                 </c:pt>
                 <c:pt idx="35" formatCode="0.00E+00">
-                  <c:v>7.9548200448945896E-4</c:v>
+                  <c:v>7.5872366827159159E-4</c:v>
                 </c:pt>
                 <c:pt idx="36" formatCode="0.00E+00">
-                  <c:v>7.9642433151988306E-4</c:v>
+                  <c:v>7.5736859928839898E-4</c:v>
                 </c:pt>
                 <c:pt idx="37" formatCode="0.00E+00">
-                  <c:v>7.9736665855030715E-4</c:v>
+                  <c:v>7.5601353030520636E-4</c:v>
                 </c:pt>
                 <c:pt idx="38" formatCode="0.00E+00">
-                  <c:v>7.9830898558073125E-4</c:v>
+                  <c:v>7.5465846132201375E-4</c:v>
                 </c:pt>
                 <c:pt idx="39" formatCode="0.00E+00">
-                  <c:v>7.9925131261115534E-4</c:v>
+                  <c:v>7.5330339233882113E-4</c:v>
                 </c:pt>
                 <c:pt idx="40" formatCode="0.00E+00">
-                  <c:v>8.0113596667200321E-4</c:v>
+                  <c:v>7.5059325437243547E-4</c:v>
                 </c:pt>
                 <c:pt idx="41" formatCode="0.00E+00">
-                  <c:v>7.9845878516365723E-4</c:v>
+                  <c:v>7.9881884585164282E-4</c:v>
                 </c:pt>
                 <c:pt idx="42" formatCode="0.00E+00">
-                  <c:v>8.1640151561645602E-4</c:v>
+                  <c:v>8.1688083112650234E-4</c:v>
                 </c:pt>
                 <c:pt idx="43" formatCode="0.00E+00">
-                  <c:v>8.3580467513954908E-4</c:v>
+                  <c:v>8.3629287314844459E-4</c:v>
                 </c:pt>
                 <c:pt idx="44" formatCode="0.00E+00">
-                  <c:v>8.5543438870170133E-4</c:v>
+                  <c:v>8.5583307627389927E-4</c:v>
                 </c:pt>
                 <c:pt idx="45" formatCode="0.00E+00">
-                  <c:v>8.7399260066729594E-4</c:v>
+                  <c:v>8.7439629834414924E-4</c:v>
                 </c:pt>
                 <c:pt idx="46" formatCode="0.00E+00">
-                  <c:v>8.9189141807499185E-4</c:v>
+                  <c:v>8.923013706603032E-4</c:v>
                 </c:pt>
                 <c:pt idx="47" formatCode="0.00E+00">
-                  <c:v>9.0673239659663221E-4</c:v>
+                  <c:v>9.0712848121526056E-4</c:v>
                 </c:pt>
                 <c:pt idx="48" formatCode="0.00E+00">
-                  <c:v>9.1976501961370109E-4</c:v>
+                  <c:v>9.2014457410586974E-4</c:v>
                 </c:pt>
                 <c:pt idx="49" formatCode="0.00E+00">
-                  <c:v>9.3002518029777076E-4</c:v>
+                  <c:v>9.3037755725635133E-4</c:v>
                 </c:pt>
                 <c:pt idx="50" formatCode="0.00E+00">
-                  <c:v>9.3783681015661687E-4</c:v>
+                  <c:v>9.3823018944795273E-4</c:v>
                 </c:pt>
                 <c:pt idx="51" formatCode="0.00E+00">
-                  <c:v>9.4375621874836048E-4</c:v>
+                  <c:v>9.4414049995634845E-4</c:v>
                 </c:pt>
                 <c:pt idx="52" formatCode="0.00E+00">
-                  <c:v>9.4747356867254048E-4</c:v>
+                  <c:v>9.4784331984983853E-4</c:v>
                 </c:pt>
                 <c:pt idx="53" formatCode="0.00E+00">
-                  <c:v>9.4775510137814763E-4</c:v>
+                  <c:v>9.4811884876174954E-4</c:v>
                 </c:pt>
                 <c:pt idx="54" formatCode="0.00E+00">
-                  <c:v>9.4790978711792664E-4</c:v>
+                  <c:v>9.4831161423624246E-4</c:v>
                 </c:pt>
                 <c:pt idx="55" formatCode="0.00E+00">
-                  <c:v>9.4764991973430679E-4</c:v>
+                  <c:v>9.4803119634490583E-4</c:v>
                 </c:pt>
                 <c:pt idx="56" formatCode="0.00E+00">
-                  <c:v>9.4786005006153686E-4</c:v>
+                  <c:v>9.4827063993248566E-4</c:v>
                 </c:pt>
                 <c:pt idx="57" formatCode="0.00E+00">
-                  <c:v>9.4781881606162595E-4</c:v>
+                  <c:v>9.4827494689055081E-4</c:v>
                 </c:pt>
                 <c:pt idx="58" formatCode="0.00E+00">
-                  <c:v>9.4773122293187136E-4</c:v>
+                  <c:v>9.4826912667694905E-4</c:v>
                 </c:pt>
                 <c:pt idx="59" formatCode="0.00E+00">
-                  <c:v>9.4772598132171319E-4</c:v>
+                  <c:v>9.4828018508279254E-4</c:v>
                 </c:pt>
                 <c:pt idx="60" formatCode="0.00E+00">
-                  <c:v>9.4744235197204304E-4</c:v>
+                  <c:v>9.4800710066059429E-4</c:v>
                 </c:pt>
                 <c:pt idx="61" formatCode="0.00E+00">
-                  <c:v>9.4735301163890236E-4</c:v>
+                  <c:v>9.4797951284812155E-4</c:v>
                 </c:pt>
                 <c:pt idx="62" formatCode="0.00E+00">
-                  <c:v>9.4724981015889911E-4</c:v>
+                  <c:v>9.4798172452929027E-4</c:v>
                 </c:pt>
                 <c:pt idx="63" formatCode="0.00E+00">
-                  <c:v>9.4708860152647881E-4</c:v>
+                  <c:v>9.4790908826353931E-4</c:v>
                 </c:pt>
                 <c:pt idx="64" formatCode="0.00E+00">
-                  <c:v>9.4692692697315531E-4</c:v>
+                  <c:v>9.4786857957687037E-4</c:v>
                 </c:pt>
                 <c:pt idx="65" formatCode="0.00E+00">
-                  <c:v>9.4625530199155417E-4</c:v>
+                  <c:v>9.4730960626254984E-4</c:v>
                 </c:pt>
                 <c:pt idx="66" formatCode="0.00E+00">
-                  <c:v>9.4605379120102872E-4</c:v>
+                  <c:v>9.4724546750865753E-4</c:v>
                 </c:pt>
                 <c:pt idx="67" formatCode="0.00E+00">
-                  <c:v>9.4587953678332564E-4</c:v>
+                  <c:v>9.472353403369903E-4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8494,123 +8494,123 @@
         <v>5</v>
       </c>
       <c r="B5" s="4">
-        <v>7.2905101417222013E-4</v>
+        <v>7.5059325437243547E-4</v>
       </c>
       <c r="C5" s="4">
         <f t="shared" si="1"/>
-        <v>7.2905101417222013E-4</v>
+        <v>7.5059325437243547E-4</v>
       </c>
       <c r="D5" s="4">
         <f t="shared" si="0"/>
-        <v>7.2905101417222013E-4</v>
+        <v>7.5059325437243547E-4</v>
       </c>
       <c r="E5" s="4">
         <f t="shared" si="0"/>
-        <v>7.2905101417222013E-4</v>
+        <v>7.5059325437243547E-4</v>
       </c>
       <c r="F5" s="4">
         <f t="shared" si="0"/>
-        <v>7.2905101417222013E-4</v>
+        <v>7.5059325437243547E-4</v>
       </c>
       <c r="G5" s="4">
         <f t="shared" si="0"/>
-        <v>7.2905101417222013E-4</v>
+        <v>7.5059325437243547E-4</v>
       </c>
       <c r="H5" s="4">
         <f t="shared" si="0"/>
-        <v>7.2905101417222013E-4</v>
+        <v>7.5059325437243547E-4</v>
       </c>
       <c r="I5" s="4">
         <f t="shared" si="0"/>
-        <v>7.2905101417222013E-4</v>
+        <v>7.5059325437243547E-4</v>
       </c>
       <c r="J5" s="4">
         <f t="shared" si="0"/>
-        <v>7.2905101417222013E-4</v>
+        <v>7.5059325437243547E-4</v>
       </c>
       <c r="K5" s="4">
         <f t="shared" si="0"/>
-        <v>7.2905101417222013E-4</v>
+        <v>7.5059325437243547E-4</v>
       </c>
       <c r="L5" s="4">
         <f t="shared" si="0"/>
-        <v>7.2905101417222013E-4</v>
+        <v>7.5059325437243547E-4</v>
       </c>
       <c r="M5" s="4">
         <f t="shared" si="0"/>
-        <v>7.2905101417222013E-4</v>
+        <v>7.5059325437243547E-4</v>
       </c>
       <c r="N5" s="4">
         <f t="shared" si="0"/>
-        <v>7.2905101417222013E-4</v>
+        <v>7.5059325437243547E-4</v>
       </c>
       <c r="O5" s="4">
         <f t="shared" si="0"/>
-        <v>7.2905101417222013E-4</v>
+        <v>7.5059325437243547E-4</v>
       </c>
       <c r="P5" s="4">
         <f t="shared" si="0"/>
-        <v>7.2905101417222013E-4</v>
+        <v>7.5059325437243547E-4</v>
       </c>
       <c r="Q5" s="4">
         <f t="shared" si="0"/>
-        <v>7.2905101417222013E-4</v>
+        <v>7.5059325437243547E-4</v>
       </c>
       <c r="R5" s="4">
         <f t="shared" si="0"/>
-        <v>7.2905101417222013E-4</v>
+        <v>7.5059325437243547E-4</v>
       </c>
       <c r="S5" s="4">
         <f t="shared" si="0"/>
-        <v>7.2905101417222013E-4</v>
+        <v>7.5059325437243547E-4</v>
       </c>
       <c r="T5" s="4">
         <f t="shared" si="0"/>
-        <v>7.2905101417222013E-4</v>
+        <v>7.5059325437243547E-4</v>
       </c>
       <c r="U5" s="4">
         <f t="shared" si="0"/>
-        <v>7.2905101417222013E-4</v>
+        <v>7.5059325437243547E-4</v>
       </c>
       <c r="V5" s="4">
         <f t="shared" si="0"/>
-        <v>7.2905101417222013E-4</v>
+        <v>7.5059325437243547E-4</v>
       </c>
       <c r="W5" s="4">
         <f t="shared" si="0"/>
-        <v>7.2905101417222013E-4</v>
+        <v>7.5059325437243547E-4</v>
       </c>
       <c r="X5" s="4">
         <f t="shared" si="0"/>
-        <v>7.2905101417222013E-4</v>
+        <v>7.5059325437243547E-4</v>
       </c>
       <c r="Y5" s="4">
         <f t="shared" si="0"/>
-        <v>7.2905101417222013E-4</v>
+        <v>7.5059325437243547E-4</v>
       </c>
       <c r="Z5" s="4">
         <f t="shared" si="0"/>
-        <v>7.2905101417222013E-4</v>
+        <v>7.5059325437243547E-4</v>
       </c>
       <c r="AA5" s="4">
         <f t="shared" si="0"/>
-        <v>7.2905101417222013E-4</v>
+        <v>7.5059325437243547E-4</v>
       </c>
       <c r="AB5" s="4">
         <f t="shared" si="0"/>
-        <v>7.2905101417222013E-4</v>
+        <v>7.5059325437243547E-4</v>
       </c>
       <c r="AC5" s="4">
         <f t="shared" si="0"/>
-        <v>7.2905101417222013E-4</v>
+        <v>7.5059325437243547E-4</v>
       </c>
       <c r="AD5" s="4">
         <f t="shared" si="0"/>
-        <v>7.2905101417222013E-4</v>
+        <v>7.5059325437243547E-4</v>
       </c>
       <c r="AE5" s="4">
         <f t="shared" si="0"/>
-        <v>7.2905101417222013E-4</v>
+        <v>7.5059325437243547E-4</v>
       </c>
       <c r="AG5" s="4"/>
       <c r="AH5" s="4"/>
@@ -16544,85 +16544,85 @@
         <v>1.0105389360616456E-3</v>
       </c>
       <c r="G10" s="4">
-        <v>1.0071619859986915E-3</v>
+        <v>1.0754660288918199E-3</v>
       </c>
       <c r="H10" s="4">
-        <v>1.0297946332597221E-3</v>
+        <v>1.0997832463414735E-3</v>
       </c>
       <c r="I10" s="4">
-        <v>1.0542694402792506E-3</v>
+        <v>1.1259180725970582E-3</v>
       </c>
       <c r="J10" s="4">
-        <v>1.0790300186124084E-3</v>
+        <v>1.1522254447480843E-3</v>
       </c>
       <c r="K10" s="4">
-        <v>1.1024390235193078E-3</v>
+        <v>1.1772174874709175E-3</v>
       </c>
       <c r="L10" s="4">
-        <v>1.1250162796311157E-3</v>
+        <v>1.2013234498187955E-3</v>
       </c>
       <c r="M10" s="4">
-        <v>1.1437364311026228E-3</v>
+        <v>1.2212854897622565E-3</v>
       </c>
       <c r="N10" s="4">
-        <v>1.1601755544794832E-3</v>
+        <v>1.238809319858962E-3</v>
       </c>
       <c r="O10" s="4">
-        <v>1.1731175422229271E-3</v>
+        <v>1.25258619281297E-3</v>
       </c>
       <c r="P10" s="4">
-        <v>1.1829709958873008E-3</v>
+        <v>1.2631583509478295E-3</v>
       </c>
       <c r="Q10" s="4">
-        <v>1.1904376346468411E-3</v>
+        <v>1.271115521969759E-3</v>
       </c>
       <c r="R10" s="4">
-        <v>1.1951266350083583E-3</v>
+        <v>1.2761007035628495E-3</v>
       </c>
       <c r="S10" s="4">
-        <v>1.1954817554531098E-3</v>
+        <v>1.2764716537304337E-3</v>
       </c>
       <c r="T10" s="4">
-        <v>1.1956768733474535E-3</v>
+        <v>1.2767311778020512E-3</v>
       </c>
       <c r="U10" s="4">
-        <v>1.1953490811620006E-3</v>
+        <v>1.276353645502216E-3</v>
       </c>
       <c r="V10" s="4">
-        <v>1.195614135891968E-3</v>
+        <v>1.2766760132650891E-3</v>
       </c>
       <c r="W10" s="4">
-        <v>1.1955621240436263E-3</v>
+        <v>1.2766818118101673E-3</v>
       </c>
       <c r="X10" s="4">
-        <v>1.1954516355974314E-3</v>
+        <v>1.2766739759384397E-3</v>
       </c>
       <c r="Y10" s="4">
-        <v>1.1954450239217949E-3</v>
+        <v>1.2766888640947222E-3</v>
       </c>
       <c r="Z10" s="4">
-        <v>1.1950872588067892E-3</v>
+        <v>1.2763212049932639E-3</v>
       </c>
       <c r="AA10" s="4">
-        <v>1.1949745664687152E-3</v>
+        <v>1.276284062961275E-3</v>
       </c>
       <c r="AB10" s="4">
-        <v>1.1948443899217356E-3</v>
+        <v>1.2762870405925318E-3</v>
       </c>
       <c r="AC10" s="4">
-        <v>1.1946410441643772E-3</v>
+        <v>1.2761892489133713E-3</v>
       </c>
       <c r="AD10" s="4">
-        <v>1.1944371107025177E-3</v>
+        <v>1.2761347112461472E-3</v>
       </c>
       <c r="AE10" s="4">
-        <v>1.193589934664274E-3</v>
+        <v>1.2753821541254299E-3</v>
       </c>
       <c r="AF10" s="4">
-        <v>1.1933357524675759E-3</v>
+        <v>1.2752958028189919E-3</v>
       </c>
       <c r="AG10" s="4">
-        <v>1.1931159509841881E-3</v>
+        <v>1.2752821684021858E-3</v>
       </c>
       <c r="AH10" s="4"/>
       <c r="AI10" s="4"/>
@@ -16646,88 +16646,88 @@
         <v>7.9651924557390657E-4</v>
       </c>
       <c r="F11" s="4">
-        <v>8.0113596667200321E-4</v>
+        <v>7.5059325437243547E-4</v>
       </c>
       <c r="G11" s="4">
-        <v>7.9845878516365723E-4</v>
+        <v>7.9881884585164282E-4</v>
       </c>
       <c r="H11" s="4">
-        <v>8.1640151561645602E-4</v>
+        <v>8.1688083112650234E-4</v>
       </c>
       <c r="I11" s="4">
-        <v>8.3580467513954908E-4</v>
+        <v>8.3629287314844459E-4</v>
       </c>
       <c r="J11" s="4">
-        <v>8.5543438870170133E-4</v>
+        <v>8.5583307627389927E-4</v>
       </c>
       <c r="K11" s="4">
-        <v>8.7399260066729594E-4</v>
+        <v>8.7439629834414924E-4</v>
       </c>
       <c r="L11" s="4">
-        <v>8.9189141807499185E-4</v>
+        <v>8.923013706603032E-4</v>
       </c>
       <c r="M11" s="4">
-        <v>9.0673239659663221E-4</v>
+        <v>9.0712848121526056E-4</v>
       </c>
       <c r="N11" s="4">
-        <v>9.1976501961370109E-4</v>
+        <v>9.2014457410586974E-4</v>
       </c>
       <c r="O11" s="4">
-        <v>9.3002518029777076E-4</v>
+        <v>9.3037755725635133E-4</v>
       </c>
       <c r="P11" s="4">
-        <v>9.3783681015661687E-4</v>
+        <v>9.3823018944795273E-4</v>
       </c>
       <c r="Q11" s="4">
-        <v>9.4375621874836048E-4</v>
+        <v>9.4414049995634845E-4</v>
       </c>
       <c r="R11" s="4">
-        <v>9.4747356867254048E-4</v>
+        <v>9.4784331984983853E-4</v>
       </c>
       <c r="S11" s="4">
-        <v>9.4775510137814763E-4</v>
+        <v>9.4811884876174954E-4</v>
       </c>
       <c r="T11" s="4">
-        <v>9.4790978711792664E-4</v>
+        <v>9.4831161423624246E-4</v>
       </c>
       <c r="U11" s="4">
-        <v>9.4764991973430679E-4</v>
+        <v>9.4803119634490583E-4</v>
       </c>
       <c r="V11" s="4">
-        <v>9.4786005006153686E-4</v>
+        <v>9.4827063993248566E-4</v>
       </c>
       <c r="W11" s="4">
-        <v>9.4781881606162595E-4</v>
+        <v>9.4827494689055081E-4</v>
       </c>
       <c r="X11" s="4">
-        <v>9.4773122293187136E-4</v>
+        <v>9.4826912667694905E-4</v>
       </c>
       <c r="Y11" s="4">
-        <v>9.4772598132171319E-4</v>
+        <v>9.4828018508279254E-4</v>
       </c>
       <c r="Z11" s="4">
-        <v>9.4744235197204304E-4</v>
+        <v>9.4800710066059429E-4</v>
       </c>
       <c r="AA11" s="4">
-        <v>9.4735301163890236E-4</v>
+        <v>9.4797951284812155E-4</v>
       </c>
       <c r="AB11" s="4">
-        <v>9.4724981015889911E-4</v>
+        <v>9.4798172452929027E-4</v>
       </c>
       <c r="AC11" s="4">
-        <v>9.4708860152647881E-4</v>
+        <v>9.4790908826353931E-4</v>
       </c>
       <c r="AD11" s="4">
-        <v>9.4692692697315531E-4</v>
+        <v>9.4786857957687037E-4</v>
       </c>
       <c r="AE11" s="4">
-        <v>9.4625530199155417E-4</v>
+        <v>9.4730960626254984E-4</v>
       </c>
       <c r="AF11" s="4">
-        <v>9.4605379120102872E-4</v>
+        <v>9.4724546750865753E-4</v>
       </c>
       <c r="AG11" s="4">
-        <v>9.4587953678332564E-4</v>
+        <v>9.472353403369903E-4</v>
       </c>
       <c r="AH11" s="4"/>
       <c r="AI11" s="4"/>
@@ -18694,7 +18694,7 @@
         <v>7.5502679371825096E-4</v>
       </c>
       <c r="E11">
-        <v>7.2905101417222013E-4</v>
+        <v>7.5059325437243547E-4</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -19851,127 +19851,127 @@
       <c r="K4" s="9"/>
       <c r="L4" s="4">
         <f>L5/M5*M4</f>
-        <v>9.8438896867039508E-4</v>
+        <v>1.0506747874471361E-3</v>
       </c>
       <c r="M4" s="4">
         <f t="shared" ref="M4:AI4" si="1">M5/N5*N4</f>
-        <v>9.8438896867039508E-4</v>
+        <v>1.0506747874471361E-3</v>
       </c>
       <c r="N4" s="4">
         <f t="shared" si="1"/>
-        <v>9.8438896867039508E-4</v>
+        <v>1.0506747874471361E-3</v>
       </c>
       <c r="O4" s="4">
         <f t="shared" si="1"/>
-        <v>9.8438896867039508E-4</v>
+        <v>1.0506747874471361E-3</v>
       </c>
       <c r="P4" s="4">
         <f t="shared" si="1"/>
-        <v>9.8438896867039508E-4</v>
+        <v>1.0506747874471361E-3</v>
       </c>
       <c r="Q4" s="4">
         <f t="shared" si="1"/>
-        <v>9.8438896867039508E-4</v>
+        <v>1.0506747874471361E-3</v>
       </c>
       <c r="R4" s="4">
         <f t="shared" si="1"/>
-        <v>9.8438896867039508E-4</v>
+        <v>1.0506747874471361E-3</v>
       </c>
       <c r="S4" s="4">
         <f t="shared" si="1"/>
-        <v>9.8438896867039508E-4</v>
+        <v>1.0506747874471361E-3</v>
       </c>
       <c r="T4" s="4">
         <f t="shared" si="1"/>
-        <v>9.8438896867039508E-4</v>
+        <v>1.0506747874471361E-3</v>
       </c>
       <c r="U4" s="4">
         <f t="shared" si="1"/>
-        <v>9.8438896867039508E-4</v>
+        <v>1.0506747874471361E-3</v>
       </c>
       <c r="V4" s="4">
         <f t="shared" si="1"/>
-        <v>9.8438896867039508E-4</v>
+        <v>1.0506747874471361E-3</v>
       </c>
       <c r="W4" s="4">
         <f t="shared" si="1"/>
-        <v>9.8557760355181558E-4</v>
+        <v>1.0488504305659774E-3</v>
       </c>
       <c r="X4" s="4">
         <f t="shared" si="1"/>
-        <v>9.8676623843323608E-4</v>
+        <v>1.0470260736848186E-3</v>
       </c>
       <c r="Y4" s="4">
         <f t="shared" si="1"/>
-        <v>9.8795487331465657E-4</v>
+        <v>1.04520171680366E-3</v>
       </c>
       <c r="Z4" s="4">
         <f t="shared" si="1"/>
-        <v>9.8914350819607707E-4</v>
+        <v>1.0433773599225014E-3</v>
       </c>
       <c r="AA4" s="4">
         <f t="shared" si="1"/>
-        <v>9.9033214307749757E-4</v>
+        <v>1.0415530030413428E-3</v>
       </c>
       <c r="AB4" s="4">
         <f t="shared" si="1"/>
-        <v>9.9152077795891806E-4</v>
+        <v>1.0397286461601841E-3</v>
       </c>
       <c r="AC4" s="4">
         <f t="shared" si="1"/>
-        <v>9.9270941284033856E-4</v>
+        <v>1.0379042892790255E-3</v>
       </c>
       <c r="AD4" s="4">
         <f t="shared" si="1"/>
-        <v>9.9389804772175906E-4</v>
+        <v>1.0360799323978669E-3</v>
       </c>
       <c r="AE4" s="4">
         <f t="shared" si="1"/>
-        <v>9.9508668260317955E-4</v>
+        <v>1.0342555755167083E-3</v>
       </c>
       <c r="AF4" s="4">
         <f t="shared" si="1"/>
-        <v>9.9627531748460005E-4</v>
+        <v>1.0324312186355497E-3</v>
       </c>
       <c r="AG4" s="4">
         <f>AG5/AH5*AH4</f>
-        <v>9.9746395236602055E-4</v>
+        <v>1.030606861754391E-3</v>
       </c>
       <c r="AH4" s="4">
         <f t="shared" si="1"/>
-        <v>9.9865258724744104E-4</v>
+        <v>1.0287825048732324E-3</v>
       </c>
       <c r="AI4" s="4">
         <f t="shared" si="1"/>
-        <v>9.9984122212886154E-4</v>
+        <v>1.0269581479920738E-3</v>
       </c>
       <c r="AJ4" s="4">
         <f>AJ5/AK5*AK4</f>
-        <v>1.001029857010282E-3</v>
+        <v>1.0251337911109152E-3</v>
       </c>
       <c r="AK4" s="19">
         <f>AK5/AL5*AL4</f>
-        <v>1.0022184918917025E-3</v>
+        <v>1.0233094342297566E-3</v>
       </c>
       <c r="AL4" s="19">
         <f>AL5/AM5*AM4</f>
-        <v>1.003407126773123E-3</v>
+        <v>1.0214850773485979E-3</v>
       </c>
       <c r="AM4" s="19">
         <f>AM5/AN5*AN4</f>
-        <v>1.0045957616545435E-3</v>
+        <v>1.0196607204674393E-3</v>
       </c>
       <c r="AN4" s="19">
         <f t="shared" ref="AN4:AQ4" si="2">AN5/AO5*AO4</f>
-        <v>1.005784396535964E-3</v>
+        <v>1.0178363635862807E-3</v>
       </c>
       <c r="AO4" s="19">
         <f t="shared" si="2"/>
-        <v>1.0069730314173845E-3</v>
+        <v>1.0160120067051221E-3</v>
       </c>
       <c r="AP4" s="19">
         <f t="shared" si="2"/>
-        <v>1.008161666298805E-3</v>
+        <v>1.0141876498239635E-3</v>
       </c>
       <c r="AQ4" s="19">
         <f t="shared" si="2"/>
@@ -19979,111 +19979,111 @@
       </c>
       <c r="AR4" s="10">
         <f>BNVFE!G10</f>
-        <v>1.0071619859986915E-3</v>
+        <v>1.0754660288918199E-3</v>
       </c>
       <c r="AS4" s="10">
         <f>BNVFE!H10</f>
-        <v>1.0297946332597221E-3</v>
+        <v>1.0997832463414735E-3</v>
       </c>
       <c r="AT4" s="10">
         <f>BNVFE!I10</f>
-        <v>1.0542694402792506E-3</v>
+        <v>1.1259180725970582E-3</v>
       </c>
       <c r="AU4" s="10">
         <f>BNVFE!J10</f>
-        <v>1.0790300186124084E-3</v>
+        <v>1.1522254447480843E-3</v>
       </c>
       <c r="AV4" s="10">
         <f>BNVFE!K10</f>
-        <v>1.1024390235193078E-3</v>
+        <v>1.1772174874709175E-3</v>
       </c>
       <c r="AW4" s="10">
         <f>BNVFE!L10</f>
-        <v>1.1250162796311157E-3</v>
+        <v>1.2013234498187955E-3</v>
       </c>
       <c r="AX4" s="10">
         <f>BNVFE!M10</f>
-        <v>1.1437364311026228E-3</v>
+        <v>1.2212854897622565E-3</v>
       </c>
       <c r="AY4" s="10">
         <f>BNVFE!N10</f>
-        <v>1.1601755544794832E-3</v>
+        <v>1.238809319858962E-3</v>
       </c>
       <c r="AZ4" s="10">
         <f>BNVFE!O10</f>
-        <v>1.1731175422229271E-3</v>
+        <v>1.25258619281297E-3</v>
       </c>
       <c r="BA4" s="10">
         <f>BNVFE!P10</f>
-        <v>1.1829709958873008E-3</v>
+        <v>1.2631583509478295E-3</v>
       </c>
       <c r="BB4" s="10">
         <f>BNVFE!Q10</f>
-        <v>1.1904376346468411E-3</v>
+        <v>1.271115521969759E-3</v>
       </c>
       <c r="BC4" s="10">
         <f>BNVFE!R10</f>
-        <v>1.1951266350083583E-3</v>
+        <v>1.2761007035628495E-3</v>
       </c>
       <c r="BD4" s="10">
         <f>BNVFE!S10</f>
-        <v>1.1954817554531098E-3</v>
+        <v>1.2764716537304337E-3</v>
       </c>
       <c r="BE4" s="10">
         <f>BNVFE!T10</f>
-        <v>1.1956768733474535E-3</v>
+        <v>1.2767311778020512E-3</v>
       </c>
       <c r="BF4" s="10">
         <f>BNVFE!U10</f>
-        <v>1.1953490811620006E-3</v>
+        <v>1.276353645502216E-3</v>
       </c>
       <c r="BG4" s="10">
         <f>BNVFE!V10</f>
-        <v>1.195614135891968E-3</v>
+        <v>1.2766760132650891E-3</v>
       </c>
       <c r="BH4" s="10">
         <f>BNVFE!W10</f>
-        <v>1.1955621240436263E-3</v>
+        <v>1.2766818118101673E-3</v>
       </c>
       <c r="BI4" s="10">
         <f>BNVFE!X10</f>
-        <v>1.1954516355974314E-3</v>
+        <v>1.2766739759384397E-3</v>
       </c>
       <c r="BJ4" s="10">
         <f>BNVFE!Y10</f>
-        <v>1.1954450239217949E-3</v>
+        <v>1.2766888640947222E-3</v>
       </c>
       <c r="BK4" s="10">
         <f>BNVFE!Z10</f>
-        <v>1.1950872588067892E-3</v>
+        <v>1.2763212049932639E-3</v>
       </c>
       <c r="BL4" s="10">
         <f>BNVFE!AA10</f>
-        <v>1.1949745664687152E-3</v>
+        <v>1.276284062961275E-3</v>
       </c>
       <c r="BM4" s="10">
         <f>BNVFE!AB10</f>
-        <v>1.1948443899217356E-3</v>
+        <v>1.2762870405925318E-3</v>
       </c>
       <c r="BN4" s="10">
         <f>BNVFE!AC10</f>
-        <v>1.1946410441643772E-3</v>
+        <v>1.2761892489133713E-3</v>
       </c>
       <c r="BO4" s="10">
         <f>BNVFE!AD10</f>
-        <v>1.1944371107025177E-3</v>
+        <v>1.2761347112461472E-3</v>
       </c>
       <c r="BP4" s="10">
         <f>BNVFE!AE10</f>
-        <v>1.193589934664274E-3</v>
+        <v>1.2753821541254299E-3</v>
       </c>
       <c r="BQ4" s="10">
         <f>BNVFE!AF10</f>
-        <v>1.1933357524675759E-3</v>
+        <v>1.2752958028189919E-3</v>
       </c>
       <c r="BR4" s="10">
         <f>BNVFE!AG10</f>
-        <v>1.1931159509841881E-3</v>
+        <v>1.2752821684021858E-3</v>
       </c>
       <c r="BS4" s="10"/>
       <c r="BT4" s="4"/>
@@ -20150,195 +20150,195 @@
       </c>
       <c r="W5" s="4">
         <f>($AQ$5-$V$5)/COUNT($V$1:$AQ$1)+V5</f>
-        <v>7.8134709903309753E-4</v>
+        <v>7.7904970301948082E-4</v>
       </c>
       <c r="X5" s="4">
         <f t="shared" ref="X5:AN5" si="4">($AQ$5-$V$5)/COUNT($V$1:$AQ$1)+W5</f>
-        <v>7.8228942606352163E-4</v>
+        <v>7.7769463403628821E-4</v>
       </c>
       <c r="Y5" s="4">
         <f t="shared" si="4"/>
-        <v>7.8323175309394572E-4</v>
+        <v>7.7633956505309559E-4</v>
       </c>
       <c r="Z5" s="4">
         <f t="shared" si="4"/>
-        <v>7.8417408012436982E-4</v>
+        <v>7.7498449606990298E-4</v>
       </c>
       <c r="AA5" s="4">
         <f t="shared" si="4"/>
-        <v>7.8511640715479391E-4</v>
+        <v>7.7362942708671036E-4</v>
       </c>
       <c r="AB5" s="4">
         <f t="shared" si="4"/>
-        <v>7.8605873418521801E-4</v>
+        <v>7.7227435810351774E-4</v>
       </c>
       <c r="AC5" s="4">
         <f t="shared" si="4"/>
-        <v>7.870010612156421E-4</v>
+        <v>7.7091928912032513E-4</v>
       </c>
       <c r="AD5" s="4">
         <f t="shared" si="4"/>
-        <v>7.879433882460662E-4</v>
+        <v>7.6956422013713251E-4</v>
       </c>
       <c r="AE5" s="4">
         <f t="shared" si="4"/>
-        <v>7.8888571527649029E-4</v>
+        <v>7.682091511539399E-4</v>
       </c>
       <c r="AF5" s="4">
         <f t="shared" si="4"/>
-        <v>7.8982804230691439E-4</v>
+        <v>7.6685408217074728E-4</v>
       </c>
       <c r="AG5" s="4">
         <f t="shared" si="4"/>
-        <v>7.9077036933733848E-4</v>
+        <v>7.6549901318755467E-4</v>
       </c>
       <c r="AH5" s="4">
         <f t="shared" si="4"/>
-        <v>7.9171269636776258E-4</v>
+        <v>7.6414394420436205E-4</v>
       </c>
       <c r="AI5" s="4">
         <f t="shared" si="4"/>
-        <v>7.9265502339818667E-4</v>
+        <v>7.6278887522116944E-4</v>
       </c>
       <c r="AJ5" s="4">
         <f t="shared" si="4"/>
-        <v>7.9359735042861077E-4</v>
+        <v>7.6143380623797682E-4</v>
       </c>
       <c r="AK5" s="4">
         <f t="shared" si="4"/>
-        <v>7.9453967745903486E-4</v>
+        <v>7.6007873725478421E-4</v>
       </c>
       <c r="AL5" s="4">
         <f t="shared" si="4"/>
-        <v>7.9548200448945896E-4</v>
+        <v>7.5872366827159159E-4</v>
       </c>
       <c r="AM5" s="4">
         <f t="shared" si="4"/>
-        <v>7.9642433151988306E-4</v>
+        <v>7.5736859928839898E-4</v>
       </c>
       <c r="AN5" s="4">
         <f t="shared" si="4"/>
-        <v>7.9736665855030715E-4</v>
+        <v>7.5601353030520636E-4</v>
       </c>
       <c r="AO5" s="4">
         <f>($AQ$5-$V$5)/COUNT($V$1:$AQ$1)+AN5</f>
-        <v>7.9830898558073125E-4</v>
+        <v>7.5465846132201375E-4</v>
       </c>
       <c r="AP5" s="4">
         <f>($AQ$5-$V$5)/COUNT($V$1:$AQ$1)+AO5</f>
-        <v>7.9925131261115534E-4</v>
+        <v>7.5330339233882113E-4</v>
       </c>
       <c r="AQ5" s="28">
         <f>BNVFE!F11</f>
-        <v>8.0113596667200321E-4</v>
+        <v>7.5059325437243547E-4</v>
       </c>
       <c r="AR5" s="10">
         <f>BNVFE!G11</f>
-        <v>7.9845878516365723E-4</v>
+        <v>7.9881884585164282E-4</v>
       </c>
       <c r="AS5" s="10">
         <f>BNVFE!H11</f>
-        <v>8.1640151561645602E-4</v>
+        <v>8.1688083112650234E-4</v>
       </c>
       <c r="AT5" s="10">
         <f>BNVFE!I11</f>
-        <v>8.3580467513954908E-4</v>
+        <v>8.3629287314844459E-4</v>
       </c>
       <c r="AU5" s="10">
         <f>BNVFE!J11</f>
-        <v>8.5543438870170133E-4</v>
+        <v>8.5583307627389927E-4</v>
       </c>
       <c r="AV5" s="10">
         <f>BNVFE!K11</f>
-        <v>8.7399260066729594E-4</v>
+        <v>8.7439629834414924E-4</v>
       </c>
       <c r="AW5" s="10">
         <f>BNVFE!L11</f>
-        <v>8.9189141807499185E-4</v>
+        <v>8.923013706603032E-4</v>
       </c>
       <c r="AX5" s="10">
         <f>BNVFE!M11</f>
-        <v>9.0673239659663221E-4</v>
+        <v>9.0712848121526056E-4</v>
       </c>
       <c r="AY5" s="10">
         <f>BNVFE!N11</f>
-        <v>9.1976501961370109E-4</v>
+        <v>9.2014457410586974E-4</v>
       </c>
       <c r="AZ5" s="10">
         <f>BNVFE!O11</f>
-        <v>9.3002518029777076E-4</v>
+        <v>9.3037755725635133E-4</v>
       </c>
       <c r="BA5" s="10">
         <f>BNVFE!P11</f>
-        <v>9.3783681015661687E-4</v>
+        <v>9.3823018944795273E-4</v>
       </c>
       <c r="BB5" s="10">
         <f>BNVFE!Q11</f>
-        <v>9.4375621874836048E-4</v>
+        <v>9.4414049995634845E-4</v>
       </c>
       <c r="BC5" s="10">
         <f>BNVFE!R11</f>
-        <v>9.4747356867254048E-4</v>
+        <v>9.4784331984983853E-4</v>
       </c>
       <c r="BD5" s="10">
         <f>BNVFE!S11</f>
-        <v>9.4775510137814763E-4</v>
+        <v>9.4811884876174954E-4</v>
       </c>
       <c r="BE5" s="10">
         <f>BNVFE!T11</f>
-        <v>9.4790978711792664E-4</v>
+        <v>9.4831161423624246E-4</v>
       </c>
       <c r="BF5" s="10">
         <f>BNVFE!U11</f>
-        <v>9.4764991973430679E-4</v>
+        <v>9.4803119634490583E-4</v>
       </c>
       <c r="BG5" s="10">
         <f>BNVFE!V11</f>
-        <v>9.4786005006153686E-4</v>
+        <v>9.4827063993248566E-4</v>
       </c>
       <c r="BH5" s="10">
         <f>BNVFE!W11</f>
-        <v>9.4781881606162595E-4</v>
+        <v>9.4827494689055081E-4</v>
       </c>
       <c r="BI5" s="10">
         <f>BNVFE!X11</f>
-        <v>9.4773122293187136E-4</v>
+        <v>9.4826912667694905E-4</v>
       </c>
       <c r="BJ5" s="10">
         <f>BNVFE!Y11</f>
-        <v>9.4772598132171319E-4</v>
+        <v>9.4828018508279254E-4</v>
       </c>
       <c r="BK5" s="10">
         <f>BNVFE!Z11</f>
-        <v>9.4744235197204304E-4</v>
+        <v>9.4800710066059429E-4</v>
       </c>
       <c r="BL5" s="10">
         <f>BNVFE!AA11</f>
-        <v>9.4735301163890236E-4</v>
+        <v>9.4797951284812155E-4</v>
       </c>
       <c r="BM5" s="10">
         <f>BNVFE!AB11</f>
-        <v>9.4724981015889911E-4</v>
+        <v>9.4798172452929027E-4</v>
       </c>
       <c r="BN5" s="10">
         <f>BNVFE!AC11</f>
-        <v>9.4708860152647881E-4</v>
+        <v>9.4790908826353931E-4</v>
       </c>
       <c r="BO5" s="10">
         <f>BNVFE!AD11</f>
-        <v>9.4692692697315531E-4</v>
+        <v>9.4786857957687037E-4</v>
       </c>
       <c r="BP5" s="10">
         <f>BNVFE!AE11</f>
-        <v>9.4625530199155417E-4</v>
+        <v>9.4730960626254984E-4</v>
       </c>
       <c r="BQ5" s="10">
         <f>BNVFE!AF11</f>
-        <v>9.4605379120102872E-4</v>
+        <v>9.4724546750865753E-4</v>
       </c>
       <c r="BR5" s="10">
         <f>BNVFE!AG11</f>
-        <v>9.4587953678332564E-4</v>
+        <v>9.472353403369903E-4</v>
       </c>
       <c r="BS5" s="10"/>
       <c r="BT5" s="4"/>

--- a/InputData/trans/BHNVFEAL/BAU Historical New Veh Fuel Economy After Lifetime.xlsx
+++ b/InputData/trans/BHNVFEAL/BAU Historical New Veh Fuel Economy After Lifetime.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OliviaAshmoore\Documents\Github Repos\eps-us\InputData\trans\BHNVFEAL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55F9D748-9F01-4D38-BD4B-76B16C273F67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F78C7657-5FEF-479C-AB5D-811D6ABB0F6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -1290,7 +1290,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1324,16 +1324,14 @@
     <xf numFmtId="11" fontId="41" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="154" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="28" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="11" fontId="0" fillId="28" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="11" fontId="0" fillId="30" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="11" fontId="41" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="11" fontId="43" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="11" fontId="0" fillId="29" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="11" fontId="0" fillId="28" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="11" fontId="0" fillId="30" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="11" fontId="41" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="11" fontId="43" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="11" fontId="0" fillId="29" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="155" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="11" fontId="0" fillId="30" borderId="19" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
@@ -3233,136 +3231,136 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="70"/>
                 <c:pt idx="24" formatCode="0.00E+00">
-                  <c:v>6.1792415736698723E-5</c:v>
+                  <c:v>5.9551063413003282E-5</c:v>
                 </c:pt>
                 <c:pt idx="25" formatCode="0.00E+00">
-                  <c:v>6.3169682072834916E-5</c:v>
+                  <c:v>6.0878373147410427E-5</c:v>
                 </c:pt>
                 <c:pt idx="26" formatCode="0.00E+00">
-                  <c:v>6.454694840897111E-5</c:v>
+                  <c:v>6.2205682881817138E-5</c:v>
                 </c:pt>
                 <c:pt idx="27" formatCode="0.00E+00">
-                  <c:v>6.5924214745107304E-5</c:v>
+                  <c:v>6.3532992616224283E-5</c:v>
                 </c:pt>
                 <c:pt idx="28" formatCode="0.00E+00">
-                  <c:v>6.7301481081243498E-5</c:v>
+                  <c:v>6.4860302350631428E-5</c:v>
                 </c:pt>
                 <c:pt idx="29" formatCode="0.00E+00">
-                  <c:v>6.8678747417379692E-5</c:v>
+                  <c:v>6.618761208503814E-5</c:v>
                 </c:pt>
                 <c:pt idx="30" formatCode="0.00E+00">
-                  <c:v>7.0056013753515885E-5</c:v>
+                  <c:v>6.7514921819445285E-5</c:v>
                 </c:pt>
                 <c:pt idx="31" formatCode="0.00E+00">
-                  <c:v>7.1433280089651646E-5</c:v>
+                  <c:v>6.8842231553851996E-5</c:v>
                 </c:pt>
                 <c:pt idx="32" formatCode="0.00E+00">
-                  <c:v>7.2810546425787839E-5</c:v>
+                  <c:v>7.0169541288259141E-5</c:v>
                 </c:pt>
                 <c:pt idx="33" formatCode="0.00E+00">
-                  <c:v>7.4187812761924033E-5</c:v>
+                  <c:v>7.1496851022665852E-5</c:v>
                 </c:pt>
                 <c:pt idx="34" formatCode="0.00E+00">
-                  <c:v>7.5565079098060227E-5</c:v>
+                  <c:v>7.2824160757072997E-5</c:v>
                 </c:pt>
                 <c:pt idx="35" formatCode="0.00E+00">
-                  <c:v>7.6942345434196421E-5</c:v>
+                  <c:v>7.4151470491480142E-5</c:v>
                 </c:pt>
                 <c:pt idx="36" formatCode="0.00E+00">
-                  <c:v>7.8319611770332614E-5</c:v>
+                  <c:v>7.5478780225886853E-5</c:v>
                 </c:pt>
                 <c:pt idx="37" formatCode="0.00E+00">
-                  <c:v>7.9696878106468808E-5</c:v>
+                  <c:v>7.6806089960293998E-5</c:v>
                 </c:pt>
                 <c:pt idx="38" formatCode="0.00E+00">
-                  <c:v>8.1074144442605002E-5</c:v>
+                  <c:v>7.8133399694700709E-5</c:v>
                 </c:pt>
                 <c:pt idx="39" formatCode="0.00E+00">
-                  <c:v>8.2778348635091648E-5</c:v>
+                  <c:v>7.977578850124848E-5</c:v>
                 </c:pt>
                 <c:pt idx="40" formatCode="0.00E+00">
-                  <c:v>8.401549874707771E-5</c:v>
+                  <c:v>8.0968064347595233E-5</c:v>
                 </c:pt>
                 <c:pt idx="41" formatCode="0.00E+00">
-                  <c:v>8.4385989241553405E-5</c:v>
+                  <c:v>8.132511630401103E-5</c:v>
                 </c:pt>
                 <c:pt idx="42" formatCode="0.00E+00">
-                  <c:v>8.7328683714801736E-5</c:v>
+                  <c:v>8.4161072514692597E-5</c:v>
                 </c:pt>
                 <c:pt idx="43" formatCode="0.00E+00">
-                  <c:v>8.8182104367561648E-5</c:v>
+                  <c:v>8.498353764742068E-5</c:v>
                 </c:pt>
                 <c:pt idx="44" formatCode="0.00E+00">
-                  <c:v>8.9003772864754401E-5</c:v>
+                  <c:v>8.5775402347925225E-5</c:v>
                 </c:pt>
                 <c:pt idx="45" formatCode="0.00E+00">
-                  <c:v>8.9734195226507302E-5</c:v>
+                  <c:v>8.6479330619128737E-5</c:v>
                 </c:pt>
                 <c:pt idx="46" formatCode="0.00E+00">
-                  <c:v>9.0462120095479015E-5</c:v>
+                  <c:v>8.7180851987329484E-5</c:v>
                 </c:pt>
                 <c:pt idx="47" formatCode="0.00E+00">
-                  <c:v>9.0976244401538644E-5</c:v>
+                  <c:v>8.7676327828293231E-5</c:v>
                 </c:pt>
                 <c:pt idx="48" formatCode="0.00E+00">
-                  <c:v>9.1398310016686457E-5</c:v>
+                  <c:v>8.808308415773043E-5</c:v>
                 </c:pt>
                 <c:pt idx="49" formatCode="0.00E+00">
-                  <c:v>9.1772134453993215E-5</c:v>
+                  <c:v>8.8443349127241298E-5</c:v>
                 </c:pt>
                 <c:pt idx="50" formatCode="0.00E+00">
-                  <c:v>9.2116170982308495E-5</c:v>
+                  <c:v>8.877490666338608E-5</c:v>
                 </c:pt>
                 <c:pt idx="51" formatCode="0.00E+00">
-                  <c:v>9.2387908899653262E-5</c:v>
+                  <c:v>8.9036788024627383E-5</c:v>
                 </c:pt>
                 <c:pt idx="52" formatCode="0.00E+00">
-                  <c:v>9.2774067997207965E-5</c:v>
+                  <c:v>8.9408940248032558E-5</c:v>
                 </c:pt>
                 <c:pt idx="53" formatCode="0.00E+00">
-                  <c:v>9.3103239258822098E-5</c:v>
+                  <c:v>8.9726171714716883E-5</c:v>
                 </c:pt>
                 <c:pt idx="54" formatCode="0.00E+00">
-                  <c:v>9.3380550032913344E-5</c:v>
+                  <c:v>8.9993423792437643E-5</c:v>
                 </c:pt>
                 <c:pt idx="55" formatCode="0.00E+00">
-                  <c:v>9.3568760633689615E-5</c:v>
+                  <c:v>9.0174807564025167E-5</c:v>
                 </c:pt>
                 <c:pt idx="56" formatCode="0.00E+00">
-                  <c:v>9.378410942377925E-5</c:v>
+                  <c:v>9.038234516069701E-5</c:v>
                 </c:pt>
                 <c:pt idx="57" formatCode="0.00E+00">
-                  <c:v>9.4376700451576006E-5</c:v>
+                  <c:v>9.0953441555838329E-5</c:v>
                 </c:pt>
                 <c:pt idx="58" formatCode="0.00E+00">
-                  <c:v>9.5219008221142745E-5</c:v>
+                  <c:v>9.1765196895077241E-5</c:v>
                 </c:pt>
                 <c:pt idx="59" formatCode="0.00E+00">
-                  <c:v>9.6097486024325845E-5</c:v>
+                  <c:v>9.2611810298042204E-5</c:v>
                 </c:pt>
                 <c:pt idx="60" formatCode="0.00E+00">
-                  <c:v>9.717217467407689E-5</c:v>
+                  <c:v>9.3647517531163859E-5</c:v>
                 </c:pt>
                 <c:pt idx="61" formatCode="0.00E+00">
-                  <c:v>9.862744958918793E-5</c:v>
+                  <c:v>9.5050006294872494E-5</c:v>
                 </c:pt>
                 <c:pt idx="62" formatCode="0.00E+00">
-                  <c:v>1.0008701258438573E-4</c:v>
+                  <c:v>9.645662760019035E-5</c:v>
                 </c:pt>
                 <c:pt idx="63" formatCode="0.00E+00">
-                  <c:v>1.0105262413170669E-4</c:v>
+                  <c:v>9.7387214206997634E-5</c:v>
                 </c:pt>
                 <c:pt idx="64" formatCode="0.00E+00">
-                  <c:v>1.019716253546731E-4</c:v>
+                  <c:v>9.8272881152577143E-5</c:v>
                 </c:pt>
                 <c:pt idx="65" formatCode="0.00E+00">
-                  <c:v>1.0305329034341948E-4</c:v>
+                  <c:v>9.9315311676914197E-5</c:v>
                 </c:pt>
                 <c:pt idx="66" formatCode="0.00E+00">
-                  <c:v>1.040015126571646E-4</c:v>
+                  <c:v>1.0022913979744075E-4</c:v>
                 </c:pt>
                 <c:pt idx="67" formatCode="0.00E+00">
-                  <c:v>1.0491854588113829E-4</c:v>
+                  <c:v>1.0111291012785455E-4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16439,88 +16437,88 @@
         <v>1.0877081887028839E-4</v>
       </c>
       <c r="F9" s="4">
-        <v>9.8677853294881047E-5</v>
+        <v>9.5098581742816967E-5</v>
       </c>
       <c r="G9" s="4">
-        <v>8.4385989241553405E-5</v>
+        <v>8.132511630401103E-5</v>
       </c>
       <c r="H9" s="4">
-        <v>8.7328683714801736E-5</v>
+        <v>8.4161072514692597E-5</v>
       </c>
       <c r="I9" s="4">
-        <v>8.8182104367561648E-5</v>
+        <v>8.498353764742068E-5</v>
       </c>
       <c r="J9" s="4">
-        <v>8.9003772864754401E-5</v>
+        <v>8.5775402347925225E-5</v>
       </c>
       <c r="K9" s="4">
-        <v>8.9734195226507302E-5</v>
+        <v>8.6479330619128737E-5</v>
       </c>
       <c r="L9" s="4">
-        <v>9.0462120095479015E-5</v>
+        <v>8.7180851987329484E-5</v>
       </c>
       <c r="M9" s="4">
-        <v>9.0976244401538644E-5</v>
+        <v>8.7676327828293231E-5</v>
       </c>
       <c r="N9" s="4">
-        <v>9.1398310016686457E-5</v>
+        <v>8.808308415773043E-5</v>
       </c>
       <c r="O9" s="4">
-        <v>9.1772134453993215E-5</v>
+        <v>8.8443349127241298E-5</v>
       </c>
       <c r="P9" s="4">
-        <v>9.2116170982308495E-5</v>
+        <v>8.877490666338608E-5</v>
       </c>
       <c r="Q9" s="4">
-        <v>9.2387908899653262E-5</v>
+        <v>8.9036788024627383E-5</v>
       </c>
       <c r="R9" s="4">
-        <v>9.2774067997207965E-5</v>
+        <v>8.9408940248032558E-5</v>
       </c>
       <c r="S9" s="4">
-        <v>9.3103239258822098E-5</v>
+        <v>8.9726171714716883E-5</v>
       </c>
       <c r="T9" s="4">
-        <v>9.3380550032913344E-5</v>
+        <v>8.9993423792437643E-5</v>
       </c>
       <c r="U9" s="4">
-        <v>9.3568760633689615E-5</v>
+        <v>9.0174807564025167E-5</v>
       </c>
       <c r="V9" s="4">
-        <v>9.378410942377925E-5</v>
+        <v>9.038234516069701E-5</v>
       </c>
       <c r="W9" s="4">
-        <v>9.4376700451576006E-5</v>
+        <v>9.0953441555838329E-5</v>
       </c>
       <c r="X9" s="4">
-        <v>9.5219008221142745E-5</v>
+        <v>9.1765196895077241E-5</v>
       </c>
       <c r="Y9" s="4">
-        <v>9.6097486024325845E-5</v>
+        <v>9.2611810298042204E-5</v>
       </c>
       <c r="Z9" s="4">
-        <v>9.717217467407689E-5</v>
+        <v>9.3647517531163859E-5</v>
       </c>
       <c r="AA9" s="4">
-        <v>9.862744958918793E-5</v>
+        <v>9.5050006294872494E-5</v>
       </c>
       <c r="AB9" s="4">
-        <v>1.0008701258438573E-4</v>
+        <v>9.645662760019035E-5</v>
       </c>
       <c r="AC9" s="4">
-        <v>1.0105262413170669E-4</v>
+        <v>9.7387214206997634E-5</v>
       </c>
       <c r="AD9" s="4">
-        <v>1.019716253546731E-4</v>
+        <v>9.8272881152577143E-5</v>
       </c>
       <c r="AE9" s="4">
-        <v>1.0305329034341948E-4</v>
+        <v>9.9315311676914197E-5</v>
       </c>
       <c r="AF9" s="4">
-        <v>1.040015126571646E-4</v>
+        <v>1.0022913979744075E-4</v>
       </c>
       <c r="AG9" s="4">
-        <v>1.0491854588113829E-4</v>
+        <v>1.0111291012785455E-4</v>
       </c>
       <c r="AH9" s="4"/>
       <c r="AI9" s="4"/>
@@ -16970,82 +16968,82 @@
         <v>5.0586266198922429E-5</v>
       </c>
       <c r="H14" s="4">
-        <v>5.9008108521891101E-5</v>
+        <v>5.1607763219151746E-5</v>
       </c>
       <c r="I14" s="4">
-        <v>6.1391229932253842E-5</v>
+        <v>5.2629260239381077E-5</v>
       </c>
       <c r="J14" s="4">
-        <v>6.3358431517704082E-5</v>
+        <v>5.4315695977812021E-5</v>
       </c>
       <c r="K14" s="4">
-        <v>6.488779147306446E-5</v>
+        <v>5.5626780365259058E-5</v>
       </c>
       <c r="L14" s="4">
-        <v>6.6328375647705154E-5</v>
+        <v>5.6861759359938993E-5</v>
       </c>
       <c r="M14" s="4">
-        <v>6.756656649836941E-5</v>
+        <v>5.7923231309231095E-5</v>
       </c>
       <c r="N14" s="4">
-        <v>6.8609689959241168E-5</v>
+        <v>5.8817476564532313E-5</v>
       </c>
       <c r="O14" s="4">
-        <v>6.9419445240348951E-5</v>
+        <v>5.9511660757725099E-5</v>
       </c>
       <c r="P14" s="4">
-        <v>7.0144135628077763E-5</v>
+        <v>6.0132920814753527E-5</v>
       </c>
       <c r="Q14" s="4">
-        <v>7.0623288245918797E-5</v>
+        <v>6.0543687105745991E-5</v>
       </c>
       <c r="R14" s="4">
-        <v>7.0801776457853202E-5</v>
+        <v>6.0696700859761384E-5</v>
       </c>
       <c r="S14" s="4">
-        <v>7.0778037136288625E-5</v>
+        <v>6.0676349696673325E-5</v>
       </c>
       <c r="T14" s="4">
-        <v>7.0748705797475485E-5</v>
+        <v>6.0651204628472715E-5</v>
       </c>
       <c r="U14" s="4">
-        <v>7.0726353704682243E-5</v>
+        <v>6.0632042704044597E-5</v>
       </c>
       <c r="V14" s="4">
-        <v>7.0706615640061361E-5</v>
+        <v>6.0615121724603387E-5</v>
       </c>
       <c r="W14" s="4">
-        <v>7.0695414825729539E-5</v>
+        <v>6.0605519529419925E-5</v>
       </c>
       <c r="X14" s="4">
-        <v>7.0671296238756034E-5</v>
+        <v>6.0584843231000183E-5</v>
       </c>
       <c r="Y14" s="4">
-        <v>7.0642361684336187E-5</v>
+        <v>6.0560038316745274E-5</v>
       </c>
       <c r="Z14" s="4">
-        <v>7.0618107772838526E-5</v>
+        <v>6.053924600778776E-5</v>
       </c>
       <c r="AA14" s="4">
-        <v>7.0596573813316591E-5</v>
+        <v>6.0520785449807174E-5</v>
       </c>
       <c r="AB14" s="4">
-        <v>7.0576119485169544E-5</v>
+        <v>6.0503250434459527E-5</v>
       </c>
       <c r="AC14" s="4">
-        <v>7.0550880378554285E-5</v>
+        <v>6.0481613540855517E-5</v>
       </c>
       <c r="AD14" s="4">
-        <v>7.0516654796407729E-5</v>
+        <v>6.0452272752739302E-5</v>
       </c>
       <c r="AE14" s="4">
-        <v>7.048110343340414E-5</v>
+        <v>6.0421795403817555E-5</v>
       </c>
       <c r="AF14" s="4">
-        <v>7.0445083651791488E-5</v>
+        <v>6.0390916490618554E-5</v>
       </c>
       <c r="AG14" s="4">
-        <v>7.0419929962861605E-5</v>
+        <v>6.0369352823591006E-5</v>
       </c>
       <c r="AH14" s="4"/>
       <c r="AI14" s="4"/>
@@ -17075,82 +17073,82 @@
         <v>6.7428486606874269E-4</v>
       </c>
       <c r="H15" s="4">
-        <v>7.8654301930868205E-4</v>
+        <v>6.8790081429402638E-4</v>
       </c>
       <c r="I15" s="4">
-        <v>8.1830861146946936E-4</v>
+        <v>7.0151676251931018E-4</v>
       </c>
       <c r="J15" s="4">
-        <v>8.4453023953665008E-4</v>
+        <v>7.2399594869901036E-4</v>
       </c>
       <c r="K15" s="4">
-        <v>8.6491569887488121E-4</v>
+        <v>7.4147192443357402E-4</v>
       </c>
       <c r="L15" s="4">
-        <v>8.8411782981371386E-4</v>
+        <v>7.5793346051039969E-4</v>
       </c>
       <c r="M15" s="4">
-        <v>9.0062217802207149E-4</v>
+        <v>7.7208225078382372E-4</v>
       </c>
       <c r="N15" s="4">
-        <v>9.1452639384897636E-4</v>
+        <v>7.8400200860568551E-4</v>
       </c>
       <c r="O15" s="4">
-        <v>9.2531995052546907E-4</v>
+        <v>7.9325507136175839E-4</v>
       </c>
       <c r="P15" s="4">
-        <v>9.3497964272551198E-4</v>
+        <v>8.0153609872005344E-4</v>
       </c>
       <c r="Q15" s="4">
-        <v>9.4136646237092628E-4</v>
+        <v>8.0701136926914386E-4</v>
       </c>
       <c r="R15" s="4">
-        <v>9.437456041641902E-4</v>
+        <v>8.0905095167728652E-4</v>
       </c>
       <c r="S15" s="4">
-        <v>9.4342917311551809E-4</v>
+        <v>8.0877968276759445E-4</v>
       </c>
       <c r="T15" s="4">
-        <v>9.4303820380014179E-4</v>
+        <v>8.0844451395166992E-4</v>
       </c>
       <c r="U15" s="4">
-        <v>9.4274026368659043E-4</v>
+        <v>8.0818909688657511E-4</v>
       </c>
       <c r="V15" s="4">
-        <v>9.4247716701511414E-4</v>
+        <v>8.0796355028640886E-4</v>
       </c>
       <c r="W15" s="4">
-        <v>9.4232786681648141E-4</v>
+        <v>8.0783555873099769E-4</v>
       </c>
       <c r="X15" s="4">
-        <v>9.4200638038529781E-4</v>
+        <v>8.0755995596055552E-4</v>
       </c>
       <c r="Y15" s="4">
-        <v>9.4162069997008341E-4</v>
+        <v>8.0722932119458072E-4</v>
       </c>
       <c r="Z15" s="4">
-        <v>9.4129740974341325E-4</v>
+        <v>8.0695217207261245E-4</v>
       </c>
       <c r="AA15" s="4">
-        <v>9.4101037486016888E-4</v>
+        <v>8.067061038054559E-4</v>
       </c>
       <c r="AB15" s="4">
-        <v>9.4073773082154919E-4</v>
+        <v>8.0647237247156566E-4</v>
       </c>
       <c r="AC15" s="4">
-        <v>9.4040130852944266E-4</v>
+        <v>8.0618396553817874E-4</v>
       </c>
       <c r="AD15" s="4">
-        <v>9.3994510185897847E-4</v>
+        <v>8.0579287026920799E-4</v>
       </c>
       <c r="AE15" s="4">
-        <v>9.3947122331757428E-4</v>
+        <v>8.0538662532013395E-4</v>
       </c>
       <c r="AF15" s="4">
-        <v>9.3899110103448245E-4</v>
+        <v>8.0497502775788527E-4</v>
       </c>
       <c r="AG15" s="4">
-        <v>9.3865581730935978E-4</v>
+        <v>8.0468759689124563E-4</v>
       </c>
       <c r="AH15" s="4"/>
       <c r="AI15" s="4"/>
@@ -18662,22 +18660,22 @@
         <v>15</v>
       </c>
       <c r="B10">
-        <v>1.3226441773833212E-4</v>
+        <v>3.0636736837912965E-4</v>
       </c>
       <c r="C10" s="4">
-        <v>7.0204850469879831E-5</v>
+        <v>7.273085411263018E-5</v>
       </c>
       <c r="D10" s="4">
-        <v>9.8677853294881047E-5</v>
+        <v>9.5098581742816967E-5</v>
       </c>
       <c r="E10" s="4">
-        <v>7.7747040895486744E-5</v>
+        <v>9.3478062847081558E-5</v>
       </c>
       <c r="F10">
-        <v>1.7525323807361898E-4</v>
+        <v>3.8357149864294821E-5</v>
       </c>
       <c r="G10" s="4">
-        <v>5.5270584840087177E-5</v>
+        <v>1.4090027704705712E-3</v>
       </c>
       <c r="H10" s="4">
         <v>8.379890176963306E-5</v>
@@ -19205,779 +19203,777 @@
   <dimension ref="A1:BT15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="14" style="23" customWidth="1"/>
-    <col min="2" max="14" width="9.140625" style="23"/>
-    <col min="15" max="15" width="11.42578125" style="23" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="23"/>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="15" max="15" width="11.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:72">
-      <c r="C1" s="23">
+      <c r="C1">
         <v>1983</v>
       </c>
-      <c r="D1" s="23">
+      <c r="D1">
         <v>1984</v>
       </c>
-      <c r="E1" s="23">
+      <c r="E1">
         <v>1985</v>
       </c>
-      <c r="F1" s="23">
+      <c r="F1">
         <v>1986</v>
       </c>
-      <c r="G1" s="23">
+      <c r="G1">
         <v>1987</v>
       </c>
-      <c r="H1" s="23">
+      <c r="H1">
         <v>1988</v>
       </c>
-      <c r="I1" s="23">
+      <c r="I1">
         <v>1989</v>
       </c>
-      <c r="J1" s="23">
+      <c r="J1">
         <v>1990</v>
       </c>
-      <c r="K1" s="23">
+      <c r="K1">
         <v>1991</v>
       </c>
-      <c r="L1" s="23">
+      <c r="L1">
         <v>1992</v>
       </c>
-      <c r="M1" s="23">
+      <c r="M1">
         <v>1993</v>
       </c>
-      <c r="N1" s="23">
+      <c r="N1">
         <v>1994</v>
       </c>
-      <c r="O1" s="23">
+      <c r="O1">
         <v>1995</v>
       </c>
-      <c r="P1" s="23">
+      <c r="P1">
         <v>1996</v>
       </c>
-      <c r="Q1" s="23">
+      <c r="Q1">
         <v>1997</v>
       </c>
-      <c r="R1" s="23">
+      <c r="R1">
         <v>1998</v>
       </c>
-      <c r="S1" s="23">
+      <c r="S1">
         <v>1999</v>
       </c>
-      <c r="T1" s="23">
+      <c r="T1">
         <v>2000</v>
       </c>
-      <c r="U1" s="23">
+      <c r="U1">
         <v>2001</v>
       </c>
-      <c r="V1" s="23">
+      <c r="V1">
         <v>2002</v>
       </c>
-      <c r="W1" s="23">
+      <c r="W1">
         <v>2003</v>
       </c>
-      <c r="X1" s="23">
+      <c r="X1">
         <v>2004</v>
       </c>
-      <c r="Y1" s="23">
+      <c r="Y1">
         <v>2005</v>
       </c>
-      <c r="Z1" s="23">
+      <c r="Z1">
         <v>2006</v>
       </c>
-      <c r="AA1" s="23">
+      <c r="AA1">
         <v>2007</v>
       </c>
-      <c r="AB1" s="23">
+      <c r="AB1">
         <v>2008</v>
       </c>
-      <c r="AC1" s="23">
+      <c r="AC1">
         <v>2009</v>
       </c>
-      <c r="AD1" s="23">
+      <c r="AD1">
         <v>2010</v>
       </c>
-      <c r="AE1" s="23">
+      <c r="AE1">
         <v>2011</v>
       </c>
-      <c r="AF1" s="23">
+      <c r="AF1">
         <v>2012</v>
       </c>
-      <c r="AG1" s="23">
+      <c r="AG1">
         <v>2013</v>
       </c>
-      <c r="AH1" s="23">
+      <c r="AH1">
         <v>2014</v>
       </c>
-      <c r="AI1" s="23">
+      <c r="AI1">
         <v>2015</v>
       </c>
-      <c r="AJ1" s="23">
+      <c r="AJ1">
         <v>2016</v>
       </c>
-      <c r="AK1" s="23">
+      <c r="AK1">
         <v>2017</v>
       </c>
-      <c r="AL1" s="23">
+      <c r="AL1">
         <v>2018</v>
       </c>
-      <c r="AM1" s="23">
+      <c r="AM1">
         <v>2019</v>
       </c>
-      <c r="AN1" s="23">
+      <c r="AN1">
         <v>2020</v>
       </c>
-      <c r="AO1" s="23">
+      <c r="AO1">
         <v>2021</v>
       </c>
-      <c r="AP1" s="23">
+      <c r="AP1">
         <v>2022</v>
       </c>
-      <c r="AQ1" s="23">
+      <c r="AQ1">
         <v>2023</v>
       </c>
       <c r="AR1" s="16">
         <v>2024</v>
       </c>
-      <c r="AS1" s="23">
+      <c r="AS1">
         <v>2025</v>
       </c>
-      <c r="AT1" s="23">
+      <c r="AT1">
         <v>2026</v>
       </c>
-      <c r="AU1" s="23">
+      <c r="AU1">
         <v>2027</v>
       </c>
-      <c r="AV1" s="23">
+      <c r="AV1">
         <v>2028</v>
       </c>
-      <c r="AW1" s="23">
+      <c r="AW1">
         <v>2029</v>
       </c>
-      <c r="AX1" s="23">
+      <c r="AX1">
         <v>2030</v>
       </c>
-      <c r="AY1" s="23">
+      <c r="AY1">
         <v>2031</v>
       </c>
-      <c r="AZ1" s="23">
+      <c r="AZ1">
         <v>2032</v>
       </c>
-      <c r="BA1" s="23">
+      <c r="BA1">
         <v>2033</v>
       </c>
-      <c r="BB1" s="23">
+      <c r="BB1">
         <v>2034</v>
       </c>
-      <c r="BC1" s="23">
+      <c r="BC1">
         <v>2035</v>
       </c>
-      <c r="BD1" s="23">
+      <c r="BD1">
         <v>2036</v>
       </c>
-      <c r="BE1" s="23">
+      <c r="BE1">
         <v>2037</v>
       </c>
-      <c r="BF1" s="23">
+      <c r="BF1">
         <v>2038</v>
       </c>
-      <c r="BG1" s="23">
+      <c r="BG1">
         <v>2039</v>
       </c>
-      <c r="BH1" s="23">
+      <c r="BH1">
         <v>2040</v>
       </c>
-      <c r="BI1" s="23">
+      <c r="BI1">
         <v>2041</v>
       </c>
-      <c r="BJ1" s="23">
+      <c r="BJ1">
         <v>2042</v>
       </c>
-      <c r="BK1" s="23">
+      <c r="BK1">
         <v>2043</v>
       </c>
-      <c r="BL1" s="23">
+      <c r="BL1">
         <v>2044</v>
       </c>
-      <c r="BM1" s="23">
+      <c r="BM1">
         <v>2045</v>
       </c>
-      <c r="BN1" s="23">
+      <c r="BN1">
         <v>2046</v>
       </c>
-      <c r="BO1" s="23">
+      <c r="BO1">
         <v>2047</v>
       </c>
-      <c r="BP1" s="23">
+      <c r="BP1">
         <v>2048</v>
       </c>
-      <c r="BQ1" s="23">
+      <c r="BQ1">
         <v>2049</v>
       </c>
-      <c r="BR1" s="23">
+      <c r="BR1">
         <v>2050</v>
       </c>
     </row>
     <row r="2" spans="1:72">
-      <c r="A2" s="23" t="s">
+      <c r="A2" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="23" t="s">
+      <c r="B2" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
-      <c r="F2" s="24"/>
-      <c r="G2" s="24"/>
-      <c r="H2" s="24"/>
-      <c r="I2" s="24"/>
-      <c r="J2" s="24"/>
-      <c r="K2" s="24"/>
-      <c r="L2" s="24"/>
-      <c r="M2" s="25"/>
-      <c r="N2" s="24"/>
-      <c r="O2" s="24"/>
-      <c r="P2" s="24"/>
-      <c r="Q2" s="24"/>
-      <c r="R2" s="24"/>
-      <c r="S2" s="24"/>
-      <c r="T2" s="24"/>
-      <c r="U2" s="24"/>
-      <c r="V2" s="24"/>
-      <c r="W2" s="24"/>
-      <c r="X2" s="24"/>
-      <c r="Y2" s="24"/>
-      <c r="Z2" s="24"/>
-      <c r="AA2" s="26">
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
+      <c r="I2" s="23"/>
+      <c r="J2" s="23"/>
+      <c r="K2" s="23"/>
+      <c r="L2" s="23"/>
+      <c r="M2" s="24"/>
+      <c r="N2" s="23"/>
+      <c r="O2" s="23"/>
+      <c r="P2" s="23"/>
+      <c r="Q2" s="23"/>
+      <c r="R2" s="23"/>
+      <c r="S2" s="23"/>
+      <c r="T2" s="23"/>
+      <c r="U2" s="23"/>
+      <c r="V2" s="23"/>
+      <c r="W2" s="23"/>
+      <c r="X2" s="23"/>
+      <c r="Y2" s="23"/>
+      <c r="Z2" s="23"/>
+      <c r="AA2" s="4">
         <f>Calculations!C16</f>
         <v>3.142498616321923E-4</v>
       </c>
-      <c r="AB2" s="27">
+      <c r="AB2" s="25">
         <f t="shared" ref="AB2:AQ2" si="0">($AS$2-$AA$2)/COUNT($AB$1:$AS$1)+AA2</f>
         <v>3.1844100144032408E-4</v>
       </c>
-      <c r="AC2" s="27">
+      <c r="AC2" s="25">
         <f t="shared" si="0"/>
         <v>3.2263214124845585E-4</v>
       </c>
-      <c r="AD2" s="27">
+      <c r="AD2" s="25">
         <f t="shared" si="0"/>
         <v>3.2682328105658763E-4</v>
       </c>
-      <c r="AE2" s="27">
+      <c r="AE2" s="25">
         <f t="shared" si="0"/>
         <v>3.310144208647194E-4</v>
       </c>
-      <c r="AF2" s="27">
+      <c r="AF2" s="25">
         <f t="shared" si="0"/>
         <v>3.3520556067285118E-4</v>
       </c>
-      <c r="AG2" s="27">
+      <c r="AG2" s="25">
         <f t="shared" si="0"/>
         <v>3.3939670048098295E-4</v>
       </c>
-      <c r="AH2" s="27">
+      <c r="AH2" s="25">
         <f t="shared" si="0"/>
         <v>3.4358784028911473E-4</v>
       </c>
-      <c r="AI2" s="27">
+      <c r="AI2" s="25">
         <f t="shared" si="0"/>
         <v>3.477789800972465E-4</v>
       </c>
-      <c r="AJ2" s="27">
+      <c r="AJ2" s="25">
         <f t="shared" si="0"/>
         <v>3.5197011990537828E-4</v>
       </c>
-      <c r="AK2" s="27">
+      <c r="AK2" s="25">
         <f t="shared" si="0"/>
         <v>3.5616125971351005E-4</v>
       </c>
-      <c r="AL2" s="27">
+      <c r="AL2" s="25">
         <f t="shared" si="0"/>
         <v>3.6035239952164183E-4</v>
       </c>
-      <c r="AM2" s="27">
+      <c r="AM2" s="25">
         <f t="shared" si="0"/>
         <v>3.645435393297736E-4</v>
       </c>
-      <c r="AN2" s="27">
+      <c r="AN2" s="25">
         <f t="shared" si="0"/>
         <v>3.6873467913790537E-4</v>
       </c>
-      <c r="AO2" s="27">
+      <c r="AO2" s="25">
         <f t="shared" si="0"/>
         <v>3.7292581894603715E-4</v>
       </c>
-      <c r="AP2" s="27">
+      <c r="AP2" s="25">
         <f t="shared" si="0"/>
         <v>3.7711695875416892E-4</v>
       </c>
-      <c r="AQ2" s="27">
+      <c r="AQ2" s="25">
         <f t="shared" si="0"/>
         <v>3.813080985623007E-4</v>
       </c>
-      <c r="AR2" s="34">
+      <c r="AR2" s="32">
         <f>($AS$2-$AA$2)/COUNT($AB$1:$AS$1)+AQ2</f>
         <v>3.8549923837043247E-4</v>
       </c>
-      <c r="AS2" s="28">
+      <c r="AS2" s="26">
         <f>BNVFE!H8</f>
         <v>3.8969037817856381E-4</v>
       </c>
-      <c r="AT2" s="28">
+      <c r="AT2" s="26">
         <f>BNVFE!I8</f>
         <v>3.9985001436006255E-4</v>
       </c>
-      <c r="AU2" s="28">
+      <c r="AU2" s="26">
         <f>BNVFE!J8</f>
         <v>4.0645495978422236E-4</v>
       </c>
-      <c r="AV2" s="28">
+      <c r="AV2" s="26">
         <f>BNVFE!K8</f>
         <v>4.1222868457836193E-4</v>
       </c>
-      <c r="AW2" s="28">
+      <c r="AW2" s="26">
         <f>BNVFE!L8</f>
         <v>4.1315950014361388E-4</v>
       </c>
-      <c r="AX2" s="28">
+      <c r="AX2" s="26">
         <f>BNVFE!M8</f>
         <v>4.1586031572729884E-4</v>
       </c>
-      <c r="AY2" s="28">
+      <c r="AY2" s="26">
         <f>BNVFE!N8</f>
         <v>4.1791006177450995E-4</v>
       </c>
-      <c r="AZ2" s="28">
+      <c r="AZ2" s="26">
         <f>BNVFE!O8</f>
         <v>4.1868747861134429E-4</v>
       </c>
-      <c r="BA2" s="28">
+      <c r="BA2" s="26">
         <f>BNVFE!P8</f>
         <v>4.2132009406936789E-4</v>
       </c>
-      <c r="BB2" s="28">
+      <c r="BB2" s="26">
         <f>BNVFE!Q8</f>
         <v>4.224153063913546E-4</v>
       </c>
-      <c r="BC2" s="28">
+      <c r="BC2" s="26">
         <f>BNVFE!R8</f>
         <v>4.2414977562549528E-4</v>
       </c>
-      <c r="BD2" s="28">
+      <c r="BD2" s="26">
         <f>BNVFE!S8</f>
         <v>4.2551597947059568E-4</v>
       </c>
-      <c r="BE2" s="28">
+      <c r="BE2" s="26">
         <f>BNVFE!T8</f>
         <v>4.2699017471707065E-4</v>
       </c>
-      <c r="BF2" s="28">
+      <c r="BF2" s="26">
         <f>BNVFE!U8</f>
         <v>4.278185027990744E-4</v>
       </c>
-      <c r="BG2" s="28">
+      <c r="BG2" s="26">
         <f>BNVFE!V8</f>
         <v>4.2962147676115707E-4</v>
       </c>
-      <c r="BH2" s="28">
+      <c r="BH2" s="26">
         <f>BNVFE!W8</f>
         <v>4.3041495518616422E-4</v>
       </c>
-      <c r="BI2" s="28">
+      <c r="BI2" s="26">
         <f>BNVFE!X8</f>
         <v>4.3058027955271102E-4</v>
       </c>
-      <c r="BJ2" s="28">
+      <c r="BJ2" s="26">
         <f>BNVFE!Y8</f>
         <v>4.3088934374883934E-4</v>
       </c>
-      <c r="BK2" s="28">
+      <c r="BK2" s="26">
         <f>BNVFE!Z8</f>
         <v>4.3093489146882265E-4</v>
       </c>
-      <c r="BL2" s="28">
+      <c r="BL2" s="26">
         <f>BNVFE!AA8</f>
         <v>4.3107618325306866E-4</v>
       </c>
-      <c r="BM2" s="28">
+      <c r="BM2" s="26">
         <f>BNVFE!AB8</f>
         <v>4.3159356456922571E-4</v>
       </c>
-      <c r="BN2" s="28">
+      <c r="BN2" s="26">
         <f>BNVFE!AC8</f>
         <v>4.3137509125134069E-4</v>
       </c>
-      <c r="BO2" s="28">
+      <c r="BO2" s="26">
         <f>BNVFE!AD8</f>
         <v>4.3181432059055414E-4</v>
       </c>
-      <c r="BP2" s="28">
+      <c r="BP2" s="26">
         <f>BNVFE!AE8</f>
         <v>4.3184298375304391E-4</v>
       </c>
-      <c r="BQ2" s="28">
+      <c r="BQ2" s="26">
         <f>BNVFE!AF8</f>
         <v>4.3221033154474715E-4</v>
       </c>
-      <c r="BR2" s="28">
+      <c r="BR2" s="26">
         <f>BNVFE!AG8</f>
         <v>4.3232208233433581E-4</v>
       </c>
-      <c r="BS2" s="28"/>
-      <c r="BT2" s="26"/>
+      <c r="BS2" s="26"/>
+      <c r="BT2" s="4"/>
     </row>
     <row r="3" spans="1:72">
-      <c r="A3" s="23" t="s">
+      <c r="A3" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="23" t="s">
+      <c r="B3" t="s">
         <v>22</v>
       </c>
-      <c r="C3" s="24"/>
-      <c r="D3" s="24"/>
-      <c r="E3" s="24"/>
-      <c r="F3" s="24"/>
-      <c r="G3" s="24"/>
-      <c r="H3" s="24"/>
-      <c r="I3" s="24"/>
-      <c r="J3" s="24"/>
-      <c r="K3" s="24"/>
-      <c r="L3" s="24"/>
-      <c r="M3" s="24"/>
-      <c r="N3" s="24"/>
-      <c r="O3" s="24"/>
-      <c r="P3" s="24"/>
-      <c r="Q3" s="24"/>
-      <c r="R3" s="24"/>
-      <c r="S3" s="24"/>
-      <c r="T3" s="24"/>
-      <c r="U3" s="24"/>
-      <c r="V3" s="24"/>
-      <c r="W3" s="24"/>
-      <c r="X3" s="24"/>
-      <c r="Y3" s="24"/>
-      <c r="Z3" s="24"/>
-      <c r="AA3" s="26" cm="1">
+      <c r="C3" s="23"/>
+      <c r="D3" s="23"/>
+      <c r="E3" s="23"/>
+      <c r="F3" s="23"/>
+      <c r="G3" s="23"/>
+      <c r="H3" s="23"/>
+      <c r="I3" s="23"/>
+      <c r="J3" s="23"/>
+      <c r="K3" s="23"/>
+      <c r="L3" s="23"/>
+      <c r="M3" s="23"/>
+      <c r="N3" s="23"/>
+      <c r="O3" s="23"/>
+      <c r="P3" s="23"/>
+      <c r="Q3" s="23"/>
+      <c r="R3" s="23"/>
+      <c r="S3" s="23"/>
+      <c r="T3" s="23"/>
+      <c r="U3" s="23"/>
+      <c r="V3" s="23"/>
+      <c r="W3" s="23"/>
+      <c r="X3" s="23"/>
+      <c r="Y3" s="23"/>
+      <c r="Z3" s="23"/>
+      <c r="AA3" s="4" cm="1">
         <f t="array" ref="AA3">TREND($AQ$3:$AU$3,$AQ$1:$AU$1,AA1)</f>
-        <v>6.1792415736698723E-5</v>
-      </c>
-      <c r="AB3" s="26" cm="1">
+        <v>5.9551063413003282E-5</v>
+      </c>
+      <c r="AB3" s="4" cm="1">
         <f t="array" ref="AB3">TREND($AQ$3:$AU$3,$AQ$1:$AU$1,AB1)</f>
-        <v>6.3169682072834916E-5</v>
-      </c>
-      <c r="AC3" s="26" cm="1">
+        <v>6.0878373147410427E-5</v>
+      </c>
+      <c r="AC3" s="4" cm="1">
         <f t="array" ref="AC3">TREND($AQ$3:$AU$3,$AQ$1:$AU$1,AC1)</f>
-        <v>6.454694840897111E-5</v>
-      </c>
-      <c r="AD3" s="26" cm="1">
+        <v>6.2205682881817138E-5</v>
+      </c>
+      <c r="AD3" s="4" cm="1">
         <f t="array" ref="AD3">TREND($AQ$3:$AU$3,$AQ$1:$AU$1,AD1)</f>
-        <v>6.5924214745107304E-5</v>
-      </c>
-      <c r="AE3" s="26" cm="1">
+        <v>6.3532992616224283E-5</v>
+      </c>
+      <c r="AE3" s="4" cm="1">
         <f t="array" ref="AE3">TREND($AQ$3:$AU$3,$AQ$1:$AU$1,AE1)</f>
-        <v>6.7301481081243498E-5</v>
-      </c>
-      <c r="AF3" s="26" cm="1">
+        <v>6.4860302350631428E-5</v>
+      </c>
+      <c r="AF3" s="4" cm="1">
         <f t="array" ref="AF3">TREND($AQ$3:$AU$3,$AQ$1:$AU$1,AF1)</f>
-        <v>6.8678747417379692E-5</v>
-      </c>
-      <c r="AG3" s="26" cm="1">
+        <v>6.618761208503814E-5</v>
+      </c>
+      <c r="AG3" s="4" cm="1">
         <f t="array" ref="AG3">TREND($AQ$3:$AU$3,$AQ$1:$AU$1,AG1)</f>
-        <v>7.0056013753515885E-5</v>
-      </c>
-      <c r="AH3" s="26" cm="1">
+        <v>6.7514921819445285E-5</v>
+      </c>
+      <c r="AH3" s="4" cm="1">
         <f t="array" ref="AH3">TREND($AQ$3:$AU$3,$AQ$1:$AU$1,AH1)</f>
-        <v>7.1433280089651646E-5</v>
-      </c>
-      <c r="AI3" s="26" cm="1">
+        <v>6.8842231553851996E-5</v>
+      </c>
+      <c r="AI3" s="4" cm="1">
         <f t="array" ref="AI3">TREND($AQ$3:$AU$3,$AQ$1:$AU$1,AI1)</f>
-        <v>7.2810546425787839E-5</v>
-      </c>
-      <c r="AJ3" s="26" cm="1">
+        <v>7.0169541288259141E-5</v>
+      </c>
+      <c r="AJ3" s="4" cm="1">
         <f t="array" ref="AJ3">TREND($AQ$3:$AU$3,$AQ$1:$AU$1,AJ1)</f>
-        <v>7.4187812761924033E-5</v>
-      </c>
-      <c r="AK3" s="26" cm="1">
+        <v>7.1496851022665852E-5</v>
+      </c>
+      <c r="AK3" s="4" cm="1">
         <f t="array" ref="AK3">TREND($AQ$3:$AU$3,$AQ$1:$AU$1,AK1)</f>
-        <v>7.5565079098060227E-5</v>
-      </c>
-      <c r="AL3" s="26" cm="1">
+        <v>7.2824160757072997E-5</v>
+      </c>
+      <c r="AL3" s="4" cm="1">
         <f t="array" ref="AL3">TREND($AQ$3:$AU$3,$AQ$1:$AU$1,AL1)</f>
-        <v>7.6942345434196421E-5</v>
-      </c>
-      <c r="AM3" s="26" cm="1">
+        <v>7.4151470491480142E-5</v>
+      </c>
+      <c r="AM3" s="4" cm="1">
         <f t="array" ref="AM3">TREND($AQ$3:$AU$3,$AQ$1:$AU$1,AM1)</f>
-        <v>7.8319611770332614E-5</v>
-      </c>
-      <c r="AN3" s="26" cm="1">
+        <v>7.5478780225886853E-5</v>
+      </c>
+      <c r="AN3" s="4" cm="1">
         <f t="array" ref="AN3">TREND($AQ$3:$AU$3,$AQ$1:$AU$1,AN1)</f>
-        <v>7.9696878106468808E-5</v>
-      </c>
-      <c r="AO3" s="26" cm="1">
+        <v>7.6806089960293998E-5</v>
+      </c>
+      <c r="AO3" s="4" cm="1">
         <f t="array" ref="AO3">TREND($AQ$3:$AU$3,$AQ$1:$AU$1,AO1)</f>
-        <v>8.1074144442605002E-5</v>
-      </c>
-      <c r="AP3" s="26" cm="1">
+        <v>7.8133399694700709E-5</v>
+      </c>
+      <c r="AP3" s="4" cm="1">
         <f t="array" ref="AP3">TREND($AR$3:$AV$3,$AR$1:$AV$1,AP1)</f>
-        <v>8.2778348635091648E-5</v>
-      </c>
-      <c r="AQ3" s="26" cm="1">
+        <v>7.977578850124848E-5</v>
+      </c>
+      <c r="AQ3" s="4" cm="1">
         <f t="array" ref="AQ3">TREND($AR$3:$AV$3,$AR$1:$AV$1,AQ1)</f>
-        <v>8.401549874707771E-5</v>
+        <v>8.0968064347595233E-5</v>
       </c>
       <c r="AR3" s="20">
         <f>BNVFE!G9</f>
-        <v>8.4385989241553405E-5</v>
-      </c>
-      <c r="AS3" s="28">
+        <v>8.132511630401103E-5</v>
+      </c>
+      <c r="AS3" s="26">
         <f>BNVFE!H9</f>
-        <v>8.7328683714801736E-5</v>
-      </c>
-      <c r="AT3" s="28">
+        <v>8.4161072514692597E-5</v>
+      </c>
+      <c r="AT3" s="26">
         <f>BNVFE!I9</f>
-        <v>8.8182104367561648E-5</v>
-      </c>
-      <c r="AU3" s="28">
+        <v>8.498353764742068E-5</v>
+      </c>
+      <c r="AU3" s="26">
         <f>BNVFE!J9</f>
-        <v>8.9003772864754401E-5</v>
-      </c>
-      <c r="AV3" s="28">
+        <v>8.5775402347925225E-5</v>
+      </c>
+      <c r="AV3" s="26">
         <f>BNVFE!K9</f>
-        <v>8.9734195226507302E-5</v>
-      </c>
-      <c r="AW3" s="28">
+        <v>8.6479330619128737E-5</v>
+      </c>
+      <c r="AW3" s="26">
         <f>BNVFE!L9</f>
-        <v>9.0462120095479015E-5</v>
-      </c>
-      <c r="AX3" s="28">
+        <v>8.7180851987329484E-5</v>
+      </c>
+      <c r="AX3" s="26">
         <f>BNVFE!M9</f>
-        <v>9.0976244401538644E-5</v>
-      </c>
-      <c r="AY3" s="28">
+        <v>8.7676327828293231E-5</v>
+      </c>
+      <c r="AY3" s="26">
         <f>BNVFE!N9</f>
-        <v>9.1398310016686457E-5</v>
-      </c>
-      <c r="AZ3" s="28">
+        <v>8.808308415773043E-5</v>
+      </c>
+      <c r="AZ3" s="26">
         <f>BNVFE!O9</f>
-        <v>9.1772134453993215E-5</v>
-      </c>
-      <c r="BA3" s="28">
+        <v>8.8443349127241298E-5</v>
+      </c>
+      <c r="BA3" s="26">
         <f>BNVFE!P9</f>
-        <v>9.2116170982308495E-5</v>
-      </c>
-      <c r="BB3" s="28">
+        <v>8.877490666338608E-5</v>
+      </c>
+      <c r="BB3" s="26">
         <f>BNVFE!Q9</f>
-        <v>9.2387908899653262E-5</v>
-      </c>
-      <c r="BC3" s="28">
+        <v>8.9036788024627383E-5</v>
+      </c>
+      <c r="BC3" s="26">
         <f>BNVFE!R9</f>
-        <v>9.2774067997207965E-5</v>
-      </c>
-      <c r="BD3" s="28">
+        <v>8.9408940248032558E-5</v>
+      </c>
+      <c r="BD3" s="26">
         <f>BNVFE!S9</f>
-        <v>9.3103239258822098E-5</v>
-      </c>
-      <c r="BE3" s="28">
+        <v>8.9726171714716883E-5</v>
+      </c>
+      <c r="BE3" s="26">
         <f>BNVFE!T9</f>
-        <v>9.3380550032913344E-5</v>
-      </c>
-      <c r="BF3" s="28">
+        <v>8.9993423792437643E-5</v>
+      </c>
+      <c r="BF3" s="26">
         <f>BNVFE!U9</f>
-        <v>9.3568760633689615E-5</v>
-      </c>
-      <c r="BG3" s="28">
+        <v>9.0174807564025167E-5</v>
+      </c>
+      <c r="BG3" s="26">
         <f>BNVFE!V9</f>
-        <v>9.378410942377925E-5</v>
-      </c>
-      <c r="BH3" s="28">
+        <v>9.038234516069701E-5</v>
+      </c>
+      <c r="BH3" s="26">
         <f>BNVFE!W9</f>
-        <v>9.4376700451576006E-5</v>
-      </c>
-      <c r="BI3" s="28">
+        <v>9.0953441555838329E-5</v>
+      </c>
+      <c r="BI3" s="26">
         <f>BNVFE!X9</f>
-        <v>9.5219008221142745E-5</v>
-      </c>
-      <c r="BJ3" s="28">
+        <v>9.1765196895077241E-5</v>
+      </c>
+      <c r="BJ3" s="26">
         <f>BNVFE!Y9</f>
-        <v>9.6097486024325845E-5</v>
-      </c>
-      <c r="BK3" s="28">
+        <v>9.2611810298042204E-5</v>
+      </c>
+      <c r="BK3" s="26">
         <f>BNVFE!Z9</f>
-        <v>9.717217467407689E-5</v>
-      </c>
-      <c r="BL3" s="28">
+        <v>9.3647517531163859E-5</v>
+      </c>
+      <c r="BL3" s="26">
         <f>BNVFE!AA9</f>
-        <v>9.862744958918793E-5</v>
-      </c>
-      <c r="BM3" s="28">
+        <v>9.5050006294872494E-5</v>
+      </c>
+      <c r="BM3" s="26">
         <f>BNVFE!AB9</f>
-        <v>1.0008701258438573E-4</v>
-      </c>
-      <c r="BN3" s="28">
+        <v>9.645662760019035E-5</v>
+      </c>
+      <c r="BN3" s="26">
         <f>BNVFE!AC9</f>
-        <v>1.0105262413170669E-4</v>
-      </c>
-      <c r="BO3" s="28">
+        <v>9.7387214206997634E-5</v>
+      </c>
+      <c r="BO3" s="26">
         <f>BNVFE!AD9</f>
-        <v>1.019716253546731E-4</v>
-      </c>
-      <c r="BP3" s="28">
+        <v>9.8272881152577143E-5</v>
+      </c>
+      <c r="BP3" s="26">
         <f>BNVFE!AE9</f>
-        <v>1.0305329034341948E-4</v>
-      </c>
-      <c r="BQ3" s="28">
+        <v>9.9315311676914197E-5</v>
+      </c>
+      <c r="BQ3" s="26">
         <f>BNVFE!AF9</f>
-        <v>1.040015126571646E-4</v>
-      </c>
-      <c r="BR3" s="28">
+        <v>1.0022913979744075E-4</v>
+      </c>
+      <c r="BR3" s="26">
         <f>BNVFE!AG9</f>
-        <v>1.0491854588113829E-4</v>
-      </c>
-      <c r="BS3" s="28"/>
-      <c r="BT3" s="26"/>
+        <v>1.0111291012785455E-4</v>
+      </c>
+      <c r="BS3" s="26"/>
+      <c r="BT3" s="4"/>
     </row>
     <row r="4" spans="1:72">
-      <c r="A4" s="23" t="s">
+      <c r="A4" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="23" t="s">
+      <c r="B4" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="24"/>
-      <c r="D4" s="24"/>
-      <c r="E4" s="24"/>
-      <c r="F4" s="24"/>
-      <c r="G4" s="24"/>
-      <c r="H4" s="24"/>
-      <c r="I4" s="24"/>
-      <c r="J4" s="24"/>
-      <c r="K4" s="24"/>
-      <c r="L4" s="26">
+      <c r="C4" s="23"/>
+      <c r="D4" s="23"/>
+      <c r="E4" s="23"/>
+      <c r="F4" s="23"/>
+      <c r="G4" s="23"/>
+      <c r="H4" s="23"/>
+      <c r="I4" s="23"/>
+      <c r="J4" s="23"/>
+      <c r="K4" s="23"/>
+      <c r="L4" s="4">
         <f>L5/M5*M4</f>
         <v>1.0741724290607476E-3</v>
       </c>
-      <c r="M4" s="26">
+      <c r="M4" s="4">
         <f t="shared" ref="M4:AI4" si="1">M5/N5*N4</f>
         <v>1.0741724290607476E-3</v>
       </c>
-      <c r="N4" s="26">
+      <c r="N4" s="4">
         <f t="shared" si="1"/>
         <v>1.0741724290607476E-3</v>
       </c>
-      <c r="O4" s="26">
+      <c r="O4" s="4">
         <f t="shared" si="1"/>
         <v>1.0741724290607476E-3</v>
       </c>
-      <c r="P4" s="26">
+      <c r="P4" s="4">
         <f t="shared" si="1"/>
         <v>1.0741724290607476E-3</v>
       </c>
-      <c r="Q4" s="26">
+      <c r="Q4" s="4">
         <f t="shared" si="1"/>
         <v>1.0741724290607476E-3</v>
       </c>
-      <c r="R4" s="26">
+      <c r="R4" s="4">
         <f t="shared" si="1"/>
         <v>1.0741724290607476E-3</v>
       </c>
-      <c r="S4" s="26">
+      <c r="S4" s="4">
         <f t="shared" si="1"/>
         <v>1.0741724290607476E-3</v>
       </c>
-      <c r="T4" s="26">
+      <c r="T4" s="4">
         <f t="shared" si="1"/>
         <v>1.0741724290607476E-3</v>
       </c>
-      <c r="U4" s="26">
+      <c r="U4" s="4">
         <f t="shared" si="1"/>
         <v>1.0741724290607476E-3</v>
       </c>
-      <c r="V4" s="26">
+      <c r="V4" s="4">
         <f t="shared" si="1"/>
         <v>1.0741724290607476E-3</v>
       </c>
-      <c r="W4" s="26">
+      <c r="W4" s="4">
         <f t="shared" si="1"/>
         <v>1.0723072716534118E-3</v>
       </c>
-      <c r="X4" s="26">
+      <c r="X4" s="4">
         <f t="shared" si="1"/>
         <v>1.0704421142460759E-3</v>
       </c>
-      <c r="Y4" s="26">
+      <c r="Y4" s="4">
         <f t="shared" si="1"/>
         <v>1.0685769568387401E-3</v>
       </c>
-      <c r="Z4" s="26">
+      <c r="Z4" s="4">
         <f t="shared" si="1"/>
         <v>1.0667117994314045E-3</v>
       </c>
-      <c r="AA4" s="26">
+      <c r="AA4" s="4">
         <f t="shared" si="1"/>
         <v>1.0648466420240688E-3</v>
       </c>
-      <c r="AB4" s="26">
+      <c r="AB4" s="4">
         <f t="shared" si="1"/>
         <v>1.0629814846167332E-3</v>
       </c>
-      <c r="AC4" s="26">
+      <c r="AC4" s="4">
         <f t="shared" si="1"/>
         <v>1.0611163272093976E-3</v>
       </c>
-      <c r="AD4" s="26">
+      <c r="AD4" s="4">
         <f t="shared" si="1"/>
         <v>1.0592511698020617E-3</v>
       </c>
-      <c r="AE4" s="26">
+      <c r="AE4" s="4">
         <f t="shared" si="1"/>
         <v>1.0573860123947261E-3</v>
       </c>
-      <c r="AF4" s="26">
+      <c r="AF4" s="4">
         <f t="shared" si="1"/>
         <v>1.0555208549873905E-3</v>
       </c>
-      <c r="AG4" s="26">
+      <c r="AG4" s="4">
         <f>AG5/AH5*AH4</f>
         <v>1.0536556975800548E-3</v>
       </c>
-      <c r="AH4" s="26">
+      <c r="AH4" s="4">
         <f t="shared" si="1"/>
         <v>1.0517905401727192E-3</v>
       </c>
-      <c r="AI4" s="26">
+      <c r="AI4" s="4">
         <f t="shared" si="1"/>
         <v>1.0499253827653836E-3</v>
       </c>
-      <c r="AJ4" s="26">
+      <c r="AJ4" s="4">
         <f>AJ5/AK5*AK4</f>
         <v>1.0480602253580479E-3</v>
       </c>
-      <c r="AK4" s="29">
+      <c r="AK4" s="27">
         <f>AK5/AL5*AL4</f>
         <v>1.0461950679507121E-3</v>
       </c>
-      <c r="AL4" s="29">
+      <c r="AL4" s="27">
         <f>AL5/AM5*AM4</f>
         <v>1.0443299105433765E-3</v>
       </c>
-      <c r="AM4" s="29">
+      <c r="AM4" s="27">
         <f>AM5/AN5*AN4</f>
         <v>1.0424647531360406E-3</v>
       </c>
-      <c r="AN4" s="29">
-        <f t="shared" ref="AN4:AR4" si="2">AN5/AO5*AO4</f>
+      <c r="AN4" s="27">
+        <f t="shared" ref="AN4:AQ4" si="2">AN5/AO5*AO4</f>
         <v>1.040599595728705E-3</v>
       </c>
-      <c r="AO4" s="29">
+      <c r="AO4" s="27">
         <f t="shared" si="2"/>
         <v>1.0387344383213694E-3</v>
       </c>
-      <c r="AP4" s="29">
+      <c r="AP4" s="27">
         <f t="shared" si="2"/>
         <v>1.0368692809140337E-3</v>
       </c>
-      <c r="AQ4" s="29">
+      <c r="AQ4" s="27">
         <f t="shared" si="2"/>
         <v>1.0331389660993618E-3</v>
       </c>
@@ -19985,254 +19981,254 @@
         <f>BNVFE!G10</f>
         <v>1.0995181101032814E-3</v>
       </c>
-      <c r="AS4" s="28">
+      <c r="AS4" s="26">
         <f>BNVFE!H10</f>
         <v>1.1178720570179867E-3</v>
       </c>
-      <c r="AT4" s="28">
+      <c r="AT4" s="26">
         <f>BNVFE!I10</f>
         <v>1.139337361078613E-3</v>
       </c>
-      <c r="AU4" s="28">
+      <c r="AU4" s="26">
         <f>BNVFE!J10</f>
         <v>1.1689067098604232E-3</v>
       </c>
-      <c r="AV4" s="28">
+      <c r="AV4" s="26">
         <f>BNVFE!K10</f>
         <v>1.1886355244649762E-3</v>
       </c>
-      <c r="AW4" s="28">
+      <c r="AW4" s="26">
         <f>BNVFE!L10</f>
         <v>1.2005104013829389E-3</v>
       </c>
-      <c r="AX4" s="28">
+      <c r="AX4" s="26">
         <f>BNVFE!M10</f>
         <v>1.2150324713986361E-3</v>
       </c>
-      <c r="AY4" s="28">
+      <c r="AY4" s="26">
         <f>BNVFE!N10</f>
         <v>1.2281657343830318E-3</v>
       </c>
-      <c r="AZ4" s="28">
+      <c r="AZ4" s="26">
         <f>BNVFE!O10</f>
         <v>1.2718191053697899E-3</v>
       </c>
-      <c r="BA4" s="28">
+      <c r="BA4" s="26">
         <f>BNVFE!P10</f>
         <v>1.2872919346060385E-3</v>
       </c>
-      <c r="BB4" s="28">
+      <c r="BB4" s="26">
         <f>BNVFE!Q10</f>
         <v>1.294373280286983E-3</v>
       </c>
-      <c r="BC4" s="28">
+      <c r="BC4" s="26">
         <f>BNVFE!R10</f>
         <v>1.2991392532857248E-3</v>
       </c>
-      <c r="BD4" s="28">
+      <c r="BD4" s="26">
         <f>BNVFE!S10</f>
         <v>1.2994994330511106E-3</v>
       </c>
-      <c r="BE4" s="28">
+      <c r="BE4" s="26">
         <f>BNVFE!T10</f>
         <v>1.2998067394523606E-3</v>
       </c>
-      <c r="BF4" s="28">
+      <c r="BF4" s="26">
         <f>BNVFE!U10</f>
         <v>1.29969410316452E-3</v>
       </c>
-      <c r="BG4" s="28">
+      <c r="BG4" s="26">
         <f>BNVFE!V10</f>
         <v>1.299580986209732E-3</v>
       </c>
-      <c r="BH4" s="28">
+      <c r="BH4" s="26">
         <f>BNVFE!W10</f>
         <v>1.2991434190659293E-3</v>
       </c>
-      <c r="BI4" s="28">
+      <c r="BI4" s="26">
         <f>BNVFE!X10</f>
         <v>1.2988513337846576E-3</v>
       </c>
-      <c r="BJ4" s="28">
+      <c r="BJ4" s="26">
         <f>BNVFE!Y10</f>
         <v>1.2983562468295675E-3</v>
       </c>
-      <c r="BK4" s="28">
+      <c r="BK4" s="26">
         <f>BNVFE!Z10</f>
         <v>1.2980781008897497E-3</v>
       </c>
-      <c r="BL4" s="28">
+      <c r="BL4" s="26">
         <f>BNVFE!AA10</f>
         <v>1.2978283142997872E-3</v>
       </c>
-      <c r="BM4" s="28">
+      <c r="BM4" s="26">
         <f>BNVFE!AB10</f>
         <v>1.2973135199998824E-3</v>
       </c>
-      <c r="BN4" s="28">
+      <c r="BN4" s="26">
         <f>BNVFE!AC10</f>
         <v>1.2970622914090792E-3</v>
       </c>
-      <c r="BO4" s="28">
+      <c r="BO4" s="26">
         <f>BNVFE!AD10</f>
         <v>1.2965591933382112E-3</v>
       </c>
-      <c r="BP4" s="28">
+      <c r="BP4" s="26">
         <f>BNVFE!AE10</f>
         <v>1.2964217225914581E-3</v>
       </c>
-      <c r="BQ4" s="28">
+      <c r="BQ4" s="26">
         <f>BNVFE!AF10</f>
         <v>1.2961902013454692E-3</v>
       </c>
-      <c r="BR4" s="28">
+      <c r="BR4" s="26">
         <f>BNVFE!AG10</f>
         <v>1.2958891436145262E-3</v>
       </c>
-      <c r="BS4" s="28"/>
-      <c r="BT4" s="26"/>
+      <c r="BS4" s="26"/>
+      <c r="BT4" s="4"/>
     </row>
     <row r="5" spans="1:72">
-      <c r="A5" s="23" t="s">
+      <c r="A5" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="23" t="s">
+      <c r="B5" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="24"/>
-      <c r="D5" s="24"/>
-      <c r="E5" s="24"/>
-      <c r="F5" s="24"/>
-      <c r="G5" s="24"/>
-      <c r="H5" s="24"/>
-      <c r="I5" s="24"/>
-      <c r="J5" s="24"/>
-      <c r="K5" s="24"/>
-      <c r="L5" s="26">
+      <c r="C5" s="23"/>
+      <c r="D5" s="23"/>
+      <c r="E5" s="23"/>
+      <c r="F5" s="23"/>
+      <c r="G5" s="23"/>
+      <c r="H5" s="23"/>
+      <c r="I5" s="23"/>
+      <c r="J5" s="23"/>
+      <c r="K5" s="23"/>
+      <c r="L5" s="4">
         <f>M5</f>
         <v>7.8040477200267344E-4</v>
       </c>
-      <c r="M5" s="26">
+      <c r="M5" s="4">
         <f t="shared" ref="M5:T5" si="3">N5</f>
         <v>7.8040477200267344E-4</v>
       </c>
-      <c r="N5" s="26">
+      <c r="N5" s="4">
         <f t="shared" si="3"/>
         <v>7.8040477200267344E-4</v>
       </c>
-      <c r="O5" s="26">
+      <c r="O5" s="4">
         <f t="shared" si="3"/>
         <v>7.8040477200267344E-4</v>
       </c>
-      <c r="P5" s="26">
+      <c r="P5" s="4">
         <f t="shared" si="3"/>
         <v>7.8040477200267344E-4</v>
       </c>
-      <c r="Q5" s="26">
+      <c r="Q5" s="4">
         <f t="shared" si="3"/>
         <v>7.8040477200267344E-4</v>
       </c>
-      <c r="R5" s="26">
+      <c r="R5" s="4">
         <f t="shared" si="3"/>
         <v>7.8040477200267344E-4</v>
       </c>
-      <c r="S5" s="26">
+      <c r="S5" s="4">
         <f t="shared" si="3"/>
         <v>7.8040477200267344E-4</v>
       </c>
-      <c r="T5" s="26">
+      <c r="T5" s="4">
         <f t="shared" si="3"/>
         <v>7.8040477200267344E-4</v>
       </c>
-      <c r="U5" s="26">
+      <c r="U5" s="4">
         <f>V5</f>
         <v>7.8040477200267344E-4</v>
       </c>
-      <c r="V5" s="30">
+      <c r="V5" s="28">
         <f>Calculations!B22</f>
         <v>7.8040477200267344E-4</v>
       </c>
-      <c r="W5" s="26">
+      <c r="W5" s="4">
         <f>($AQ$5-$V$5)/COUNT($V$1:$AQ$1)+V5</f>
         <v>7.7904970301948082E-4</v>
       </c>
-      <c r="X5" s="26">
+      <c r="X5" s="4">
         <f t="shared" ref="X5:AN5" si="4">($AQ$5-$V$5)/COUNT($V$1:$AQ$1)+W5</f>
         <v>7.7769463403628821E-4</v>
       </c>
-      <c r="Y5" s="26">
+      <c r="Y5" s="4">
         <f t="shared" si="4"/>
         <v>7.7633956505309559E-4</v>
       </c>
-      <c r="Z5" s="26">
+      <c r="Z5" s="4">
         <f t="shared" si="4"/>
         <v>7.7498449606990298E-4</v>
       </c>
-      <c r="AA5" s="26">
+      <c r="AA5" s="4">
         <f t="shared" si="4"/>
         <v>7.7362942708671036E-4</v>
       </c>
-      <c r="AB5" s="26">
+      <c r="AB5" s="4">
         <f t="shared" si="4"/>
         <v>7.7227435810351774E-4</v>
       </c>
-      <c r="AC5" s="26">
+      <c r="AC5" s="4">
         <f t="shared" si="4"/>
         <v>7.7091928912032513E-4</v>
       </c>
-      <c r="AD5" s="26">
+      <c r="AD5" s="4">
         <f t="shared" si="4"/>
         <v>7.6956422013713251E-4</v>
       </c>
-      <c r="AE5" s="26">
+      <c r="AE5" s="4">
         <f t="shared" si="4"/>
         <v>7.682091511539399E-4</v>
       </c>
-      <c r="AF5" s="26">
+      <c r="AF5" s="4">
         <f t="shared" si="4"/>
         <v>7.6685408217074728E-4</v>
       </c>
-      <c r="AG5" s="26">
+      <c r="AG5" s="4">
         <f t="shared" si="4"/>
         <v>7.6549901318755467E-4</v>
       </c>
-      <c r="AH5" s="26">
+      <c r="AH5" s="4">
         <f t="shared" si="4"/>
         <v>7.6414394420436205E-4</v>
       </c>
-      <c r="AI5" s="26">
+      <c r="AI5" s="4">
         <f t="shared" si="4"/>
         <v>7.6278887522116944E-4</v>
       </c>
-      <c r="AJ5" s="26">
+      <c r="AJ5" s="4">
         <f t="shared" si="4"/>
         <v>7.6143380623797682E-4</v>
       </c>
-      <c r="AK5" s="26">
+      <c r="AK5" s="4">
         <f t="shared" si="4"/>
         <v>7.6007873725478421E-4</v>
       </c>
-      <c r="AL5" s="26">
+      <c r="AL5" s="4">
         <f t="shared" si="4"/>
         <v>7.5872366827159159E-4</v>
       </c>
-      <c r="AM5" s="26">
+      <c r="AM5" s="4">
         <f t="shared" si="4"/>
         <v>7.5736859928839898E-4</v>
       </c>
-      <c r="AN5" s="26">
+      <c r="AN5" s="4">
         <f t="shared" si="4"/>
         <v>7.5601353030520636E-4</v>
       </c>
-      <c r="AO5" s="26">
+      <c r="AO5" s="4">
         <f>($AQ$5-$V$5)/COUNT($V$1:$AQ$1)+AN5</f>
         <v>7.5465846132201375E-4</v>
       </c>
-      <c r="AP5" s="26">
+      <c r="AP5" s="4">
         <f>($AQ$5-$V$5)/COUNT($V$1:$AQ$1)+AO5</f>
         <v>7.5330339233882113E-4</v>
       </c>
-      <c r="AQ5" s="28">
+      <c r="AQ5" s="26">
         <f>BNVFE!F11</f>
         <v>7.5059325437243547E-4</v>
       </c>
@@ -20240,242 +20236,242 @@
         <f>BNVFE!G11</f>
         <v>7.9881884585164282E-4</v>
       </c>
-      <c r="AS5" s="28">
+      <c r="AS5" s="26">
         <f>BNVFE!H11</f>
         <v>8.1215330442627252E-4</v>
       </c>
-      <c r="AT5" s="28">
+      <c r="AT5" s="26">
         <f>BNVFE!I11</f>
         <v>8.277482175595845E-4</v>
       </c>
-      <c r="AU5" s="28">
+      <c r="AU5" s="26">
         <f>BNVFE!J11</f>
         <v>8.4923085877251694E-4</v>
       </c>
-      <c r="AV5" s="28">
+      <c r="AV5" s="26">
         <f>BNVFE!K11</f>
         <v>8.6356418240549429E-4</v>
       </c>
-      <c r="AW5" s="28">
+      <c r="AW5" s="26">
         <f>BNVFE!L11</f>
         <v>8.721914850275005E-4</v>
       </c>
-      <c r="AX5" s="28">
+      <c r="AX5" s="26">
         <f>BNVFE!M11</f>
         <v>8.8274201903209843E-4</v>
       </c>
-      <c r="AY5" s="28">
+      <c r="AY5" s="26">
         <f>BNVFE!N11</f>
         <v>8.9228356080668159E-4</v>
       </c>
-      <c r="AZ5" s="28">
+      <c r="AZ5" s="26">
         <f>BNVFE!O11</f>
         <v>9.2399848674446351E-4</v>
       </c>
-      <c r="BA5" s="28">
+      <c r="BA5" s="26">
         <f>BNVFE!P11</f>
         <v>9.3523976369932777E-4</v>
       </c>
-      <c r="BB5" s="28">
+      <c r="BB5" s="26">
         <f>BNVFE!Q11</f>
         <v>9.4038448331053737E-4</v>
       </c>
-      <c r="BC5" s="28">
+      <c r="BC5" s="26">
         <f>BNVFE!R11</f>
         <v>9.4384704478654366E-4</v>
       </c>
-      <c r="BD5" s="28">
+      <c r="BD5" s="26">
         <f>BNVFE!S11</f>
         <v>9.4410872159008232E-4</v>
       </c>
-      <c r="BE5" s="28">
+      <c r="BE5" s="26">
         <f>BNVFE!T11</f>
         <v>9.443319849838489E-4</v>
       </c>
-      <c r="BF5" s="28">
+      <c r="BF5" s="26">
         <f>BNVFE!U11</f>
         <v>9.4425015278060706E-4</v>
       </c>
-      <c r="BG5" s="28">
+      <c r="BG5" s="26">
         <f>BNVFE!V11</f>
         <v>9.4416797136454901E-4</v>
       </c>
-      <c r="BH5" s="28">
+      <c r="BH5" s="26">
         <f>BNVFE!W11</f>
         <v>9.4385007129761667E-4</v>
       </c>
-      <c r="BI5" s="28">
+      <c r="BI5" s="26">
         <f>BNVFE!X11</f>
         <v>9.4363786630969357E-4</v>
       </c>
-      <c r="BJ5" s="28">
+      <c r="BJ5" s="26">
         <f>BNVFE!Y11</f>
         <v>9.4327817710909993E-4</v>
       </c>
-      <c r="BK5" s="28">
+      <c r="BK5" s="26">
         <f>BNVFE!Z11</f>
         <v>9.4307609929284396E-4</v>
       </c>
-      <c r="BL5" s="28">
+      <c r="BL5" s="26">
         <f>BNVFE!AA11</f>
         <v>9.4289462503273878E-4</v>
       </c>
-      <c r="BM5" s="28">
+      <c r="BM5" s="26">
         <f>BNVFE!AB11</f>
         <v>9.4252061810668451E-4</v>
       </c>
-      <c r="BN5" s="28">
+      <c r="BN5" s="26">
         <f>BNVFE!AC11</f>
         <v>9.4233809620813079E-4</v>
       </c>
-      <c r="BO5" s="28">
+      <c r="BO5" s="26">
         <f>BNVFE!AD11</f>
         <v>9.4197258679393529E-4</v>
       </c>
-      <c r="BP5" s="28">
+      <c r="BP5" s="26">
         <f>BNVFE!AE11</f>
         <v>9.4187271192852781E-4</v>
       </c>
-      <c r="BQ5" s="28">
+      <c r="BQ5" s="26">
         <f>BNVFE!AF11</f>
         <v>9.4170450775543462E-4</v>
       </c>
-      <c r="BR5" s="28">
+      <c r="BR5" s="26">
         <f>BNVFE!AG11</f>
         <v>9.4148578412827765E-4</v>
       </c>
-      <c r="BS5" s="28"/>
-      <c r="BT5" s="26"/>
+      <c r="BS5" s="26"/>
+      <c r="BT5" s="4"/>
     </row>
     <row r="6" spans="1:72">
-      <c r="A6" s="23" t="s">
+      <c r="A6" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="23" t="s">
+      <c r="B6" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="24"/>
-      <c r="D6" s="24"/>
-      <c r="E6" s="24"/>
-      <c r="F6" s="24"/>
-      <c r="G6" s="24"/>
-      <c r="H6" s="24"/>
-      <c r="I6" s="24"/>
-      <c r="J6" s="24"/>
-      <c r="K6" s="24"/>
-      <c r="L6" s="24"/>
-      <c r="M6" s="24"/>
-      <c r="N6" s="24"/>
-      <c r="O6" s="24"/>
-      <c r="P6" s="26">
+      <c r="C6" s="23"/>
+      <c r="D6" s="23"/>
+      <c r="E6" s="23"/>
+      <c r="F6" s="23"/>
+      <c r="G6" s="23"/>
+      <c r="H6" s="23"/>
+      <c r="I6" s="23"/>
+      <c r="J6" s="23"/>
+      <c r="K6" s="23"/>
+      <c r="L6" s="23"/>
+      <c r="M6" s="23"/>
+      <c r="N6" s="23"/>
+      <c r="O6" s="23"/>
+      <c r="P6" s="4">
         <f t="shared" ref="P6:AM6" si="5">TREND($AQ6:$BR6,$AQ$1:$BR$1,P$1)</f>
         <v>3.3000958546164708E-4</v>
       </c>
-      <c r="Q6" s="26">
+      <c r="Q6" s="4">
         <f>TREND($AQ6:$BR6,$AQ$1:$BR$1,Q$1)</f>
         <v>3.3397333498517805E-4</v>
       </c>
-      <c r="R6" s="26">
+      <c r="R6" s="4">
         <f t="shared" si="5"/>
         <v>3.3793708450870902E-4</v>
       </c>
-      <c r="S6" s="26">
+      <c r="S6" s="4">
         <f t="shared" si="5"/>
         <v>3.4190083403223999E-4</v>
       </c>
-      <c r="T6" s="26">
+      <c r="T6" s="4">
         <f t="shared" si="5"/>
         <v>3.4586458355577096E-4</v>
       </c>
-      <c r="U6" s="26">
+      <c r="U6" s="4">
         <f t="shared" si="5"/>
         <v>3.4982833307930193E-4</v>
       </c>
-      <c r="V6" s="26">
+      <c r="V6" s="4">
         <f t="shared" si="5"/>
         <v>3.537920826028329E-4</v>
       </c>
-      <c r="W6" s="26">
+      <c r="W6" s="4">
         <f t="shared" si="5"/>
         <v>3.5775583212636387E-4</v>
       </c>
-      <c r="X6" s="26">
+      <c r="X6" s="4">
         <f t="shared" si="5"/>
         <v>3.6171958164989484E-4</v>
       </c>
-      <c r="Y6" s="26">
+      <c r="Y6" s="4">
         <f t="shared" si="5"/>
         <v>3.6568333117342582E-4</v>
       </c>
-      <c r="Z6" s="26">
+      <c r="Z6" s="4">
         <f t="shared" si="5"/>
         <v>3.6964708069695679E-4</v>
       </c>
-      <c r="AA6" s="26">
+      <c r="AA6" s="4">
         <f t="shared" si="5"/>
         <v>3.7361083022048776E-4</v>
       </c>
-      <c r="AB6" s="26">
+      <c r="AB6" s="4">
         <f t="shared" si="5"/>
         <v>3.7757457974401873E-4</v>
       </c>
-      <c r="AC6" s="26">
+      <c r="AC6" s="4">
         <f t="shared" si="5"/>
         <v>3.815383292675497E-4</v>
       </c>
-      <c r="AD6" s="26">
+      <c r="AD6" s="4">
         <f t="shared" si="5"/>
         <v>3.8550207879108067E-4</v>
       </c>
-      <c r="AE6" s="26">
+      <c r="AE6" s="4">
         <f t="shared" si="5"/>
         <v>3.8946582831461164E-4</v>
       </c>
-      <c r="AF6" s="26">
+      <c r="AF6" s="4">
         <f t="shared" si="5"/>
         <v>3.9342957783814261E-4</v>
       </c>
-      <c r="AG6" s="26">
+      <c r="AG6" s="4">
         <f t="shared" si="5"/>
         <v>3.9739332736167358E-4</v>
       </c>
-      <c r="AH6" s="26">
+      <c r="AH6" s="4">
         <f t="shared" si="5"/>
         <v>4.0135707688520629E-4</v>
       </c>
-      <c r="AI6" s="26">
+      <c r="AI6" s="4">
         <f t="shared" si="5"/>
         <v>4.0532082640873726E-4</v>
       </c>
-      <c r="AJ6" s="26">
+      <c r="AJ6" s="4">
         <f t="shared" si="5"/>
         <v>4.0928457593226823E-4</v>
       </c>
-      <c r="AK6" s="26">
+      <c r="AK6" s="4">
         <f t="shared" si="5"/>
         <v>4.132483254557992E-4</v>
       </c>
-      <c r="AL6" s="26">
+      <c r="AL6" s="4">
         <f t="shared" si="5"/>
         <v>4.1721207497933017E-4</v>
       </c>
-      <c r="AM6" s="26">
+      <c r="AM6" s="4">
         <f t="shared" si="5"/>
         <v>4.2117582450286115E-4</v>
       </c>
-      <c r="AN6" s="26">
+      <c r="AN6" s="4">
         <f>TREND($AQ6:$BR6,$AQ$1:$BR$1,AN$1)</f>
         <v>4.2513957402639212E-4</v>
       </c>
-      <c r="AO6" s="26">
+      <c r="AO6" s="4">
         <f t="shared" ref="AO6:AP6" si="6">TREND($AQ6:$BR6,$AQ$1:$BR$1,AO$1)</f>
         <v>4.2910332354992309E-4</v>
       </c>
-      <c r="AP6" s="26">
+      <c r="AP6" s="4">
         <f t="shared" si="6"/>
         <v>4.3306707307345406E-4</v>
       </c>
-      <c r="AQ6" s="28">
+      <c r="AQ6" s="26">
         <f>BNVFE!F12</f>
         <v>4.3956547255263602E-4</v>
       </c>
@@ -20483,242 +20479,242 @@
         <f>BNVFE!G12</f>
         <v>4.4366680476890972E-4</v>
       </c>
-      <c r="AS6" s="28">
+      <c r="AS6" s="26">
         <f>BNVFE!H12</f>
         <v>4.4597245060431232E-4</v>
       </c>
-      <c r="AT6" s="28">
+      <c r="AT6" s="26">
         <f>BNVFE!I12</f>
         <v>4.4931411605150481E-4</v>
       </c>
-      <c r="AU6" s="28">
+      <c r="AU6" s="26">
         <f>BNVFE!J12</f>
         <v>4.5288823478004158E-4</v>
       </c>
-      <c r="AV6" s="28">
+      <c r="AV6" s="26">
         <f>BNVFE!K12</f>
         <v>4.5662840926832999E-4</v>
       </c>
-      <c r="AW6" s="28">
+      <c r="AW6" s="26">
         <f>BNVFE!L12</f>
         <v>4.6040875969022651E-4</v>
       </c>
-      <c r="AX6" s="28">
+      <c r="AX6" s="26">
         <f>BNVFE!M12</f>
         <v>4.6419842254086203E-4</v>
       </c>
-      <c r="AY6" s="28">
+      <c r="AY6" s="26">
         <f>BNVFE!N12</f>
         <v>4.6802171784268048E-4</v>
       </c>
-      <c r="AZ6" s="28">
+      <c r="AZ6" s="26">
         <f>BNVFE!O12</f>
         <v>4.718495549789862E-4</v>
       </c>
-      <c r="BA6" s="28">
+      <c r="BA6" s="26">
         <f>BNVFE!P12</f>
         <v>4.7569706545502331E-4</v>
       </c>
-      <c r="BB6" s="28">
+      <c r="BB6" s="26">
         <f>BNVFE!Q12</f>
         <v>4.7956228574948121E-4</v>
       </c>
-      <c r="BC6" s="28">
+      <c r="BC6" s="26">
         <f>BNVFE!R12</f>
         <v>4.8344561142611898E-4</v>
       </c>
-      <c r="BD6" s="28">
+      <c r="BD6" s="26">
         <f>BNVFE!S12</f>
         <v>4.8740041976327717E-4</v>
       </c>
-      <c r="BE6" s="28">
+      <c r="BE6" s="26">
         <f>BNVFE!T12</f>
         <v>4.9138744510057676E-4</v>
       </c>
-      <c r="BF6" s="28">
+      <c r="BF6" s="26">
         <f>BNVFE!U12</f>
         <v>4.9540734035651132E-4</v>
       </c>
-      <c r="BG6" s="28">
+      <c r="BG6" s="26">
         <f>BNVFE!V12</f>
         <v>4.9946276009751292E-4</v>
       </c>
-      <c r="BH6" s="28">
+      <c r="BH6" s="26">
         <f>BNVFE!W12</f>
         <v>5.0354741343006288E-4</v>
       </c>
-      <c r="BI6" s="28">
+      <c r="BI6" s="26">
         <f>BNVFE!X12</f>
         <v>5.076679534506399E-4</v>
       </c>
-      <c r="BJ6" s="28">
+      <c r="BJ6" s="26">
         <f>BNVFE!Y12</f>
         <v>5.1181172688478038E-4</v>
       </c>
-      <c r="BK6" s="28">
+      <c r="BK6" s="26">
         <f>BNVFE!Z12</f>
         <v>5.1597913882790009E-4</v>
       </c>
-      <c r="BL6" s="28">
+      <c r="BL6" s="26">
         <f>BNVFE!AA12</f>
         <v>5.2017698058550235E-4</v>
       </c>
-      <c r="BM6" s="28">
+      <c r="BM6" s="26">
         <f>BNVFE!AB12</f>
         <v>5.2440413218790766E-4</v>
       </c>
-      <c r="BN6" s="28">
+      <c r="BN6" s="26">
         <f>BNVFE!AC12</f>
         <v>5.2866665576887042E-4</v>
       </c>
-      <c r="BO6" s="28">
+      <c r="BO6" s="26">
         <f>BNVFE!AD12</f>
         <v>5.3296936481509794E-4</v>
       </c>
-      <c r="BP6" s="28">
+      <c r="BP6" s="26">
         <f>BNVFE!AE12</f>
         <v>5.3730424796901105E-4</v>
       </c>
-      <c r="BQ6" s="28">
+      <c r="BQ6" s="26">
         <f>BNVFE!AF12</f>
         <v>5.4167698609809006E-4</v>
       </c>
-      <c r="BR6" s="28">
+      <c r="BR6" s="26">
         <f>BNVFE!AG12</f>
         <v>5.4607888156546253E-4</v>
       </c>
-      <c r="BS6" s="28"/>
-      <c r="BT6" s="26"/>
+      <c r="BS6" s="26"/>
+      <c r="BT6" s="4"/>
     </row>
     <row r="7" spans="1:72">
-      <c r="A7" s="23" t="s">
+      <c r="A7" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="23" t="s">
+      <c r="B7" t="s">
         <v>22</v>
       </c>
-      <c r="C7" s="24"/>
-      <c r="D7" s="24"/>
-      <c r="E7" s="24"/>
-      <c r="F7" s="24"/>
-      <c r="G7" s="24"/>
-      <c r="H7" s="24"/>
-      <c r="I7" s="24"/>
-      <c r="J7" s="24"/>
-      <c r="K7" s="24"/>
-      <c r="L7" s="24"/>
-      <c r="M7" s="24"/>
-      <c r="N7" s="24"/>
-      <c r="O7" s="24"/>
-      <c r="P7" s="28">
+      <c r="C7" s="23"/>
+      <c r="D7" s="23"/>
+      <c r="E7" s="23"/>
+      <c r="F7" s="23"/>
+      <c r="G7" s="23"/>
+      <c r="H7" s="23"/>
+      <c r="I7" s="23"/>
+      <c r="J7" s="23"/>
+      <c r="K7" s="23"/>
+      <c r="L7" s="23"/>
+      <c r="M7" s="23"/>
+      <c r="N7" s="23"/>
+      <c r="O7" s="23"/>
+      <c r="P7" s="26">
         <f t="shared" ref="P7:AP7" si="7">Q7</f>
         <v>1.8223851973329149E-4</v>
       </c>
-      <c r="Q7" s="28">
+      <c r="Q7" s="26">
         <f t="shared" si="7"/>
         <v>1.8223851973329149E-4</v>
       </c>
-      <c r="R7" s="28">
+      <c r="R7" s="26">
         <f t="shared" si="7"/>
         <v>1.8223851973329149E-4</v>
       </c>
-      <c r="S7" s="28">
+      <c r="S7" s="26">
         <f t="shared" si="7"/>
         <v>1.8223851973329149E-4</v>
       </c>
-      <c r="T7" s="28">
+      <c r="T7" s="26">
         <f t="shared" si="7"/>
         <v>1.8223851973329149E-4</v>
       </c>
-      <c r="U7" s="28">
+      <c r="U7" s="26">
         <f t="shared" si="7"/>
         <v>1.8223851973329149E-4</v>
       </c>
-      <c r="V7" s="28">
+      <c r="V7" s="26">
         <f t="shared" si="7"/>
         <v>1.8223851973329149E-4</v>
       </c>
-      <c r="W7" s="28">
+      <c r="W7" s="26">
         <f t="shared" si="7"/>
         <v>1.8223851973329149E-4</v>
       </c>
-      <c r="X7" s="28">
+      <c r="X7" s="26">
         <f t="shared" si="7"/>
         <v>1.8223851973329149E-4</v>
       </c>
-      <c r="Y7" s="28">
+      <c r="Y7" s="26">
         <f t="shared" si="7"/>
         <v>1.8223851973329149E-4</v>
       </c>
-      <c r="Z7" s="28">
+      <c r="Z7" s="26">
         <f t="shared" si="7"/>
         <v>1.8223851973329149E-4</v>
       </c>
-      <c r="AA7" s="28">
+      <c r="AA7" s="26">
         <f t="shared" si="7"/>
         <v>1.8223851973329149E-4</v>
       </c>
-      <c r="AB7" s="28">
+      <c r="AB7" s="26">
         <f t="shared" si="7"/>
         <v>1.8223851973329149E-4</v>
       </c>
-      <c r="AC7" s="28">
+      <c r="AC7" s="26">
         <f t="shared" si="7"/>
         <v>1.8223851973329149E-4</v>
       </c>
-      <c r="AD7" s="28">
+      <c r="AD7" s="26">
         <f t="shared" si="7"/>
         <v>1.8223851973329149E-4</v>
       </c>
-      <c r="AE7" s="28">
+      <c r="AE7" s="26">
         <f t="shared" si="7"/>
         <v>1.8223851973329149E-4</v>
       </c>
-      <c r="AF7" s="28">
+      <c r="AF7" s="26">
         <f t="shared" si="7"/>
         <v>1.8223851973329149E-4</v>
       </c>
-      <c r="AG7" s="28">
+      <c r="AG7" s="26">
         <f t="shared" si="7"/>
         <v>1.8223851973329149E-4</v>
       </c>
-      <c r="AH7" s="28">
+      <c r="AH7" s="26">
         <f t="shared" si="7"/>
         <v>1.8223851973329149E-4</v>
       </c>
-      <c r="AI7" s="28">
+      <c r="AI7" s="26">
         <f t="shared" si="7"/>
         <v>1.8223851973329149E-4</v>
       </c>
-      <c r="AJ7" s="28">
+      <c r="AJ7" s="26">
         <f t="shared" si="7"/>
         <v>1.8223851973329149E-4</v>
       </c>
-      <c r="AK7" s="28">
+      <c r="AK7" s="26">
         <f t="shared" si="7"/>
         <v>1.8223851973329149E-4</v>
       </c>
-      <c r="AL7" s="28">
+      <c r="AL7" s="26">
         <f t="shared" si="7"/>
         <v>1.8223851973329149E-4</v>
       </c>
-      <c r="AM7" s="28">
+      <c r="AM7" s="26">
         <f t="shared" si="7"/>
         <v>1.8223851973329149E-4</v>
       </c>
-      <c r="AN7" s="28">
+      <c r="AN7" s="26">
         <f t="shared" si="7"/>
         <v>1.8223851973329149E-4</v>
       </c>
-      <c r="AO7" s="28">
+      <c r="AO7" s="26">
         <f t="shared" si="7"/>
         <v>1.8223851973329149E-4</v>
       </c>
-      <c r="AP7" s="28">
+      <c r="AP7" s="26">
         <f t="shared" si="7"/>
         <v>1.8223851973329149E-4</v>
       </c>
-      <c r="AQ7" s="28">
+      <c r="AQ7" s="26">
         <f>AR7</f>
         <v>1.8223851973329149E-4</v>
       </c>
@@ -20726,272 +20722,272 @@
         <f>BNVFE!G13</f>
         <v>1.8223851973329149E-4</v>
       </c>
-      <c r="AS7" s="28">
+      <c r="AS7" s="26">
         <f>BNVFE!H13</f>
         <v>1.8223851973329149E-4</v>
       </c>
-      <c r="AT7" s="28">
+      <c r="AT7" s="26">
         <f>BNVFE!I13</f>
         <v>1.8223851973329149E-4</v>
       </c>
-      <c r="AU7" s="28">
+      <c r="AU7" s="26">
         <f>BNVFE!J13</f>
         <v>1.8223851973329149E-4</v>
       </c>
-      <c r="AV7" s="28">
+      <c r="AV7" s="26">
         <f>BNVFE!K13</f>
         <v>1.8223851973329149E-4</v>
       </c>
-      <c r="AW7" s="28">
+      <c r="AW7" s="26">
         <f>BNVFE!L13</f>
         <v>1.8223851973329149E-4</v>
       </c>
-      <c r="AX7" s="28">
+      <c r="AX7" s="26">
         <f>BNVFE!M13</f>
         <v>1.8223851973329149E-4</v>
       </c>
-      <c r="AY7" s="28">
+      <c r="AY7" s="26">
         <f>BNVFE!N13</f>
         <v>1.8223851973329149E-4</v>
       </c>
-      <c r="AZ7" s="28">
+      <c r="AZ7" s="26">
         <f>BNVFE!O13</f>
         <v>1.8223851973329149E-4</v>
       </c>
-      <c r="BA7" s="28">
+      <c r="BA7" s="26">
         <f>BNVFE!P13</f>
         <v>1.8223851973329149E-4</v>
       </c>
-      <c r="BB7" s="28">
+      <c r="BB7" s="26">
         <f>BNVFE!Q13</f>
         <v>1.8223851973329149E-4</v>
       </c>
-      <c r="BC7" s="28">
+      <c r="BC7" s="26">
         <f>BNVFE!R13</f>
         <v>1.8223851973329149E-4</v>
       </c>
-      <c r="BD7" s="28">
+      <c r="BD7" s="26">
         <f>BNVFE!S13</f>
         <v>1.8223851973329149E-4</v>
       </c>
-      <c r="BE7" s="28">
+      <c r="BE7" s="26">
         <f>BNVFE!T13</f>
         <v>1.8223851973329149E-4</v>
       </c>
-      <c r="BF7" s="28">
+      <c r="BF7" s="26">
         <f>BNVFE!U13</f>
         <v>1.8223851973329149E-4</v>
       </c>
-      <c r="BG7" s="28">
+      <c r="BG7" s="26">
         <f>BNVFE!V13</f>
         <v>1.8223851973329149E-4</v>
       </c>
-      <c r="BH7" s="28">
+      <c r="BH7" s="26">
         <f>BNVFE!W13</f>
         <v>1.8223851973329149E-4</v>
       </c>
-      <c r="BI7" s="28">
+      <c r="BI7" s="26">
         <f>BNVFE!X13</f>
         <v>1.8223851973329149E-4</v>
       </c>
-      <c r="BJ7" s="28">
+      <c r="BJ7" s="26">
         <f>BNVFE!Y13</f>
         <v>1.8223851973329149E-4</v>
       </c>
-      <c r="BK7" s="28">
+      <c r="BK7" s="26">
         <f>BNVFE!Z13</f>
         <v>1.8223851973329149E-4</v>
       </c>
-      <c r="BL7" s="28">
+      <c r="BL7" s="26">
         <f>BNVFE!AA13</f>
         <v>1.8223851973329149E-4</v>
       </c>
-      <c r="BM7" s="28">
+      <c r="BM7" s="26">
         <f>BNVFE!AB13</f>
         <v>1.8223851973329149E-4</v>
       </c>
-      <c r="BN7" s="28">
+      <c r="BN7" s="26">
         <f>BNVFE!AC13</f>
         <v>1.8223851973329149E-4</v>
       </c>
-      <c r="BO7" s="28">
+      <c r="BO7" s="26">
         <f>BNVFE!AD13</f>
         <v>1.8223851973329149E-4</v>
       </c>
-      <c r="BP7" s="28">
+      <c r="BP7" s="26">
         <f>BNVFE!AE13</f>
         <v>1.8223851973329149E-4</v>
       </c>
-      <c r="BQ7" s="28">
+      <c r="BQ7" s="26">
         <f>BNVFE!AF13</f>
         <v>1.8223851973329149E-4</v>
       </c>
-      <c r="BR7" s="28">
+      <c r="BR7" s="26">
         <f>BNVFE!AG13</f>
         <v>1.8223851973329149E-4</v>
       </c>
-      <c r="BS7" s="28"/>
-      <c r="BT7" s="26"/>
+      <c r="BS7" s="26"/>
+      <c r="BT7" s="4"/>
     </row>
     <row r="8" spans="1:72">
-      <c r="A8" s="23" t="s">
+      <c r="A8" t="s">
         <v>16</v>
       </c>
-      <c r="B8" s="23" t="s">
+      <c r="B8" t="s">
         <v>89</v>
       </c>
-      <c r="C8" s="24"/>
-      <c r="D8" s="24"/>
-      <c r="E8" s="24"/>
-      <c r="F8" s="26">
+      <c r="C8" s="23"/>
+      <c r="D8" s="23"/>
+      <c r="E8" s="23"/>
+      <c r="F8" s="4">
         <f>SYFAFE!$E$5</f>
         <v>5.0586266198922429E-5</v>
       </c>
-      <c r="G8" s="26">
+      <c r="G8" s="4">
         <f>F8</f>
         <v>5.0586266198922429E-5</v>
       </c>
-      <c r="H8" s="26">
+      <c r="H8" s="4">
         <f t="shared" ref="H8:BR8" si="8">G8</f>
         <v>5.0586266198922429E-5</v>
       </c>
-      <c r="I8" s="26">
+      <c r="I8" s="4">
         <f t="shared" si="8"/>
         <v>5.0586266198922429E-5</v>
       </c>
-      <c r="J8" s="26">
+      <c r="J8" s="4">
         <f t="shared" si="8"/>
         <v>5.0586266198922429E-5</v>
       </c>
-      <c r="K8" s="26">
+      <c r="K8" s="4">
         <f t="shared" si="8"/>
         <v>5.0586266198922429E-5</v>
       </c>
-      <c r="L8" s="26">
+      <c r="L8" s="4">
         <f t="shared" si="8"/>
         <v>5.0586266198922429E-5</v>
       </c>
-      <c r="M8" s="26">
+      <c r="M8" s="4">
         <f t="shared" si="8"/>
         <v>5.0586266198922429E-5</v>
       </c>
-      <c r="N8" s="26">
+      <c r="N8" s="4">
         <f t="shared" si="8"/>
         <v>5.0586266198922429E-5</v>
       </c>
-      <c r="O8" s="26">
+      <c r="O8" s="4">
         <f t="shared" si="8"/>
         <v>5.0586266198922429E-5</v>
       </c>
-      <c r="P8" s="26">
+      <c r="P8" s="4">
         <f t="shared" si="8"/>
         <v>5.0586266198922429E-5</v>
       </c>
-      <c r="Q8" s="26">
+      <c r="Q8" s="4">
         <f t="shared" si="8"/>
         <v>5.0586266198922429E-5</v>
       </c>
-      <c r="R8" s="26">
+      <c r="R8" s="4">
         <f t="shared" si="8"/>
         <v>5.0586266198922429E-5</v>
       </c>
-      <c r="S8" s="26">
+      <c r="S8" s="4">
         <f t="shared" si="8"/>
         <v>5.0586266198922429E-5</v>
       </c>
-      <c r="T8" s="26">
+      <c r="T8" s="4">
         <f t="shared" si="8"/>
         <v>5.0586266198922429E-5</v>
       </c>
-      <c r="U8" s="26">
+      <c r="U8" s="4">
         <f t="shared" si="8"/>
         <v>5.0586266198922429E-5</v>
       </c>
-      <c r="V8" s="26">
+      <c r="V8" s="4">
         <f t="shared" si="8"/>
         <v>5.0586266198922429E-5</v>
       </c>
-      <c r="W8" s="26">
+      <c r="W8" s="4">
         <f t="shared" si="8"/>
         <v>5.0586266198922429E-5</v>
       </c>
-      <c r="X8" s="26">
+      <c r="X8" s="4">
         <f t="shared" si="8"/>
         <v>5.0586266198922429E-5</v>
       </c>
-      <c r="Y8" s="26">
+      <c r="Y8" s="4">
         <f t="shared" si="8"/>
         <v>5.0586266198922429E-5</v>
       </c>
-      <c r="Z8" s="26">
+      <c r="Z8" s="4">
         <f t="shared" si="8"/>
         <v>5.0586266198922429E-5</v>
       </c>
-      <c r="AA8" s="26">
+      <c r="AA8" s="4">
         <f t="shared" si="8"/>
         <v>5.0586266198922429E-5</v>
       </c>
-      <c r="AB8" s="26">
+      <c r="AB8" s="4">
         <f t="shared" si="8"/>
         <v>5.0586266198922429E-5</v>
       </c>
-      <c r="AC8" s="26">
+      <c r="AC8" s="4">
         <f t="shared" si="8"/>
         <v>5.0586266198922429E-5</v>
       </c>
-      <c r="AD8" s="26">
+      <c r="AD8" s="4">
         <f t="shared" si="8"/>
         <v>5.0586266198922429E-5</v>
       </c>
-      <c r="AE8" s="26">
+      <c r="AE8" s="4">
         <f t="shared" si="8"/>
         <v>5.0586266198922429E-5</v>
       </c>
-      <c r="AF8" s="26">
+      <c r="AF8" s="4">
         <f t="shared" si="8"/>
         <v>5.0586266198922429E-5</v>
       </c>
-      <c r="AG8" s="26">
+      <c r="AG8" s="4">
         <f t="shared" si="8"/>
         <v>5.0586266198922429E-5</v>
       </c>
-      <c r="AH8" s="26">
+      <c r="AH8" s="4">
         <f t="shared" si="8"/>
         <v>5.0586266198922429E-5</v>
       </c>
-      <c r="AI8" s="26">
+      <c r="AI8" s="4">
         <f t="shared" si="8"/>
         <v>5.0586266198922429E-5</v>
       </c>
-      <c r="AJ8" s="26">
+      <c r="AJ8" s="4">
         <f t="shared" si="8"/>
         <v>5.0586266198922429E-5</v>
       </c>
-      <c r="AK8" s="26">
+      <c r="AK8" s="4">
         <f t="shared" si="8"/>
         <v>5.0586266198922429E-5</v>
       </c>
-      <c r="AL8" s="26">
+      <c r="AL8" s="4">
         <f t="shared" si="8"/>
         <v>5.0586266198922429E-5</v>
       </c>
-      <c r="AM8" s="26">
+      <c r="AM8" s="4">
         <f t="shared" si="8"/>
         <v>5.0586266198922429E-5</v>
       </c>
-      <c r="AN8" s="26">
+      <c r="AN8" s="4">
         <f t="shared" si="8"/>
         <v>5.0586266198922429E-5</v>
       </c>
-      <c r="AO8" s="26">
+      <c r="AO8" s="4">
         <f t="shared" si="8"/>
         <v>5.0586266198922429E-5</v>
       </c>
-      <c r="AP8" s="26">
+      <c r="AP8" s="4">
         <f>AO8</f>
         <v>5.0586266198922429E-5</v>
       </c>
-      <c r="AQ8" s="26">
+      <c r="AQ8" s="4">
         <f>AP8</f>
         <v>5.0586266198922429E-5</v>
       </c>
@@ -20999,272 +20995,272 @@
         <f t="shared" si="8"/>
         <v>5.0586266198922429E-5</v>
       </c>
-      <c r="AS8" s="26">
+      <c r="AS8" s="4">
         <f t="shared" si="8"/>
         <v>5.0586266198922429E-5</v>
       </c>
-      <c r="AT8" s="26">
+      <c r="AT8" s="4">
         <f t="shared" si="8"/>
         <v>5.0586266198922429E-5</v>
       </c>
-      <c r="AU8" s="26">
+      <c r="AU8" s="4">
         <f t="shared" si="8"/>
         <v>5.0586266198922429E-5</v>
       </c>
-      <c r="AV8" s="26">
+      <c r="AV8" s="4">
         <f t="shared" si="8"/>
         <v>5.0586266198922429E-5</v>
       </c>
-      <c r="AW8" s="26">
+      <c r="AW8" s="4">
         <f t="shared" si="8"/>
         <v>5.0586266198922429E-5</v>
       </c>
-      <c r="AX8" s="26">
+      <c r="AX8" s="4">
         <f t="shared" si="8"/>
         <v>5.0586266198922429E-5</v>
       </c>
-      <c r="AY8" s="26">
+      <c r="AY8" s="4">
         <f t="shared" si="8"/>
         <v>5.0586266198922429E-5</v>
       </c>
-      <c r="AZ8" s="26">
+      <c r="AZ8" s="4">
         <f t="shared" si="8"/>
         <v>5.0586266198922429E-5</v>
       </c>
-      <c r="BA8" s="26">
+      <c r="BA8" s="4">
         <f t="shared" si="8"/>
         <v>5.0586266198922429E-5</v>
       </c>
-      <c r="BB8" s="26">
+      <c r="BB8" s="4">
         <f t="shared" si="8"/>
         <v>5.0586266198922429E-5</v>
       </c>
-      <c r="BC8" s="26">
+      <c r="BC8" s="4">
         <f t="shared" si="8"/>
         <v>5.0586266198922429E-5</v>
       </c>
-      <c r="BD8" s="26">
+      <c r="BD8" s="4">
         <f t="shared" si="8"/>
         <v>5.0586266198922429E-5</v>
       </c>
-      <c r="BE8" s="26">
+      <c r="BE8" s="4">
         <f t="shared" si="8"/>
         <v>5.0586266198922429E-5</v>
       </c>
-      <c r="BF8" s="26">
+      <c r="BF8" s="4">
         <f t="shared" si="8"/>
         <v>5.0586266198922429E-5</v>
       </c>
-      <c r="BG8" s="26">
+      <c r="BG8" s="4">
         <f t="shared" si="8"/>
         <v>5.0586266198922429E-5</v>
       </c>
-      <c r="BH8" s="26">
+      <c r="BH8" s="4">
         <f t="shared" si="8"/>
         <v>5.0586266198922429E-5</v>
       </c>
-      <c r="BI8" s="26">
+      <c r="BI8" s="4">
         <f t="shared" si="8"/>
         <v>5.0586266198922429E-5</v>
       </c>
-      <c r="BJ8" s="26">
+      <c r="BJ8" s="4">
         <f t="shared" si="8"/>
         <v>5.0586266198922429E-5</v>
       </c>
-      <c r="BK8" s="26">
+      <c r="BK8" s="4">
         <f t="shared" si="8"/>
         <v>5.0586266198922429E-5</v>
       </c>
-      <c r="BL8" s="26">
+      <c r="BL8" s="4">
         <f t="shared" si="8"/>
         <v>5.0586266198922429E-5</v>
       </c>
-      <c r="BM8" s="26">
+      <c r="BM8" s="4">
         <f t="shared" si="8"/>
         <v>5.0586266198922429E-5</v>
       </c>
-      <c r="BN8" s="26">
+      <c r="BN8" s="4">
         <f t="shared" si="8"/>
         <v>5.0586266198922429E-5</v>
       </c>
-      <c r="BO8" s="26">
+      <c r="BO8" s="4">
         <f t="shared" si="8"/>
         <v>5.0586266198922429E-5</v>
       </c>
-      <c r="BP8" s="26">
+      <c r="BP8" s="4">
         <f t="shared" si="8"/>
         <v>5.0586266198922429E-5</v>
       </c>
-      <c r="BQ8" s="26">
+      <c r="BQ8" s="4">
         <f t="shared" si="8"/>
         <v>5.0586266198922429E-5</v>
       </c>
-      <c r="BR8" s="26">
+      <c r="BR8" s="4">
         <f t="shared" si="8"/>
         <v>5.0586266198922429E-5</v>
       </c>
-      <c r="BS8" s="28"/>
-      <c r="BT8" s="26"/>
+      <c r="BS8" s="26"/>
+      <c r="BT8" s="4"/>
     </row>
     <row r="9" spans="1:72">
-      <c r="A9" s="23" t="s">
+      <c r="A9" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="23" t="s">
+      <c r="B9" t="s">
         <v>90</v>
       </c>
-      <c r="C9" s="24"/>
-      <c r="D9" s="24"/>
-      <c r="E9" s="24"/>
-      <c r="F9" s="29">
+      <c r="C9" s="23"/>
+      <c r="D9" s="23"/>
+      <c r="E9" s="23"/>
+      <c r="F9" s="27">
         <f>SYFAFE!$B$5</f>
         <v>6.7428486606874269E-4</v>
       </c>
-      <c r="G9" s="26">
+      <c r="G9" s="4">
         <f>F9</f>
         <v>6.7428486606874269E-4</v>
       </c>
-      <c r="H9" s="26">
+      <c r="H9" s="4">
         <f t="shared" ref="H9:BR9" si="9">G9</f>
         <v>6.7428486606874269E-4</v>
       </c>
-      <c r="I9" s="26">
+      <c r="I9" s="4">
         <f t="shared" si="9"/>
         <v>6.7428486606874269E-4</v>
       </c>
-      <c r="J9" s="26">
+      <c r="J9" s="4">
         <f t="shared" si="9"/>
         <v>6.7428486606874269E-4</v>
       </c>
-      <c r="K9" s="26">
+      <c r="K9" s="4">
         <f t="shared" si="9"/>
         <v>6.7428486606874269E-4</v>
       </c>
-      <c r="L9" s="26">
+      <c r="L9" s="4">
         <f t="shared" si="9"/>
         <v>6.7428486606874269E-4</v>
       </c>
-      <c r="M9" s="26">
+      <c r="M9" s="4">
         <f t="shared" si="9"/>
         <v>6.7428486606874269E-4</v>
       </c>
-      <c r="N9" s="26">
+      <c r="N9" s="4">
         <f t="shared" si="9"/>
         <v>6.7428486606874269E-4</v>
       </c>
-      <c r="O9" s="26">
+      <c r="O9" s="4">
         <f t="shared" si="9"/>
         <v>6.7428486606874269E-4</v>
       </c>
-      <c r="P9" s="26">
+      <c r="P9" s="4">
         <f t="shared" si="9"/>
         <v>6.7428486606874269E-4</v>
       </c>
-      <c r="Q9" s="26">
+      <c r="Q9" s="4">
         <f t="shared" si="9"/>
         <v>6.7428486606874269E-4</v>
       </c>
-      <c r="R9" s="26">
+      <c r="R9" s="4">
         <f t="shared" si="9"/>
         <v>6.7428486606874269E-4</v>
       </c>
-      <c r="S9" s="26">
+      <c r="S9" s="4">
         <f t="shared" si="9"/>
         <v>6.7428486606874269E-4</v>
       </c>
-      <c r="T9" s="26">
+      <c r="T9" s="4">
         <f t="shared" si="9"/>
         <v>6.7428486606874269E-4</v>
       </c>
-      <c r="U9" s="26">
+      <c r="U9" s="4">
         <f t="shared" si="9"/>
         <v>6.7428486606874269E-4</v>
       </c>
-      <c r="V9" s="26">
+      <c r="V9" s="4">
         <f t="shared" si="9"/>
         <v>6.7428486606874269E-4</v>
       </c>
-      <c r="W9" s="26">
+      <c r="W9" s="4">
         <f t="shared" si="9"/>
         <v>6.7428486606874269E-4</v>
       </c>
-      <c r="X9" s="26">
+      <c r="X9" s="4">
         <f t="shared" si="9"/>
         <v>6.7428486606874269E-4</v>
       </c>
-      <c r="Y9" s="26">
+      <c r="Y9" s="4">
         <f t="shared" si="9"/>
         <v>6.7428486606874269E-4</v>
       </c>
-      <c r="Z9" s="26">
+      <c r="Z9" s="4">
         <f t="shared" si="9"/>
         <v>6.7428486606874269E-4</v>
       </c>
-      <c r="AA9" s="26">
+      <c r="AA9" s="4">
         <f t="shared" si="9"/>
         <v>6.7428486606874269E-4</v>
       </c>
-      <c r="AB9" s="26">
+      <c r="AB9" s="4">
         <f t="shared" si="9"/>
         <v>6.7428486606874269E-4</v>
       </c>
-      <c r="AC9" s="26">
+      <c r="AC9" s="4">
         <f t="shared" si="9"/>
         <v>6.7428486606874269E-4</v>
       </c>
-      <c r="AD9" s="26">
+      <c r="AD9" s="4">
         <f t="shared" si="9"/>
         <v>6.7428486606874269E-4</v>
       </c>
-      <c r="AE9" s="26">
+      <c r="AE9" s="4">
         <f t="shared" si="9"/>
         <v>6.7428486606874269E-4</v>
       </c>
-      <c r="AF9" s="26">
+      <c r="AF9" s="4">
         <f t="shared" si="9"/>
         <v>6.7428486606874269E-4</v>
       </c>
-      <c r="AG9" s="26">
+      <c r="AG9" s="4">
         <f t="shared" si="9"/>
         <v>6.7428486606874269E-4</v>
       </c>
-      <c r="AH9" s="26">
+      <c r="AH9" s="4">
         <f t="shared" si="9"/>
         <v>6.7428486606874269E-4</v>
       </c>
-      <c r="AI9" s="26">
+      <c r="AI9" s="4">
         <f t="shared" si="9"/>
         <v>6.7428486606874269E-4</v>
       </c>
-      <c r="AJ9" s="26">
+      <c r="AJ9" s="4">
         <f t="shared" si="9"/>
         <v>6.7428486606874269E-4</v>
       </c>
-      <c r="AK9" s="26">
+      <c r="AK9" s="4">
         <f t="shared" si="9"/>
         <v>6.7428486606874269E-4</v>
       </c>
-      <c r="AL9" s="26">
+      <c r="AL9" s="4">
         <f t="shared" si="9"/>
         <v>6.7428486606874269E-4</v>
       </c>
-      <c r="AM9" s="26">
+      <c r="AM9" s="4">
         <f t="shared" si="9"/>
         <v>6.7428486606874269E-4</v>
       </c>
-      <c r="AN9" s="26">
+      <c r="AN9" s="4">
         <f t="shared" si="9"/>
         <v>6.7428486606874269E-4</v>
       </c>
-      <c r="AO9" s="26">
+      <c r="AO9" s="4">
         <f t="shared" si="9"/>
         <v>6.7428486606874269E-4</v>
       </c>
-      <c r="AP9" s="26">
+      <c r="AP9" s="4">
         <f t="shared" si="9"/>
         <v>6.7428486606874269E-4</v>
       </c>
-      <c r="AQ9" s="26">
+      <c r="AQ9" s="4">
         <f t="shared" si="9"/>
         <v>6.7428486606874269E-4</v>
       </c>
@@ -21272,272 +21268,272 @@
         <f t="shared" si="9"/>
         <v>6.7428486606874269E-4</v>
       </c>
-      <c r="AS9" s="26">
+      <c r="AS9" s="4">
         <f t="shared" si="9"/>
         <v>6.7428486606874269E-4</v>
       </c>
-      <c r="AT9" s="26">
+      <c r="AT9" s="4">
         <f t="shared" si="9"/>
         <v>6.7428486606874269E-4</v>
       </c>
-      <c r="AU9" s="26">
+      <c r="AU9" s="4">
         <f t="shared" si="9"/>
         <v>6.7428486606874269E-4</v>
       </c>
-      <c r="AV9" s="26">
+      <c r="AV9" s="4">
         <f t="shared" si="9"/>
         <v>6.7428486606874269E-4</v>
       </c>
-      <c r="AW9" s="26">
+      <c r="AW9" s="4">
         <f t="shared" si="9"/>
         <v>6.7428486606874269E-4</v>
       </c>
-      <c r="AX9" s="26">
+      <c r="AX9" s="4">
         <f t="shared" si="9"/>
         <v>6.7428486606874269E-4</v>
       </c>
-      <c r="AY9" s="26">
+      <c r="AY9" s="4">
         <f t="shared" si="9"/>
         <v>6.7428486606874269E-4</v>
       </c>
-      <c r="AZ9" s="26">
+      <c r="AZ9" s="4">
         <f t="shared" si="9"/>
         <v>6.7428486606874269E-4</v>
       </c>
-      <c r="BA9" s="26">
+      <c r="BA9" s="4">
         <f t="shared" si="9"/>
         <v>6.7428486606874269E-4</v>
       </c>
-      <c r="BB9" s="26">
+      <c r="BB9" s="4">
         <f t="shared" si="9"/>
         <v>6.7428486606874269E-4</v>
       </c>
-      <c r="BC9" s="26">
+      <c r="BC9" s="4">
         <f t="shared" si="9"/>
         <v>6.7428486606874269E-4</v>
       </c>
-      <c r="BD9" s="26">
+      <c r="BD9" s="4">
         <f t="shared" si="9"/>
         <v>6.7428486606874269E-4</v>
       </c>
-      <c r="BE9" s="26">
+      <c r="BE9" s="4">
         <f t="shared" si="9"/>
         <v>6.7428486606874269E-4</v>
       </c>
-      <c r="BF9" s="26">
+      <c r="BF9" s="4">
         <f t="shared" si="9"/>
         <v>6.7428486606874269E-4</v>
       </c>
-      <c r="BG9" s="26">
+      <c r="BG9" s="4">
         <f t="shared" si="9"/>
         <v>6.7428486606874269E-4</v>
       </c>
-      <c r="BH9" s="26">
+      <c r="BH9" s="4">
         <f t="shared" si="9"/>
         <v>6.7428486606874269E-4</v>
       </c>
-      <c r="BI9" s="26">
+      <c r="BI9" s="4">
         <f t="shared" si="9"/>
         <v>6.7428486606874269E-4</v>
       </c>
-      <c r="BJ9" s="26">
+      <c r="BJ9" s="4">
         <f t="shared" si="9"/>
         <v>6.7428486606874269E-4</v>
       </c>
-      <c r="BK9" s="26">
+      <c r="BK9" s="4">
         <f t="shared" si="9"/>
         <v>6.7428486606874269E-4</v>
       </c>
-      <c r="BL9" s="26">
+      <c r="BL9" s="4">
         <f t="shared" si="9"/>
         <v>6.7428486606874269E-4</v>
       </c>
-      <c r="BM9" s="26">
+      <c r="BM9" s="4">
         <f t="shared" si="9"/>
         <v>6.7428486606874269E-4</v>
       </c>
-      <c r="BN9" s="26">
+      <c r="BN9" s="4">
         <f t="shared" si="9"/>
         <v>6.7428486606874269E-4</v>
       </c>
-      <c r="BO9" s="26">
+      <c r="BO9" s="4">
         <f t="shared" si="9"/>
         <v>6.7428486606874269E-4</v>
       </c>
-      <c r="BP9" s="26">
+      <c r="BP9" s="4">
         <f t="shared" si="9"/>
         <v>6.7428486606874269E-4</v>
       </c>
-      <c r="BQ9" s="26">
+      <c r="BQ9" s="4">
         <f t="shared" si="9"/>
         <v>6.7428486606874269E-4</v>
       </c>
-      <c r="BR9" s="26">
+      <c r="BR9" s="4">
         <f t="shared" si="9"/>
         <v>6.7428486606874269E-4</v>
       </c>
-      <c r="BS9" s="28"/>
-      <c r="BT9" s="26"/>
+      <c r="BS9" s="26"/>
+      <c r="BT9" s="4"/>
     </row>
     <row r="10" spans="1:72">
-      <c r="A10" s="23" t="s">
+      <c r="A10" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="23" t="s">
+      <c r="B10" t="s">
         <v>22</v>
       </c>
-      <c r="C10" s="24"/>
-      <c r="D10" s="24"/>
-      <c r="E10" s="24"/>
-      <c r="F10" s="26">
+      <c r="C10" s="23"/>
+      <c r="D10" s="23"/>
+      <c r="E10" s="23"/>
+      <c r="F10" s="4">
         <f>TREND($AR10:$BR10,$AR$1:$BR$1,F$1)</f>
         <v>3.2361562983312985E-3</v>
       </c>
-      <c r="G10" s="26">
-        <f t="shared" ref="G10:AR13" si="10">TREND($AR10:$BR10,$AR$1:$BR$1,G$1)</f>
+      <c r="G10" s="4">
+        <f t="shared" ref="G10:AQ13" si="10">TREND($AR10:$BR10,$AR$1:$BR$1,G$1)</f>
         <v>3.2397638770858776E-3</v>
       </c>
-      <c r="H10" s="26">
+      <c r="H10" s="4">
         <f t="shared" si="10"/>
         <v>3.2433714558404558E-3</v>
       </c>
-      <c r="I10" s="26">
+      <c r="I10" s="4">
         <f t="shared" si="10"/>
         <v>3.2469790345950348E-3</v>
       </c>
-      <c r="J10" s="26">
+      <c r="J10" s="4">
         <f t="shared" si="10"/>
         <v>3.2505866133496139E-3</v>
       </c>
-      <c r="K10" s="26">
+      <c r="K10" s="4">
         <f t="shared" si="10"/>
         <v>3.2541941921041921E-3</v>
       </c>
-      <c r="L10" s="26">
+      <c r="L10" s="4">
         <f t="shared" si="10"/>
         <v>3.2578017708587712E-3</v>
       </c>
-      <c r="M10" s="26">
+      <c r="M10" s="4">
         <f t="shared" si="10"/>
         <v>3.2614093496133494E-3</v>
       </c>
-      <c r="N10" s="26">
+      <c r="N10" s="4">
         <f t="shared" si="10"/>
         <v>3.2650169283679285E-3</v>
       </c>
-      <c r="O10" s="26">
+      <c r="O10" s="4">
         <f t="shared" si="10"/>
         <v>3.2686245071225075E-3</v>
       </c>
-      <c r="P10" s="26">
+      <c r="P10" s="4">
         <f t="shared" si="10"/>
         <v>3.2722320858770857E-3</v>
       </c>
-      <c r="Q10" s="26">
+      <c r="Q10" s="4">
         <f t="shared" si="10"/>
         <v>3.2758396646316648E-3</v>
       </c>
-      <c r="R10" s="26">
+      <c r="R10" s="4">
         <f t="shared" si="10"/>
         <v>3.2794472433862439E-3</v>
       </c>
-      <c r="S10" s="26">
+      <c r="S10" s="4">
         <f t="shared" si="10"/>
         <v>3.2830548221408221E-3</v>
       </c>
-      <c r="T10" s="26">
+      <c r="T10" s="4">
         <f t="shared" si="10"/>
         <v>3.2866624008954012E-3</v>
       </c>
-      <c r="U10" s="26">
+      <c r="U10" s="4">
         <f t="shared" si="10"/>
         <v>3.2902699796499802E-3</v>
       </c>
-      <c r="V10" s="26">
+      <c r="V10" s="4">
         <f t="shared" si="10"/>
         <v>3.2938775584045584E-3</v>
       </c>
-      <c r="W10" s="26">
+      <c r="W10" s="4">
         <f t="shared" si="10"/>
         <v>3.2974851371591375E-3</v>
       </c>
-      <c r="X10" s="26">
+      <c r="X10" s="4">
         <f t="shared" si="10"/>
         <v>3.3010927159137157E-3</v>
       </c>
-      <c r="Y10" s="26">
+      <c r="Y10" s="4">
         <f t="shared" si="10"/>
         <v>3.3047002946682948E-3</v>
       </c>
-      <c r="Z10" s="26">
+      <c r="Z10" s="4">
         <f t="shared" si="10"/>
         <v>3.3083078734228739E-3</v>
       </c>
-      <c r="AA10" s="26">
+      <c r="AA10" s="4">
         <f t="shared" si="10"/>
         <v>3.3119154521774521E-3</v>
       </c>
-      <c r="AB10" s="26">
+      <c r="AB10" s="4">
         <f t="shared" si="10"/>
         <v>3.3155230309320311E-3</v>
       </c>
-      <c r="AC10" s="26">
+      <c r="AC10" s="4">
         <f t="shared" si="10"/>
         <v>3.3191306096866102E-3</v>
       </c>
-      <c r="AD10" s="26">
+      <c r="AD10" s="4">
         <f t="shared" si="10"/>
         <v>3.3227381884411884E-3</v>
       </c>
-      <c r="AE10" s="26">
+      <c r="AE10" s="4">
         <f t="shared" si="10"/>
         <v>3.3263457671957675E-3</v>
       </c>
-      <c r="AF10" s="26">
+      <c r="AF10" s="4">
         <f t="shared" si="10"/>
         <v>3.3299533459503457E-3</v>
       </c>
-      <c r="AG10" s="26">
+      <c r="AG10" s="4">
         <f t="shared" si="10"/>
         <v>3.3335609247049248E-3</v>
       </c>
-      <c r="AH10" s="26">
+      <c r="AH10" s="4">
         <f t="shared" si="10"/>
         <v>3.3371685034595039E-3</v>
       </c>
-      <c r="AI10" s="26">
+      <c r="AI10" s="4">
         <f t="shared" si="10"/>
         <v>3.3407760822140821E-3</v>
       </c>
-      <c r="AJ10" s="26">
+      <c r="AJ10" s="4">
         <f t="shared" si="10"/>
         <v>3.3443836609686611E-3</v>
       </c>
-      <c r="AK10" s="26">
+      <c r="AK10" s="4">
         <f t="shared" si="10"/>
         <v>3.3479912397232402E-3</v>
       </c>
-      <c r="AL10" s="26">
+      <c r="AL10" s="4">
         <f t="shared" si="10"/>
         <v>3.3515988184778184E-3</v>
       </c>
-      <c r="AM10" s="26">
+      <c r="AM10" s="4">
         <f t="shared" si="10"/>
         <v>3.3552063972323975E-3</v>
       </c>
-      <c r="AN10" s="26">
+      <c r="AN10" s="4">
         <f t="shared" si="10"/>
         <v>3.3588139759869757E-3</v>
       </c>
-      <c r="AO10" s="26">
+      <c r="AO10" s="4">
         <f t="shared" si="10"/>
         <v>3.3624215547415548E-3</v>
       </c>
-      <c r="AP10" s="26">
+      <c r="AP10" s="4">
         <f t="shared" si="10"/>
         <v>3.3660291334961338E-3</v>
       </c>
-      <c r="AQ10" s="26">
+      <c r="AQ10" s="4">
         <f>TREND($AR10:$BR10,$AR$1:$BR$1,AQ$1)</f>
         <v>3.369636712250712E-3</v>
       </c>
@@ -21545,269 +21541,269 @@
         <f>BNVFE!G16</f>
         <v>3.3734500000000001E-3</v>
       </c>
-      <c r="AS10" s="28">
+      <c r="AS10" s="26">
         <f>BNVFE!H16</f>
         <v>3.3770099999999997E-3</v>
       </c>
-      <c r="AT10" s="28">
+      <c r="AT10" s="26">
         <f>BNVFE!I16</f>
         <v>3.3805740000000003E-3</v>
       </c>
-      <c r="AU10" s="28">
+      <c r="AU10" s="26">
         <f>BNVFE!J16</f>
         <v>3.3841420000000001E-3</v>
       </c>
-      <c r="AV10" s="28">
+      <c r="AV10" s="26">
         <f>BNVFE!K16</f>
         <v>3.3877130000000001E-3</v>
       </c>
-      <c r="AW10" s="28">
+      <c r="AW10" s="26">
         <f>BNVFE!L16</f>
         <v>3.391289E-3</v>
       </c>
-      <c r="AX10" s="28">
+      <c r="AX10" s="26">
         <f>BNVFE!M16</f>
         <v>3.3948680000000001E-3</v>
       </c>
-      <c r="AY10" s="28">
+      <c r="AY10" s="26">
         <f>BNVFE!N16</f>
         <v>3.3984510000000002E-3</v>
       </c>
-      <c r="AZ10" s="28">
+      <c r="AZ10" s="26">
         <f>BNVFE!O16</f>
         <v>3.4020370000000001E-3</v>
       </c>
-      <c r="BA10" s="28">
+      <c r="BA10" s="26">
         <f>BNVFE!P16</f>
         <v>3.405628E-3</v>
       </c>
-      <c r="BB10" s="28">
+      <c r="BB10" s="26">
         <f>BNVFE!Q16</f>
         <v>3.4092220000000004E-3</v>
       </c>
-      <c r="BC10" s="28">
+      <c r="BC10" s="26">
         <f>BNVFE!R16</f>
         <v>3.41282E-3</v>
       </c>
-      <c r="BD10" s="28">
+      <c r="BD10" s="26">
         <f>BNVFE!S16</f>
         <v>3.4164219999999997E-3</v>
       </c>
-      <c r="BE10" s="28">
+      <c r="BE10" s="26">
         <f>BNVFE!T16</f>
         <v>3.420027E-3</v>
       </c>
-      <c r="BF10" s="28">
+      <c r="BF10" s="26">
         <f>BNVFE!U16</f>
         <v>3.4236369999999998E-3</v>
       </c>
-      <c r="BG10" s="28">
+      <c r="BG10" s="26">
         <f>BNVFE!V16</f>
         <v>3.4272499999999997E-3</v>
       </c>
-      <c r="BH10" s="28">
+      <c r="BH10" s="26">
         <f>BNVFE!W16</f>
         <v>3.4308670000000002E-3</v>
       </c>
-      <c r="BI10" s="28">
+      <c r="BI10" s="26">
         <f>BNVFE!X16</f>
         <v>3.4344879999999999E-3</v>
       </c>
-      <c r="BJ10" s="28">
+      <c r="BJ10" s="26">
         <f>BNVFE!Y16</f>
         <v>3.438113E-3</v>
       </c>
-      <c r="BK10" s="28">
+      <c r="BK10" s="26">
         <f>BNVFE!Z16</f>
         <v>3.4417409999999999E-3</v>
       </c>
-      <c r="BL10" s="28">
+      <c r="BL10" s="26">
         <f>BNVFE!AA16</f>
         <v>3.4453729999999998E-3</v>
       </c>
-      <c r="BM10" s="28">
+      <c r="BM10" s="26">
         <f>BNVFE!AB16</f>
         <v>3.4490099999999997E-3</v>
       </c>
-      <c r="BN10" s="28">
+      <c r="BN10" s="26">
         <f>BNVFE!AC16</f>
         <v>3.4526489999999999E-3</v>
       </c>
-      <c r="BO10" s="28">
+      <c r="BO10" s="26">
         <f>BNVFE!AD16</f>
         <v>3.456293E-3</v>
       </c>
-      <c r="BP10" s="28">
+      <c r="BP10" s="26">
         <f>BNVFE!AE16</f>
         <v>3.4599410000000002E-3</v>
       </c>
-      <c r="BQ10" s="28">
+      <c r="BQ10" s="26">
         <f>BNVFE!AF16</f>
         <v>3.4635930000000001E-3</v>
       </c>
-      <c r="BR10" s="28">
+      <c r="BR10" s="26">
         <f>BNVFE!AG16</f>
         <v>3.467248E-3</v>
       </c>
-      <c r="BS10" s="28"/>
-      <c r="BT10" s="26"/>
+      <c r="BS10" s="26"/>
+      <c r="BT10" s="4"/>
     </row>
     <row r="11" spans="1:72">
-      <c r="A11" s="23" t="s">
+      <c r="A11" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="23" t="s">
+      <c r="B11" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="24"/>
-      <c r="D11" s="24"/>
-      <c r="E11" s="24"/>
-      <c r="F11" s="24"/>
-      <c r="G11" s="26">
+      <c r="C11" s="23"/>
+      <c r="D11" s="23"/>
+      <c r="E11" s="23"/>
+      <c r="F11" s="23"/>
+      <c r="G11" s="4">
         <f>TREND($AR11:$BR11,$AR$1:$BR$1,G$1)</f>
         <v>1.187239917321092E-5</v>
       </c>
-      <c r="H11" s="26">
+      <c r="H11" s="4">
         <f t="shared" si="10"/>
         <v>1.187239917321092E-5</v>
       </c>
-      <c r="I11" s="26">
+      <c r="I11" s="4">
         <f t="shared" si="10"/>
         <v>1.187239917321092E-5</v>
       </c>
-      <c r="J11" s="26">
+      <c r="J11" s="4">
         <f t="shared" si="10"/>
         <v>1.187239917321092E-5</v>
       </c>
-      <c r="K11" s="26">
+      <c r="K11" s="4">
         <f t="shared" si="10"/>
         <v>1.187239917321092E-5</v>
       </c>
-      <c r="L11" s="26">
+      <c r="L11" s="4">
         <f t="shared" si="10"/>
         <v>1.187239917321092E-5</v>
       </c>
-      <c r="M11" s="26">
+      <c r="M11" s="4">
         <f t="shared" si="10"/>
         <v>1.187239917321092E-5</v>
       </c>
-      <c r="N11" s="26">
+      <c r="N11" s="4">
         <f t="shared" si="10"/>
         <v>1.187239917321092E-5</v>
       </c>
-      <c r="O11" s="26">
+      <c r="O11" s="4">
         <f t="shared" si="10"/>
         <v>1.187239917321092E-5</v>
       </c>
-      <c r="P11" s="26">
+      <c r="P11" s="4">
         <f t="shared" si="10"/>
         <v>1.187239917321092E-5</v>
       </c>
-      <c r="Q11" s="26">
+      <c r="Q11" s="4">
         <f t="shared" si="10"/>
         <v>1.187239917321092E-5</v>
       </c>
-      <c r="R11" s="26">
+      <c r="R11" s="4">
         <f t="shared" si="10"/>
         <v>1.187239917321092E-5</v>
       </c>
-      <c r="S11" s="26">
+      <c r="S11" s="4">
         <f t="shared" si="10"/>
         <v>1.187239917321092E-5</v>
       </c>
-      <c r="T11" s="26">
+      <c r="T11" s="4">
         <f t="shared" si="10"/>
         <v>1.187239917321092E-5</v>
       </c>
-      <c r="U11" s="26">
+      <c r="U11" s="4">
         <f t="shared" si="10"/>
         <v>1.187239917321092E-5</v>
       </c>
-      <c r="V11" s="26">
+      <c r="V11" s="4">
         <f t="shared" si="10"/>
         <v>1.187239917321092E-5</v>
       </c>
-      <c r="W11" s="26">
+      <c r="W11" s="4">
         <f t="shared" si="10"/>
         <v>1.187239917321092E-5</v>
       </c>
-      <c r="X11" s="26">
+      <c r="X11" s="4">
         <f t="shared" si="10"/>
         <v>1.187239917321092E-5</v>
       </c>
-      <c r="Y11" s="26">
+      <c r="Y11" s="4">
         <f t="shared" si="10"/>
         <v>1.187239917321092E-5</v>
       </c>
-      <c r="Z11" s="26">
+      <c r="Z11" s="4">
         <f t="shared" si="10"/>
         <v>1.187239917321092E-5</v>
       </c>
-      <c r="AA11" s="26">
+      <c r="AA11" s="4">
         <f t="shared" si="10"/>
         <v>1.187239917321092E-5</v>
       </c>
-      <c r="AB11" s="26">
+      <c r="AB11" s="4">
         <f t="shared" si="10"/>
         <v>1.187239917321092E-5</v>
       </c>
-      <c r="AC11" s="26">
+      <c r="AC11" s="4">
         <f t="shared" si="10"/>
         <v>1.187239917321092E-5</v>
       </c>
-      <c r="AD11" s="26">
+      <c r="AD11" s="4">
         <f t="shared" si="10"/>
         <v>1.187239917321092E-5</v>
       </c>
-      <c r="AE11" s="26">
+      <c r="AE11" s="4">
         <f t="shared" si="10"/>
         <v>1.187239917321092E-5</v>
       </c>
-      <c r="AF11" s="26">
+      <c r="AF11" s="4">
         <f t="shared" si="10"/>
         <v>1.187239917321092E-5</v>
       </c>
-      <c r="AG11" s="26">
+      <c r="AG11" s="4">
         <f t="shared" si="10"/>
         <v>1.187239917321092E-5</v>
       </c>
-      <c r="AH11" s="26">
+      <c r="AH11" s="4">
         <f t="shared" si="10"/>
         <v>1.187239917321092E-5</v>
       </c>
-      <c r="AI11" s="26">
+      <c r="AI11" s="4">
         <f t="shared" si="10"/>
         <v>1.187239917321092E-5</v>
       </c>
-      <c r="AJ11" s="26">
+      <c r="AJ11" s="4">
         <f t="shared" si="10"/>
         <v>1.187239917321092E-5</v>
       </c>
-      <c r="AK11" s="26">
+      <c r="AK11" s="4">
         <f t="shared" si="10"/>
         <v>1.187239917321092E-5</v>
       </c>
-      <c r="AL11" s="26">
+      <c r="AL11" s="4">
         <f t="shared" si="10"/>
         <v>1.187239917321092E-5</v>
       </c>
-      <c r="AM11" s="26">
+      <c r="AM11" s="4">
         <f t="shared" si="10"/>
         <v>1.187239917321092E-5</v>
       </c>
-      <c r="AN11" s="26">
+      <c r="AN11" s="4">
         <f t="shared" si="10"/>
         <v>1.187239917321092E-5</v>
       </c>
-      <c r="AO11" s="26">
+      <c r="AO11" s="4">
         <f t="shared" si="10"/>
         <v>1.187239917321092E-5</v>
       </c>
-      <c r="AP11" s="26">
+      <c r="AP11" s="4">
         <f t="shared" si="10"/>
         <v>1.187239917321092E-5</v>
       </c>
-      <c r="AQ11" s="26">
+      <c r="AQ11" s="4">
         <f t="shared" si="10"/>
         <v>1.187239917321092E-5</v>
       </c>
@@ -21815,269 +21811,269 @@
         <f>BNVFE!G17</f>
         <v>1.1872399173210917E-5</v>
       </c>
-      <c r="AS11" s="28">
+      <c r="AS11" s="26">
         <f>BNVFE!H17</f>
         <v>1.1872399173210917E-5</v>
       </c>
-      <c r="AT11" s="28">
+      <c r="AT11" s="26">
         <f>BNVFE!I17</f>
         <v>1.1872399173210917E-5</v>
       </c>
-      <c r="AU11" s="28">
+      <c r="AU11" s="26">
         <f>BNVFE!J17</f>
         <v>1.1872399173210917E-5</v>
       </c>
-      <c r="AV11" s="28">
+      <c r="AV11" s="26">
         <f>BNVFE!K17</f>
         <v>1.1872399173210917E-5</v>
       </c>
-      <c r="AW11" s="28">
+      <c r="AW11" s="26">
         <f>BNVFE!L17</f>
         <v>1.1872399173210917E-5</v>
       </c>
-      <c r="AX11" s="28">
+      <c r="AX11" s="26">
         <f>BNVFE!M17</f>
         <v>1.1872399173210917E-5</v>
       </c>
-      <c r="AY11" s="28">
+      <c r="AY11" s="26">
         <f>BNVFE!N17</f>
         <v>1.1872399173210917E-5</v>
       </c>
-      <c r="AZ11" s="28">
+      <c r="AZ11" s="26">
         <f>BNVFE!O17</f>
         <v>1.1872399173210917E-5</v>
       </c>
-      <c r="BA11" s="28">
+      <c r="BA11" s="26">
         <f>BNVFE!P17</f>
         <v>1.1872399173210917E-5</v>
       </c>
-      <c r="BB11" s="28">
+      <c r="BB11" s="26">
         <f>BNVFE!Q17</f>
         <v>1.1872399173210917E-5</v>
       </c>
-      <c r="BC11" s="28">
+      <c r="BC11" s="26">
         <f>BNVFE!R17</f>
         <v>1.1872399173210917E-5</v>
       </c>
-      <c r="BD11" s="28">
+      <c r="BD11" s="26">
         <f>BNVFE!S17</f>
         <v>1.1872399173210917E-5</v>
       </c>
-      <c r="BE11" s="28">
+      <c r="BE11" s="26">
         <f>BNVFE!T17</f>
         <v>1.1872399173210917E-5</v>
       </c>
-      <c r="BF11" s="28">
+      <c r="BF11" s="26">
         <f>BNVFE!U17</f>
         <v>1.1872399173210917E-5</v>
       </c>
-      <c r="BG11" s="28">
+      <c r="BG11" s="26">
         <f>BNVFE!V17</f>
         <v>1.1872399173210917E-5</v>
       </c>
-      <c r="BH11" s="28">
+      <c r="BH11" s="26">
         <f>BNVFE!W17</f>
         <v>1.1872399173210917E-5</v>
       </c>
-      <c r="BI11" s="28">
+      <c r="BI11" s="26">
         <f>BNVFE!X17</f>
         <v>1.1872399173210917E-5</v>
       </c>
-      <c r="BJ11" s="28">
+      <c r="BJ11" s="26">
         <f>BNVFE!Y17</f>
         <v>1.1872399173210917E-5</v>
       </c>
-      <c r="BK11" s="28">
+      <c r="BK11" s="26">
         <f>BNVFE!Z17</f>
         <v>1.1872399173210917E-5</v>
       </c>
-      <c r="BL11" s="28">
+      <c r="BL11" s="26">
         <f>BNVFE!AA17</f>
         <v>1.1872399173210917E-5</v>
       </c>
-      <c r="BM11" s="28">
+      <c r="BM11" s="26">
         <f>BNVFE!AB17</f>
         <v>1.1872399173210917E-5</v>
       </c>
-      <c r="BN11" s="28">
+      <c r="BN11" s="26">
         <f>BNVFE!AC17</f>
         <v>1.1872399173210917E-5</v>
       </c>
-      <c r="BO11" s="28">
+      <c r="BO11" s="26">
         <f>BNVFE!AD17</f>
         <v>1.1872399173210917E-5</v>
       </c>
-      <c r="BP11" s="28">
+      <c r="BP11" s="26">
         <f>BNVFE!AE17</f>
         <v>1.1872399173210917E-5</v>
       </c>
-      <c r="BQ11" s="28">
+      <c r="BQ11" s="26">
         <f>BNVFE!AF17</f>
         <v>1.1872399173210917E-5</v>
       </c>
-      <c r="BR11" s="28">
+      <c r="BR11" s="26">
         <f>BNVFE!AG17</f>
         <v>1.1872399173210917E-5</v>
       </c>
-      <c r="BS11" s="28"/>
-      <c r="BT11" s="26"/>
+      <c r="BS11" s="26"/>
+      <c r="BT11" s="4"/>
     </row>
     <row r="12" spans="1:72">
-      <c r="A12" s="23" t="s">
+      <c r="A12" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="23" t="s">
+      <c r="B12" t="s">
         <v>22</v>
       </c>
-      <c r="C12" s="24"/>
-      <c r="D12" s="24"/>
-      <c r="E12" s="24"/>
-      <c r="F12" s="24"/>
-      <c r="G12" s="26">
+      <c r="C12" s="23"/>
+      <c r="D12" s="23"/>
+      <c r="E12" s="23"/>
+      <c r="F12" s="23"/>
+      <c r="G12" s="4">
         <f t="shared" ref="G12" si="11">TREND($AR12:$BR12,$AR$1:$BR$1,G$1)</f>
         <v>4.1199493300773313E-3</v>
       </c>
-      <c r="H12" s="26">
+      <c r="H12" s="4">
         <f t="shared" si="10"/>
         <v>4.139779079772081E-3</v>
       </c>
-      <c r="I12" s="26">
+      <c r="I12" s="4">
         <f t="shared" si="10"/>
         <v>4.1596088294668307E-3</v>
       </c>
-      <c r="J12" s="26">
+      <c r="J12" s="4">
         <f t="shared" si="10"/>
         <v>4.1794385791615804E-3</v>
       </c>
-      <c r="K12" s="26">
+      <c r="K12" s="4">
         <f t="shared" si="10"/>
         <v>4.1992683288563301E-3</v>
       </c>
-      <c r="L12" s="26">
+      <c r="L12" s="4">
         <f t="shared" si="10"/>
         <v>4.2190980785510798E-3</v>
       </c>
-      <c r="M12" s="26">
+      <c r="M12" s="4">
         <f t="shared" si="10"/>
         <v>4.2389278282458295E-3</v>
       </c>
-      <c r="N12" s="26">
+      <c r="N12" s="4">
         <f t="shared" si="10"/>
         <v>4.2587575779405792E-3</v>
       </c>
-      <c r="O12" s="26">
+      <c r="O12" s="4">
         <f t="shared" si="10"/>
         <v>4.278587327635329E-3</v>
       </c>
-      <c r="P12" s="26">
+      <c r="P12" s="4">
         <f t="shared" si="10"/>
         <v>4.2984170773300787E-3</v>
       </c>
-      <c r="Q12" s="26">
+      <c r="Q12" s="4">
         <f t="shared" si="10"/>
         <v>4.3182468270248284E-3</v>
       </c>
-      <c r="R12" s="26">
+      <c r="R12" s="4">
         <f t="shared" si="10"/>
         <v>4.3380765767195781E-3</v>
       </c>
-      <c r="S12" s="26">
+      <c r="S12" s="4">
         <f t="shared" si="10"/>
         <v>4.3579063264143278E-3</v>
       </c>
-      <c r="T12" s="26">
+      <c r="T12" s="4">
         <f t="shared" si="10"/>
         <v>4.3777360761090775E-3</v>
       </c>
-      <c r="U12" s="26">
+      <c r="U12" s="4">
         <f t="shared" si="10"/>
         <v>4.3975658258038272E-3</v>
       </c>
-      <c r="V12" s="26">
+      <c r="V12" s="4">
         <f t="shared" si="10"/>
         <v>4.4173955754985769E-3</v>
       </c>
-      <c r="W12" s="26">
+      <c r="W12" s="4">
         <f t="shared" si="10"/>
         <v>4.4372253251933266E-3</v>
       </c>
-      <c r="X12" s="26">
+      <c r="X12" s="4">
         <f t="shared" si="10"/>
         <v>4.4570550748880763E-3</v>
       </c>
-      <c r="Y12" s="26">
+      <c r="Y12" s="4">
         <f t="shared" si="10"/>
         <v>4.4768848245828261E-3</v>
       </c>
-      <c r="Z12" s="26">
+      <c r="Z12" s="4">
         <f t="shared" si="10"/>
         <v>4.4967145742775758E-3</v>
       </c>
-      <c r="AA12" s="26">
+      <c r="AA12" s="4">
         <f t="shared" si="10"/>
         <v>4.5165443239723255E-3</v>
       </c>
-      <c r="AB12" s="26">
+      <c r="AB12" s="4">
         <f t="shared" si="10"/>
         <v>4.5363740736670752E-3</v>
       </c>
-      <c r="AC12" s="26">
+      <c r="AC12" s="4">
         <f t="shared" si="10"/>
         <v>4.5562038233618249E-3</v>
       </c>
-      <c r="AD12" s="26">
+      <c r="AD12" s="4">
         <f t="shared" si="10"/>
         <v>4.5760335730565746E-3</v>
       </c>
-      <c r="AE12" s="26">
+      <c r="AE12" s="4">
         <f t="shared" si="10"/>
         <v>4.5958633227513243E-3</v>
       </c>
-      <c r="AF12" s="26">
+      <c r="AF12" s="4">
         <f t="shared" si="10"/>
         <v>4.615693072446074E-3</v>
       </c>
-      <c r="AG12" s="26">
+      <c r="AG12" s="4">
         <f t="shared" si="10"/>
         <v>4.6355228221408237E-3</v>
       </c>
-      <c r="AH12" s="26">
+      <c r="AH12" s="4">
         <f t="shared" si="10"/>
         <v>4.6553525718355734E-3</v>
       </c>
-      <c r="AI12" s="26">
+      <c r="AI12" s="4">
         <f t="shared" si="10"/>
         <v>4.6751823215303231E-3</v>
       </c>
-      <c r="AJ12" s="26">
+      <c r="AJ12" s="4">
         <f t="shared" si="10"/>
         <v>4.6950120712250729E-3</v>
       </c>
-      <c r="AK12" s="26">
+      <c r="AK12" s="4">
         <f t="shared" si="10"/>
         <v>4.7148418209198226E-3</v>
       </c>
-      <c r="AL12" s="26">
+      <c r="AL12" s="4">
         <f t="shared" si="10"/>
         <v>4.7346715706145723E-3</v>
       </c>
-      <c r="AM12" s="26">
+      <c r="AM12" s="4">
         <f t="shared" si="10"/>
         <v>4.754501320309322E-3</v>
       </c>
-      <c r="AN12" s="26">
+      <c r="AN12" s="4">
         <f t="shared" si="10"/>
         <v>4.7743310700040717E-3</v>
       </c>
-      <c r="AO12" s="26">
+      <c r="AO12" s="4">
         <f>TREND($AR12:$BR12,$AR$1:$BR$1,AO$1)</f>
         <v>4.7941608196988214E-3</v>
       </c>
-      <c r="AP12" s="26">
+      <c r="AP12" s="4">
         <f t="shared" si="10"/>
         <v>4.8139905693935711E-3</v>
       </c>
-      <c r="AQ12" s="26">
+      <c r="AQ12" s="4">
         <f t="shared" si="10"/>
         <v>4.8338203190883208E-3</v>
       </c>
@@ -22085,221 +22081,221 @@
         <f>BNVFE!G18</f>
         <v>4.8577789999999996E-3</v>
       </c>
-      <c r="AS12" s="28">
+      <c r="AS12" s="26">
         <f>BNVFE!H18</f>
         <v>4.8766649999999996E-3</v>
       </c>
-      <c r="AT12" s="28">
+      <c r="AT12" s="26">
         <f>BNVFE!I18</f>
         <v>4.8956239999999995E-3</v>
       </c>
-      <c r="AU12" s="28">
+      <c r="AU12" s="26">
         <f>BNVFE!J18</f>
         <v>4.9146570000000002E-3</v>
       </c>
-      <c r="AV12" s="28">
+      <c r="AV12" s="26">
         <f>BNVFE!K18</f>
         <v>4.9337640000000002E-3</v>
       </c>
-      <c r="AW12" s="28">
+      <c r="AW12" s="26">
         <f>BNVFE!L18</f>
         <v>4.9529449999999994E-3</v>
       </c>
-      <c r="AX12" s="28">
+      <c r="AX12" s="26">
         <f>BNVFE!M18</f>
         <v>4.9721999999999995E-3</v>
       </c>
-      <c r="AY12" s="28">
+      <c r="AY12" s="26">
         <f>BNVFE!N18</f>
         <v>4.9915310000000004E-3</v>
       </c>
-      <c r="AZ12" s="28">
+      <c r="AZ12" s="26">
         <f>BNVFE!O18</f>
         <v>5.010937E-3</v>
       </c>
-      <c r="BA12" s="28">
+      <c r="BA12" s="26">
         <f>BNVFE!P18</f>
         <v>5.030418E-3</v>
       </c>
-      <c r="BB12" s="28">
+      <c r="BB12" s="26">
         <f>BNVFE!Q18</f>
         <v>5.049975E-3</v>
       </c>
-      <c r="BC12" s="28">
+      <c r="BC12" s="26">
         <f>BNVFE!R18</f>
         <v>5.0696079999999998E-3</v>
       </c>
-      <c r="BD12" s="28">
+      <c r="BD12" s="26">
         <f>BNVFE!S18</f>
         <v>5.0893170000000003E-3</v>
       </c>
-      <c r="BE12" s="28">
+      <c r="BE12" s="26">
         <f>BNVFE!T18</f>
         <v>5.1091030000000003E-3</v>
       </c>
-      <c r="BF12" s="28">
+      <c r="BF12" s="26">
         <f>BNVFE!U18</f>
         <v>5.1289660000000004E-3</v>
       </c>
-      <c r="BG12" s="28">
+      <c r="BG12" s="26">
         <f>BNVFE!V18</f>
         <v>5.148906E-3</v>
       </c>
-      <c r="BH12" s="28">
+      <c r="BH12" s="26">
         <f>BNVFE!W18</f>
         <v>5.1689230000000006E-3</v>
       </c>
-      <c r="BI12" s="28">
+      <c r="BI12" s="26">
         <f>BNVFE!X18</f>
         <v>5.1890190000000004E-3</v>
       </c>
-      <c r="BJ12" s="28">
+      <c r="BJ12" s="26">
         <f>BNVFE!Y18</f>
         <v>5.2091919999999996E-3</v>
       </c>
-      <c r="BK12" s="28">
+      <c r="BK12" s="26">
         <f>BNVFE!Z18</f>
         <v>5.2294450000000001E-3</v>
       </c>
-      <c r="BL12" s="28">
+      <c r="BL12" s="26">
         <f>BNVFE!AA18</f>
         <v>5.2497749999999999E-3</v>
       </c>
-      <c r="BM12" s="28">
+      <c r="BM12" s="26">
         <f>BNVFE!AB18</f>
         <v>5.2701849999999993E-3</v>
       </c>
-      <c r="BN12" s="28">
+      <c r="BN12" s="26">
         <f>BNVFE!AC18</f>
         <v>5.2906740000000004E-3</v>
       </c>
-      <c r="BO12" s="28">
+      <c r="BO12" s="26">
         <f>BNVFE!AD18</f>
         <v>5.3112430000000002E-3</v>
       </c>
-      <c r="BP12" s="28">
+      <c r="BP12" s="26">
         <f>BNVFE!AE18</f>
         <v>5.3318919999999995E-3</v>
       </c>
-      <c r="BQ12" s="28">
+      <c r="BQ12" s="26">
         <f>BNVFE!AF18</f>
         <v>5.3526210000000001E-3</v>
       </c>
-      <c r="BR12" s="28">
+      <c r="BR12" s="26">
         <f>BNVFE!AG18</f>
         <v>5.3734300000000002E-3</v>
       </c>
-      <c r="BS12" s="28"/>
-      <c r="BT12" s="26"/>
+      <c r="BS12" s="26"/>
+      <c r="BT12" s="4"/>
     </row>
     <row r="13" spans="1:72">
-      <c r="A13" s="23" t="s">
+      <c r="A13" t="s">
         <v>18</v>
       </c>
-      <c r="B13" s="23" t="s">
+      <c r="B13" t="s">
         <v>21</v>
       </c>
-      <c r="C13" s="25"/>
-      <c r="D13" s="25"/>
-      <c r="E13" s="25"/>
-      <c r="F13" s="25"/>
-      <c r="G13" s="25"/>
-      <c r="H13" s="25"/>
-      <c r="I13" s="25"/>
-      <c r="J13" s="25"/>
-      <c r="K13" s="25"/>
-      <c r="L13" s="25"/>
-      <c r="M13" s="25"/>
-      <c r="N13" s="25"/>
-      <c r="O13" s="25"/>
-      <c r="P13" s="25"/>
-      <c r="Q13" s="25"/>
-      <c r="R13" s="25"/>
-      <c r="S13" s="25"/>
-      <c r="T13" s="25"/>
-      <c r="U13" s="25"/>
-      <c r="V13" s="25"/>
-      <c r="W13" s="26">
+      <c r="C13" s="24"/>
+      <c r="D13" s="24"/>
+      <c r="E13" s="24"/>
+      <c r="F13" s="24"/>
+      <c r="G13" s="24"/>
+      <c r="H13" s="24"/>
+      <c r="I13" s="24"/>
+      <c r="J13" s="24"/>
+      <c r="K13" s="24"/>
+      <c r="L13" s="24"/>
+      <c r="M13" s="24"/>
+      <c r="N13" s="24"/>
+      <c r="O13" s="24"/>
+      <c r="P13" s="24"/>
+      <c r="Q13" s="24"/>
+      <c r="R13" s="24"/>
+      <c r="S13" s="24"/>
+      <c r="T13" s="24"/>
+      <c r="U13" s="24"/>
+      <c r="V13" s="24"/>
+      <c r="W13" s="4">
         <f>TREND($AR13:$BR13,$AR$1:$BR$1,W$1)</f>
         <v>1.8223914406069761E-3</v>
       </c>
-      <c r="X13" s="26">
+      <c r="X13" s="4">
         <f t="shared" si="10"/>
         <v>1.8223914406069761E-3</v>
       </c>
-      <c r="Y13" s="26">
+      <c r="Y13" s="4">
         <f t="shared" si="10"/>
         <v>1.8223914406069761E-3</v>
       </c>
-      <c r="Z13" s="26">
+      <c r="Z13" s="4">
         <f t="shared" si="10"/>
         <v>1.8223914406069761E-3</v>
       </c>
-      <c r="AA13" s="26">
+      <c r="AA13" s="4">
         <f t="shared" si="10"/>
         <v>1.8223914406069761E-3</v>
       </c>
-      <c r="AB13" s="26">
+      <c r="AB13" s="4">
         <f t="shared" si="10"/>
         <v>1.8223914406069761E-3</v>
       </c>
-      <c r="AC13" s="26">
+      <c r="AC13" s="4">
         <f t="shared" si="10"/>
         <v>1.8223914406069761E-3</v>
       </c>
-      <c r="AD13" s="26">
+      <c r="AD13" s="4">
         <f t="shared" si="10"/>
         <v>1.8223914406069761E-3</v>
       </c>
-      <c r="AE13" s="26">
+      <c r="AE13" s="4">
         <f t="shared" si="10"/>
         <v>1.8223914406069761E-3</v>
       </c>
-      <c r="AF13" s="26">
+      <c r="AF13" s="4">
         <f t="shared" si="10"/>
         <v>1.8223914406069761E-3</v>
       </c>
-      <c r="AG13" s="26">
+      <c r="AG13" s="4">
         <f t="shared" si="10"/>
         <v>1.8223914406069761E-3</v>
       </c>
-      <c r="AH13" s="26">
+      <c r="AH13" s="4">
         <f t="shared" si="10"/>
         <v>1.8223914406069761E-3</v>
       </c>
-      <c r="AI13" s="26">
+      <c r="AI13" s="4">
         <f t="shared" si="10"/>
         <v>1.8223914406069761E-3</v>
       </c>
-      <c r="AJ13" s="26">
+      <c r="AJ13" s="4">
         <f t="shared" si="10"/>
         <v>1.8223914406069761E-3</v>
       </c>
-      <c r="AK13" s="26">
+      <c r="AK13" s="4">
         <f t="shared" si="10"/>
         <v>1.8223914406069761E-3</v>
       </c>
-      <c r="AL13" s="26">
+      <c r="AL13" s="4">
         <f t="shared" si="10"/>
         <v>1.8223914406069761E-3</v>
       </c>
-      <c r="AM13" s="26">
+      <c r="AM13" s="4">
         <f t="shared" si="10"/>
         <v>1.8223914406069761E-3</v>
       </c>
-      <c r="AN13" s="26">
+      <c r="AN13" s="4">
         <f t="shared" si="10"/>
         <v>1.8223914406069761E-3</v>
       </c>
-      <c r="AO13" s="26">
+      <c r="AO13" s="4">
         <f t="shared" si="10"/>
         <v>1.8223914406069761E-3</v>
       </c>
-      <c r="AP13" s="26">
+      <c r="AP13" s="4">
         <f t="shared" si="10"/>
         <v>1.8223914406069761E-3</v>
       </c>
-      <c r="AQ13" s="26">
+      <c r="AQ13" s="4">
         <f t="shared" si="10"/>
         <v>1.8223914406069761E-3</v>
       </c>
@@ -22307,221 +22303,221 @@
         <f>BNVFE!G19</f>
         <v>1.8223914406069774E-3</v>
       </c>
-      <c r="AS13" s="28">
+      <c r="AS13" s="26">
         <f>BNVFE!H19</f>
         <v>1.8223914406069774E-3</v>
       </c>
-      <c r="AT13" s="28">
+      <c r="AT13" s="26">
         <f>BNVFE!I19</f>
         <v>1.8223914406069774E-3</v>
       </c>
-      <c r="AU13" s="28">
+      <c r="AU13" s="26">
         <f>BNVFE!J19</f>
         <v>1.8223914406069774E-3</v>
       </c>
-      <c r="AV13" s="28">
+      <c r="AV13" s="26">
         <f>BNVFE!K19</f>
         <v>1.8223914406069774E-3</v>
       </c>
-      <c r="AW13" s="28">
+      <c r="AW13" s="26">
         <f>BNVFE!L19</f>
         <v>1.8223914406069774E-3</v>
       </c>
-      <c r="AX13" s="28">
+      <c r="AX13" s="26">
         <f>BNVFE!M19</f>
         <v>1.8223914406069774E-3</v>
       </c>
-      <c r="AY13" s="28">
+      <c r="AY13" s="26">
         <f>BNVFE!N19</f>
         <v>1.8223914406069774E-3</v>
       </c>
-      <c r="AZ13" s="28">
+      <c r="AZ13" s="26">
         <f>BNVFE!O19</f>
         <v>1.8223914406069774E-3</v>
       </c>
-      <c r="BA13" s="28">
+      <c r="BA13" s="26">
         <f>BNVFE!P19</f>
         <v>1.8223914406069774E-3</v>
       </c>
-      <c r="BB13" s="28">
+      <c r="BB13" s="26">
         <f>BNVFE!Q19</f>
         <v>1.8223914406069774E-3</v>
       </c>
-      <c r="BC13" s="28">
+      <c r="BC13" s="26">
         <f>BNVFE!R19</f>
         <v>1.8223914406069774E-3</v>
       </c>
-      <c r="BD13" s="28">
+      <c r="BD13" s="26">
         <f>BNVFE!S19</f>
         <v>1.8223914406069774E-3</v>
       </c>
-      <c r="BE13" s="28">
+      <c r="BE13" s="26">
         <f>BNVFE!T19</f>
         <v>1.8223914406069774E-3</v>
       </c>
-      <c r="BF13" s="28">
+      <c r="BF13" s="26">
         <f>BNVFE!U19</f>
         <v>1.8223914406069774E-3</v>
       </c>
-      <c r="BG13" s="28">
+      <c r="BG13" s="26">
         <f>BNVFE!V19</f>
         <v>1.8223914406069774E-3</v>
       </c>
-      <c r="BH13" s="28">
+      <c r="BH13" s="26">
         <f>BNVFE!W19</f>
         <v>1.8223914406069774E-3</v>
       </c>
-      <c r="BI13" s="28">
+      <c r="BI13" s="26">
         <f>BNVFE!X19</f>
         <v>1.8223914406069774E-3</v>
       </c>
-      <c r="BJ13" s="28">
+      <c r="BJ13" s="26">
         <f>BNVFE!Y19</f>
         <v>1.8223914406069774E-3</v>
       </c>
-      <c r="BK13" s="28">
+      <c r="BK13" s="26">
         <f>BNVFE!Z19</f>
         <v>1.8223914406069774E-3</v>
       </c>
-      <c r="BL13" s="28">
+      <c r="BL13" s="26">
         <f>BNVFE!AA19</f>
         <v>1.8223914406069774E-3</v>
       </c>
-      <c r="BM13" s="28">
+      <c r="BM13" s="26">
         <f>BNVFE!AB19</f>
         <v>1.8223914406069774E-3</v>
       </c>
-      <c r="BN13" s="28">
+      <c r="BN13" s="26">
         <f>BNVFE!AC19</f>
         <v>1.8223914406069774E-3</v>
       </c>
-      <c r="BO13" s="28">
+      <c r="BO13" s="26">
         <f>BNVFE!AD19</f>
         <v>1.8223914406069774E-3</v>
       </c>
-      <c r="BP13" s="28">
+      <c r="BP13" s="26">
         <f>BNVFE!AE19</f>
         <v>1.8223914406069774E-3</v>
       </c>
-      <c r="BQ13" s="28">
+      <c r="BQ13" s="26">
         <f>BNVFE!AF19</f>
         <v>1.8223914406069774E-3</v>
       </c>
-      <c r="BR13" s="28">
+      <c r="BR13" s="26">
         <f>BNVFE!AG19</f>
         <v>1.8223914406069774E-3</v>
       </c>
-      <c r="BS13" s="28"/>
-      <c r="BT13" s="26"/>
+      <c r="BS13" s="26"/>
+      <c r="BT13" s="4"/>
     </row>
     <row r="14" spans="1:72">
-      <c r="A14" s="23" t="s">
+      <c r="A14" t="s">
         <v>18</v>
       </c>
-      <c r="B14" s="23" t="s">
+      <c r="B14" t="s">
         <v>22</v>
       </c>
-      <c r="C14" s="24"/>
-      <c r="D14" s="24"/>
-      <c r="E14" s="24"/>
-      <c r="F14" s="24"/>
-      <c r="G14" s="24"/>
-      <c r="H14" s="24"/>
-      <c r="I14" s="24"/>
-      <c r="J14" s="24"/>
-      <c r="K14" s="24"/>
-      <c r="L14" s="24"/>
-      <c r="M14" s="24"/>
-      <c r="N14" s="24"/>
-      <c r="O14" s="24"/>
-      <c r="P14" s="24"/>
-      <c r="Q14" s="24"/>
-      <c r="R14" s="24"/>
-      <c r="S14" s="24"/>
-      <c r="T14" s="24"/>
-      <c r="U14" s="24"/>
-      <c r="V14" s="24"/>
-      <c r="W14" s="23">
+      <c r="C14" s="23"/>
+      <c r="D14" s="23"/>
+      <c r="E14" s="23"/>
+      <c r="F14" s="23"/>
+      <c r="G14" s="23"/>
+      <c r="H14" s="23"/>
+      <c r="I14" s="23"/>
+      <c r="J14" s="23"/>
+      <c r="K14" s="23"/>
+      <c r="L14" s="23"/>
+      <c r="M14" s="23"/>
+      <c r="N14" s="23"/>
+      <c r="O14" s="23"/>
+      <c r="P14" s="23"/>
+      <c r="Q14" s="23"/>
+      <c r="R14" s="23"/>
+      <c r="S14" s="23"/>
+      <c r="T14" s="23"/>
+      <c r="U14" s="23"/>
+      <c r="V14" s="23"/>
+      <c r="W14">
         <f t="shared" ref="W14:AM14" si="12">$AO14</f>
         <v>0</v>
       </c>
-      <c r="X14" s="23">
+      <c r="X14">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="Y14" s="23">
+      <c r="Y14">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="Z14" s="23">
+      <c r="Z14">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AA14" s="23">
+      <c r="AA14">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AB14" s="23">
+      <c r="AB14">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AC14" s="23">
+      <c r="AC14">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AD14" s="23">
+      <c r="AD14">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AE14" s="23">
+      <c r="AE14">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AF14" s="23">
+      <c r="AF14">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AG14" s="23">
+      <c r="AG14">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AH14" s="23">
+      <c r="AH14">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AI14" s="23">
+      <c r="AI14">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AJ14" s="23">
+      <c r="AJ14">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AK14" s="31">
+      <c r="AK14" s="29">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AL14" s="31">
+      <c r="AL14" s="29">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AM14" s="31">
+      <c r="AM14" s="29">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AN14" s="31">
+      <c r="AN14" s="29">
         <f>$AO14</f>
         <v>0</v>
       </c>
-      <c r="AO14" s="32">
+      <c r="AO14" s="30">
         <f>BNVFE!D20</f>
         <v>0</v>
       </c>
-      <c r="AP14" s="32">
+      <c r="AP14" s="30">
         <f>BNVFE!E20</f>
         <v>0</v>
       </c>
-      <c r="AQ14" s="32">
+      <c r="AQ14" s="30">
         <f>BNVFE!F20</f>
         <v>0</v>
       </c>
@@ -22529,116 +22525,116 @@
         <f>BNVFE!G20</f>
         <v>0</v>
       </c>
-      <c r="AS14" s="32">
+      <c r="AS14" s="30">
         <f>BNVFE!H20</f>
         <v>0</v>
       </c>
-      <c r="AT14" s="32">
+      <c r="AT14" s="30">
         <f>BNVFE!I20</f>
         <v>0</v>
       </c>
-      <c r="AU14" s="32">
+      <c r="AU14" s="30">
         <f>BNVFE!J20</f>
         <v>0</v>
       </c>
-      <c r="AV14" s="32">
+      <c r="AV14" s="30">
         <f>BNVFE!K20</f>
         <v>0</v>
       </c>
-      <c r="AW14" s="32">
+      <c r="AW14" s="30">
         <f>BNVFE!L20</f>
         <v>0</v>
       </c>
-      <c r="AX14" s="32">
+      <c r="AX14" s="30">
         <f>BNVFE!M20</f>
         <v>0</v>
       </c>
-      <c r="AY14" s="32">
+      <c r="AY14" s="30">
         <f>BNVFE!N20</f>
         <v>0</v>
       </c>
-      <c r="AZ14" s="32">
+      <c r="AZ14" s="30">
         <f>BNVFE!O20</f>
         <v>0</v>
       </c>
-      <c r="BA14" s="32">
+      <c r="BA14" s="30">
         <f>BNVFE!P20</f>
         <v>0</v>
       </c>
-      <c r="BB14" s="32">
+      <c r="BB14" s="30">
         <f>BNVFE!Q20</f>
         <v>0</v>
       </c>
-      <c r="BC14" s="32">
+      <c r="BC14" s="30">
         <f>BNVFE!R20</f>
         <v>0</v>
       </c>
-      <c r="BD14" s="32">
+      <c r="BD14" s="30">
         <f>BNVFE!S20</f>
         <v>0</v>
       </c>
-      <c r="BE14" s="32">
+      <c r="BE14" s="30">
         <f>BNVFE!T20</f>
         <v>0</v>
       </c>
-      <c r="BF14" s="32">
+      <c r="BF14" s="30">
         <f>BNVFE!U20</f>
         <v>0</v>
       </c>
-      <c r="BG14" s="32">
+      <c r="BG14" s="30">
         <f>BNVFE!V20</f>
         <v>0</v>
       </c>
-      <c r="BH14" s="32">
+      <c r="BH14" s="30">
         <f>BNVFE!W20</f>
         <v>0</v>
       </c>
-      <c r="BI14" s="32">
+      <c r="BI14" s="30">
         <f>BNVFE!X20</f>
         <v>0</v>
       </c>
-      <c r="BJ14" s="32">
+      <c r="BJ14" s="30">
         <f>BNVFE!Y20</f>
         <v>0</v>
       </c>
-      <c r="BK14" s="32">
+      <c r="BK14" s="30">
         <f>BNVFE!Z20</f>
         <v>0</v>
       </c>
-      <c r="BL14" s="32">
+      <c r="BL14" s="30">
         <f>BNVFE!AA20</f>
         <v>0</v>
       </c>
-      <c r="BM14" s="32">
+      <c r="BM14" s="30">
         <f>BNVFE!AB20</f>
         <v>0</v>
       </c>
-      <c r="BN14" s="32">
+      <c r="BN14" s="30">
         <f>BNVFE!AC20</f>
         <v>0</v>
       </c>
-      <c r="BO14" s="32">
+      <c r="BO14" s="30">
         <f>BNVFE!AD20</f>
         <v>0</v>
       </c>
-      <c r="BP14" s="32">
+      <c r="BP14" s="30">
         <f>BNVFE!AE20</f>
         <v>0</v>
       </c>
-      <c r="BQ14" s="32">
+      <c r="BQ14" s="30">
         <f>BNVFE!AF20</f>
         <v>0</v>
       </c>
-      <c r="BR14" s="32">
+      <c r="BR14" s="30">
         <f>BNVFE!AG20</f>
         <v>0</v>
       </c>
-      <c r="BS14" s="32"/>
+      <c r="BS14" s="30"/>
     </row>
     <row r="15" spans="1:72">
-      <c r="E15" s="33"/>
-      <c r="X15" s="26"/>
-      <c r="AH15" s="26"/>
+      <c r="E15" s="31"/>
+      <c r="X15" s="4"/>
+      <c r="AH15" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -23792,123 +23788,123 @@
       </c>
       <c r="B2" s="4">
         <f t="array" ref="B2:B8">TRANSPOSE(SYFAFE!B10:H10)</f>
-        <v>1.3226441773833212E-4</v>
+        <v>3.0636736837912965E-4</v>
       </c>
       <c r="C2" s="4">
         <f>B2</f>
-        <v>1.3226441773833212E-4</v>
+        <v>3.0636736837912965E-4</v>
       </c>
       <c r="D2" s="4">
         <f t="shared" ref="D2:AE8" si="0">C2</f>
-        <v>1.3226441773833212E-4</v>
+        <v>3.0636736837912965E-4</v>
       </c>
       <c r="E2" s="4">
         <f t="shared" si="0"/>
-        <v>1.3226441773833212E-4</v>
+        <v>3.0636736837912965E-4</v>
       </c>
       <c r="F2" s="4">
         <f t="shared" si="0"/>
-        <v>1.3226441773833212E-4</v>
+        <v>3.0636736837912965E-4</v>
       </c>
       <c r="G2" s="4">
         <f t="shared" si="0"/>
-        <v>1.3226441773833212E-4</v>
+        <v>3.0636736837912965E-4</v>
       </c>
       <c r="H2" s="4">
         <f t="shared" si="0"/>
-        <v>1.3226441773833212E-4</v>
+        <v>3.0636736837912965E-4</v>
       </c>
       <c r="I2" s="4">
         <f t="shared" si="0"/>
-        <v>1.3226441773833212E-4</v>
+        <v>3.0636736837912965E-4</v>
       </c>
       <c r="J2" s="4">
         <f t="shared" si="0"/>
-        <v>1.3226441773833212E-4</v>
+        <v>3.0636736837912965E-4</v>
       </c>
       <c r="K2" s="4">
         <f t="shared" si="0"/>
-        <v>1.3226441773833212E-4</v>
+        <v>3.0636736837912965E-4</v>
       </c>
       <c r="L2" s="4">
         <f t="shared" si="0"/>
-        <v>1.3226441773833212E-4</v>
+        <v>3.0636736837912965E-4</v>
       </c>
       <c r="M2" s="4">
         <f t="shared" si="0"/>
-        <v>1.3226441773833212E-4</v>
+        <v>3.0636736837912965E-4</v>
       </c>
       <c r="N2" s="4">
         <f t="shared" si="0"/>
-        <v>1.3226441773833212E-4</v>
+        <v>3.0636736837912965E-4</v>
       </c>
       <c r="O2" s="4">
         <f t="shared" si="0"/>
-        <v>1.3226441773833212E-4</v>
+        <v>3.0636736837912965E-4</v>
       </c>
       <c r="P2" s="4">
         <f t="shared" si="0"/>
-        <v>1.3226441773833212E-4</v>
+        <v>3.0636736837912965E-4</v>
       </c>
       <c r="Q2" s="4">
         <f t="shared" si="0"/>
-        <v>1.3226441773833212E-4</v>
+        <v>3.0636736837912965E-4</v>
       </c>
       <c r="R2" s="4">
         <f t="shared" si="0"/>
-        <v>1.3226441773833212E-4</v>
+        <v>3.0636736837912965E-4</v>
       </c>
       <c r="S2" s="4">
         <f t="shared" si="0"/>
-        <v>1.3226441773833212E-4</v>
+        <v>3.0636736837912965E-4</v>
       </c>
       <c r="T2" s="4">
         <f t="shared" si="0"/>
-        <v>1.3226441773833212E-4</v>
+        <v>3.0636736837912965E-4</v>
       </c>
       <c r="U2" s="4">
         <f t="shared" si="0"/>
-        <v>1.3226441773833212E-4</v>
+        <v>3.0636736837912965E-4</v>
       </c>
       <c r="V2" s="4">
         <f t="shared" si="0"/>
-        <v>1.3226441773833212E-4</v>
+        <v>3.0636736837912965E-4</v>
       </c>
       <c r="W2" s="4">
         <f t="shared" si="0"/>
-        <v>1.3226441773833212E-4</v>
+        <v>3.0636736837912965E-4</v>
       </c>
       <c r="X2" s="4">
         <f t="shared" si="0"/>
-        <v>1.3226441773833212E-4</v>
+        <v>3.0636736837912965E-4</v>
       </c>
       <c r="Y2" s="4">
         <f t="shared" si="0"/>
-        <v>1.3226441773833212E-4</v>
+        <v>3.0636736837912965E-4</v>
       </c>
       <c r="Z2" s="4">
         <f t="shared" si="0"/>
-        <v>1.3226441773833212E-4</v>
+        <v>3.0636736837912965E-4</v>
       </c>
       <c r="AA2" s="4">
         <f t="shared" si="0"/>
-        <v>1.3226441773833212E-4</v>
+        <v>3.0636736837912965E-4</v>
       </c>
       <c r="AB2" s="4">
         <f t="shared" si="0"/>
-        <v>1.3226441773833212E-4</v>
+        <v>3.0636736837912965E-4</v>
       </c>
       <c r="AC2" s="4">
         <f t="shared" si="0"/>
-        <v>1.3226441773833212E-4</v>
+        <v>3.0636736837912965E-4</v>
       </c>
       <c r="AD2" s="4">
         <f t="shared" si="0"/>
-        <v>1.3226441773833212E-4</v>
+        <v>3.0636736837912965E-4</v>
       </c>
       <c r="AE2" s="4">
         <f t="shared" si="0"/>
-        <v>1.3226441773833212E-4</v>
+        <v>3.0636736837912965E-4</v>
       </c>
       <c r="AG2" s="4"/>
       <c r="AH2" s="4"/>
@@ -23918,123 +23914,123 @@
         <v>3</v>
       </c>
       <c r="B3" s="4">
-        <v>7.0204850469879831E-5</v>
+        <v>7.273085411263018E-5</v>
       </c>
       <c r="C3" s="4">
         <f t="shared" ref="C3:C8" si="1">B3</f>
-        <v>7.0204850469879831E-5</v>
+        <v>7.273085411263018E-5</v>
       </c>
       <c r="D3" s="4">
         <f t="shared" ref="D3:Q3" si="2">C3</f>
-        <v>7.0204850469879831E-5</v>
+        <v>7.273085411263018E-5</v>
       </c>
       <c r="E3" s="4">
         <f t="shared" si="2"/>
-        <v>7.0204850469879831E-5</v>
+        <v>7.273085411263018E-5</v>
       </c>
       <c r="F3" s="4">
         <f t="shared" si="2"/>
-        <v>7.0204850469879831E-5</v>
+        <v>7.273085411263018E-5</v>
       </c>
       <c r="G3" s="4">
         <f t="shared" si="2"/>
-        <v>7.0204850469879831E-5</v>
+        <v>7.273085411263018E-5</v>
       </c>
       <c r="H3" s="4">
         <f t="shared" si="2"/>
-        <v>7.0204850469879831E-5</v>
+        <v>7.273085411263018E-5</v>
       </c>
       <c r="I3" s="4">
         <f t="shared" si="2"/>
-        <v>7.0204850469879831E-5</v>
+        <v>7.273085411263018E-5</v>
       </c>
       <c r="J3" s="4">
         <f t="shared" si="2"/>
-        <v>7.0204850469879831E-5</v>
+        <v>7.273085411263018E-5</v>
       </c>
       <c r="K3" s="4">
         <f t="shared" si="2"/>
-        <v>7.0204850469879831E-5</v>
+        <v>7.273085411263018E-5</v>
       </c>
       <c r="L3" s="4">
         <f t="shared" si="2"/>
-        <v>7.0204850469879831E-5</v>
+        <v>7.273085411263018E-5</v>
       </c>
       <c r="M3" s="4">
         <f t="shared" si="2"/>
-        <v>7.0204850469879831E-5</v>
+        <v>7.273085411263018E-5</v>
       </c>
       <c r="N3" s="4">
         <f t="shared" si="2"/>
-        <v>7.0204850469879831E-5</v>
+        <v>7.273085411263018E-5</v>
       </c>
       <c r="O3" s="4">
         <f t="shared" si="2"/>
-        <v>7.0204850469879831E-5</v>
+        <v>7.273085411263018E-5</v>
       </c>
       <c r="P3" s="4">
         <f t="shared" si="2"/>
-        <v>7.0204850469879831E-5</v>
+        <v>7.273085411263018E-5</v>
       </c>
       <c r="Q3" s="4">
         <f t="shared" si="2"/>
-        <v>7.0204850469879831E-5</v>
+        <v>7.273085411263018E-5</v>
       </c>
       <c r="R3" s="4">
         <f t="shared" si="0"/>
-        <v>7.0204850469879831E-5</v>
+        <v>7.273085411263018E-5</v>
       </c>
       <c r="S3" s="4">
         <f t="shared" si="0"/>
-        <v>7.0204850469879831E-5</v>
+        <v>7.273085411263018E-5</v>
       </c>
       <c r="T3" s="4">
         <f t="shared" si="0"/>
-        <v>7.0204850469879831E-5</v>
+        <v>7.273085411263018E-5</v>
       </c>
       <c r="U3" s="4">
         <f t="shared" si="0"/>
-        <v>7.0204850469879831E-5</v>
+        <v>7.273085411263018E-5</v>
       </c>
       <c r="V3" s="4">
         <f t="shared" si="0"/>
-        <v>7.0204850469879831E-5</v>
+        <v>7.273085411263018E-5</v>
       </c>
       <c r="W3" s="4">
         <f t="shared" si="0"/>
-        <v>7.0204850469879831E-5</v>
+        <v>7.273085411263018E-5</v>
       </c>
       <c r="X3" s="4">
         <f t="shared" si="0"/>
-        <v>7.0204850469879831E-5</v>
+        <v>7.273085411263018E-5</v>
       </c>
       <c r="Y3" s="4">
         <f t="shared" si="0"/>
-        <v>7.0204850469879831E-5</v>
+        <v>7.273085411263018E-5</v>
       </c>
       <c r="Z3" s="4">
         <f t="shared" si="0"/>
-        <v>7.0204850469879831E-5</v>
+        <v>7.273085411263018E-5</v>
       </c>
       <c r="AA3" s="4">
         <f t="shared" si="0"/>
-        <v>7.0204850469879831E-5</v>
+        <v>7.273085411263018E-5</v>
       </c>
       <c r="AB3" s="4">
         <f t="shared" si="0"/>
-        <v>7.0204850469879831E-5</v>
+        <v>7.273085411263018E-5</v>
       </c>
       <c r="AC3" s="4">
         <f t="shared" si="0"/>
-        <v>7.0204850469879831E-5</v>
+        <v>7.273085411263018E-5</v>
       </c>
       <c r="AD3" s="4">
         <f t="shared" si="0"/>
-        <v>7.0204850469879831E-5</v>
+        <v>7.273085411263018E-5</v>
       </c>
       <c r="AE3" s="4">
         <f t="shared" si="0"/>
-        <v>7.0204850469879831E-5</v>
+        <v>7.273085411263018E-5</v>
       </c>
       <c r="AG3" s="4"/>
       <c r="AH3" s="4"/>
@@ -24044,123 +24040,123 @@
         <v>4</v>
       </c>
       <c r="B4" s="4">
-        <v>9.8677853294881047E-5</v>
+        <v>9.5098581742816967E-5</v>
       </c>
       <c r="C4" s="4">
         <f t="shared" si="1"/>
-        <v>9.8677853294881047E-5</v>
+        <v>9.5098581742816967E-5</v>
       </c>
       <c r="D4" s="4">
         <f t="shared" si="0"/>
-        <v>9.8677853294881047E-5</v>
+        <v>9.5098581742816967E-5</v>
       </c>
       <c r="E4" s="4">
         <f t="shared" si="0"/>
-        <v>9.8677853294881047E-5</v>
+        <v>9.5098581742816967E-5</v>
       </c>
       <c r="F4" s="4">
         <f t="shared" si="0"/>
-        <v>9.8677853294881047E-5</v>
+        <v>9.5098581742816967E-5</v>
       </c>
       <c r="G4" s="4">
         <f t="shared" si="0"/>
-        <v>9.8677853294881047E-5</v>
+        <v>9.5098581742816967E-5</v>
       </c>
       <c r="H4" s="4">
         <f t="shared" si="0"/>
-        <v>9.8677853294881047E-5</v>
+        <v>9.5098581742816967E-5</v>
       </c>
       <c r="I4" s="4">
         <f t="shared" si="0"/>
-        <v>9.8677853294881047E-5</v>
+        <v>9.5098581742816967E-5</v>
       </c>
       <c r="J4" s="4">
         <f t="shared" si="0"/>
-        <v>9.8677853294881047E-5</v>
+        <v>9.5098581742816967E-5</v>
       </c>
       <c r="K4" s="4">
         <f t="shared" si="0"/>
-        <v>9.8677853294881047E-5</v>
+        <v>9.5098581742816967E-5</v>
       </c>
       <c r="L4" s="4">
         <f t="shared" si="0"/>
-        <v>9.8677853294881047E-5</v>
+        <v>9.5098581742816967E-5</v>
       </c>
       <c r="M4" s="4">
         <f t="shared" si="0"/>
-        <v>9.8677853294881047E-5</v>
+        <v>9.5098581742816967E-5</v>
       </c>
       <c r="N4" s="4">
         <f t="shared" si="0"/>
-        <v>9.8677853294881047E-5</v>
+        <v>9.5098581742816967E-5</v>
       </c>
       <c r="O4" s="4">
         <f t="shared" si="0"/>
-        <v>9.8677853294881047E-5</v>
+        <v>9.5098581742816967E-5</v>
       </c>
       <c r="P4" s="4">
         <f t="shared" si="0"/>
-        <v>9.8677853294881047E-5</v>
+        <v>9.5098581742816967E-5</v>
       </c>
       <c r="Q4" s="4">
         <f t="shared" si="0"/>
-        <v>9.8677853294881047E-5</v>
+        <v>9.5098581742816967E-5</v>
       </c>
       <c r="R4" s="4">
         <f t="shared" si="0"/>
-        <v>9.8677853294881047E-5</v>
+        <v>9.5098581742816967E-5</v>
       </c>
       <c r="S4" s="4">
         <f t="shared" si="0"/>
-        <v>9.8677853294881047E-5</v>
+        <v>9.5098581742816967E-5</v>
       </c>
       <c r="T4" s="4">
         <f t="shared" si="0"/>
-        <v>9.8677853294881047E-5</v>
+        <v>9.5098581742816967E-5</v>
       </c>
       <c r="U4" s="4">
         <f t="shared" si="0"/>
-        <v>9.8677853294881047E-5</v>
+        <v>9.5098581742816967E-5</v>
       </c>
       <c r="V4" s="4">
         <f t="shared" si="0"/>
-        <v>9.8677853294881047E-5</v>
+        <v>9.5098581742816967E-5</v>
       </c>
       <c r="W4" s="4">
         <f t="shared" si="0"/>
-        <v>9.8677853294881047E-5</v>
+        <v>9.5098581742816967E-5</v>
       </c>
       <c r="X4" s="4">
         <f t="shared" si="0"/>
-        <v>9.8677853294881047E-5</v>
+        <v>9.5098581742816967E-5</v>
       </c>
       <c r="Y4" s="4">
         <f t="shared" si="0"/>
-        <v>9.8677853294881047E-5</v>
+        <v>9.5098581742816967E-5</v>
       </c>
       <c r="Z4" s="4">
         <f t="shared" si="0"/>
-        <v>9.8677853294881047E-5</v>
+        <v>9.5098581742816967E-5</v>
       </c>
       <c r="AA4" s="4">
         <f t="shared" si="0"/>
-        <v>9.8677853294881047E-5</v>
+        <v>9.5098581742816967E-5</v>
       </c>
       <c r="AB4" s="4">
         <f t="shared" si="0"/>
-        <v>9.8677853294881047E-5</v>
+        <v>9.5098581742816967E-5</v>
       </c>
       <c r="AC4" s="4">
         <f t="shared" si="0"/>
-        <v>9.8677853294881047E-5</v>
+        <v>9.5098581742816967E-5</v>
       </c>
       <c r="AD4" s="4">
         <f t="shared" si="0"/>
-        <v>9.8677853294881047E-5</v>
+        <v>9.5098581742816967E-5</v>
       </c>
       <c r="AE4" s="4">
         <f t="shared" si="0"/>
-        <v>9.8677853294881047E-5</v>
+        <v>9.5098581742816967E-5</v>
       </c>
       <c r="AG4" s="4"/>
       <c r="AH4" s="4"/>
@@ -24170,123 +24166,123 @@
         <v>5</v>
       </c>
       <c r="B5" s="4">
-        <v>7.7747040895486744E-5</v>
+        <v>9.3478062847081558E-5</v>
       </c>
       <c r="C5" s="4">
         <f t="shared" si="1"/>
-        <v>7.7747040895486744E-5</v>
+        <v>9.3478062847081558E-5</v>
       </c>
       <c r="D5" s="4">
         <f t="shared" si="0"/>
-        <v>7.7747040895486744E-5</v>
+        <v>9.3478062847081558E-5</v>
       </c>
       <c r="E5" s="4">
         <f t="shared" si="0"/>
-        <v>7.7747040895486744E-5</v>
+        <v>9.3478062847081558E-5</v>
       </c>
       <c r="F5" s="4">
         <f t="shared" si="0"/>
-        <v>7.7747040895486744E-5</v>
+        <v>9.3478062847081558E-5</v>
       </c>
       <c r="G5" s="4">
         <f t="shared" si="0"/>
-        <v>7.7747040895486744E-5</v>
+        <v>9.3478062847081558E-5</v>
       </c>
       <c r="H5" s="4">
         <f t="shared" si="0"/>
-        <v>7.7747040895486744E-5</v>
+        <v>9.3478062847081558E-5</v>
       </c>
       <c r="I5" s="4">
         <f t="shared" si="0"/>
-        <v>7.7747040895486744E-5</v>
+        <v>9.3478062847081558E-5</v>
       </c>
       <c r="J5" s="4">
         <f t="shared" si="0"/>
-        <v>7.7747040895486744E-5</v>
+        <v>9.3478062847081558E-5</v>
       </c>
       <c r="K5" s="4">
         <f t="shared" si="0"/>
-        <v>7.7747040895486744E-5</v>
+        <v>9.3478062847081558E-5</v>
       </c>
       <c r="L5" s="4">
         <f t="shared" si="0"/>
-        <v>7.7747040895486744E-5</v>
+        <v>9.3478062847081558E-5</v>
       </c>
       <c r="M5" s="4">
         <f t="shared" si="0"/>
-        <v>7.7747040895486744E-5</v>
+        <v>9.3478062847081558E-5</v>
       </c>
       <c r="N5" s="4">
         <f t="shared" si="0"/>
-        <v>7.7747040895486744E-5</v>
+        <v>9.3478062847081558E-5</v>
       </c>
       <c r="O5" s="4">
         <f t="shared" si="0"/>
-        <v>7.7747040895486744E-5</v>
+        <v>9.3478062847081558E-5</v>
       </c>
       <c r="P5" s="4">
         <f t="shared" si="0"/>
-        <v>7.7747040895486744E-5</v>
+        <v>9.3478062847081558E-5</v>
       </c>
       <c r="Q5" s="4">
         <f t="shared" si="0"/>
-        <v>7.7747040895486744E-5</v>
+        <v>9.3478062847081558E-5</v>
       </c>
       <c r="R5" s="4">
         <f t="shared" si="0"/>
-        <v>7.7747040895486744E-5</v>
+        <v>9.3478062847081558E-5</v>
       </c>
       <c r="S5" s="4">
         <f t="shared" si="0"/>
-        <v>7.7747040895486744E-5</v>
+        <v>9.3478062847081558E-5</v>
       </c>
       <c r="T5" s="4">
         <f t="shared" si="0"/>
-        <v>7.7747040895486744E-5</v>
+        <v>9.3478062847081558E-5</v>
       </c>
       <c r="U5" s="4">
         <f t="shared" si="0"/>
-        <v>7.7747040895486744E-5</v>
+        <v>9.3478062847081558E-5</v>
       </c>
       <c r="V5" s="4">
         <f t="shared" si="0"/>
-        <v>7.7747040895486744E-5</v>
+        <v>9.3478062847081558E-5</v>
       </c>
       <c r="W5" s="4">
         <f t="shared" si="0"/>
-        <v>7.7747040895486744E-5</v>
+        <v>9.3478062847081558E-5</v>
       </c>
       <c r="X5" s="4">
         <f t="shared" si="0"/>
-        <v>7.7747040895486744E-5</v>
+        <v>9.3478062847081558E-5</v>
       </c>
       <c r="Y5" s="4">
         <f t="shared" si="0"/>
-        <v>7.7747040895486744E-5</v>
+        <v>9.3478062847081558E-5</v>
       </c>
       <c r="Z5" s="4">
         <f t="shared" si="0"/>
-        <v>7.7747040895486744E-5</v>
+        <v>9.3478062847081558E-5</v>
       </c>
       <c r="AA5" s="4">
         <f t="shared" si="0"/>
-        <v>7.7747040895486744E-5</v>
+        <v>9.3478062847081558E-5</v>
       </c>
       <c r="AB5" s="4">
         <f t="shared" si="0"/>
-        <v>7.7747040895486744E-5</v>
+        <v>9.3478062847081558E-5</v>
       </c>
       <c r="AC5" s="4">
         <f t="shared" si="0"/>
-        <v>7.7747040895486744E-5</v>
+        <v>9.3478062847081558E-5</v>
       </c>
       <c r="AD5" s="4">
         <f t="shared" si="0"/>
-        <v>7.7747040895486744E-5</v>
+        <v>9.3478062847081558E-5</v>
       </c>
       <c r="AE5" s="4">
         <f t="shared" si="0"/>
-        <v>7.7747040895486744E-5</v>
+        <v>9.3478062847081558E-5</v>
       </c>
       <c r="AG5" s="4"/>
       <c r="AH5" s="4"/>
@@ -24296,123 +24292,123 @@
         <v>6</v>
       </c>
       <c r="B6" s="4">
-        <v>1.7525323807361898E-4</v>
+        <v>3.8357149864294821E-5</v>
       </c>
       <c r="C6" s="4">
         <f t="shared" si="1"/>
-        <v>1.7525323807361898E-4</v>
+        <v>3.8357149864294821E-5</v>
       </c>
       <c r="D6" s="4">
         <f t="shared" si="0"/>
-        <v>1.7525323807361898E-4</v>
+        <v>3.8357149864294821E-5</v>
       </c>
       <c r="E6" s="4">
         <f t="shared" si="0"/>
-        <v>1.7525323807361898E-4</v>
+        <v>3.8357149864294821E-5</v>
       </c>
       <c r="F6" s="4">
         <f t="shared" si="0"/>
-        <v>1.7525323807361898E-4</v>
+        <v>3.8357149864294821E-5</v>
       </c>
       <c r="G6" s="4">
         <f t="shared" si="0"/>
-        <v>1.7525323807361898E-4</v>
+        <v>3.8357149864294821E-5</v>
       </c>
       <c r="H6" s="4">
         <f t="shared" si="0"/>
-        <v>1.7525323807361898E-4</v>
+        <v>3.8357149864294821E-5</v>
       </c>
       <c r="I6" s="4">
         <f t="shared" si="0"/>
-        <v>1.7525323807361898E-4</v>
+        <v>3.8357149864294821E-5</v>
       </c>
       <c r="J6" s="4">
         <f t="shared" si="0"/>
-        <v>1.7525323807361898E-4</v>
+        <v>3.8357149864294821E-5</v>
       </c>
       <c r="K6" s="4">
         <f t="shared" si="0"/>
-        <v>1.7525323807361898E-4</v>
+        <v>3.8357149864294821E-5</v>
       </c>
       <c r="L6" s="4">
         <f t="shared" si="0"/>
-        <v>1.7525323807361898E-4</v>
+        <v>3.8357149864294821E-5</v>
       </c>
       <c r="M6" s="4">
         <f t="shared" si="0"/>
-        <v>1.7525323807361898E-4</v>
+        <v>3.8357149864294821E-5</v>
       </c>
       <c r="N6" s="4">
         <f t="shared" si="0"/>
-        <v>1.7525323807361898E-4</v>
+        <v>3.8357149864294821E-5</v>
       </c>
       <c r="O6" s="4">
         <f t="shared" si="0"/>
-        <v>1.7525323807361898E-4</v>
+        <v>3.8357149864294821E-5</v>
       </c>
       <c r="P6" s="4">
         <f t="shared" si="0"/>
-        <v>1.7525323807361898E-4</v>
+        <v>3.8357149864294821E-5</v>
       </c>
       <c r="Q6" s="4">
         <f t="shared" si="0"/>
-        <v>1.7525323807361898E-4</v>
+        <v>3.8357149864294821E-5</v>
       </c>
       <c r="R6" s="4">
         <f t="shared" si="0"/>
-        <v>1.7525323807361898E-4</v>
+        <v>3.8357149864294821E-5</v>
       </c>
       <c r="S6" s="4">
         <f t="shared" si="0"/>
-        <v>1.7525323807361898E-4</v>
+        <v>3.8357149864294821E-5</v>
       </c>
       <c r="T6" s="4">
         <f t="shared" si="0"/>
-        <v>1.7525323807361898E-4</v>
+        <v>3.8357149864294821E-5</v>
       </c>
       <c r="U6" s="4">
         <f t="shared" si="0"/>
-        <v>1.7525323807361898E-4</v>
+        <v>3.8357149864294821E-5</v>
       </c>
       <c r="V6" s="4">
         <f t="shared" si="0"/>
-        <v>1.7525323807361898E-4</v>
+        <v>3.8357149864294821E-5</v>
       </c>
       <c r="W6" s="4">
         <f t="shared" si="0"/>
-        <v>1.7525323807361898E-4</v>
+        <v>3.8357149864294821E-5</v>
       </c>
       <c r="X6" s="4">
         <f t="shared" si="0"/>
-        <v>1.7525323807361898E-4</v>
+        <v>3.8357149864294821E-5</v>
       </c>
       <c r="Y6" s="4">
         <f t="shared" si="0"/>
-        <v>1.7525323807361898E-4</v>
+        <v>3.8357149864294821E-5</v>
       </c>
       <c r="Z6" s="4">
         <f t="shared" si="0"/>
-        <v>1.7525323807361898E-4</v>
+        <v>3.8357149864294821E-5</v>
       </c>
       <c r="AA6" s="4">
         <f t="shared" si="0"/>
-        <v>1.7525323807361898E-4</v>
+        <v>3.8357149864294821E-5</v>
       </c>
       <c r="AB6" s="4">
         <f t="shared" si="0"/>
-        <v>1.7525323807361898E-4</v>
+        <v>3.8357149864294821E-5</v>
       </c>
       <c r="AC6" s="4">
         <f t="shared" si="0"/>
-        <v>1.7525323807361898E-4</v>
+        <v>3.8357149864294821E-5</v>
       </c>
       <c r="AD6" s="4">
         <f t="shared" si="0"/>
-        <v>1.7525323807361898E-4</v>
+        <v>3.8357149864294821E-5</v>
       </c>
       <c r="AE6" s="4">
         <f t="shared" si="0"/>
-        <v>1.7525323807361898E-4</v>
+        <v>3.8357149864294821E-5</v>
       </c>
       <c r="AG6" s="4"/>
       <c r="AH6" s="4"/>
@@ -24422,123 +24418,123 @@
         <v>84</v>
       </c>
       <c r="B7" s="4">
-        <v>5.5270584840087177E-5</v>
+        <v>1.4090027704705712E-3</v>
       </c>
       <c r="C7" s="4">
         <f t="shared" si="1"/>
-        <v>5.5270584840087177E-5</v>
+        <v>1.4090027704705712E-3</v>
       </c>
       <c r="D7" s="4">
         <f t="shared" si="0"/>
-        <v>5.5270584840087177E-5</v>
+        <v>1.4090027704705712E-3</v>
       </c>
       <c r="E7" s="4">
         <f t="shared" si="0"/>
-        <v>5.5270584840087177E-5</v>
+        <v>1.4090027704705712E-3</v>
       </c>
       <c r="F7" s="4">
         <f t="shared" si="0"/>
-        <v>5.5270584840087177E-5</v>
+        <v>1.4090027704705712E-3</v>
       </c>
       <c r="G7" s="4">
         <f t="shared" si="0"/>
-        <v>5.5270584840087177E-5</v>
+        <v>1.4090027704705712E-3</v>
       </c>
       <c r="H7" s="4">
         <f t="shared" si="0"/>
-        <v>5.5270584840087177E-5</v>
+        <v>1.4090027704705712E-3</v>
       </c>
       <c r="I7" s="4">
         <f t="shared" si="0"/>
-        <v>5.5270584840087177E-5</v>
+        <v>1.4090027704705712E-3</v>
       </c>
       <c r="J7" s="4">
         <f t="shared" si="0"/>
-        <v>5.5270584840087177E-5</v>
+        <v>1.4090027704705712E-3</v>
       </c>
       <c r="K7" s="4">
         <f t="shared" si="0"/>
-        <v>5.5270584840087177E-5</v>
+        <v>1.4090027704705712E-3</v>
       </c>
       <c r="L7" s="4">
         <f t="shared" si="0"/>
-        <v>5.5270584840087177E-5</v>
+        <v>1.4090027704705712E-3</v>
       </c>
       <c r="M7" s="4">
         <f t="shared" si="0"/>
-        <v>5.5270584840087177E-5</v>
+        <v>1.4090027704705712E-3</v>
       </c>
       <c r="N7" s="4">
         <f t="shared" si="0"/>
-        <v>5.5270584840087177E-5</v>
+        <v>1.4090027704705712E-3</v>
       </c>
       <c r="O7" s="4">
         <f t="shared" si="0"/>
-        <v>5.5270584840087177E-5</v>
+        <v>1.4090027704705712E-3</v>
       </c>
       <c r="P7" s="4">
         <f t="shared" si="0"/>
-        <v>5.5270584840087177E-5</v>
+        <v>1.4090027704705712E-3</v>
       </c>
       <c r="Q7" s="4">
         <f t="shared" si="0"/>
-        <v>5.5270584840087177E-5</v>
+        <v>1.4090027704705712E-3</v>
       </c>
       <c r="R7" s="4">
         <f t="shared" si="0"/>
-        <v>5.5270584840087177E-5</v>
+        <v>1.4090027704705712E-3</v>
       </c>
       <c r="S7" s="4">
         <f t="shared" si="0"/>
-        <v>5.5270584840087177E-5</v>
+        <v>1.4090027704705712E-3</v>
       </c>
       <c r="T7" s="4">
         <f t="shared" si="0"/>
-        <v>5.5270584840087177E-5</v>
+        <v>1.4090027704705712E-3</v>
       </c>
       <c r="U7" s="4">
         <f t="shared" si="0"/>
-        <v>5.5270584840087177E-5</v>
+        <v>1.4090027704705712E-3</v>
       </c>
       <c r="V7" s="4">
         <f t="shared" si="0"/>
-        <v>5.5270584840087177E-5</v>
+        <v>1.4090027704705712E-3</v>
       </c>
       <c r="W7" s="4">
         <f t="shared" si="0"/>
-        <v>5.5270584840087177E-5</v>
+        <v>1.4090027704705712E-3</v>
       </c>
       <c r="X7" s="4">
         <f t="shared" si="0"/>
-        <v>5.5270584840087177E-5</v>
+        <v>1.4090027704705712E-3</v>
       </c>
       <c r="Y7" s="4">
         <f t="shared" si="0"/>
-        <v>5.5270584840087177E-5</v>
+        <v>1.4090027704705712E-3</v>
       </c>
       <c r="Z7" s="4">
         <f t="shared" si="0"/>
-        <v>5.5270584840087177E-5</v>
+        <v>1.4090027704705712E-3</v>
       </c>
       <c r="AA7" s="4">
         <f t="shared" si="0"/>
-        <v>5.5270584840087177E-5</v>
+        <v>1.4090027704705712E-3</v>
       </c>
       <c r="AB7" s="4">
         <f t="shared" si="0"/>
-        <v>5.5270584840087177E-5</v>
+        <v>1.4090027704705712E-3</v>
       </c>
       <c r="AC7" s="4">
         <f t="shared" si="0"/>
-        <v>5.5270584840087177E-5</v>
+        <v>1.4090027704705712E-3</v>
       </c>
       <c r="AD7" s="4">
         <f t="shared" si="0"/>
-        <v>5.5270584840087177E-5</v>
+        <v>1.4090027704705712E-3</v>
       </c>
       <c r="AE7" s="4">
         <f t="shared" si="0"/>
-        <v>5.5270584840087177E-5</v>
+        <v>1.4090027704705712E-3</v>
       </c>
       <c r="AG7" s="4"/>
       <c r="AH7" s="4"/>

--- a/InputData/trans/BHNVFEAL/BAU Historical New Veh Fuel Economy After Lifetime.xlsx
+++ b/InputData/trans/BHNVFEAL/BAU Historical New Veh Fuel Economy After Lifetime.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OliviaAshmoore\Documents\Github Repos\eps-us\InputData\trans\BHNVFEAL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F78C7657-5FEF-479C-AB5D-811D6ABB0F6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B65B1C6E-2B31-47A2-A24A-04186B1BE671}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4710,169 +4710,169 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="70"/>
                 <c:pt idx="13" formatCode="0.00E+00">
-                  <c:v>3.3000958546164708E-4</c:v>
+                  <c:v>2.290338125160345E-4</c:v>
                 </c:pt>
                 <c:pt idx="14" formatCode="0.00E+00">
-                  <c:v>3.3397333498517805E-4</c:v>
+                  <c:v>2.3241910879234773E-4</c:v>
                 </c:pt>
                 <c:pt idx="15" formatCode="0.00E+00">
-                  <c:v>3.3793708450870902E-4</c:v>
+                  <c:v>2.3580440506866095E-4</c:v>
                 </c:pt>
                 <c:pt idx="16" formatCode="0.00E+00">
-                  <c:v>3.4190083403223999E-4</c:v>
+                  <c:v>2.3918970134497418E-4</c:v>
                 </c:pt>
                 <c:pt idx="17" formatCode="0.00E+00">
-                  <c:v>3.4586458355577096E-4</c:v>
+                  <c:v>2.4257499762128654E-4</c:v>
                 </c:pt>
                 <c:pt idx="18" formatCode="0.00E+00">
-                  <c:v>3.4982833307930193E-4</c:v>
+                  <c:v>2.4596029389759976E-4</c:v>
                 </c:pt>
                 <c:pt idx="19" formatCode="0.00E+00">
-                  <c:v>3.537920826028329E-4</c:v>
+                  <c:v>2.4934559017391299E-4</c:v>
                 </c:pt>
                 <c:pt idx="20" formatCode="0.00E+00">
-                  <c:v>3.5775583212636387E-4</c:v>
+                  <c:v>2.5273088645022621E-4</c:v>
                 </c:pt>
                 <c:pt idx="21" formatCode="0.00E+00">
-                  <c:v>3.6171958164989484E-4</c:v>
+                  <c:v>2.5611618272653944E-4</c:v>
                 </c:pt>
                 <c:pt idx="22" formatCode="0.00E+00">
-                  <c:v>3.6568333117342582E-4</c:v>
+                  <c:v>2.595014790028518E-4</c:v>
                 </c:pt>
                 <c:pt idx="23" formatCode="0.00E+00">
-                  <c:v>3.6964708069695679E-4</c:v>
+                  <c:v>2.6288677527916502E-4</c:v>
                 </c:pt>
                 <c:pt idx="24" formatCode="0.00E+00">
-                  <c:v>3.7361083022048776E-4</c:v>
+                  <c:v>2.6627207155547825E-4</c:v>
                 </c:pt>
                 <c:pt idx="25" formatCode="0.00E+00">
-                  <c:v>3.7757457974401873E-4</c:v>
+                  <c:v>2.6965736783179147E-4</c:v>
                 </c:pt>
                 <c:pt idx="26" formatCode="0.00E+00">
-                  <c:v>3.815383292675497E-4</c:v>
+                  <c:v>2.7304266410810383E-4</c:v>
                 </c:pt>
                 <c:pt idx="27" formatCode="0.00E+00">
-                  <c:v>3.8550207879108067E-4</c:v>
+                  <c:v>2.7642796038441705E-4</c:v>
                 </c:pt>
                 <c:pt idx="28" formatCode="0.00E+00">
-                  <c:v>3.8946582831461164E-4</c:v>
+                  <c:v>2.7981325666073028E-4</c:v>
                 </c:pt>
                 <c:pt idx="29" formatCode="0.00E+00">
-                  <c:v>3.9342957783814261E-4</c:v>
+                  <c:v>2.831985529370435E-4</c:v>
                 </c:pt>
                 <c:pt idx="30" formatCode="0.00E+00">
-                  <c:v>3.9739332736167358E-4</c:v>
+                  <c:v>2.8658384921335586E-4</c:v>
                 </c:pt>
                 <c:pt idx="31" formatCode="0.00E+00">
-                  <c:v>4.0135707688520629E-4</c:v>
+                  <c:v>2.8996914548966909E-4</c:v>
                 </c:pt>
                 <c:pt idx="32" formatCode="0.00E+00">
-                  <c:v>4.0532082640873726E-4</c:v>
+                  <c:v>2.9335444176598231E-4</c:v>
                 </c:pt>
                 <c:pt idx="33" formatCode="0.00E+00">
-                  <c:v>4.0928457593226823E-4</c:v>
+                  <c:v>2.9673973804229554E-4</c:v>
                 </c:pt>
                 <c:pt idx="34" formatCode="0.00E+00">
-                  <c:v>4.132483254557992E-4</c:v>
+                  <c:v>3.001250343186079E-4</c:v>
                 </c:pt>
                 <c:pt idx="35" formatCode="0.00E+00">
-                  <c:v>4.1721207497933017E-4</c:v>
+                  <c:v>3.0351033059492112E-4</c:v>
                 </c:pt>
                 <c:pt idx="36" formatCode="0.00E+00">
-                  <c:v>4.2117582450286115E-4</c:v>
+                  <c:v>3.0689562687123435E-4</c:v>
                 </c:pt>
                 <c:pt idx="37" formatCode="0.00E+00">
-                  <c:v>4.2513957402639212E-4</c:v>
+                  <c:v>3.1028092314754757E-4</c:v>
                 </c:pt>
                 <c:pt idx="38" formatCode="0.00E+00">
-                  <c:v>4.2910332354992309E-4</c:v>
+                  <c:v>3.1366621942385993E-4</c:v>
                 </c:pt>
                 <c:pt idx="39" formatCode="0.00E+00">
-                  <c:v>4.3306707307345406E-4</c:v>
+                  <c:v>3.1705151570017315E-4</c:v>
                 </c:pt>
                 <c:pt idx="40" formatCode="0.00E+00">
-                  <c:v>4.3956547255263602E-4</c:v>
+                  <c:v>3.0464933987873528E-4</c:v>
                 </c:pt>
                 <c:pt idx="41" formatCode="0.00E+00">
-                  <c:v>4.4366680476890972E-4</c:v>
+                  <c:v>3.0464933987873528E-4</c:v>
                 </c:pt>
                 <c:pt idx="42" formatCode="0.00E+00">
-                  <c:v>4.4597245060431232E-4</c:v>
+                  <c:v>3.3408269543052564E-4</c:v>
                 </c:pt>
                 <c:pt idx="43" formatCode="0.00E+00">
-                  <c:v>4.4931411605150481E-4</c:v>
+                  <c:v>3.3665348546582375E-4</c:v>
                 </c:pt>
                 <c:pt idx="44" formatCode="0.00E+00">
-                  <c:v>4.5288823478004158E-4</c:v>
+                  <c:v>3.3935581504087849E-4</c:v>
                 </c:pt>
                 <c:pt idx="45" formatCode="0.00E+00">
-                  <c:v>4.5662840926832999E-4</c:v>
+                  <c:v>3.4216015354620157E-4</c:v>
                 </c:pt>
                 <c:pt idx="46" formatCode="0.00E+00">
-                  <c:v>4.6040875969022651E-4</c:v>
+                  <c:v>3.4502111275582734E-4</c:v>
                 </c:pt>
                 <c:pt idx="47" formatCode="0.00E+00">
-                  <c:v>4.6419842254086203E-4</c:v>
+                  <c:v>3.4790902074721106E-4</c:v>
                 </c:pt>
                 <c:pt idx="48" formatCode="0.00E+00">
-                  <c:v>4.6802171784268048E-4</c:v>
+                  <c:v>3.5081980617662339E-4</c:v>
                 </c:pt>
                 <c:pt idx="49" formatCode="0.00E+00">
-                  <c:v>4.718495549789862E-4</c:v>
+                  <c:v>3.5375247221412683E-4</c:v>
                 </c:pt>
                 <c:pt idx="50" formatCode="0.00E+00">
-                  <c:v>4.7569706545502331E-4</c:v>
+                  <c:v>3.5670603348759934E-4</c:v>
                 </c:pt>
                 <c:pt idx="51" formatCode="0.00E+00">
-                  <c:v>4.7956228574948121E-4</c:v>
+                  <c:v>3.5968007751568736E-4</c:v>
                 </c:pt>
                 <c:pt idx="52" formatCode="0.00E+00">
-                  <c:v>4.8344561142611898E-4</c:v>
+                  <c:v>3.626744897202374E-4</c:v>
                 </c:pt>
                 <c:pt idx="53" formatCode="0.00E+00">
-                  <c:v>4.8740041976327717E-4</c:v>
+                  <c:v>3.656928831323635E-4</c:v>
                 </c:pt>
                 <c:pt idx="54" formatCode="0.00E+00">
-                  <c:v>4.9138744510057676E-4</c:v>
+                  <c:v>3.6873385989859042E-4</c:v>
                 </c:pt>
                 <c:pt idx="55" formatCode="0.00E+00">
-                  <c:v>4.9540734035651132E-4</c:v>
+                  <c:v>3.7179596105709373E-4</c:v>
                 </c:pt>
                 <c:pt idx="56" formatCode="0.00E+00">
-                  <c:v>4.9946276009751292E-4</c:v>
+                  <c:v>3.7487939284855035E-4</c:v>
                 </c:pt>
                 <c:pt idx="57" formatCode="0.00E+00">
-                  <c:v>5.0354741343006288E-4</c:v>
+                  <c:v>3.7798229146832611E-4</c:v>
                 </c:pt>
                 <c:pt idx="58" formatCode="0.00E+00">
-                  <c:v>5.076679534506399E-4</c:v>
+                  <c:v>3.8110333926765313E-4</c:v>
                 </c:pt>
                 <c:pt idx="59" formatCode="0.00E+00">
-                  <c:v>5.1181172688478038E-4</c:v>
+                  <c:v>3.8424184495833714E-4</c:v>
                 </c:pt>
                 <c:pt idx="60" formatCode="0.00E+00">
-                  <c:v>5.1597913882790009E-4</c:v>
+                  <c:v>3.8739917202040771E-4</c:v>
                 </c:pt>
                 <c:pt idx="61" formatCode="0.00E+00">
-                  <c:v>5.2017698058550235E-4</c:v>
+                  <c:v>3.9057663428336076E-4</c:v>
                 </c:pt>
                 <c:pt idx="62" formatCode="0.00E+00">
-                  <c:v>5.2440413218790766E-4</c:v>
+                  <c:v>3.937746365900064E-4</c:v>
                 </c:pt>
                 <c:pt idx="63" formatCode="0.00E+00">
-                  <c:v>5.2866665576887042E-4</c:v>
+                  <c:v>3.9699374037329777E-4</c:v>
                 </c:pt>
                 <c:pt idx="64" formatCode="0.00E+00">
-                  <c:v>5.3296936481509794E-4</c:v>
+                  <c:v>4.0023428554842422E-4</c:v>
                 </c:pt>
                 <c:pt idx="65" formatCode="0.00E+00">
-                  <c:v>5.3730424796901105E-4</c:v>
+                  <c:v>4.0349549298394053E-4</c:v>
                 </c:pt>
                 <c:pt idx="66" formatCode="0.00E+00">
-                  <c:v>5.4167698609809006E-4</c:v>
+                  <c:v>4.067774772580003E-4</c:v>
                 </c:pt>
                 <c:pt idx="67" formatCode="0.00E+00">
-                  <c:v>5.4607888156546253E-4</c:v>
+                  <c:v>4.1007787424136491E-4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5206,169 +5206,169 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="70"/>
                 <c:pt idx="13" formatCode="0.00E+00">
-                  <c:v>1.8223851973329149E-4</c:v>
+                  <c:v>9.3239985476639982E-5</c:v>
                 </c:pt>
                 <c:pt idx="14" formatCode="0.00E+00">
-                  <c:v>1.8223851973329149E-4</c:v>
+                  <c:v>9.3239985476639982E-5</c:v>
                 </c:pt>
                 <c:pt idx="15" formatCode="0.00E+00">
-                  <c:v>1.8223851973329149E-4</c:v>
+                  <c:v>9.3239985476639982E-5</c:v>
                 </c:pt>
                 <c:pt idx="16" formatCode="0.00E+00">
-                  <c:v>1.8223851973329149E-4</c:v>
+                  <c:v>9.3239985476639982E-5</c:v>
                 </c:pt>
                 <c:pt idx="17" formatCode="0.00E+00">
-                  <c:v>1.8223851973329149E-4</c:v>
+                  <c:v>9.3239985476639982E-5</c:v>
                 </c:pt>
                 <c:pt idx="18" formatCode="0.00E+00">
-                  <c:v>1.8223851973329149E-4</c:v>
+                  <c:v>9.3239985476639982E-5</c:v>
                 </c:pt>
                 <c:pt idx="19" formatCode="0.00E+00">
-                  <c:v>1.8223851973329149E-4</c:v>
+                  <c:v>9.3239985476639982E-5</c:v>
                 </c:pt>
                 <c:pt idx="20" formatCode="0.00E+00">
-                  <c:v>1.8223851973329149E-4</c:v>
+                  <c:v>9.3239985476639982E-5</c:v>
                 </c:pt>
                 <c:pt idx="21" formatCode="0.00E+00">
-                  <c:v>1.8223851973329149E-4</c:v>
+                  <c:v>9.3239985476639982E-5</c:v>
                 </c:pt>
                 <c:pt idx="22" formatCode="0.00E+00">
-                  <c:v>1.8223851973329149E-4</c:v>
+                  <c:v>9.3239985476639982E-5</c:v>
                 </c:pt>
                 <c:pt idx="23" formatCode="0.00E+00">
-                  <c:v>1.8223851973329149E-4</c:v>
+                  <c:v>9.3239985476639982E-5</c:v>
                 </c:pt>
                 <c:pt idx="24" formatCode="0.00E+00">
-                  <c:v>1.8223851973329149E-4</c:v>
+                  <c:v>9.3239985476639982E-5</c:v>
                 </c:pt>
                 <c:pt idx="25" formatCode="0.00E+00">
-                  <c:v>1.8223851973329149E-4</c:v>
+                  <c:v>9.3239985476639982E-5</c:v>
                 </c:pt>
                 <c:pt idx="26" formatCode="0.00E+00">
-                  <c:v>1.8223851973329149E-4</c:v>
+                  <c:v>9.3239985476639982E-5</c:v>
                 </c:pt>
                 <c:pt idx="27" formatCode="0.00E+00">
-                  <c:v>1.8223851973329149E-4</c:v>
+                  <c:v>9.3239985476639982E-5</c:v>
                 </c:pt>
                 <c:pt idx="28" formatCode="0.00E+00">
-                  <c:v>1.8223851973329149E-4</c:v>
+                  <c:v>9.3239985476639982E-5</c:v>
                 </c:pt>
                 <c:pt idx="29" formatCode="0.00E+00">
-                  <c:v>1.8223851973329149E-4</c:v>
+                  <c:v>9.3239985476639982E-5</c:v>
                 </c:pt>
                 <c:pt idx="30" formatCode="0.00E+00">
-                  <c:v>1.8223851973329149E-4</c:v>
+                  <c:v>9.3239985476639982E-5</c:v>
                 </c:pt>
                 <c:pt idx="31" formatCode="0.00E+00">
-                  <c:v>1.8223851973329149E-4</c:v>
+                  <c:v>9.3239985476639982E-5</c:v>
                 </c:pt>
                 <c:pt idx="32" formatCode="0.00E+00">
-                  <c:v>1.8223851973329149E-4</c:v>
+                  <c:v>9.3239985476639982E-5</c:v>
                 </c:pt>
                 <c:pt idx="33" formatCode="0.00E+00">
-                  <c:v>1.8223851973329149E-4</c:v>
+                  <c:v>9.3239985476639982E-5</c:v>
                 </c:pt>
                 <c:pt idx="34" formatCode="0.00E+00">
-                  <c:v>1.8223851973329149E-4</c:v>
+                  <c:v>9.3239985476639982E-5</c:v>
                 </c:pt>
                 <c:pt idx="35" formatCode="0.00E+00">
-                  <c:v>1.8223851973329149E-4</c:v>
+                  <c:v>9.3239985476639982E-5</c:v>
                 </c:pt>
                 <c:pt idx="36" formatCode="0.00E+00">
-                  <c:v>1.8223851973329149E-4</c:v>
+                  <c:v>9.3239985476639982E-5</c:v>
                 </c:pt>
                 <c:pt idx="37" formatCode="0.00E+00">
-                  <c:v>1.8223851973329149E-4</c:v>
+                  <c:v>9.3239985476639982E-5</c:v>
                 </c:pt>
                 <c:pt idx="38" formatCode="0.00E+00">
-                  <c:v>1.8223851973329149E-4</c:v>
+                  <c:v>9.3239985476639982E-5</c:v>
                 </c:pt>
                 <c:pt idx="39" formatCode="0.00E+00">
-                  <c:v>1.8223851973329149E-4</c:v>
+                  <c:v>9.3239985476639982E-5</c:v>
                 </c:pt>
                 <c:pt idx="40" formatCode="0.00E+00">
-                  <c:v>1.8223851973329149E-4</c:v>
+                  <c:v>9.3239985476639982E-5</c:v>
                 </c:pt>
                 <c:pt idx="41" formatCode="0.00E+00">
-                  <c:v>1.8223851973329149E-4</c:v>
+                  <c:v>9.3239985476639982E-5</c:v>
                 </c:pt>
                 <c:pt idx="42" formatCode="0.00E+00">
-                  <c:v>1.8223851973329149E-4</c:v>
+                  <c:v>1.0224826248544657E-4</c:v>
                 </c:pt>
                 <c:pt idx="43" formatCode="0.00E+00">
-                  <c:v>1.8223851973329149E-4</c:v>
+                  <c:v>1.0303507011696843E-4</c:v>
                 </c:pt>
                 <c:pt idx="44" formatCode="0.00E+00">
-                  <c:v>1.8223851973329149E-4</c:v>
+                  <c:v>1.0386213631193046E-4</c:v>
                 </c:pt>
                 <c:pt idx="45" formatCode="0.00E+00">
-                  <c:v>1.8223851973329149E-4</c:v>
+                  <c:v>1.0472042302810055E-4</c:v>
                 </c:pt>
                 <c:pt idx="46" formatCode="0.00E+00">
-                  <c:v>1.8223851973329149E-4</c:v>
+                  <c:v>1.0559603889275644E-4</c:v>
                 </c:pt>
                 <c:pt idx="47" formatCode="0.00E+00">
-                  <c:v>1.8223851973329149E-4</c:v>
+                  <c:v>1.0647990261385189E-4</c:v>
                 </c:pt>
                 <c:pt idx="48" formatCode="0.00E+00">
-                  <c:v>1.8223851973329149E-4</c:v>
+                  <c:v>1.0737076812917535E-4</c:v>
                 </c:pt>
                 <c:pt idx="49" formatCode="0.00E+00">
-                  <c:v>1.8223851973329149E-4</c:v>
+                  <c:v>1.0826833035220035E-4</c:v>
                 </c:pt>
                 <c:pt idx="50" formatCode="0.00E+00">
-                  <c:v>1.8223851973329149E-4</c:v>
+                  <c:v>1.0917228770314212E-4</c:v>
                 </c:pt>
                 <c:pt idx="51" formatCode="0.00E+00">
-                  <c:v>1.8223851973329149E-4</c:v>
+                  <c:v>1.1008251393930003E-4</c:v>
                 </c:pt>
                 <c:pt idx="52" formatCode="0.00E+00">
-                  <c:v>1.8223851973329149E-4</c:v>
+                  <c:v>1.1099897399325733E-4</c:v>
                 </c:pt>
                 <c:pt idx="53" formatCode="0.00E+00">
-                  <c:v>1.8223851973329149E-4</c:v>
+                  <c:v>1.1192277365755811E-4</c:v>
                 </c:pt>
                 <c:pt idx="54" formatCode="0.00E+00">
-                  <c:v>1.8223851973329149E-4</c:v>
+                  <c:v>1.1285348510971702E-4</c:v>
                 </c:pt>
                 <c:pt idx="55" formatCode="0.00E+00">
-                  <c:v>1.8223851973329149E-4</c:v>
+                  <c:v>1.1379066182462636E-4</c:v>
                 </c:pt>
                 <c:pt idx="56" formatCode="0.00E+00">
-                  <c:v>1.8223851973329149E-4</c:v>
+                  <c:v>1.1473436692363647E-4</c:v>
                 </c:pt>
                 <c:pt idx="57" formatCode="0.00E+00">
-                  <c:v>1.8223851973329149E-4</c:v>
+                  <c:v>1.156840299767668E-4</c:v>
                 </c:pt>
                 <c:pt idx="58" formatCode="0.00E+00">
-                  <c:v>1.8223851973329149E-4</c:v>
+                  <c:v>1.1663924770872375E-4</c:v>
                 </c:pt>
                 <c:pt idx="59" formatCode="0.00E+00">
-                  <c:v>1.8223851973329149E-4</c:v>
+                  <c:v>1.1759980854609242E-4</c:v>
                 </c:pt>
                 <c:pt idx="60" formatCode="0.00E+00">
-                  <c:v>1.8223851973329149E-4</c:v>
+                  <c:v>1.1856612979113317E-4</c:v>
                 </c:pt>
                 <c:pt idx="61" formatCode="0.00E+00">
-                  <c:v>1.8223851973329149E-4</c:v>
+                  <c:v>1.1953861355022565E-4</c:v>
                 </c:pt>
                 <c:pt idx="62" formatCode="0.00E+00">
-                  <c:v>1.8223851973329149E-4</c:v>
+                  <c:v>1.2051738372824274E-4</c:v>
                 </c:pt>
                 <c:pt idx="63" formatCode="0.00E+00">
-                  <c:v>1.8223851973329149E-4</c:v>
+                  <c:v>1.2150261215552689E-4</c:v>
                 </c:pt>
                 <c:pt idx="64" formatCode="0.00E+00">
-                  <c:v>1.8223851973329149E-4</c:v>
+                  <c:v>1.2249440286541473E-4</c:v>
                 </c:pt>
                 <c:pt idx="65" formatCode="0.00E+00">
-                  <c:v>1.8223851973329149E-4</c:v>
+                  <c:v>1.2349251739947177E-4</c:v>
                 </c:pt>
                 <c:pt idx="66" formatCode="0.00E+00">
-                  <c:v>1.8223851973329149E-4</c:v>
+                  <c:v>1.2449699082511483E-4</c:v>
                 </c:pt>
                 <c:pt idx="67" formatCode="0.00E+00">
-                  <c:v>1.8223851973329149E-4</c:v>
+                  <c:v>1.2550709958464328E-4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9112,123 +9112,123 @@
       </c>
       <c r="B2" s="4">
         <f>B$5/(1-'Other Values'!$B$3)</f>
-        <v>1.0732148425526729E-3</v>
+        <v>7.4687291205413782E-4</v>
       </c>
       <c r="C2" s="4">
         <f>C$5/(1-'Other Values'!$B$3)</f>
-        <v>1.085952251127532E-3</v>
+        <v>7.5775147578839195E-4</v>
       </c>
       <c r="D2" s="4">
         <f>D$5/(1-'Other Values'!$B$3)</f>
-        <v>1.0986896597023912E-3</v>
+        <v>7.6863003952264597E-4</v>
       </c>
       <c r="E2" s="4">
         <f>E$5/(1-'Other Values'!$B$3)</f>
-        <v>1.1114270682772503E-3</v>
+        <v>7.7950860325689728E-4</v>
       </c>
       <c r="F2" s="4">
         <f>F$5/(1-'Other Values'!$B$3)</f>
-        <v>1.1241644768521094E-3</v>
+        <v>7.9038716699115141E-4</v>
       </c>
       <c r="G2" s="4">
         <f>G$5/(1-'Other Values'!$B$3)</f>
-        <v>1.1369018854269686E-3</v>
+        <v>8.0126573072540543E-4</v>
       </c>
       <c r="H2" s="4">
         <f>H$5/(1-'Other Values'!$B$3)</f>
-        <v>1.1496392940018279E-3</v>
+        <v>8.1214429445965956E-4</v>
       </c>
       <c r="I2" s="4">
         <f>I$5/(1-'Other Values'!$B$3)</f>
-        <v>1.1623767025766871E-3</v>
+        <v>8.2302285819391358E-4</v>
       </c>
       <c r="J2" s="4">
         <f>J$5/(1-'Other Values'!$B$3)</f>
-        <v>1.1751141111515462E-3</v>
+        <v>8.3390142192816489E-4</v>
       </c>
       <c r="K2" s="4">
         <f>K$5/(1-'Other Values'!$B$3)</f>
-        <v>1.1878515197264053E-3</v>
+        <v>8.4477998566241902E-4</v>
       </c>
       <c r="L2" s="4">
         <f>L$5/(1-'Other Values'!$B$3)</f>
-        <v>1.2005889283012645E-3</v>
+        <v>8.5565854939667304E-4</v>
       </c>
       <c r="M2" s="4">
         <f>M$5/(1-'Other Values'!$B$3)</f>
-        <v>1.2133263368761238E-3</v>
+        <v>8.6653711313092717E-4</v>
       </c>
       <c r="N2" s="4">
         <f>N$5/(1-'Other Values'!$B$3)</f>
-        <v>1.226063745450983E-3</v>
+        <v>8.7741567686517848E-4</v>
       </c>
       <c r="O2" s="4">
         <f>O$5/(1-'Other Values'!$B$3)</f>
-        <v>1.2388011540258421E-3</v>
+        <v>8.882942405994325E-4</v>
       </c>
       <c r="P2" s="4">
         <f>P$5/(1-'Other Values'!$B$3)</f>
-        <v>1.2515385626007012E-3</v>
+        <v>8.9917280433368663E-4</v>
       </c>
       <c r="Q2" s="4">
         <f>Q$5/(1-'Other Values'!$B$3)</f>
-        <v>1.2642759711755604E-3</v>
+        <v>9.1005136806794065E-4</v>
       </c>
       <c r="R2" s="4">
         <f>R$5/(1-'Other Values'!$B$3)</f>
-        <v>1.2770133797504195E-3</v>
+        <v>9.2092993180219196E-4</v>
       </c>
       <c r="S2" s="4">
         <f>S$5/(1-'Other Values'!$B$3)</f>
-        <v>1.2897507883252843E-3</v>
+        <v>9.3180849553644609E-4</v>
       </c>
       <c r="T2" s="4">
         <f>T$5/(1-'Other Values'!$B$3)</f>
-        <v>1.3024881969001436E-3</v>
+        <v>9.4268705927070011E-4</v>
       </c>
       <c r="U2" s="4">
         <f>U$5/(1-'Other Values'!$B$3)</f>
-        <v>1.3152256054750028E-3</v>
+        <v>9.5356562300495423E-4</v>
       </c>
       <c r="V2" s="4">
         <f>V$5/(1-'Other Values'!$B$3)</f>
-        <v>1.3279630140498619E-3</v>
+        <v>9.6444418673920554E-4</v>
       </c>
       <c r="W2" s="4">
         <f>W$5/(1-'Other Values'!$B$3)</f>
-        <v>1.340700422624721E-3</v>
+        <v>9.7532275047345956E-4</v>
       </c>
       <c r="X2" s="4">
         <f>X$5/(1-'Other Values'!$B$3)</f>
-        <v>1.3534378311995802E-3</v>
+        <v>9.8620131420771358E-4</v>
       </c>
       <c r="Y2" s="4">
         <f>Y$5/(1-'Other Values'!$B$3)</f>
-        <v>1.3661752397744393E-3</v>
+        <v>9.9707987794196771E-4</v>
       </c>
       <c r="Z2" s="4">
         <f>Z$5/(1-'Other Values'!$B$3)</f>
-        <v>1.3789126483492987E-3</v>
+        <v>1.007958441676219E-3</v>
       </c>
       <c r="AA2" s="4">
         <f>AA$5/(1-'Other Values'!$B$3)</f>
-        <v>1.3916500569241578E-3</v>
+        <v>1.0188370054104732E-3</v>
       </c>
       <c r="AB2" s="4">
         <f>AB$5/(1-'Other Values'!$B$3)</f>
-        <v>1.412532498853853E-3</v>
+        <v>9.7898292792220369E-4</v>
       </c>
       <c r="AC2" s="4">
         <f>AC$5/(1-'Other Values'!$B$3)</f>
-        <v>1.4257120259228021E-3</v>
+        <v>9.7898292792220369E-4</v>
       </c>
       <c r="AD2" s="4">
         <f>AD$5/(1-'Other Values'!$B$3)</f>
-        <v>1.4331211603446675E-3</v>
+        <v>1.0735662695704627E-3</v>
       </c>
       <c r="AE2" s="4">
         <f>AE$5/(1-'Other Values'!$B$3)</f>
-        <v>1.4438595175160014E-3</v>
+        <v>1.0818274381547478E-3</v>
       </c>
       <c r="AG2" s="4"/>
       <c r="AH2" s="4"/>
@@ -9429,123 +9429,123 @@
       </c>
       <c r="B5">
         <f>Extrapolations!Q6</f>
-        <v>3.3397333498517805E-4</v>
+        <v>2.3241910879234773E-4</v>
       </c>
       <c r="C5" s="4">
         <f>Extrapolations!R6</f>
-        <v>3.3793708450870902E-4</v>
+        <v>2.3580440506866095E-4</v>
       </c>
       <c r="D5" s="4">
         <f>Extrapolations!S6</f>
-        <v>3.4190083403223999E-4</v>
+        <v>2.3918970134497418E-4</v>
       </c>
       <c r="E5" s="4">
         <f>Extrapolations!T6</f>
-        <v>3.4586458355577096E-4</v>
+        <v>2.4257499762128654E-4</v>
       </c>
       <c r="F5" s="4">
         <f>Extrapolations!U6</f>
-        <v>3.4982833307930193E-4</v>
+        <v>2.4596029389759976E-4</v>
       </c>
       <c r="G5" s="4">
         <f>Extrapolations!V6</f>
-        <v>3.537920826028329E-4</v>
+        <v>2.4934559017391299E-4</v>
       </c>
       <c r="H5" s="4">
         <f>Extrapolations!W6</f>
-        <v>3.5775583212636387E-4</v>
+        <v>2.5273088645022621E-4</v>
       </c>
       <c r="I5" s="4">
         <f>Extrapolations!X6</f>
-        <v>3.6171958164989484E-4</v>
+        <v>2.5611618272653944E-4</v>
       </c>
       <c r="J5" s="4">
         <f>Extrapolations!Y6</f>
-        <v>3.6568333117342582E-4</v>
+        <v>2.595014790028518E-4</v>
       </c>
       <c r="K5" s="4">
         <f>Extrapolations!Z6</f>
-        <v>3.6964708069695679E-4</v>
+        <v>2.6288677527916502E-4</v>
       </c>
       <c r="L5" s="4">
         <f>Extrapolations!AA6</f>
-        <v>3.7361083022048776E-4</v>
+        <v>2.6627207155547825E-4</v>
       </c>
       <c r="M5" s="4">
         <f>Extrapolations!AB6</f>
-        <v>3.7757457974401873E-4</v>
+        <v>2.6965736783179147E-4</v>
       </c>
       <c r="N5" s="4">
         <f>Extrapolations!AC6</f>
-        <v>3.815383292675497E-4</v>
+        <v>2.7304266410810383E-4</v>
       </c>
       <c r="O5" s="4">
         <f>Extrapolations!AD6</f>
-        <v>3.8550207879108067E-4</v>
+        <v>2.7642796038441705E-4</v>
       </c>
       <c r="P5" s="4">
         <f>Extrapolations!AE6</f>
-        <v>3.8946582831461164E-4</v>
+        <v>2.7981325666073028E-4</v>
       </c>
       <c r="Q5" s="4">
         <f>Extrapolations!AF6</f>
-        <v>3.9342957783814261E-4</v>
+        <v>2.831985529370435E-4</v>
       </c>
       <c r="R5" s="4">
         <f>Extrapolations!AG6</f>
-        <v>3.9739332736167358E-4</v>
+        <v>2.8658384921335586E-4</v>
       </c>
       <c r="S5" s="4">
         <f>Extrapolations!AH6</f>
-        <v>4.0135707688520629E-4</v>
+        <v>2.8996914548966909E-4</v>
       </c>
       <c r="T5" s="4">
         <f>Extrapolations!AI6</f>
-        <v>4.0532082640873726E-4</v>
+        <v>2.9335444176598231E-4</v>
       </c>
       <c r="U5" s="4">
         <f>Extrapolations!AJ6</f>
-        <v>4.0928457593226823E-4</v>
+        <v>2.9673973804229554E-4</v>
       </c>
       <c r="V5" s="4">
         <f>Extrapolations!AK6</f>
-        <v>4.132483254557992E-4</v>
+        <v>3.001250343186079E-4</v>
       </c>
       <c r="W5" s="4">
         <f>Extrapolations!AL6</f>
-        <v>4.1721207497933017E-4</v>
+        <v>3.0351033059492112E-4</v>
       </c>
       <c r="X5" s="4">
         <f>Extrapolations!AM6</f>
-        <v>4.2117582450286115E-4</v>
+        <v>3.0689562687123435E-4</v>
       </c>
       <c r="Y5" s="4">
         <f>Extrapolations!AN6</f>
-        <v>4.2513957402639212E-4</v>
+        <v>3.1028092314754757E-4</v>
       </c>
       <c r="Z5" s="4">
         <f>Extrapolations!AO6</f>
-        <v>4.2910332354992309E-4</v>
+        <v>3.1366621942385993E-4</v>
       </c>
       <c r="AA5" s="4">
         <f>Extrapolations!AP6</f>
-        <v>4.3306707307345406E-4</v>
+        <v>3.1705151570017315E-4</v>
       </c>
       <c r="AB5" s="4">
         <f>Extrapolations!AQ6</f>
-        <v>4.3956547255263602E-4</v>
+        <v>3.0464933987873528E-4</v>
       </c>
       <c r="AC5" s="4">
         <f>Extrapolations!AR6</f>
-        <v>4.4366680476890972E-4</v>
+        <v>3.0464933987873528E-4</v>
       </c>
       <c r="AD5" s="4">
         <f>Extrapolations!AS6</f>
-        <v>4.4597245060431232E-4</v>
+        <v>3.3408269543052564E-4</v>
       </c>
       <c r="AE5" s="4">
         <f>Extrapolations!AT6</f>
-        <v>4.4931411605150481E-4</v>
+        <v>3.3665348546582375E-4</v>
       </c>
       <c r="AG5" s="4"/>
       <c r="AH5" s="4"/>
@@ -9746,123 +9746,123 @@
       </c>
       <c r="B8" s="4">
         <f>B$5*Calculations!$B$27</f>
-        <v>1.0019200049555339E-3</v>
+        <v>6.9725732637704308E-4</v>
       </c>
       <c r="C8" s="4">
         <f>C$5*Calculations!$B$27</f>
-        <v>1.0138112535261268E-3</v>
+        <v>7.0741321520598275E-4</v>
       </c>
       <c r="D8" s="4">
         <f>D$5*Calculations!$B$27</f>
-        <v>1.0257025020967198E-3</v>
+        <v>7.1756910403492243E-4</v>
       </c>
       <c r="E8" s="4">
         <f>E$5*Calculations!$B$27</f>
-        <v>1.0375937506673127E-3</v>
+        <v>7.277249928638595E-4</v>
       </c>
       <c r="F8" s="4">
         <f>F$5*Calculations!$B$27</f>
-        <v>1.0494849992379056E-3</v>
+        <v>7.3788088169279918E-4</v>
       </c>
       <c r="G8" s="4">
         <f>G$5*Calculations!$B$27</f>
-        <v>1.0613762478084985E-3</v>
+        <v>7.4803677052173885E-4</v>
       </c>
       <c r="H8" s="4">
         <f>H$5*Calculations!$B$27</f>
-        <v>1.0732674963790914E-3</v>
+        <v>7.5819265935067853E-4</v>
       </c>
       <c r="I8" s="4">
         <f>I$5*Calculations!$B$27</f>
-        <v>1.0851587449496843E-3</v>
+        <v>7.683485481796182E-4</v>
       </c>
       <c r="J8" s="4">
         <f>J$5*Calculations!$B$27</f>
-        <v>1.0970499935202772E-3</v>
+        <v>7.7850443700855528E-4</v>
       </c>
       <c r="K8" s="4">
         <f>K$5*Calculations!$B$27</f>
-        <v>1.1089412420908701E-3</v>
+        <v>7.8866032583749495E-4</v>
       </c>
       <c r="L8" s="4">
         <f>L$5*Calculations!$B$27</f>
-        <v>1.1208324906614631E-3</v>
+        <v>7.9881621466643463E-4</v>
       </c>
       <c r="M8" s="4">
         <f>M$5*Calculations!$B$27</f>
-        <v>1.132723739232056E-3</v>
+        <v>8.089721034953743E-4</v>
       </c>
       <c r="N8" s="4">
         <f>N$5*Calculations!$B$27</f>
-        <v>1.1446149878026489E-3</v>
+        <v>8.1912799232431138E-4</v>
       </c>
       <c r="O8" s="4">
         <f>O$5*Calculations!$B$27</f>
-        <v>1.1565062363732418E-3</v>
+        <v>8.2928388115325105E-4</v>
       </c>
       <c r="P8" s="4">
         <f>P$5*Calculations!$B$27</f>
-        <v>1.1683974849438347E-3</v>
+        <v>8.3943976998219073E-4</v>
       </c>
       <c r="Q8" s="4">
         <f>Q$5*Calculations!$B$27</f>
-        <v>1.1802887335144276E-3</v>
+        <v>8.4959565881113041E-4</v>
       </c>
       <c r="R8" s="4">
         <f>R$5*Calculations!$B$27</f>
-        <v>1.1921799820850205E-3</v>
+        <v>8.5975154764006748E-4</v>
       </c>
       <c r="S8" s="4">
         <f>S$5*Calculations!$B$27</f>
-        <v>1.2040712306556187E-3</v>
+        <v>8.6990743646900715E-4</v>
       </c>
       <c r="T8" s="4">
         <f>T$5*Calculations!$B$27</f>
-        <v>1.2159624792262116E-3</v>
+        <v>8.8006332529794683E-4</v>
       </c>
       <c r="U8" s="4">
         <f>U$5*Calculations!$B$27</f>
-        <v>1.2278537277968045E-3</v>
+        <v>8.9021921412688651E-4</v>
       </c>
       <c r="V8" s="4">
         <f>V$5*Calculations!$B$27</f>
-        <v>1.2397449763673974E-3</v>
+        <v>9.0037510295582358E-4</v>
       </c>
       <c r="W8" s="4">
         <f>W$5*Calculations!$B$27</f>
-        <v>1.2516362249379903E-3</v>
+        <v>9.1053099178476325E-4</v>
       </c>
       <c r="X8" s="4">
         <f>X$5*Calculations!$B$27</f>
-        <v>1.2635274735085832E-3</v>
+        <v>9.2068688061370293E-4</v>
       </c>
       <c r="Y8" s="4">
         <f>Y$5*Calculations!$B$27</f>
-        <v>1.2754187220791761E-3</v>
+        <v>9.3084276944264261E-4</v>
       </c>
       <c r="Z8" s="4">
         <f>Z$5*Calculations!$B$27</f>
-        <v>1.287309970649769E-3</v>
+        <v>9.4099865827157968E-4</v>
       </c>
       <c r="AA8" s="4">
         <f>AA$5*Calculations!$B$27</f>
-        <v>1.299201219220362E-3</v>
+        <v>9.5115454710051936E-4</v>
       </c>
       <c r="AB8" s="4">
         <f>AB$5*Calculations!$B$27</f>
-        <v>1.3186964176579079E-3</v>
+        <v>9.1394801963620568E-4</v>
       </c>
       <c r="AC8" s="4">
         <f>AC$5*Calculations!$B$27</f>
-        <v>1.331000414306729E-3</v>
+        <v>9.1394801963620568E-4</v>
       </c>
       <c r="AD8" s="4">
         <f>AD$5*Calculations!$B$27</f>
-        <v>1.3379173518129367E-3</v>
+        <v>1.0022480862915768E-3</v>
       </c>
       <c r="AE8" s="4">
         <f>AE$5*Calculations!$B$27</f>
-        <v>1.3479423481545143E-3</v>
+        <v>1.0099604563974711E-3</v>
       </c>
       <c r="AG8" s="4"/>
       <c r="AH8" s="4"/>
@@ -9984,123 +9984,123 @@
       </c>
       <c r="B2" s="4">
         <f>B$5/(1-'Other Values'!$B$3)</f>
-        <v>5.8561886167132651E-4</v>
+        <v>2.9962432880267732E-4</v>
       </c>
       <c r="C2" s="4">
         <f>C$5/(1-'Other Values'!$B$3)</f>
-        <v>5.8561886167132651E-4</v>
+        <v>2.9962432880267732E-4</v>
       </c>
       <c r="D2" s="4">
         <f>D$5/(1-'Other Values'!$B$3)</f>
-        <v>5.8561886167132651E-4</v>
+        <v>2.9962432880267732E-4</v>
       </c>
       <c r="E2" s="4">
         <f>E$5/(1-'Other Values'!$B$3)</f>
-        <v>5.8561886167132651E-4</v>
+        <v>2.9962432880267732E-4</v>
       </c>
       <c r="F2" s="4">
         <f>F$5/(1-'Other Values'!$B$3)</f>
-        <v>5.8561886167132651E-4</v>
+        <v>2.9962432880267732E-4</v>
       </c>
       <c r="G2" s="4">
         <f>G$5/(1-'Other Values'!$B$3)</f>
-        <v>5.8561886167132651E-4</v>
+        <v>2.9962432880267732E-4</v>
       </c>
       <c r="H2" s="4">
         <f>H$5/(1-'Other Values'!$B$3)</f>
-        <v>5.8561886167132651E-4</v>
+        <v>2.9962432880267732E-4</v>
       </c>
       <c r="I2" s="4">
         <f>I$5/(1-'Other Values'!$B$3)</f>
-        <v>5.8561886167132651E-4</v>
+        <v>2.9962432880267732E-4</v>
       </c>
       <c r="J2" s="4">
         <f>J$5/(1-'Other Values'!$B$3)</f>
-        <v>5.8561886167132651E-4</v>
+        <v>2.9962432880267732E-4</v>
       </c>
       <c r="K2" s="4">
         <f>K$5/(1-'Other Values'!$B$3)</f>
-        <v>5.8561886167132651E-4</v>
+        <v>2.9962432880267732E-4</v>
       </c>
       <c r="L2" s="4">
         <f>L$5/(1-'Other Values'!$B$3)</f>
-        <v>5.8561886167132651E-4</v>
+        <v>2.9962432880267732E-4</v>
       </c>
       <c r="M2" s="4">
         <f>M$5/(1-'Other Values'!$B$3)</f>
-        <v>5.8561886167132651E-4</v>
+        <v>2.9962432880267732E-4</v>
       </c>
       <c r="N2" s="4">
         <f>N$5/(1-'Other Values'!$B$3)</f>
-        <v>5.8561886167132651E-4</v>
+        <v>2.9962432880267732E-4</v>
       </c>
       <c r="O2" s="4">
         <f>O$5/(1-'Other Values'!$B$3)</f>
-        <v>5.8561886167132651E-4</v>
+        <v>2.9962432880267732E-4</v>
       </c>
       <c r="P2" s="4">
         <f>P$5/(1-'Other Values'!$B$3)</f>
-        <v>5.8561886167132651E-4</v>
+        <v>2.9962432880267732E-4</v>
       </c>
       <c r="Q2" s="4">
         <f>Q$5/(1-'Other Values'!$B$3)</f>
-        <v>5.8561886167132651E-4</v>
+        <v>2.9962432880267732E-4</v>
       </c>
       <c r="R2" s="4">
         <f>R$5/(1-'Other Values'!$B$3)</f>
-        <v>5.8561886167132651E-4</v>
+        <v>2.9962432880267732E-4</v>
       </c>
       <c r="S2" s="4">
         <f>S$5/(1-'Other Values'!$B$3)</f>
-        <v>5.8561886167132651E-4</v>
+        <v>2.9962432880267732E-4</v>
       </c>
       <c r="T2" s="4">
         <f>T$5/(1-'Other Values'!$B$3)</f>
-        <v>5.8561886167132651E-4</v>
+        <v>2.9962432880267732E-4</v>
       </c>
       <c r="U2" s="4">
         <f>U$5/(1-'Other Values'!$B$3)</f>
-        <v>5.8561886167132651E-4</v>
+        <v>2.9962432880267732E-4</v>
       </c>
       <c r="V2" s="4">
         <f>V$5/(1-'Other Values'!$B$3)</f>
-        <v>5.8561886167132651E-4</v>
+        <v>2.9962432880267732E-4</v>
       </c>
       <c r="W2" s="4">
         <f>W$5/(1-'Other Values'!$B$3)</f>
-        <v>5.8561886167132651E-4</v>
+        <v>2.9962432880267732E-4</v>
       </c>
       <c r="X2" s="4">
         <f>X$5/(1-'Other Values'!$B$3)</f>
-        <v>5.8561886167132651E-4</v>
+        <v>2.9962432880267732E-4</v>
       </c>
       <c r="Y2" s="4">
         <f>Y$5/(1-'Other Values'!$B$3)</f>
-        <v>5.8561886167132651E-4</v>
+        <v>2.9962432880267732E-4</v>
       </c>
       <c r="Z2" s="4">
         <f>Z$5/(1-'Other Values'!$B$3)</f>
-        <v>5.8561886167132651E-4</v>
+        <v>2.9962432880267732E-4</v>
       </c>
       <c r="AA2" s="4">
         <f>AA$5/(1-'Other Values'!$B$3)</f>
-        <v>5.8561886167132651E-4</v>
+        <v>2.9962432880267732E-4</v>
       </c>
       <c r="AB2" s="4">
         <f>AB$5/(1-'Other Values'!$B$3)</f>
-        <v>5.8561886167132651E-4</v>
+        <v>2.9962432880267732E-4</v>
       </c>
       <c r="AC2" s="4">
         <f>AC$5/(1-'Other Values'!$B$3)</f>
-        <v>5.8561886167132651E-4</v>
+        <v>2.9962432880267732E-4</v>
       </c>
       <c r="AD2" s="4">
         <f>AD$5/(1-'Other Values'!$B$3)</f>
-        <v>5.8561886167132651E-4</v>
+        <v>3.2857219852439111E-4</v>
       </c>
       <c r="AE2" s="4">
         <f>AE$5/(1-'Other Values'!$B$3)</f>
-        <v>5.8561886167132651E-4</v>
+        <v>3.3110058489517865E-4</v>
       </c>
       <c r="AG2" s="4"/>
       <c r="AH2" s="4"/>
@@ -10301,123 +10301,123 @@
       </c>
       <c r="B5" s="4">
         <f>Extrapolations!Q7</f>
-        <v>1.8223851973329149E-4</v>
+        <v>9.3239985476639982E-5</v>
       </c>
       <c r="C5" s="4">
         <f>Extrapolations!R7</f>
-        <v>1.8223851973329149E-4</v>
+        <v>9.3239985476639982E-5</v>
       </c>
       <c r="D5" s="4">
         <f>Extrapolations!S7</f>
-        <v>1.8223851973329149E-4</v>
+        <v>9.3239985476639982E-5</v>
       </c>
       <c r="E5" s="4">
         <f>Extrapolations!T7</f>
-        <v>1.8223851973329149E-4</v>
+        <v>9.3239985476639982E-5</v>
       </c>
       <c r="F5" s="4">
         <f>Extrapolations!U7</f>
-        <v>1.8223851973329149E-4</v>
+        <v>9.3239985476639982E-5</v>
       </c>
       <c r="G5" s="4">
         <f>Extrapolations!V7</f>
-        <v>1.8223851973329149E-4</v>
+        <v>9.3239985476639982E-5</v>
       </c>
       <c r="H5" s="4">
         <f>Extrapolations!W7</f>
-        <v>1.8223851973329149E-4</v>
+        <v>9.3239985476639982E-5</v>
       </c>
       <c r="I5" s="4">
         <f>Extrapolations!X7</f>
-        <v>1.8223851973329149E-4</v>
+        <v>9.3239985476639982E-5</v>
       </c>
       <c r="J5" s="4">
         <f>Extrapolations!Y7</f>
-        <v>1.8223851973329149E-4</v>
+        <v>9.3239985476639982E-5</v>
       </c>
       <c r="K5" s="4">
         <f>Extrapolations!Z7</f>
-        <v>1.8223851973329149E-4</v>
+        <v>9.3239985476639982E-5</v>
       </c>
       <c r="L5" s="4">
         <f>Extrapolations!AA7</f>
-        <v>1.8223851973329149E-4</v>
+        <v>9.3239985476639982E-5</v>
       </c>
       <c r="M5" s="4">
         <f>Extrapolations!AB7</f>
-        <v>1.8223851973329149E-4</v>
+        <v>9.3239985476639982E-5</v>
       </c>
       <c r="N5" s="4">
         <f>Extrapolations!AC7</f>
-        <v>1.8223851973329149E-4</v>
+        <v>9.3239985476639982E-5</v>
       </c>
       <c r="O5" s="4">
         <f>Extrapolations!AD7</f>
-        <v>1.8223851973329149E-4</v>
+        <v>9.3239985476639982E-5</v>
       </c>
       <c r="P5" s="4">
         <f>Extrapolations!AE7</f>
-        <v>1.8223851973329149E-4</v>
+        <v>9.3239985476639982E-5</v>
       </c>
       <c r="Q5" s="4">
         <f>Extrapolations!AF7</f>
-        <v>1.8223851973329149E-4</v>
+        <v>9.3239985476639982E-5</v>
       </c>
       <c r="R5" s="4">
         <f>Extrapolations!AG7</f>
-        <v>1.8223851973329149E-4</v>
+        <v>9.3239985476639982E-5</v>
       </c>
       <c r="S5" s="4">
         <f>Extrapolations!AH7</f>
-        <v>1.8223851973329149E-4</v>
+        <v>9.3239985476639982E-5</v>
       </c>
       <c r="T5" s="4">
         <f>Extrapolations!AI7</f>
-        <v>1.8223851973329149E-4</v>
+        <v>9.3239985476639982E-5</v>
       </c>
       <c r="U5" s="4">
         <f>Extrapolations!AJ7</f>
-        <v>1.8223851973329149E-4</v>
+        <v>9.3239985476639982E-5</v>
       </c>
       <c r="V5" s="4">
         <f>Extrapolations!AK7</f>
-        <v>1.8223851973329149E-4</v>
+        <v>9.3239985476639982E-5</v>
       </c>
       <c r="W5" s="4">
         <f>Extrapolations!AL7</f>
-        <v>1.8223851973329149E-4</v>
+        <v>9.3239985476639982E-5</v>
       </c>
       <c r="X5" s="4">
         <f>Extrapolations!AM7</f>
-        <v>1.8223851973329149E-4</v>
+        <v>9.3239985476639982E-5</v>
       </c>
       <c r="Y5" s="4">
         <f>Extrapolations!AN7</f>
-        <v>1.8223851973329149E-4</v>
+        <v>9.3239985476639982E-5</v>
       </c>
       <c r="Z5" s="4">
         <f>Extrapolations!AO7</f>
-        <v>1.8223851973329149E-4</v>
+        <v>9.3239985476639982E-5</v>
       </c>
       <c r="AA5" s="4">
         <f>Extrapolations!AP7</f>
-        <v>1.8223851973329149E-4</v>
+        <v>9.3239985476639982E-5</v>
       </c>
       <c r="AB5" s="4">
         <f>Extrapolations!AQ7</f>
-        <v>1.8223851973329149E-4</v>
+        <v>9.3239985476639982E-5</v>
       </c>
       <c r="AC5" s="4">
         <f>Extrapolations!AR7</f>
-        <v>1.8223851973329149E-4</v>
+        <v>9.3239985476639982E-5</v>
       </c>
       <c r="AD5" s="4">
         <f>Extrapolations!AS7</f>
-        <v>1.8223851973329149E-4</v>
+        <v>1.0224826248544657E-4</v>
       </c>
       <c r="AE5" s="4">
         <f>Extrapolations!AT7</f>
-        <v>1.8223851973329149E-4</v>
+        <v>1.0303507011696843E-4</v>
       </c>
       <c r="AG5" s="4"/>
       <c r="AH5" s="4"/>
@@ -10618,123 +10618,123 @@
       </c>
       <c r="B8" s="4">
         <f>B$5*Calculations!$B$27</f>
-        <v>5.4671555919987437E-4</v>
+        <v>2.7971995642991991E-4</v>
       </c>
       <c r="C8" s="4">
         <f>C$5*Calculations!$B$27</f>
-        <v>5.4671555919987437E-4</v>
+        <v>2.7971995642991991E-4</v>
       </c>
       <c r="D8" s="4">
         <f>D$5*Calculations!$B$27</f>
-        <v>5.4671555919987437E-4</v>
+        <v>2.7971995642991991E-4</v>
       </c>
       <c r="E8" s="4">
         <f>E$5*Calculations!$B$27</f>
-        <v>5.4671555919987437E-4</v>
+        <v>2.7971995642991991E-4</v>
       </c>
       <c r="F8" s="4">
         <f>F$5*Calculations!$B$27</f>
-        <v>5.4671555919987437E-4</v>
+        <v>2.7971995642991991E-4</v>
       </c>
       <c r="G8" s="4">
         <f>G$5*Calculations!$B$27</f>
-        <v>5.4671555919987437E-4</v>
+        <v>2.7971995642991991E-4</v>
       </c>
       <c r="H8" s="4">
         <f>H$5*Calculations!$B$27</f>
-        <v>5.4671555919987437E-4</v>
+        <v>2.7971995642991991E-4</v>
       </c>
       <c r="I8" s="4">
         <f>I$5*Calculations!$B$27</f>
-        <v>5.4671555919987437E-4</v>
+        <v>2.7971995642991991E-4</v>
       </c>
       <c r="J8" s="4">
         <f>J$5*Calculations!$B$27</f>
-        <v>5.4671555919987437E-4</v>
+        <v>2.7971995642991991E-4</v>
       </c>
       <c r="K8" s="4">
         <f>K$5*Calculations!$B$27</f>
-        <v>5.4671555919987437E-4</v>
+        <v>2.7971995642991991E-4</v>
       </c>
       <c r="L8" s="4">
         <f>L$5*Calculations!$B$27</f>
-        <v>5.4671555919987437E-4</v>
+        <v>2.7971995642991991E-4</v>
       </c>
       <c r="M8" s="4">
         <f>M$5*Calculations!$B$27</f>
-        <v>5.4671555919987437E-4</v>
+        <v>2.7971995642991991E-4</v>
       </c>
       <c r="N8" s="4">
         <f>N$5*Calculations!$B$27</f>
-        <v>5.4671555919987437E-4</v>
+        <v>2.7971995642991991E-4</v>
       </c>
       <c r="O8" s="4">
         <f>O$5*Calculations!$B$27</f>
-        <v>5.4671555919987437E-4</v>
+        <v>2.7971995642991991E-4</v>
       </c>
       <c r="P8" s="4">
         <f>P$5*Calculations!$B$27</f>
-        <v>5.4671555919987437E-4</v>
+        <v>2.7971995642991991E-4</v>
       </c>
       <c r="Q8" s="4">
         <f>Q$5*Calculations!$B$27</f>
-        <v>5.4671555919987437E-4</v>
+        <v>2.7971995642991991E-4</v>
       </c>
       <c r="R8" s="4">
         <f>R$5*Calculations!$B$27</f>
-        <v>5.4671555919987437E-4</v>
+        <v>2.7971995642991991E-4</v>
       </c>
       <c r="S8" s="4">
         <f>S$5*Calculations!$B$27</f>
-        <v>5.4671555919987437E-4</v>
+        <v>2.7971995642991991E-4</v>
       </c>
       <c r="T8" s="4">
         <f>T$5*Calculations!$B$27</f>
-        <v>5.4671555919987437E-4</v>
+        <v>2.7971995642991991E-4</v>
       </c>
       <c r="U8" s="4">
         <f>U$5*Calculations!$B$27</f>
-        <v>5.4671555919987437E-4</v>
+        <v>2.7971995642991991E-4</v>
       </c>
       <c r="V8" s="4">
         <f>V$5*Calculations!$B$27</f>
-        <v>5.4671555919987437E-4</v>
+        <v>2.7971995642991991E-4</v>
       </c>
       <c r="W8" s="4">
         <f>W$5*Calculations!$B$27</f>
-        <v>5.4671555919987437E-4</v>
+        <v>2.7971995642991991E-4</v>
       </c>
       <c r="X8" s="4">
         <f>X$5*Calculations!$B$27</f>
-        <v>5.4671555919987437E-4</v>
+        <v>2.7971995642991991E-4</v>
       </c>
       <c r="Y8" s="4">
         <f>Y$5*Calculations!$B$27</f>
-        <v>5.4671555919987437E-4</v>
+        <v>2.7971995642991991E-4</v>
       </c>
       <c r="Z8" s="4">
         <f>Z$5*Calculations!$B$27</f>
-        <v>5.4671555919987437E-4</v>
+        <v>2.7971995642991991E-4</v>
       </c>
       <c r="AA8" s="4">
         <f>AA$5*Calculations!$B$27</f>
-        <v>5.4671555919987437E-4</v>
+        <v>2.7971995642991991E-4</v>
       </c>
       <c r="AB8" s="4">
         <f>AB$5*Calculations!$B$27</f>
-        <v>5.4671555919987437E-4</v>
+        <v>2.7971995642991991E-4</v>
       </c>
       <c r="AC8" s="4">
         <f>AC$5*Calculations!$B$27</f>
-        <v>5.4671555919987437E-4</v>
+        <v>2.7971995642991991E-4</v>
       </c>
       <c r="AD8" s="4">
         <f>AD$5*Calculations!$B$27</f>
-        <v>5.4671555919987437E-4</v>
+        <v>3.0674478745633968E-4</v>
       </c>
       <c r="AE8" s="4">
         <f>AE$5*Calculations!$B$27</f>
-        <v>5.4671555919987437E-4</v>
+        <v>3.0910521035090526E-4</v>
       </c>
       <c r="AG8" s="4"/>
       <c r="AH8" s="4"/>
@@ -16752,88 +16752,88 @@
         <v>5.7245968727451246E-4</v>
       </c>
       <c r="F12" s="4">
-        <v>4.3956547255263602E-4</v>
+        <v>3.0464933987873528E-4</v>
       </c>
       <c r="G12" s="4">
-        <v>4.4366680476890972E-4</v>
+        <v>3.0464933987873528E-4</v>
       </c>
       <c r="H12" s="4">
-        <v>4.4597245060431232E-4</v>
+        <v>3.3408269543052564E-4</v>
       </c>
       <c r="I12" s="4">
-        <v>4.4931411605150481E-4</v>
+        <v>3.3665348546582375E-4</v>
       </c>
       <c r="J12" s="4">
-        <v>4.5288823478004158E-4</v>
+        <v>3.3935581504087849E-4</v>
       </c>
       <c r="K12" s="4">
-        <v>4.5662840926832999E-4</v>
+        <v>3.4216015354620157E-4</v>
       </c>
       <c r="L12" s="4">
-        <v>4.6040875969022651E-4</v>
+        <v>3.4502111275582734E-4</v>
       </c>
       <c r="M12" s="4">
-        <v>4.6419842254086203E-4</v>
+        <v>3.4790902074721106E-4</v>
       </c>
       <c r="N12" s="4">
-        <v>4.6802171784268048E-4</v>
+        <v>3.5081980617662339E-4</v>
       </c>
       <c r="O12" s="4">
-        <v>4.718495549789862E-4</v>
+        <v>3.5375247221412683E-4</v>
       </c>
       <c r="P12" s="4">
-        <v>4.7569706545502331E-4</v>
+        <v>3.5670603348759934E-4</v>
       </c>
       <c r="Q12" s="4">
-        <v>4.7956228574948121E-4</v>
+        <v>3.5968007751568736E-4</v>
       </c>
       <c r="R12" s="4">
-        <v>4.8344561142611898E-4</v>
+        <v>3.626744897202374E-4</v>
       </c>
       <c r="S12" s="4">
-        <v>4.8740041976327717E-4</v>
+        <v>3.656928831323635E-4</v>
       </c>
       <c r="T12" s="4">
-        <v>4.9138744510057676E-4</v>
+        <v>3.6873385989859042E-4</v>
       </c>
       <c r="U12" s="4">
-        <v>4.9540734035651132E-4</v>
+        <v>3.7179596105709373E-4</v>
       </c>
       <c r="V12" s="4">
-        <v>4.9946276009751292E-4</v>
+        <v>3.7487939284855035E-4</v>
       </c>
       <c r="W12" s="4">
-        <v>5.0354741343006288E-4</v>
+        <v>3.7798229146832611E-4</v>
       </c>
       <c r="X12" s="4">
-        <v>5.076679534506399E-4</v>
+        <v>3.8110333926765313E-4</v>
       </c>
       <c r="Y12" s="4">
-        <v>5.1181172688478038E-4</v>
+        <v>3.8424184495833714E-4</v>
       </c>
       <c r="Z12" s="4">
-        <v>5.1597913882790009E-4</v>
+        <v>3.8739917202040771E-4</v>
       </c>
       <c r="AA12" s="4">
-        <v>5.2017698058550235E-4</v>
+        <v>3.9057663428336076E-4</v>
       </c>
       <c r="AB12" s="4">
-        <v>5.2440413218790766E-4</v>
+        <v>3.937746365900064E-4</v>
       </c>
       <c r="AC12" s="4">
-        <v>5.2866665576887042E-4</v>
+        <v>3.9699374037329777E-4</v>
       </c>
       <c r="AD12" s="4">
-        <v>5.3296936481509794E-4</v>
+        <v>4.0023428554842422E-4</v>
       </c>
       <c r="AE12" s="4">
-        <v>5.3730424796901105E-4</v>
+        <v>4.0349549298394053E-4</v>
       </c>
       <c r="AF12" s="4">
-        <v>5.4167698609809006E-4</v>
+        <v>4.067774772580003E-4</v>
       </c>
       <c r="AG12" s="4">
-        <v>5.4607888156546253E-4</v>
+        <v>4.1007787424136491E-4</v>
       </c>
       <c r="AH12" s="4"/>
       <c r="AI12" s="4"/>
@@ -16857,88 +16857,88 @@
         <v>4.7951937565239972E-5</v>
       </c>
       <c r="F13" s="4">
-        <v>1.8223851973329149E-4</v>
+        <v>9.3239985476639982E-5</v>
       </c>
       <c r="G13" s="4">
-        <v>1.8223851973329149E-4</v>
+        <v>9.3239985476639982E-5</v>
       </c>
       <c r="H13" s="4">
-        <v>1.8223851973329149E-4</v>
+        <v>1.0224826248544657E-4</v>
       </c>
       <c r="I13" s="4">
-        <v>1.8223851973329149E-4</v>
+        <v>1.0303507011696843E-4</v>
       </c>
       <c r="J13" s="4">
-        <v>1.8223851973329149E-4</v>
+        <v>1.0386213631193046E-4</v>
       </c>
       <c r="K13" s="4">
-        <v>1.8223851973329149E-4</v>
+        <v>1.0472042302810055E-4</v>
       </c>
       <c r="L13" s="4">
-        <v>1.8223851973329149E-4</v>
+        <v>1.0559603889275644E-4</v>
       </c>
       <c r="M13" s="4">
-        <v>1.8223851973329149E-4</v>
+        <v>1.0647990261385189E-4</v>
       </c>
       <c r="N13" s="4">
-        <v>1.8223851973329149E-4</v>
+        <v>1.0737076812917535E-4</v>
       </c>
       <c r="O13" s="4">
-        <v>1.8223851973329149E-4</v>
+        <v>1.0826833035220035E-4</v>
       </c>
       <c r="P13" s="4">
-        <v>1.8223851973329149E-4</v>
+        <v>1.0917228770314212E-4</v>
       </c>
       <c r="Q13" s="4">
-        <v>1.8223851973329149E-4</v>
+        <v>1.1008251393930003E-4</v>
       </c>
       <c r="R13" s="4">
-        <v>1.8223851973329149E-4</v>
+        <v>1.1099897399325733E-4</v>
       </c>
       <c r="S13" s="4">
-        <v>1.8223851973329149E-4</v>
+        <v>1.1192277365755811E-4</v>
       </c>
       <c r="T13" s="4">
-        <v>1.8223851973329149E-4</v>
+        <v>1.1285348510971702E-4</v>
       </c>
       <c r="U13" s="4">
-        <v>1.8223851973329149E-4</v>
+        <v>1.1379066182462636E-4</v>
       </c>
       <c r="V13" s="4">
-        <v>1.8223851973329149E-4</v>
+        <v>1.1473436692363647E-4</v>
       </c>
       <c r="W13" s="4">
-        <v>1.8223851973329149E-4</v>
+        <v>1.156840299767668E-4</v>
       </c>
       <c r="X13" s="4">
-        <v>1.8223851973329149E-4</v>
+        <v>1.1663924770872375E-4</v>
       </c>
       <c r="Y13" s="4">
-        <v>1.8223851973329149E-4</v>
+        <v>1.1759980854609242E-4</v>
       </c>
       <c r="Z13" s="4">
-        <v>1.8223851973329149E-4</v>
+        <v>1.1856612979113317E-4</v>
       </c>
       <c r="AA13" s="4">
-        <v>1.8223851973329149E-4</v>
+        <v>1.1953861355022565E-4</v>
       </c>
       <c r="AB13" s="4">
-        <v>1.8223851973329149E-4</v>
+        <v>1.2051738372824274E-4</v>
       </c>
       <c r="AC13" s="4">
-        <v>1.8223851973329149E-4</v>
+        <v>1.2150261215552689E-4</v>
       </c>
       <c r="AD13" s="4">
-        <v>1.8223851973329149E-4</v>
+        <v>1.2249440286541473E-4</v>
       </c>
       <c r="AE13" s="4">
-        <v>1.8223851973329149E-4</v>
+        <v>1.2349251739947177E-4</v>
       </c>
       <c r="AF13" s="4">
-        <v>1.8223851973329149E-4</v>
+        <v>1.2449699082511483E-4</v>
       </c>
       <c r="AG13" s="4">
-        <v>1.8223851973329149E-4</v>
+        <v>1.2550709958464328E-4</v>
       </c>
       <c r="AH13" s="4"/>
       <c r="AI13" s="4"/>
@@ -18530,16 +18530,16 @@
         <v>7</v>
       </c>
       <c r="B4">
-        <v>1.3074072528197812E-3</v>
+        <v>9.7898292792220369E-4</v>
       </c>
       <c r="C4">
-        <v>4.0685158562424757E-4</v>
+        <v>3.0464933987873528E-4</v>
       </c>
       <c r="D4">
-        <v>4.0685158562424757E-4</v>
+        <v>3.0464933987873528E-4</v>
       </c>
       <c r="E4">
-        <v>4.0685158562424757E-4</v>
+        <v>3.0464933987873528E-4</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -18548,7 +18548,7 @@
         <v>0</v>
       </c>
       <c r="H4">
-        <v>1.2205547568727424E-3</v>
+        <v>9.1394801963620568E-4</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -18712,16 +18712,16 @@
         <v>7</v>
       </c>
       <c r="B12">
-        <v>5.437858374844844E-4</v>
+        <v>2.9962432880267732E-4</v>
       </c>
       <c r="C12">
-        <v>1.6922051621130835E-4</v>
+        <v>9.3239985476639982E-5</v>
       </c>
       <c r="D12">
-        <v>1.6922051621130835E-4</v>
+        <v>9.3239985476639982E-5</v>
       </c>
       <c r="E12">
-        <v>1.6922051621130835E-4</v>
+        <v>9.3239985476639982E-5</v>
       </c>
       <c r="F12">
         <v>0</v>
@@ -18730,7 +18730,7 @@
         <v>0</v>
       </c>
       <c r="H12">
-        <v>5.0766154863392504E-4</v>
+        <v>2.7971995642991991E-4</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -20365,223 +20365,223 @@
       <c r="O6" s="23"/>
       <c r="P6" s="4">
         <f t="shared" ref="P6:AM6" si="5">TREND($AQ6:$BR6,$AQ$1:$BR$1,P$1)</f>
-        <v>3.3000958546164708E-4</v>
+        <v>2.290338125160345E-4</v>
       </c>
       <c r="Q6" s="4">
         <f>TREND($AQ6:$BR6,$AQ$1:$BR$1,Q$1)</f>
-        <v>3.3397333498517805E-4</v>
+        <v>2.3241910879234773E-4</v>
       </c>
       <c r="R6" s="4">
         <f t="shared" si="5"/>
-        <v>3.3793708450870902E-4</v>
+        <v>2.3580440506866095E-4</v>
       </c>
       <c r="S6" s="4">
         <f t="shared" si="5"/>
-        <v>3.4190083403223999E-4</v>
+        <v>2.3918970134497418E-4</v>
       </c>
       <c r="T6" s="4">
         <f t="shared" si="5"/>
-        <v>3.4586458355577096E-4</v>
+        <v>2.4257499762128654E-4</v>
       </c>
       <c r="U6" s="4">
         <f t="shared" si="5"/>
-        <v>3.4982833307930193E-4</v>
+        <v>2.4596029389759976E-4</v>
       </c>
       <c r="V6" s="4">
         <f t="shared" si="5"/>
-        <v>3.537920826028329E-4</v>
+        <v>2.4934559017391299E-4</v>
       </c>
       <c r="W6" s="4">
         <f t="shared" si="5"/>
-        <v>3.5775583212636387E-4</v>
+        <v>2.5273088645022621E-4</v>
       </c>
       <c r="X6" s="4">
         <f t="shared" si="5"/>
-        <v>3.6171958164989484E-4</v>
+        <v>2.5611618272653944E-4</v>
       </c>
       <c r="Y6" s="4">
         <f t="shared" si="5"/>
-        <v>3.6568333117342582E-4</v>
+        <v>2.595014790028518E-4</v>
       </c>
       <c r="Z6" s="4">
         <f t="shared" si="5"/>
-        <v>3.6964708069695679E-4</v>
+        <v>2.6288677527916502E-4</v>
       </c>
       <c r="AA6" s="4">
         <f t="shared" si="5"/>
-        <v>3.7361083022048776E-4</v>
+        <v>2.6627207155547825E-4</v>
       </c>
       <c r="AB6" s="4">
         <f t="shared" si="5"/>
-        <v>3.7757457974401873E-4</v>
+        <v>2.6965736783179147E-4</v>
       </c>
       <c r="AC6" s="4">
         <f t="shared" si="5"/>
-        <v>3.815383292675497E-4</v>
+        <v>2.7304266410810383E-4</v>
       </c>
       <c r="AD6" s="4">
         <f t="shared" si="5"/>
-        <v>3.8550207879108067E-4</v>
+        <v>2.7642796038441705E-4</v>
       </c>
       <c r="AE6" s="4">
         <f t="shared" si="5"/>
-        <v>3.8946582831461164E-4</v>
+        <v>2.7981325666073028E-4</v>
       </c>
       <c r="AF6" s="4">
         <f t="shared" si="5"/>
-        <v>3.9342957783814261E-4</v>
+        <v>2.831985529370435E-4</v>
       </c>
       <c r="AG6" s="4">
         <f t="shared" si="5"/>
-        <v>3.9739332736167358E-4</v>
+        <v>2.8658384921335586E-4</v>
       </c>
       <c r="AH6" s="4">
         <f t="shared" si="5"/>
-        <v>4.0135707688520629E-4</v>
+        <v>2.8996914548966909E-4</v>
       </c>
       <c r="AI6" s="4">
         <f t="shared" si="5"/>
-        <v>4.0532082640873726E-4</v>
+        <v>2.9335444176598231E-4</v>
       </c>
       <c r="AJ6" s="4">
         <f t="shared" si="5"/>
-        <v>4.0928457593226823E-4</v>
+        <v>2.9673973804229554E-4</v>
       </c>
       <c r="AK6" s="4">
         <f t="shared" si="5"/>
-        <v>4.132483254557992E-4</v>
+        <v>3.001250343186079E-4</v>
       </c>
       <c r="AL6" s="4">
         <f t="shared" si="5"/>
-        <v>4.1721207497933017E-4</v>
+        <v>3.0351033059492112E-4</v>
       </c>
       <c r="AM6" s="4">
         <f t="shared" si="5"/>
-        <v>4.2117582450286115E-4</v>
+        <v>3.0689562687123435E-4</v>
       </c>
       <c r="AN6" s="4">
         <f>TREND($AQ6:$BR6,$AQ$1:$BR$1,AN$1)</f>
-        <v>4.2513957402639212E-4</v>
+        <v>3.1028092314754757E-4</v>
       </c>
       <c r="AO6" s="4">
         <f t="shared" ref="AO6:AP6" si="6">TREND($AQ6:$BR6,$AQ$1:$BR$1,AO$1)</f>
-        <v>4.2910332354992309E-4</v>
+        <v>3.1366621942385993E-4</v>
       </c>
       <c r="AP6" s="4">
         <f t="shared" si="6"/>
-        <v>4.3306707307345406E-4</v>
+        <v>3.1705151570017315E-4</v>
       </c>
       <c r="AQ6" s="26">
         <f>BNVFE!F12</f>
-        <v>4.3956547255263602E-4</v>
+        <v>3.0464933987873528E-4</v>
       </c>
       <c r="AR6" s="20">
         <f>BNVFE!G12</f>
-        <v>4.4366680476890972E-4</v>
+        <v>3.0464933987873528E-4</v>
       </c>
       <c r="AS6" s="26">
         <f>BNVFE!H12</f>
-        <v>4.4597245060431232E-4</v>
+        <v>3.3408269543052564E-4</v>
       </c>
       <c r="AT6" s="26">
         <f>BNVFE!I12</f>
-        <v>4.4931411605150481E-4</v>
+        <v>3.3665348546582375E-4</v>
       </c>
       <c r="AU6" s="26">
         <f>BNVFE!J12</f>
-        <v>4.5288823478004158E-4</v>
+        <v>3.3935581504087849E-4</v>
       </c>
       <c r="AV6" s="26">
         <f>BNVFE!K12</f>
-        <v>4.5662840926832999E-4</v>
+        <v>3.4216015354620157E-4</v>
       </c>
       <c r="AW6" s="26">
         <f>BNVFE!L12</f>
-        <v>4.6040875969022651E-4</v>
+        <v>3.4502111275582734E-4</v>
       </c>
       <c r="AX6" s="26">
         <f>BNVFE!M12</f>
-        <v>4.6419842254086203E-4</v>
+        <v>3.4790902074721106E-4</v>
       </c>
       <c r="AY6" s="26">
         <f>BNVFE!N12</f>
-        <v>4.6802171784268048E-4</v>
+        <v>3.5081980617662339E-4</v>
       </c>
       <c r="AZ6" s="26">
         <f>BNVFE!O12</f>
-        <v>4.718495549789862E-4</v>
+        <v>3.5375247221412683E-4</v>
       </c>
       <c r="BA6" s="26">
         <f>BNVFE!P12</f>
-        <v>4.7569706545502331E-4</v>
+        <v>3.5670603348759934E-4</v>
       </c>
       <c r="BB6" s="26">
         <f>BNVFE!Q12</f>
-        <v>4.7956228574948121E-4</v>
+        <v>3.5968007751568736E-4</v>
       </c>
       <c r="BC6" s="26">
         <f>BNVFE!R12</f>
-        <v>4.8344561142611898E-4</v>
+        <v>3.626744897202374E-4</v>
       </c>
       <c r="BD6" s="26">
         <f>BNVFE!S12</f>
-        <v>4.8740041976327717E-4</v>
+        <v>3.656928831323635E-4</v>
       </c>
       <c r="BE6" s="26">
         <f>BNVFE!T12</f>
-        <v>4.9138744510057676E-4</v>
+        <v>3.6873385989859042E-4</v>
       </c>
       <c r="BF6" s="26">
         <f>BNVFE!U12</f>
-        <v>4.9540734035651132E-4</v>
+        <v>3.7179596105709373E-4</v>
       </c>
       <c r="BG6" s="26">
         <f>BNVFE!V12</f>
-        <v>4.9946276009751292E-4</v>
+        <v>3.7487939284855035E-4</v>
       </c>
       <c r="BH6" s="26">
         <f>BNVFE!W12</f>
-        <v>5.0354741343006288E-4</v>
+        <v>3.7798229146832611E-4</v>
       </c>
       <c r="BI6" s="26">
         <f>BNVFE!X12</f>
-        <v>5.076679534506399E-4</v>
+        <v>3.8110333926765313E-4</v>
       </c>
       <c r="BJ6" s="26">
         <f>BNVFE!Y12</f>
-        <v>5.1181172688478038E-4</v>
+        <v>3.8424184495833714E-4</v>
       </c>
       <c r="BK6" s="26">
         <f>BNVFE!Z12</f>
-        <v>5.1597913882790009E-4</v>
+        <v>3.8739917202040771E-4</v>
       </c>
       <c r="BL6" s="26">
         <f>BNVFE!AA12</f>
-        <v>5.2017698058550235E-4</v>
+        <v>3.9057663428336076E-4</v>
       </c>
       <c r="BM6" s="26">
         <f>BNVFE!AB12</f>
-        <v>5.2440413218790766E-4</v>
+        <v>3.937746365900064E-4</v>
       </c>
       <c r="BN6" s="26">
         <f>BNVFE!AC12</f>
-        <v>5.2866665576887042E-4</v>
+        <v>3.9699374037329777E-4</v>
       </c>
       <c r="BO6" s="26">
         <f>BNVFE!AD12</f>
-        <v>5.3296936481509794E-4</v>
+        <v>4.0023428554842422E-4</v>
       </c>
       <c r="BP6" s="26">
         <f>BNVFE!AE12</f>
-        <v>5.3730424796901105E-4</v>
+        <v>4.0349549298394053E-4</v>
       </c>
       <c r="BQ6" s="26">
         <f>BNVFE!AF12</f>
-        <v>5.4167698609809006E-4</v>
+        <v>4.067774772580003E-4</v>
       </c>
       <c r="BR6" s="26">
         <f>BNVFE!AG12</f>
-        <v>5.4607888156546253E-4</v>
+        <v>4.1007787424136491E-4</v>
       </c>
       <c r="BS6" s="26"/>
       <c r="BT6" s="4"/>
@@ -20608,223 +20608,223 @@
       <c r="O7" s="23"/>
       <c r="P7" s="26">
         <f t="shared" ref="P7:AP7" si="7">Q7</f>
-        <v>1.8223851973329149E-4</v>
+        <v>9.3239985476639982E-5</v>
       </c>
       <c r="Q7" s="26">
         <f t="shared" si="7"/>
-        <v>1.8223851973329149E-4</v>
+        <v>9.3239985476639982E-5</v>
       </c>
       <c r="R7" s="26">
         <f t="shared" si="7"/>
-        <v>1.8223851973329149E-4</v>
+        <v>9.3239985476639982E-5</v>
       </c>
       <c r="S7" s="26">
         <f t="shared" si="7"/>
-        <v>1.8223851973329149E-4</v>
+        <v>9.3239985476639982E-5</v>
       </c>
       <c r="T7" s="26">
         <f t="shared" si="7"/>
-        <v>1.8223851973329149E-4</v>
+        <v>9.3239985476639982E-5</v>
       </c>
       <c r="U7" s="26">
         <f t="shared" si="7"/>
-        <v>1.8223851973329149E-4</v>
+        <v>9.3239985476639982E-5</v>
       </c>
       <c r="V7" s="26">
         <f t="shared" si="7"/>
-        <v>1.8223851973329149E-4</v>
+        <v>9.3239985476639982E-5</v>
       </c>
       <c r="W7" s="26">
         <f t="shared" si="7"/>
-        <v>1.8223851973329149E-4</v>
+        <v>9.3239985476639982E-5</v>
       </c>
       <c r="X7" s="26">
         <f t="shared" si="7"/>
-        <v>1.8223851973329149E-4</v>
+        <v>9.3239985476639982E-5</v>
       </c>
       <c r="Y7" s="26">
         <f t="shared" si="7"/>
-        <v>1.8223851973329149E-4</v>
+        <v>9.3239985476639982E-5</v>
       </c>
       <c r="Z7" s="26">
         <f t="shared" si="7"/>
-        <v>1.8223851973329149E-4</v>
+        <v>9.3239985476639982E-5</v>
       </c>
       <c r="AA7" s="26">
         <f t="shared" si="7"/>
-        <v>1.8223851973329149E-4</v>
+        <v>9.3239985476639982E-5</v>
       </c>
       <c r="AB7" s="26">
         <f t="shared" si="7"/>
-        <v>1.8223851973329149E-4</v>
+        <v>9.3239985476639982E-5</v>
       </c>
       <c r="AC7" s="26">
         <f t="shared" si="7"/>
-        <v>1.8223851973329149E-4</v>
+        <v>9.3239985476639982E-5</v>
       </c>
       <c r="AD7" s="26">
         <f t="shared" si="7"/>
-        <v>1.8223851973329149E-4</v>
+        <v>9.3239985476639982E-5</v>
       </c>
       <c r="AE7" s="26">
         <f t="shared" si="7"/>
-        <v>1.8223851973329149E-4</v>
+        <v>9.3239985476639982E-5</v>
       </c>
       <c r="AF7" s="26">
         <f t="shared" si="7"/>
-        <v>1.8223851973329149E-4</v>
+        <v>9.3239985476639982E-5</v>
       </c>
       <c r="AG7" s="26">
         <f t="shared" si="7"/>
-        <v>1.8223851973329149E-4</v>
+        <v>9.3239985476639982E-5</v>
       </c>
       <c r="AH7" s="26">
         <f t="shared" si="7"/>
-        <v>1.8223851973329149E-4</v>
+        <v>9.3239985476639982E-5</v>
       </c>
       <c r="AI7" s="26">
         <f t="shared" si="7"/>
-        <v>1.8223851973329149E-4</v>
+        <v>9.3239985476639982E-5</v>
       </c>
       <c r="AJ7" s="26">
         <f t="shared" si="7"/>
-        <v>1.8223851973329149E-4</v>
+        <v>9.3239985476639982E-5</v>
       </c>
       <c r="AK7" s="26">
         <f t="shared" si="7"/>
-        <v>1.8223851973329149E-4</v>
+        <v>9.3239985476639982E-5</v>
       </c>
       <c r="AL7" s="26">
         <f t="shared" si="7"/>
-        <v>1.8223851973329149E-4</v>
+        <v>9.3239985476639982E-5</v>
       </c>
       <c r="AM7" s="26">
         <f t="shared" si="7"/>
-        <v>1.8223851973329149E-4</v>
+        <v>9.3239985476639982E-5</v>
       </c>
       <c r="AN7" s="26">
         <f t="shared" si="7"/>
-        <v>1.8223851973329149E-4</v>
+        <v>9.3239985476639982E-5</v>
       </c>
       <c r="AO7" s="26">
         <f t="shared" si="7"/>
-        <v>1.8223851973329149E-4</v>
+        <v>9.3239985476639982E-5</v>
       </c>
       <c r="AP7" s="26">
         <f t="shared" si="7"/>
-        <v>1.8223851973329149E-4</v>
+        <v>9.3239985476639982E-5</v>
       </c>
       <c r="AQ7" s="26">
         <f>AR7</f>
-        <v>1.8223851973329149E-4</v>
+        <v>9.3239985476639982E-5</v>
       </c>
       <c r="AR7" s="20">
         <f>BNVFE!G13</f>
-        <v>1.8223851973329149E-4</v>
+        <v>9.3239985476639982E-5</v>
       </c>
       <c r="AS7" s="26">
         <f>BNVFE!H13</f>
-        <v>1.8223851973329149E-4</v>
+        <v>1.0224826248544657E-4</v>
       </c>
       <c r="AT7" s="26">
         <f>BNVFE!I13</f>
-        <v>1.8223851973329149E-4</v>
+        <v>1.0303507011696843E-4</v>
       </c>
       <c r="AU7" s="26">
         <f>BNVFE!J13</f>
-        <v>1.8223851973329149E-4</v>
+        <v>1.0386213631193046E-4</v>
       </c>
       <c r="AV7" s="26">
         <f>BNVFE!K13</f>
-        <v>1.8223851973329149E-4</v>
+        <v>1.0472042302810055E-4</v>
       </c>
       <c r="AW7" s="26">
         <f>BNVFE!L13</f>
-        <v>1.8223851973329149E-4</v>
+        <v>1.0559603889275644E-4</v>
       </c>
       <c r="AX7" s="26">
         <f>BNVFE!M13</f>
-        <v>1.8223851973329149E-4</v>
+        <v>1.0647990261385189E-4</v>
       </c>
       <c r="AY7" s="26">
         <f>BNVFE!N13</f>
-        <v>1.8223851973329149E-4</v>
+        <v>1.0737076812917535E-4</v>
       </c>
       <c r="AZ7" s="26">
         <f>BNVFE!O13</f>
-        <v>1.8223851973329149E-4</v>
+        <v>1.0826833035220035E-4</v>
       </c>
       <c r="BA7" s="26">
         <f>BNVFE!P13</f>
-        <v>1.8223851973329149E-4</v>
+        <v>1.0917228770314212E-4</v>
       </c>
       <c r="BB7" s="26">
         <f>BNVFE!Q13</f>
-        <v>1.8223851973329149E-4</v>
+        <v>1.1008251393930003E-4</v>
       </c>
       <c r="BC7" s="26">
         <f>BNVFE!R13</f>
-        <v>1.8223851973329149E-4</v>
+        <v>1.1099897399325733E-4</v>
       </c>
       <c r="BD7" s="26">
         <f>BNVFE!S13</f>
-        <v>1.8223851973329149E-4</v>
+        <v>1.1192277365755811E-4</v>
       </c>
       <c r="BE7" s="26">
         <f>BNVFE!T13</f>
-        <v>1.8223851973329149E-4</v>
+        <v>1.1285348510971702E-4</v>
       </c>
       <c r="BF7" s="26">
         <f>BNVFE!U13</f>
-        <v>1.8223851973329149E-4</v>
+        <v>1.1379066182462636E-4</v>
       </c>
       <c r="BG7" s="26">
         <f>BNVFE!V13</f>
-        <v>1.8223851973329149E-4</v>
+        <v>1.1473436692363647E-4</v>
       </c>
       <c r="BH7" s="26">
         <f>BNVFE!W13</f>
-        <v>1.8223851973329149E-4</v>
+        <v>1.156840299767668E-4</v>
       </c>
       <c r="BI7" s="26">
         <f>BNVFE!X13</f>
-        <v>1.8223851973329149E-4</v>
+        <v>1.1663924770872375E-4</v>
       </c>
       <c r="BJ7" s="26">
         <f>BNVFE!Y13</f>
-        <v>1.8223851973329149E-4</v>
+        <v>1.1759980854609242E-4</v>
       </c>
       <c r="BK7" s="26">
         <f>BNVFE!Z13</f>
-        <v>1.8223851973329149E-4</v>
+        <v>1.1856612979113317E-4</v>
       </c>
       <c r="BL7" s="26">
         <f>BNVFE!AA13</f>
-        <v>1.8223851973329149E-4</v>
+        <v>1.1953861355022565E-4</v>
       </c>
       <c r="BM7" s="26">
         <f>BNVFE!AB13</f>
-        <v>1.8223851973329149E-4</v>
+        <v>1.2051738372824274E-4</v>
       </c>
       <c r="BN7" s="26">
         <f>BNVFE!AC13</f>
-        <v>1.8223851973329149E-4</v>
+        <v>1.2150261215552689E-4</v>
       </c>
       <c r="BO7" s="26">
         <f>BNVFE!AD13</f>
-        <v>1.8223851973329149E-4</v>
+        <v>1.2249440286541473E-4</v>
       </c>
       <c r="BP7" s="26">
         <f>BNVFE!AE13</f>
-        <v>1.8223851973329149E-4</v>
+        <v>1.2349251739947177E-4</v>
       </c>
       <c r="BQ7" s="26">
         <f>BNVFE!AF13</f>
-        <v>1.8223851973329149E-4</v>
+        <v>1.2449699082511483E-4</v>
       </c>
       <c r="BR7" s="26">
         <f>BNVFE!AG13</f>
-        <v>1.8223851973329149E-4</v>
+        <v>1.2550709958464328E-4</v>
       </c>
       <c r="BS7" s="26"/>
       <c r="BT7" s="4"/>

--- a/InputData/trans/BHNVFEAL/BAU Historical New Veh Fuel Economy After Lifetime.xlsx
+++ b/InputData/trans/BHNVFEAL/BAU Historical New Veh Fuel Economy After Lifetime.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OliviaAshmoore\Documents\Github Repos\eps-us\InputData\trans\BHNVFEAL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B65B1C6E-2B31-47A2-A24A-04186B1BE671}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46122336-199E-4D3F-9ABC-740C7AD03B73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="615" yWindow="45" windowWidth="20370" windowHeight="17025" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -3231,136 +3231,136 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="70"/>
                 <c:pt idx="24" formatCode="0.00E+00">
-                  <c:v>5.9551063413003282E-5</c:v>
+                  <c:v>5.8438727152645888E-5</c:v>
                 </c:pt>
                 <c:pt idx="25" formatCode="0.00E+00">
-                  <c:v>6.0878373147410427E-5</c:v>
+                  <c:v>5.9741244470903031E-5</c:v>
                 </c:pt>
                 <c:pt idx="26" formatCode="0.00E+00">
-                  <c:v>6.2205682881817138E-5</c:v>
+                  <c:v>6.1043761789159739E-5</c:v>
                 </c:pt>
                 <c:pt idx="27" formatCode="0.00E+00">
-                  <c:v>6.3532992616224283E-5</c:v>
+                  <c:v>6.2346279107416882E-5</c:v>
                 </c:pt>
                 <c:pt idx="28" formatCode="0.00E+00">
-                  <c:v>6.4860302350631428E-5</c:v>
+                  <c:v>6.3648796425673591E-5</c:v>
                 </c:pt>
                 <c:pt idx="29" formatCode="0.00E+00">
-                  <c:v>6.618761208503814E-5</c:v>
+                  <c:v>6.4951313743930733E-5</c:v>
                 </c:pt>
                 <c:pt idx="30" formatCode="0.00E+00">
-                  <c:v>6.7514921819445285E-5</c:v>
+                  <c:v>6.6253831062187442E-5</c:v>
                 </c:pt>
                 <c:pt idx="31" formatCode="0.00E+00">
-                  <c:v>6.8842231553851996E-5</c:v>
+                  <c:v>6.7556348380444584E-5</c:v>
                 </c:pt>
                 <c:pt idx="32" formatCode="0.00E+00">
-                  <c:v>7.0169541288259141E-5</c:v>
+                  <c:v>6.8858865698701293E-5</c:v>
                 </c:pt>
                 <c:pt idx="33" formatCode="0.00E+00">
-                  <c:v>7.1496851022665852E-5</c:v>
+                  <c:v>7.0161383016958435E-5</c:v>
                 </c:pt>
                 <c:pt idx="34" formatCode="0.00E+00">
-                  <c:v>7.2824160757072997E-5</c:v>
+                  <c:v>7.1463900335215144E-5</c:v>
                 </c:pt>
                 <c:pt idx="35" formatCode="0.00E+00">
-                  <c:v>7.4151470491480142E-5</c:v>
+                  <c:v>7.2766417653472287E-5</c:v>
                 </c:pt>
                 <c:pt idx="36" formatCode="0.00E+00">
-                  <c:v>7.5478780225886853E-5</c:v>
+                  <c:v>7.4068934971728995E-5</c:v>
                 </c:pt>
                 <c:pt idx="37" formatCode="0.00E+00">
-                  <c:v>7.6806089960293998E-5</c:v>
+                  <c:v>7.5371452289986138E-5</c:v>
                 </c:pt>
                 <c:pt idx="38" formatCode="0.00E+00">
-                  <c:v>7.8133399694700709E-5</c:v>
+                  <c:v>7.6673969608242847E-5</c:v>
                 </c:pt>
                 <c:pt idx="39" formatCode="0.00E+00">
-                  <c:v>7.977578850124848E-5</c:v>
+                  <c:v>7.8285680732168971E-5</c:v>
                 </c:pt>
                 <c:pt idx="40" formatCode="0.00E+00">
-                  <c:v>8.0968064347595233E-5</c:v>
+                  <c:v>7.9455686419425183E-5</c:v>
                 </c:pt>
                 <c:pt idx="41" formatCode="0.00E+00">
-                  <c:v>8.132511630401103E-5</c:v>
+                  <c:v>7.9806069110588361E-5</c:v>
                 </c:pt>
                 <c:pt idx="42" formatCode="0.00E+00">
-                  <c:v>8.4161072514692597E-5</c:v>
+                  <c:v>8.2589053354941577E-5</c:v>
                 </c:pt>
                 <c:pt idx="43" formatCode="0.00E+00">
-                  <c:v>8.498353764742068E-5</c:v>
+                  <c:v>8.3396155910788876E-5</c:v>
                 </c:pt>
                 <c:pt idx="44" formatCode="0.00E+00">
-                  <c:v>8.5775402347925225E-5</c:v>
+                  <c:v>8.4173229610609506E-5</c:v>
                 </c:pt>
                 <c:pt idx="45" formatCode="0.00E+00">
-                  <c:v>8.6479330619128737E-5</c:v>
+                  <c:v>8.4864009419033756E-5</c:v>
                 </c:pt>
                 <c:pt idx="46" formatCode="0.00E+00">
-                  <c:v>8.7180851987329484E-5</c:v>
+                  <c:v>8.5552427282266762E-5</c:v>
                 </c:pt>
                 <c:pt idx="47" formatCode="0.00E+00">
-                  <c:v>8.7676327828293231E-5</c:v>
+                  <c:v>8.6038648280202556E-5</c:v>
                 </c:pt>
                 <c:pt idx="48" formatCode="0.00E+00">
-                  <c:v>8.808308415773043E-5</c:v>
+                  <c:v>8.6437806931471918E-5</c:v>
                 </c:pt>
                 <c:pt idx="49" formatCode="0.00E+00">
-                  <c:v>8.8443349127241298E-5</c:v>
+                  <c:v>8.6791342620833007E-5</c:v>
                 </c:pt>
                 <c:pt idx="50" formatCode="0.00E+00">
-                  <c:v>8.877490666338608E-5</c:v>
+                  <c:v>8.7116707094273078E-5</c:v>
                 </c:pt>
                 <c:pt idx="51" formatCode="0.00E+00">
-                  <c:v>8.9036788024627383E-5</c:v>
+                  <c:v>8.7373696852958087E-5</c:v>
                 </c:pt>
                 <c:pt idx="52" formatCode="0.00E+00">
-                  <c:v>8.9408940248032558E-5</c:v>
+                  <c:v>8.7738897757801631E-5</c:v>
                 </c:pt>
                 <c:pt idx="53" formatCode="0.00E+00">
-                  <c:v>8.9726171714716883E-5</c:v>
+                  <c:v>8.8050203754089717E-5</c:v>
                 </c:pt>
                 <c:pt idx="54" formatCode="0.00E+00">
-                  <c:v>8.9993423792437643E-5</c:v>
+                  <c:v>8.8312463911269213E-5</c:v>
                 </c:pt>
                 <c:pt idx="55" formatCode="0.00E+00">
-                  <c:v>9.0174807564025167E-5</c:v>
+                  <c:v>8.8490459670374438E-5</c:v>
                 </c:pt>
                 <c:pt idx="56" formatCode="0.00E+00">
-                  <c:v>9.038234516069701E-5</c:v>
+                  <c:v>8.8694120735193857E-5</c:v>
                 </c:pt>
                 <c:pt idx="57" formatCode="0.00E+00">
-                  <c:v>9.0953441555838329E-5</c:v>
+                  <c:v>8.9254549793900385E-5</c:v>
                 </c:pt>
                 <c:pt idx="58" formatCode="0.00E+00">
-                  <c:v>9.1765196895077241E-5</c:v>
+                  <c:v>9.005114260124438E-5</c:v>
                 </c:pt>
                 <c:pt idx="59" formatCode="0.00E+00">
-                  <c:v>9.2611810298042204E-5</c:v>
+                  <c:v>9.0881942369109463E-5</c:v>
                 </c:pt>
                 <c:pt idx="60" formatCode="0.00E+00">
-                  <c:v>9.3647517531163859E-5</c:v>
+                  <c:v>9.1898303940802261E-5</c:v>
                 </c:pt>
                 <c:pt idx="61" formatCode="0.00E+00">
-                  <c:v>9.5050006294872494E-5</c:v>
+                  <c:v>9.3274596042063404E-5</c:v>
                 </c:pt>
                 <c:pt idx="62" formatCode="0.00E+00">
-                  <c:v>9.645662760019035E-5</c:v>
+                  <c:v>9.4654943494441841E-5</c:v>
                 </c:pt>
                 <c:pt idx="63" formatCode="0.00E+00">
-                  <c:v>9.7387214206997634E-5</c:v>
+                  <c:v>9.5568147956131454E-5</c:v>
                 </c:pt>
                 <c:pt idx="64" formatCode="0.00E+00">
-                  <c:v>9.8272881152577143E-5</c:v>
+                  <c:v>9.643727179732782E-5</c:v>
                 </c:pt>
                 <c:pt idx="65" formatCode="0.00E+00">
-                  <c:v>9.9315311676914197E-5</c:v>
+                  <c:v>9.7460231077917589E-5</c:v>
                 </c:pt>
                 <c:pt idx="66" formatCode="0.00E+00">
-                  <c:v>1.0022913979744075E-4</c:v>
+                  <c:v>9.8356990080011308E-5</c:v>
                 </c:pt>
                 <c:pt idx="67" formatCode="0.00E+00">
-                  <c:v>1.0111291012785455E-4</c:v>
+                  <c:v>9.9224252732341657E-5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16437,88 +16437,88 @@
         <v>1.0877081887028839E-4</v>
       </c>
       <c r="F9" s="4">
-        <v>9.5098581742816967E-5</v>
+        <v>9.3322264163941547E-5</v>
       </c>
       <c r="G9" s="4">
-        <v>8.132511630401103E-5</v>
+        <v>7.9806069110588361E-5</v>
       </c>
       <c r="H9" s="4">
-        <v>8.4161072514692597E-5</v>
+        <v>8.2589053354941577E-5</v>
       </c>
       <c r="I9" s="4">
-        <v>8.498353764742068E-5</v>
+        <v>8.3396155910788876E-5</v>
       </c>
       <c r="J9" s="4">
-        <v>8.5775402347925225E-5</v>
+        <v>8.4173229610609506E-5</v>
       </c>
       <c r="K9" s="4">
-        <v>8.6479330619128737E-5</v>
+        <v>8.4864009419033756E-5</v>
       </c>
       <c r="L9" s="4">
-        <v>8.7180851987329484E-5</v>
+        <v>8.5552427282266762E-5</v>
       </c>
       <c r="M9" s="4">
-        <v>8.7676327828293231E-5</v>
+        <v>8.6038648280202556E-5</v>
       </c>
       <c r="N9" s="4">
-        <v>8.808308415773043E-5</v>
+        <v>8.6437806931471918E-5</v>
       </c>
       <c r="O9" s="4">
-        <v>8.8443349127241298E-5</v>
+        <v>8.6791342620833007E-5</v>
       </c>
       <c r="P9" s="4">
-        <v>8.877490666338608E-5</v>
+        <v>8.7116707094273078E-5</v>
       </c>
       <c r="Q9" s="4">
-        <v>8.9036788024627383E-5</v>
+        <v>8.7373696852958087E-5</v>
       </c>
       <c r="R9" s="4">
-        <v>8.9408940248032558E-5</v>
+        <v>8.7738897757801631E-5</v>
       </c>
       <c r="S9" s="4">
-        <v>8.9726171714716883E-5</v>
+        <v>8.8050203754089717E-5</v>
       </c>
       <c r="T9" s="4">
-        <v>8.9993423792437643E-5</v>
+        <v>8.8312463911269213E-5</v>
       </c>
       <c r="U9" s="4">
-        <v>9.0174807564025167E-5</v>
+        <v>8.8490459670374438E-5</v>
       </c>
       <c r="V9" s="4">
-        <v>9.038234516069701E-5</v>
+        <v>8.8694120735193857E-5</v>
       </c>
       <c r="W9" s="4">
-        <v>9.0953441555838329E-5</v>
+        <v>8.9254549793900385E-5</v>
       </c>
       <c r="X9" s="4">
-        <v>9.1765196895077241E-5</v>
+        <v>9.005114260124438E-5</v>
       </c>
       <c r="Y9" s="4">
-        <v>9.2611810298042204E-5</v>
+        <v>9.0881942369109463E-5</v>
       </c>
       <c r="Z9" s="4">
-        <v>9.3647517531163859E-5</v>
+        <v>9.1898303940802261E-5</v>
       </c>
       <c r="AA9" s="4">
-        <v>9.5050006294872494E-5</v>
+        <v>9.3274596042063404E-5</v>
       </c>
       <c r="AB9" s="4">
-        <v>9.645662760019035E-5</v>
+        <v>9.4654943494441841E-5</v>
       </c>
       <c r="AC9" s="4">
-        <v>9.7387214206997634E-5</v>
+        <v>9.5568147956131454E-5</v>
       </c>
       <c r="AD9" s="4">
-        <v>9.8272881152577143E-5</v>
+        <v>9.643727179732782E-5</v>
       </c>
       <c r="AE9" s="4">
-        <v>9.9315311676914197E-5</v>
+        <v>9.7460231077917589E-5</v>
       </c>
       <c r="AF9" s="4">
-        <v>1.0022913979744075E-4</v>
+        <v>9.8356990080011308E-5</v>
       </c>
       <c r="AG9" s="4">
-        <v>1.0111291012785455E-4</v>
+        <v>9.9224252732341657E-5</v>
       </c>
       <c r="AH9" s="4"/>
       <c r="AI9" s="4"/>
@@ -18660,22 +18660,22 @@
         <v>15</v>
       </c>
       <c r="B10">
-        <v>3.0636736837912965E-4</v>
+        <v>3.0156650473713915E-4</v>
       </c>
       <c r="C10" s="4">
-        <v>7.273085411263018E-5</v>
+        <v>7.0213473556835903E-5</v>
       </c>
       <c r="D10" s="4">
-        <v>9.5098581742816967E-5</v>
+        <v>9.3322264163941547E-5</v>
       </c>
       <c r="E10" s="4">
-        <v>9.3478062847081558E-5</v>
+        <v>8.9590243650741159E-5</v>
       </c>
       <c r="F10">
-        <v>3.8357149864294821E-5</v>
+        <v>1.5342859945717928E-4</v>
       </c>
       <c r="G10" s="4">
-        <v>1.4090027704705712E-3</v>
+        <v>1.1549320628198341E-4</v>
       </c>
       <c r="H10" s="4">
         <v>8.379890176963306E-5</v>
@@ -19656,179 +19656,179 @@
       <c r="Z3" s="23"/>
       <c r="AA3" s="4" cm="1">
         <f t="array" ref="AA3">TREND($AQ$3:$AU$3,$AQ$1:$AU$1,AA1)</f>
-        <v>5.9551063413003282E-5</v>
+        <v>5.8438727152645888E-5</v>
       </c>
       <c r="AB3" s="4" cm="1">
         <f t="array" ref="AB3">TREND($AQ$3:$AU$3,$AQ$1:$AU$1,AB1)</f>
-        <v>6.0878373147410427E-5</v>
+        <v>5.9741244470903031E-5</v>
       </c>
       <c r="AC3" s="4" cm="1">
         <f t="array" ref="AC3">TREND($AQ$3:$AU$3,$AQ$1:$AU$1,AC1)</f>
-        <v>6.2205682881817138E-5</v>
+        <v>6.1043761789159739E-5</v>
       </c>
       <c r="AD3" s="4" cm="1">
         <f t="array" ref="AD3">TREND($AQ$3:$AU$3,$AQ$1:$AU$1,AD1)</f>
-        <v>6.3532992616224283E-5</v>
+        <v>6.2346279107416882E-5</v>
       </c>
       <c r="AE3" s="4" cm="1">
         <f t="array" ref="AE3">TREND($AQ$3:$AU$3,$AQ$1:$AU$1,AE1)</f>
-        <v>6.4860302350631428E-5</v>
+        <v>6.3648796425673591E-5</v>
       </c>
       <c r="AF3" s="4" cm="1">
         <f t="array" ref="AF3">TREND($AQ$3:$AU$3,$AQ$1:$AU$1,AF1)</f>
-        <v>6.618761208503814E-5</v>
+        <v>6.4951313743930733E-5</v>
       </c>
       <c r="AG3" s="4" cm="1">
         <f t="array" ref="AG3">TREND($AQ$3:$AU$3,$AQ$1:$AU$1,AG1)</f>
-        <v>6.7514921819445285E-5</v>
+        <v>6.6253831062187442E-5</v>
       </c>
       <c r="AH3" s="4" cm="1">
         <f t="array" ref="AH3">TREND($AQ$3:$AU$3,$AQ$1:$AU$1,AH1)</f>
-        <v>6.8842231553851996E-5</v>
+        <v>6.7556348380444584E-5</v>
       </c>
       <c r="AI3" s="4" cm="1">
         <f t="array" ref="AI3">TREND($AQ$3:$AU$3,$AQ$1:$AU$1,AI1)</f>
-        <v>7.0169541288259141E-5</v>
+        <v>6.8858865698701293E-5</v>
       </c>
       <c r="AJ3" s="4" cm="1">
         <f t="array" ref="AJ3">TREND($AQ$3:$AU$3,$AQ$1:$AU$1,AJ1)</f>
-        <v>7.1496851022665852E-5</v>
+        <v>7.0161383016958435E-5</v>
       </c>
       <c r="AK3" s="4" cm="1">
         <f t="array" ref="AK3">TREND($AQ$3:$AU$3,$AQ$1:$AU$1,AK1)</f>
-        <v>7.2824160757072997E-5</v>
+        <v>7.1463900335215144E-5</v>
       </c>
       <c r="AL3" s="4" cm="1">
         <f t="array" ref="AL3">TREND($AQ$3:$AU$3,$AQ$1:$AU$1,AL1)</f>
-        <v>7.4151470491480142E-5</v>
+        <v>7.2766417653472287E-5</v>
       </c>
       <c r="AM3" s="4" cm="1">
         <f t="array" ref="AM3">TREND($AQ$3:$AU$3,$AQ$1:$AU$1,AM1)</f>
-        <v>7.5478780225886853E-5</v>
+        <v>7.4068934971728995E-5</v>
       </c>
       <c r="AN3" s="4" cm="1">
         <f t="array" ref="AN3">TREND($AQ$3:$AU$3,$AQ$1:$AU$1,AN1)</f>
-        <v>7.6806089960293998E-5</v>
+        <v>7.5371452289986138E-5</v>
       </c>
       <c r="AO3" s="4" cm="1">
         <f t="array" ref="AO3">TREND($AQ$3:$AU$3,$AQ$1:$AU$1,AO1)</f>
-        <v>7.8133399694700709E-5</v>
+        <v>7.6673969608242847E-5</v>
       </c>
       <c r="AP3" s="4" cm="1">
         <f t="array" ref="AP3">TREND($AR$3:$AV$3,$AR$1:$AV$1,AP1)</f>
-        <v>7.977578850124848E-5</v>
+        <v>7.8285680732168971E-5</v>
       </c>
       <c r="AQ3" s="4" cm="1">
         <f t="array" ref="AQ3">TREND($AR$3:$AV$3,$AR$1:$AV$1,AQ1)</f>
-        <v>8.0968064347595233E-5</v>
+        <v>7.9455686419425183E-5</v>
       </c>
       <c r="AR3" s="20">
         <f>BNVFE!G9</f>
-        <v>8.132511630401103E-5</v>
+        <v>7.9806069110588361E-5</v>
       </c>
       <c r="AS3" s="26">
         <f>BNVFE!H9</f>
-        <v>8.4161072514692597E-5</v>
+        <v>8.2589053354941577E-5</v>
       </c>
       <c r="AT3" s="26">
         <f>BNVFE!I9</f>
-        <v>8.498353764742068E-5</v>
+        <v>8.3396155910788876E-5</v>
       </c>
       <c r="AU3" s="26">
         <f>BNVFE!J9</f>
-        <v>8.5775402347925225E-5</v>
+        <v>8.4173229610609506E-5</v>
       </c>
       <c r="AV3" s="26">
         <f>BNVFE!K9</f>
-        <v>8.6479330619128737E-5</v>
+        <v>8.4864009419033756E-5</v>
       </c>
       <c r="AW3" s="26">
         <f>BNVFE!L9</f>
-        <v>8.7180851987329484E-5</v>
+        <v>8.5552427282266762E-5</v>
       </c>
       <c r="AX3" s="26">
         <f>BNVFE!M9</f>
-        <v>8.7676327828293231E-5</v>
+        <v>8.6038648280202556E-5</v>
       </c>
       <c r="AY3" s="26">
         <f>BNVFE!N9</f>
-        <v>8.808308415773043E-5</v>
+        <v>8.6437806931471918E-5</v>
       </c>
       <c r="AZ3" s="26">
         <f>BNVFE!O9</f>
-        <v>8.8443349127241298E-5</v>
+        <v>8.6791342620833007E-5</v>
       </c>
       <c r="BA3" s="26">
         <f>BNVFE!P9</f>
-        <v>8.877490666338608E-5</v>
+        <v>8.7116707094273078E-5</v>
       </c>
       <c r="BB3" s="26">
         <f>BNVFE!Q9</f>
-        <v>8.9036788024627383E-5</v>
+        <v>8.7373696852958087E-5</v>
       </c>
       <c r="BC3" s="26">
         <f>BNVFE!R9</f>
-        <v>8.9408940248032558E-5</v>
+        <v>8.7738897757801631E-5</v>
       </c>
       <c r="BD3" s="26">
         <f>BNVFE!S9</f>
-        <v>8.9726171714716883E-5</v>
+        <v>8.8050203754089717E-5</v>
       </c>
       <c r="BE3" s="26">
         <f>BNVFE!T9</f>
-        <v>8.9993423792437643E-5</v>
+        <v>8.8312463911269213E-5</v>
       </c>
       <c r="BF3" s="26">
         <f>BNVFE!U9</f>
-        <v>9.0174807564025167E-5</v>
+        <v>8.8490459670374438E-5</v>
       </c>
       <c r="BG3" s="26">
         <f>BNVFE!V9</f>
-        <v>9.038234516069701E-5</v>
+        <v>8.8694120735193857E-5</v>
       </c>
       <c r="BH3" s="26">
         <f>BNVFE!W9</f>
-        <v>9.0953441555838329E-5</v>
+        <v>8.9254549793900385E-5</v>
       </c>
       <c r="BI3" s="26">
         <f>BNVFE!X9</f>
-        <v>9.1765196895077241E-5</v>
+        <v>9.005114260124438E-5</v>
       </c>
       <c r="BJ3" s="26">
         <f>BNVFE!Y9</f>
-        <v>9.2611810298042204E-5</v>
+        <v>9.0881942369109463E-5</v>
       </c>
       <c r="BK3" s="26">
         <f>BNVFE!Z9</f>
-        <v>9.3647517531163859E-5</v>
+        <v>9.1898303940802261E-5</v>
       </c>
       <c r="BL3" s="26">
         <f>BNVFE!AA9</f>
-        <v>9.5050006294872494E-5</v>
+        <v>9.3274596042063404E-5</v>
       </c>
       <c r="BM3" s="26">
         <f>BNVFE!AB9</f>
-        <v>9.645662760019035E-5</v>
+        <v>9.4654943494441841E-5</v>
       </c>
       <c r="BN3" s="26">
         <f>BNVFE!AC9</f>
-        <v>9.7387214206997634E-5</v>
+        <v>9.5568147956131454E-5</v>
       </c>
       <c r="BO3" s="26">
         <f>BNVFE!AD9</f>
-        <v>9.8272881152577143E-5</v>
+        <v>9.643727179732782E-5</v>
       </c>
       <c r="BP3" s="26">
         <f>BNVFE!AE9</f>
-        <v>9.9315311676914197E-5</v>
+        <v>9.7460231077917589E-5</v>
       </c>
       <c r="BQ3" s="26">
         <f>BNVFE!AF9</f>
-        <v>1.0022913979744075E-4</v>
+        <v>9.8356990080011308E-5</v>
       </c>
       <c r="BR3" s="26">
         <f>BNVFE!AG9</f>
-        <v>1.0111291012785455E-4</v>
+        <v>9.9224252732341657E-5</v>
       </c>
       <c r="BS3" s="26"/>
       <c r="BT3" s="4"/>
@@ -23788,123 +23788,123 @@
       </c>
       <c r="B2" s="4">
         <f t="array" ref="B2:B8">TRANSPOSE(SYFAFE!B10:H10)</f>
-        <v>3.0636736837912965E-4</v>
+        <v>3.0156650473713915E-4</v>
       </c>
       <c r="C2" s="4">
         <f>B2</f>
-        <v>3.0636736837912965E-4</v>
+        <v>3.0156650473713915E-4</v>
       </c>
       <c r="D2" s="4">
         <f t="shared" ref="D2:AE8" si="0">C2</f>
-        <v>3.0636736837912965E-4</v>
+        <v>3.0156650473713915E-4</v>
       </c>
       <c r="E2" s="4">
         <f t="shared" si="0"/>
-        <v>3.0636736837912965E-4</v>
+        <v>3.0156650473713915E-4</v>
       </c>
       <c r="F2" s="4">
         <f t="shared" si="0"/>
-        <v>3.0636736837912965E-4</v>
+        <v>3.0156650473713915E-4</v>
       </c>
       <c r="G2" s="4">
         <f t="shared" si="0"/>
-        <v>3.0636736837912965E-4</v>
+        <v>3.0156650473713915E-4</v>
       </c>
       <c r="H2" s="4">
         <f t="shared" si="0"/>
-        <v>3.0636736837912965E-4</v>
+        <v>3.0156650473713915E-4</v>
       </c>
       <c r="I2" s="4">
         <f t="shared" si="0"/>
-        <v>3.0636736837912965E-4</v>
+        <v>3.0156650473713915E-4</v>
       </c>
       <c r="J2" s="4">
         <f t="shared" si="0"/>
-        <v>3.0636736837912965E-4</v>
+        <v>3.0156650473713915E-4</v>
       </c>
       <c r="K2" s="4">
         <f t="shared" si="0"/>
-        <v>3.0636736837912965E-4</v>
+        <v>3.0156650473713915E-4</v>
       </c>
       <c r="L2" s="4">
         <f t="shared" si="0"/>
-        <v>3.0636736837912965E-4</v>
+        <v>3.0156650473713915E-4</v>
       </c>
       <c r="M2" s="4">
         <f t="shared" si="0"/>
-        <v>3.0636736837912965E-4</v>
+        <v>3.0156650473713915E-4</v>
       </c>
       <c r="N2" s="4">
         <f t="shared" si="0"/>
-        <v>3.0636736837912965E-4</v>
+        <v>3.0156650473713915E-4</v>
       </c>
       <c r="O2" s="4">
         <f t="shared" si="0"/>
-        <v>3.0636736837912965E-4</v>
+        <v>3.0156650473713915E-4</v>
       </c>
       <c r="P2" s="4">
         <f t="shared" si="0"/>
-        <v>3.0636736837912965E-4</v>
+        <v>3.0156650473713915E-4</v>
       </c>
       <c r="Q2" s="4">
         <f t="shared" si="0"/>
-        <v>3.0636736837912965E-4</v>
+        <v>3.0156650473713915E-4</v>
       </c>
       <c r="R2" s="4">
         <f t="shared" si="0"/>
-        <v>3.0636736837912965E-4</v>
+        <v>3.0156650473713915E-4</v>
       </c>
       <c r="S2" s="4">
         <f t="shared" si="0"/>
-        <v>3.0636736837912965E-4</v>
+        <v>3.0156650473713915E-4</v>
       </c>
       <c r="T2" s="4">
         <f t="shared" si="0"/>
-        <v>3.0636736837912965E-4</v>
+        <v>3.0156650473713915E-4</v>
       </c>
       <c r="U2" s="4">
         <f t="shared" si="0"/>
-        <v>3.0636736837912965E-4</v>
+        <v>3.0156650473713915E-4</v>
       </c>
       <c r="V2" s="4">
         <f t="shared" si="0"/>
-        <v>3.0636736837912965E-4</v>
+        <v>3.0156650473713915E-4</v>
       </c>
       <c r="W2" s="4">
         <f t="shared" si="0"/>
-        <v>3.0636736837912965E-4</v>
+        <v>3.0156650473713915E-4</v>
       </c>
       <c r="X2" s="4">
         <f t="shared" si="0"/>
-        <v>3.0636736837912965E-4</v>
+        <v>3.0156650473713915E-4</v>
       </c>
       <c r="Y2" s="4">
         <f t="shared" si="0"/>
-        <v>3.0636736837912965E-4</v>
+        <v>3.0156650473713915E-4</v>
       </c>
       <c r="Z2" s="4">
         <f t="shared" si="0"/>
-        <v>3.0636736837912965E-4</v>
+        <v>3.0156650473713915E-4</v>
       </c>
       <c r="AA2" s="4">
         <f t="shared" si="0"/>
-        <v>3.0636736837912965E-4</v>
+        <v>3.0156650473713915E-4</v>
       </c>
       <c r="AB2" s="4">
         <f t="shared" si="0"/>
-        <v>3.0636736837912965E-4</v>
+        <v>3.0156650473713915E-4</v>
       </c>
       <c r="AC2" s="4">
         <f t="shared" si="0"/>
-        <v>3.0636736837912965E-4</v>
+        <v>3.0156650473713915E-4</v>
       </c>
       <c r="AD2" s="4">
         <f t="shared" si="0"/>
-        <v>3.0636736837912965E-4</v>
+        <v>3.0156650473713915E-4</v>
       </c>
       <c r="AE2" s="4">
         <f t="shared" si="0"/>
-        <v>3.0636736837912965E-4</v>
+        <v>3.0156650473713915E-4</v>
       </c>
       <c r="AG2" s="4"/>
       <c r="AH2" s="4"/>
@@ -23914,123 +23914,123 @@
         <v>3</v>
       </c>
       <c r="B3" s="4">
-        <v>7.273085411263018E-5</v>
+        <v>7.0213473556835903E-5</v>
       </c>
       <c r="C3" s="4">
         <f t="shared" ref="C3:C8" si="1">B3</f>
-        <v>7.273085411263018E-5</v>
+        <v>7.0213473556835903E-5</v>
       </c>
       <c r="D3" s="4">
         <f t="shared" ref="D3:Q3" si="2">C3</f>
-        <v>7.273085411263018E-5</v>
+        <v>7.0213473556835903E-5</v>
       </c>
       <c r="E3" s="4">
         <f t="shared" si="2"/>
-        <v>7.273085411263018E-5</v>
+        <v>7.0213473556835903E-5</v>
       </c>
       <c r="F3" s="4">
         <f t="shared" si="2"/>
-        <v>7.273085411263018E-5</v>
+        <v>7.0213473556835903E-5</v>
       </c>
       <c r="G3" s="4">
         <f t="shared" si="2"/>
-        <v>7.273085411263018E-5</v>
+        <v>7.0213473556835903E-5</v>
       </c>
       <c r="H3" s="4">
         <f t="shared" si="2"/>
-        <v>7.273085411263018E-5</v>
+        <v>7.0213473556835903E-5</v>
       </c>
       <c r="I3" s="4">
         <f t="shared" si="2"/>
-        <v>7.273085411263018E-5</v>
+        <v>7.0213473556835903E-5</v>
       </c>
       <c r="J3" s="4">
         <f t="shared" si="2"/>
-        <v>7.273085411263018E-5</v>
+        <v>7.0213473556835903E-5</v>
       </c>
       <c r="K3" s="4">
         <f t="shared" si="2"/>
-        <v>7.273085411263018E-5</v>
+        <v>7.0213473556835903E-5</v>
       </c>
       <c r="L3" s="4">
         <f t="shared" si="2"/>
-        <v>7.273085411263018E-5</v>
+        <v>7.0213473556835903E-5</v>
       </c>
       <c r="M3" s="4">
         <f t="shared" si="2"/>
-        <v>7.273085411263018E-5</v>
+        <v>7.0213473556835903E-5</v>
       </c>
       <c r="N3" s="4">
         <f t="shared" si="2"/>
-        <v>7.273085411263018E-5</v>
+        <v>7.0213473556835903E-5</v>
       </c>
       <c r="O3" s="4">
         <f t="shared" si="2"/>
-        <v>7.273085411263018E-5</v>
+        <v>7.0213473556835903E-5</v>
       </c>
       <c r="P3" s="4">
         <f t="shared" si="2"/>
-        <v>7.273085411263018E-5</v>
+        <v>7.0213473556835903E-5</v>
       </c>
       <c r="Q3" s="4">
         <f t="shared" si="2"/>
-        <v>7.273085411263018E-5</v>
+        <v>7.0213473556835903E-5</v>
       </c>
       <c r="R3" s="4">
         <f t="shared" si="0"/>
-        <v>7.273085411263018E-5</v>
+        <v>7.0213473556835903E-5</v>
       </c>
       <c r="S3" s="4">
         <f t="shared" si="0"/>
-        <v>7.273085411263018E-5</v>
+        <v>7.0213473556835903E-5</v>
       </c>
       <c r="T3" s="4">
         <f t="shared" si="0"/>
-        <v>7.273085411263018E-5</v>
+        <v>7.0213473556835903E-5</v>
       </c>
       <c r="U3" s="4">
         <f t="shared" si="0"/>
-        <v>7.273085411263018E-5</v>
+        <v>7.0213473556835903E-5</v>
       </c>
       <c r="V3" s="4">
         <f t="shared" si="0"/>
-        <v>7.273085411263018E-5</v>
+        <v>7.0213473556835903E-5</v>
       </c>
       <c r="W3" s="4">
         <f t="shared" si="0"/>
-        <v>7.273085411263018E-5</v>
+        <v>7.0213473556835903E-5</v>
       </c>
       <c r="X3" s="4">
         <f t="shared" si="0"/>
-        <v>7.273085411263018E-5</v>
+        <v>7.0213473556835903E-5</v>
       </c>
       <c r="Y3" s="4">
         <f t="shared" si="0"/>
-        <v>7.273085411263018E-5</v>
+        <v>7.0213473556835903E-5</v>
       </c>
       <c r="Z3" s="4">
         <f t="shared" si="0"/>
-        <v>7.273085411263018E-5</v>
+        <v>7.0213473556835903E-5</v>
       </c>
       <c r="AA3" s="4">
         <f t="shared" si="0"/>
-        <v>7.273085411263018E-5</v>
+        <v>7.0213473556835903E-5</v>
       </c>
       <c r="AB3" s="4">
         <f t="shared" si="0"/>
-        <v>7.273085411263018E-5</v>
+        <v>7.0213473556835903E-5</v>
       </c>
       <c r="AC3" s="4">
         <f t="shared" si="0"/>
-        <v>7.273085411263018E-5</v>
+        <v>7.0213473556835903E-5</v>
       </c>
       <c r="AD3" s="4">
         <f t="shared" si="0"/>
-        <v>7.273085411263018E-5</v>
+        <v>7.0213473556835903E-5</v>
       </c>
       <c r="AE3" s="4">
         <f t="shared" si="0"/>
-        <v>7.273085411263018E-5</v>
+        <v>7.0213473556835903E-5</v>
       </c>
       <c r="AG3" s="4"/>
       <c r="AH3" s="4"/>
@@ -24040,123 +24040,123 @@
         <v>4</v>
       </c>
       <c r="B4" s="4">
-        <v>9.5098581742816967E-5</v>
+        <v>9.3322264163941547E-5</v>
       </c>
       <c r="C4" s="4">
         <f t="shared" si="1"/>
-        <v>9.5098581742816967E-5</v>
+        <v>9.3322264163941547E-5</v>
       </c>
       <c r="D4" s="4">
         <f t="shared" si="0"/>
-        <v>9.5098581742816967E-5</v>
+        <v>9.3322264163941547E-5</v>
       </c>
       <c r="E4" s="4">
         <f t="shared" si="0"/>
-        <v>9.5098581742816967E-5</v>
+        <v>9.3322264163941547E-5</v>
       </c>
       <c r="F4" s="4">
         <f t="shared" si="0"/>
-        <v>9.5098581742816967E-5</v>
+        <v>9.3322264163941547E-5</v>
       </c>
       <c r="G4" s="4">
         <f t="shared" si="0"/>
-        <v>9.5098581742816967E-5</v>
+        <v>9.3322264163941547E-5</v>
       </c>
       <c r="H4" s="4">
         <f t="shared" si="0"/>
-        <v>9.5098581742816967E-5</v>
+        <v>9.3322264163941547E-5</v>
       </c>
       <c r="I4" s="4">
         <f t="shared" si="0"/>
-        <v>9.5098581742816967E-5</v>
+        <v>9.3322264163941547E-5</v>
       </c>
       <c r="J4" s="4">
         <f t="shared" si="0"/>
-        <v>9.5098581742816967E-5</v>
+        <v>9.3322264163941547E-5</v>
       </c>
       <c r="K4" s="4">
         <f t="shared" si="0"/>
-        <v>9.5098581742816967E-5</v>
+        <v>9.3322264163941547E-5</v>
       </c>
       <c r="L4" s="4">
         <f t="shared" si="0"/>
-        <v>9.5098581742816967E-5</v>
+        <v>9.3322264163941547E-5</v>
       </c>
       <c r="M4" s="4">
         <f t="shared" si="0"/>
-        <v>9.5098581742816967E-5</v>
+        <v>9.3322264163941547E-5</v>
       </c>
       <c r="N4" s="4">
         <f t="shared" si="0"/>
-        <v>9.5098581742816967E-5</v>
+        <v>9.3322264163941547E-5</v>
       </c>
       <c r="O4" s="4">
         <f t="shared" si="0"/>
-        <v>9.5098581742816967E-5</v>
+        <v>9.3322264163941547E-5</v>
       </c>
       <c r="P4" s="4">
         <f t="shared" si="0"/>
-        <v>9.5098581742816967E-5</v>
+        <v>9.3322264163941547E-5</v>
       </c>
       <c r="Q4" s="4">
         <f t="shared" si="0"/>
-        <v>9.5098581742816967E-5</v>
+        <v>9.3322264163941547E-5</v>
       </c>
       <c r="R4" s="4">
         <f t="shared" si="0"/>
-        <v>9.5098581742816967E-5</v>
+        <v>9.3322264163941547E-5</v>
       </c>
       <c r="S4" s="4">
         <f t="shared" si="0"/>
-        <v>9.5098581742816967E-5</v>
+        <v>9.3322264163941547E-5</v>
       </c>
       <c r="T4" s="4">
         <f t="shared" si="0"/>
-        <v>9.5098581742816967E-5</v>
+        <v>9.3322264163941547E-5</v>
       </c>
       <c r="U4" s="4">
         <f t="shared" si="0"/>
-        <v>9.5098581742816967E-5</v>
+        <v>9.3322264163941547E-5</v>
       </c>
       <c r="V4" s="4">
         <f t="shared" si="0"/>
-        <v>9.5098581742816967E-5</v>
+        <v>9.3322264163941547E-5</v>
       </c>
       <c r="W4" s="4">
         <f t="shared" si="0"/>
-        <v>9.5098581742816967E-5</v>
+        <v>9.3322264163941547E-5</v>
       </c>
       <c r="X4" s="4">
         <f t="shared" si="0"/>
-        <v>9.5098581742816967E-5</v>
+        <v>9.3322264163941547E-5</v>
       </c>
       <c r="Y4" s="4">
         <f t="shared" si="0"/>
-        <v>9.5098581742816967E-5</v>
+        <v>9.3322264163941547E-5</v>
       </c>
       <c r="Z4" s="4">
         <f t="shared" si="0"/>
-        <v>9.5098581742816967E-5</v>
+        <v>9.3322264163941547E-5</v>
       </c>
       <c r="AA4" s="4">
         <f t="shared" si="0"/>
-        <v>9.5098581742816967E-5</v>
+        <v>9.3322264163941547E-5</v>
       </c>
       <c r="AB4" s="4">
         <f t="shared" si="0"/>
-        <v>9.5098581742816967E-5</v>
+        <v>9.3322264163941547E-5</v>
       </c>
       <c r="AC4" s="4">
         <f t="shared" si="0"/>
-        <v>9.5098581742816967E-5</v>
+        <v>9.3322264163941547E-5</v>
       </c>
       <c r="AD4" s="4">
         <f t="shared" si="0"/>
-        <v>9.5098581742816967E-5</v>
+        <v>9.3322264163941547E-5</v>
       </c>
       <c r="AE4" s="4">
         <f t="shared" si="0"/>
-        <v>9.5098581742816967E-5</v>
+        <v>9.3322264163941547E-5</v>
       </c>
       <c r="AG4" s="4"/>
       <c r="AH4" s="4"/>
@@ -24166,123 +24166,123 @@
         <v>5</v>
       </c>
       <c r="B5" s="4">
-        <v>9.3478062847081558E-5</v>
+        <v>8.9590243650741159E-5</v>
       </c>
       <c r="C5" s="4">
         <f t="shared" si="1"/>
-        <v>9.3478062847081558E-5</v>
+        <v>8.9590243650741159E-5</v>
       </c>
       <c r="D5" s="4">
         <f t="shared" si="0"/>
-        <v>9.3478062847081558E-5</v>
+        <v>8.9590243650741159E-5</v>
       </c>
       <c r="E5" s="4">
         <f t="shared" si="0"/>
-        <v>9.3478062847081558E-5</v>
+        <v>8.9590243650741159E-5</v>
       </c>
       <c r="F5" s="4">
         <f t="shared" si="0"/>
-        <v>9.3478062847081558E-5</v>
+        <v>8.9590243650741159E-5</v>
       </c>
       <c r="G5" s="4">
         <f t="shared" si="0"/>
-        <v>9.3478062847081558E-5</v>
+        <v>8.9590243650741159E-5</v>
       </c>
       <c r="H5" s="4">
         <f t="shared" si="0"/>
-        <v>9.3478062847081558E-5</v>
+        <v>8.9590243650741159E-5</v>
       </c>
       <c r="I5" s="4">
         <f t="shared" si="0"/>
-        <v>9.3478062847081558E-5</v>
+        <v>8.9590243650741159E-5</v>
       </c>
       <c r="J5" s="4">
         <f t="shared" si="0"/>
-        <v>9.3478062847081558E-5</v>
+        <v>8.9590243650741159E-5</v>
       </c>
       <c r="K5" s="4">
         <f t="shared" si="0"/>
-        <v>9.3478062847081558E-5</v>
+        <v>8.9590243650741159E-5</v>
       </c>
       <c r="L5" s="4">
         <f t="shared" si="0"/>
-        <v>9.3478062847081558E-5</v>
+        <v>8.9590243650741159E-5</v>
       </c>
       <c r="M5" s="4">
         <f t="shared" si="0"/>
-        <v>9.3478062847081558E-5</v>
+        <v>8.9590243650741159E-5</v>
       </c>
       <c r="N5" s="4">
         <f t="shared" si="0"/>
-        <v>9.3478062847081558E-5</v>
+        <v>8.9590243650741159E-5</v>
       </c>
       <c r="O5" s="4">
         <f t="shared" si="0"/>
-        <v>9.3478062847081558E-5</v>
+        <v>8.9590243650741159E-5</v>
       </c>
       <c r="P5" s="4">
         <f t="shared" si="0"/>
-        <v>9.3478062847081558E-5</v>
+        <v>8.9590243650741159E-5</v>
       </c>
       <c r="Q5" s="4">
         <f t="shared" si="0"/>
-        <v>9.3478062847081558E-5</v>
+        <v>8.9590243650741159E-5</v>
       </c>
       <c r="R5" s="4">
         <f t="shared" si="0"/>
-        <v>9.3478062847081558E-5</v>
+        <v>8.9590243650741159E-5</v>
       </c>
       <c r="S5" s="4">
         <f t="shared" si="0"/>
-        <v>9.3478062847081558E-5</v>
+        <v>8.9590243650741159E-5</v>
       </c>
       <c r="T5" s="4">
         <f t="shared" si="0"/>
-        <v>9.3478062847081558E-5</v>
+        <v>8.9590243650741159E-5</v>
       </c>
       <c r="U5" s="4">
         <f t="shared" si="0"/>
-        <v>9.3478062847081558E-5</v>
+        <v>8.9590243650741159E-5</v>
       </c>
       <c r="V5" s="4">
         <f t="shared" si="0"/>
-        <v>9.3478062847081558E-5</v>
+        <v>8.9590243650741159E-5</v>
       </c>
       <c r="W5" s="4">
         <f t="shared" si="0"/>
-        <v>9.3478062847081558E-5</v>
+        <v>8.9590243650741159E-5</v>
       </c>
       <c r="X5" s="4">
         <f t="shared" si="0"/>
-        <v>9.3478062847081558E-5</v>
+        <v>8.9590243650741159E-5</v>
       </c>
       <c r="Y5" s="4">
         <f t="shared" si="0"/>
-        <v>9.3478062847081558E-5</v>
+        <v>8.9590243650741159E-5</v>
       </c>
       <c r="Z5" s="4">
         <f t="shared" si="0"/>
-        <v>9.3478062847081558E-5</v>
+        <v>8.9590243650741159E-5</v>
       </c>
       <c r="AA5" s="4">
         <f t="shared" si="0"/>
-        <v>9.3478062847081558E-5</v>
+        <v>8.9590243650741159E-5</v>
       </c>
       <c r="AB5" s="4">
         <f t="shared" si="0"/>
-        <v>9.3478062847081558E-5</v>
+        <v>8.9590243650741159E-5</v>
       </c>
       <c r="AC5" s="4">
         <f t="shared" si="0"/>
-        <v>9.3478062847081558E-5</v>
+        <v>8.9590243650741159E-5</v>
       </c>
       <c r="AD5" s="4">
         <f t="shared" si="0"/>
-        <v>9.3478062847081558E-5</v>
+        <v>8.9590243650741159E-5</v>
       </c>
       <c r="AE5" s="4">
         <f t="shared" si="0"/>
-        <v>9.3478062847081558E-5</v>
+        <v>8.9590243650741159E-5</v>
       </c>
       <c r="AG5" s="4"/>
       <c r="AH5" s="4"/>
@@ -24292,123 +24292,123 @@
         <v>6</v>
       </c>
       <c r="B6" s="4">
-        <v>3.8357149864294821E-5</v>
+        <v>1.5342859945717928E-4</v>
       </c>
       <c r="C6" s="4">
         <f t="shared" si="1"/>
-        <v>3.8357149864294821E-5</v>
+        <v>1.5342859945717928E-4</v>
       </c>
       <c r="D6" s="4">
         <f t="shared" si="0"/>
-        <v>3.8357149864294821E-5</v>
+        <v>1.5342859945717928E-4</v>
       </c>
       <c r="E6" s="4">
         <f t="shared" si="0"/>
-        <v>3.8357149864294821E-5</v>
+        <v>1.5342859945717928E-4</v>
       </c>
       <c r="F6" s="4">
         <f t="shared" si="0"/>
-        <v>3.8357149864294821E-5</v>
+        <v>1.5342859945717928E-4</v>
       </c>
       <c r="G6" s="4">
         <f t="shared" si="0"/>
-        <v>3.8357149864294821E-5</v>
+        <v>1.5342859945717928E-4</v>
       </c>
       <c r="H6" s="4">
         <f t="shared" si="0"/>
-        <v>3.8357149864294821E-5</v>
+        <v>1.5342859945717928E-4</v>
       </c>
       <c r="I6" s="4">
         <f t="shared" si="0"/>
-        <v>3.8357149864294821E-5</v>
+        <v>1.5342859945717928E-4</v>
       </c>
       <c r="J6" s="4">
         <f t="shared" si="0"/>
-        <v>3.8357149864294821E-5</v>
+        <v>1.5342859945717928E-4</v>
       </c>
       <c r="K6" s="4">
         <f t="shared" si="0"/>
-        <v>3.8357149864294821E-5</v>
+        <v>1.5342859945717928E-4</v>
       </c>
       <c r="L6" s="4">
         <f t="shared" si="0"/>
-        <v>3.8357149864294821E-5</v>
+        <v>1.5342859945717928E-4</v>
       </c>
       <c r="M6" s="4">
         <f t="shared" si="0"/>
-        <v>3.8357149864294821E-5</v>
+        <v>1.5342859945717928E-4</v>
       </c>
       <c r="N6" s="4">
         <f t="shared" si="0"/>
-        <v>3.8357149864294821E-5</v>
+        <v>1.5342859945717928E-4</v>
       </c>
       <c r="O6" s="4">
         <f t="shared" si="0"/>
-        <v>3.8357149864294821E-5</v>
+        <v>1.5342859945717928E-4</v>
       </c>
       <c r="P6" s="4">
         <f t="shared" si="0"/>
-        <v>3.8357149864294821E-5</v>
+        <v>1.5342859945717928E-4</v>
       </c>
       <c r="Q6" s="4">
         <f t="shared" si="0"/>
-        <v>3.8357149864294821E-5</v>
+        <v>1.5342859945717928E-4</v>
       </c>
       <c r="R6" s="4">
         <f t="shared" si="0"/>
-        <v>3.8357149864294821E-5</v>
+        <v>1.5342859945717928E-4</v>
       </c>
       <c r="S6" s="4">
         <f t="shared" si="0"/>
-        <v>3.8357149864294821E-5</v>
+        <v>1.5342859945717928E-4</v>
       </c>
       <c r="T6" s="4">
         <f t="shared" si="0"/>
-        <v>3.8357149864294821E-5</v>
+        <v>1.5342859945717928E-4</v>
       </c>
       <c r="U6" s="4">
         <f t="shared" si="0"/>
-        <v>3.8357149864294821E-5</v>
+        <v>1.5342859945717928E-4</v>
       </c>
       <c r="V6" s="4">
         <f t="shared" si="0"/>
-        <v>3.8357149864294821E-5</v>
+        <v>1.5342859945717928E-4</v>
       </c>
       <c r="W6" s="4">
         <f t="shared" si="0"/>
-        <v>3.8357149864294821E-5</v>
+        <v>1.5342859945717928E-4</v>
       </c>
       <c r="X6" s="4">
         <f t="shared" si="0"/>
-        <v>3.8357149864294821E-5</v>
+        <v>1.5342859945717928E-4</v>
       </c>
       <c r="Y6" s="4">
         <f t="shared" si="0"/>
-        <v>3.8357149864294821E-5</v>
+        <v>1.5342859945717928E-4</v>
       </c>
       <c r="Z6" s="4">
         <f t="shared" si="0"/>
-        <v>3.8357149864294821E-5</v>
+        <v>1.5342859945717928E-4</v>
       </c>
       <c r="AA6" s="4">
         <f t="shared" si="0"/>
-        <v>3.8357149864294821E-5</v>
+        <v>1.5342859945717928E-4</v>
       </c>
       <c r="AB6" s="4">
         <f t="shared" si="0"/>
-        <v>3.8357149864294821E-5</v>
+        <v>1.5342859945717928E-4</v>
       </c>
       <c r="AC6" s="4">
         <f t="shared" si="0"/>
-        <v>3.8357149864294821E-5</v>
+        <v>1.5342859945717928E-4</v>
       </c>
       <c r="AD6" s="4">
         <f t="shared" si="0"/>
-        <v>3.8357149864294821E-5</v>
+        <v>1.5342859945717928E-4</v>
       </c>
       <c r="AE6" s="4">
         <f t="shared" si="0"/>
-        <v>3.8357149864294821E-5</v>
+        <v>1.5342859945717928E-4</v>
       </c>
       <c r="AG6" s="4"/>
       <c r="AH6" s="4"/>
@@ -24418,123 +24418,123 @@
         <v>84</v>
       </c>
       <c r="B7" s="4">
-        <v>1.4090027704705712E-3</v>
+        <v>1.1549320628198341E-4</v>
       </c>
       <c r="C7" s="4">
         <f t="shared" si="1"/>
-        <v>1.4090027704705712E-3</v>
+        <v>1.1549320628198341E-4</v>
       </c>
       <c r="D7" s="4">
         <f t="shared" si="0"/>
-        <v>1.4090027704705712E-3</v>
+        <v>1.1549320628198341E-4</v>
       </c>
       <c r="E7" s="4">
         <f t="shared" si="0"/>
-        <v>1.4090027704705712E-3</v>
+        <v>1.1549320628198341E-4</v>
       </c>
       <c r="F7" s="4">
         <f t="shared" si="0"/>
-        <v>1.4090027704705712E-3</v>
+        <v>1.1549320628198341E-4</v>
       </c>
       <c r="G7" s="4">
         <f t="shared" si="0"/>
-        <v>1.4090027704705712E-3</v>
+        <v>1.1549320628198341E-4</v>
       </c>
       <c r="H7" s="4">
         <f t="shared" si="0"/>
-        <v>1.4090027704705712E-3</v>
+        <v>1.1549320628198341E-4</v>
       </c>
       <c r="I7" s="4">
         <f t="shared" si="0"/>
-        <v>1.4090027704705712E-3</v>
+        <v>1.1549320628198341E-4</v>
       </c>
       <c r="J7" s="4">
         <f t="shared" si="0"/>
-        <v>1.4090027704705712E-3</v>
+        <v>1.1549320628198341E-4</v>
       </c>
       <c r="K7" s="4">
         <f t="shared" si="0"/>
-        <v>1.4090027704705712E-3</v>
+        <v>1.1549320628198341E-4</v>
       </c>
       <c r="L7" s="4">
         <f t="shared" si="0"/>
-        <v>1.4090027704705712E-3</v>
+        <v>1.1549320628198341E-4</v>
       </c>
       <c r="M7" s="4">
         <f t="shared" si="0"/>
-        <v>1.4090027704705712E-3</v>
+        <v>1.1549320628198341E-4</v>
       </c>
       <c r="N7" s="4">
         <f t="shared" si="0"/>
-        <v>1.4090027704705712E-3</v>
+        <v>1.1549320628198341E-4</v>
       </c>
       <c r="O7" s="4">
         <f t="shared" si="0"/>
-        <v>1.4090027704705712E-3</v>
+        <v>1.1549320628198341E-4</v>
       </c>
       <c r="P7" s="4">
         <f t="shared" si="0"/>
-        <v>1.4090027704705712E-3</v>
+        <v>1.1549320628198341E-4</v>
       </c>
       <c r="Q7" s="4">
         <f t="shared" si="0"/>
-        <v>1.4090027704705712E-3</v>
+        <v>1.1549320628198341E-4</v>
       </c>
       <c r="R7" s="4">
         <f t="shared" si="0"/>
-        <v>1.4090027704705712E-3</v>
+        <v>1.1549320628198341E-4</v>
       </c>
       <c r="S7" s="4">
         <f t="shared" si="0"/>
-        <v>1.4090027704705712E-3</v>
+        <v>1.1549320628198341E-4</v>
       </c>
       <c r="T7" s="4">
         <f t="shared" si="0"/>
-        <v>1.4090027704705712E-3</v>
+        <v>1.1549320628198341E-4</v>
       </c>
       <c r="U7" s="4">
         <f t="shared" si="0"/>
-        <v>1.4090027704705712E-3</v>
+        <v>1.1549320628198341E-4</v>
       </c>
       <c r="V7" s="4">
         <f t="shared" si="0"/>
-        <v>1.4090027704705712E-3</v>
+        <v>1.1549320628198341E-4</v>
       </c>
       <c r="W7" s="4">
         <f t="shared" si="0"/>
-        <v>1.4090027704705712E-3</v>
+        <v>1.1549320628198341E-4</v>
       </c>
       <c r="X7" s="4">
         <f t="shared" si="0"/>
-        <v>1.4090027704705712E-3</v>
+        <v>1.1549320628198341E-4</v>
       </c>
       <c r="Y7" s="4">
         <f t="shared" si="0"/>
-        <v>1.4090027704705712E-3</v>
+        <v>1.1549320628198341E-4</v>
       </c>
       <c r="Z7" s="4">
         <f t="shared" si="0"/>
-        <v>1.4090027704705712E-3</v>
+        <v>1.1549320628198341E-4</v>
       </c>
       <c r="AA7" s="4">
         <f t="shared" si="0"/>
-        <v>1.4090027704705712E-3</v>
+        <v>1.1549320628198341E-4</v>
       </c>
       <c r="AB7" s="4">
         <f t="shared" si="0"/>
-        <v>1.4090027704705712E-3</v>
+        <v>1.1549320628198341E-4</v>
       </c>
       <c r="AC7" s="4">
         <f t="shared" si="0"/>
-        <v>1.4090027704705712E-3</v>
+        <v>1.1549320628198341E-4</v>
       </c>
       <c r="AD7" s="4">
         <f t="shared" si="0"/>
-        <v>1.4090027704705712E-3</v>
+        <v>1.1549320628198341E-4</v>
       </c>
       <c r="AE7" s="4">
         <f t="shared" si="0"/>
-        <v>1.4090027704705712E-3</v>
+        <v>1.1549320628198341E-4</v>
       </c>
       <c r="AG7" s="4"/>
       <c r="AH7" s="4"/>

--- a/InputData/trans/BHNVFEAL/BAU Historical New Veh Fuel Economy After Lifetime.xlsx
+++ b/InputData/trans/BHNVFEAL/BAU Historical New Veh Fuel Economy After Lifetime.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OliviaAshmoore\Documents\Github Repos\eps-us\InputData\trans\BHNVFEAL\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\trans\BHNVFEAL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46122336-199E-4D3F-9ABC-740C7AD03B73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B49189A5-499E-4812-B686-83989CBCADAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="615" yWindow="45" windowWidth="20370" windowHeight="17025" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1520" yWindow="1520" windowWidth="19200" windowHeight="10050" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -53,6 +53,7 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -82,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="106">
   <si>
     <t>Sources:</t>
   </si>
@@ -379,6 +380,27 @@
   </si>
   <si>
     <t>energy consumption that more closely matches EIA's AEO trajectory: freight LDVs, passenger HDVs, freight HDVs, passenger ships, passenger motorbikes.</t>
+  </si>
+  <si>
+    <t>Motorbike fuel-economy refresh (2026-09-03, pending staff review):</t>
+  </si>
+  <si>
+    <t>The internal 'SYFAFE' tab's passenger motorbike row was refreshed from the SYFAFE workbook, where</t>
+  </si>
+  <si>
+    <t>motorbike fuel economy was re-derived after replacing the old x5 activity calibration multiplier with</t>
+  </si>
+  <si>
+    <t>FHWA VM-1 2024 data (gasoline 0.00182 -&gt; 0.00050 passenger-miles/BTU; see the SYFAFE and BAADTbVT</t>
+  </si>
+  <si>
+    <t>About tabs and memo-aeo-vmt-seam-2026-08-31.md at the repo root). The BHNVFEAL motorbike outputs are</t>
+  </si>
+  <si>
+    <t>the SYFAFE motorbike row held flat across historical years, so they update with it. Note the motorbike</t>
+  </si>
+  <si>
+    <t>outputs read the SYFAFE tab, not the BNVFE tab.</t>
   </si>
 </sst>
 </file>
@@ -7784,11 +7806,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B48"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:B56"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="13.42578125" customWidth="1"/>
-    <col min="2" max="2" width="107.42578125" customWidth="1"/>
+    <col min="1" max="1" width="13.453125" customWidth="1"/>
+    <col min="2" max="2" width="107.453125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -7994,6 +8016,41 @@
     <row r="48" spans="1:1">
       <c r="A48" t="s">
         <v>98</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56" t="s">
+        <v>105</v>
       </c>
     </row>
   </sheetData>
@@ -8011,12 +8068,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AH8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="31.140625" customWidth="1"/>
+    <col min="1" max="1" width="31.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" ht="30">
+    <row r="1" spans="1:34">
       <c r="A1" s="14" t="s">
         <v>87</v>
       </c>
@@ -9005,13 +9062,13 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AH8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="31.140625" customWidth="1"/>
-    <col min="2" max="2" width="21.28515625" customWidth="1"/>
+    <col min="1" max="1" width="31.1796875" customWidth="1"/>
+    <col min="2" max="2" width="21.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" ht="30">
+    <row r="1" spans="1:34">
       <c r="A1" s="14" t="s">
         <v>87</v>
       </c>
@@ -9878,12 +9935,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AH8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="31.140625" customWidth="1"/>
+    <col min="1" max="1" width="31.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" ht="30">
+    <row r="1" spans="1:34">
       <c r="A1" s="14" t="s">
         <v>87</v>
       </c>
@@ -10750,14 +10807,14 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AF13"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="31.140625" customWidth="1"/>
-    <col min="2" max="2" width="10.42578125" customWidth="1"/>
-    <col min="3" max="3" width="10.7109375" customWidth="1"/>
+    <col min="1" max="1" width="31.1796875" customWidth="1"/>
+    <col min="2" max="2" width="10.453125" customWidth="1"/>
+    <col min="3" max="3" width="10.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" ht="30">
+    <row r="1" spans="1:32">
       <c r="A1" s="14" t="s">
         <v>87</v>
       </c>
@@ -11651,12 +11708,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AH8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="31.140625" customWidth="1"/>
+    <col min="1" max="1" width="31.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" ht="30">
+    <row r="1" spans="1:34">
       <c r="A1" s="14" t="s">
         <v>87</v>
       </c>
@@ -12523,12 +12580,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AH8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="31.140625" customWidth="1"/>
+    <col min="1" max="1" width="31.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" ht="30">
+    <row r="1" spans="1:34">
       <c r="A1" s="14" t="s">
         <v>87</v>
       </c>
@@ -13509,12 +13566,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AH8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="31.140625" customWidth="1"/>
+    <col min="1" max="1" width="31.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" ht="30">
+    <row r="1" spans="1:34">
       <c r="A1" s="14" t="s">
         <v>87</v>
       </c>
@@ -14381,12 +14438,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AH8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="31.140625" customWidth="1"/>
+    <col min="1" max="1" width="31.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" ht="30">
+    <row r="1" spans="1:34">
       <c r="A1" s="14" t="s">
         <v>87</v>
       </c>
@@ -14487,123 +14544,123 @@
       </c>
       <c r="B2" s="4">
         <f t="array" ref="B2:B8">TRANSPOSE(SYFAFE!B7:H7)</f>
-        <v>5.8028780082485321E-3</v>
+        <v>1.583802E-3</v>
       </c>
       <c r="C2" s="4">
         <f>B2</f>
-        <v>5.8028780082485321E-3</v>
+        <v>1.583802E-3</v>
       </c>
       <c r="D2" s="4">
         <f t="shared" ref="D2:AE8" si="0">C2</f>
-        <v>5.8028780082485321E-3</v>
+        <v>1.583802E-3</v>
       </c>
       <c r="E2" s="4">
         <f t="shared" si="0"/>
-        <v>5.8028780082485321E-3</v>
+        <v>1.583802E-3</v>
       </c>
       <c r="F2" s="4">
         <f t="shared" si="0"/>
-        <v>5.8028780082485321E-3</v>
+        <v>1.583802E-3</v>
       </c>
       <c r="G2" s="4">
         <f t="shared" si="0"/>
-        <v>5.8028780082485321E-3</v>
+        <v>1.583802E-3</v>
       </c>
       <c r="H2" s="4">
         <f t="shared" si="0"/>
-        <v>5.8028780082485321E-3</v>
+        <v>1.583802E-3</v>
       </c>
       <c r="I2" s="4">
         <f t="shared" si="0"/>
-        <v>5.8028780082485321E-3</v>
+        <v>1.583802E-3</v>
       </c>
       <c r="J2" s="4">
         <f t="shared" si="0"/>
-        <v>5.8028780082485321E-3</v>
+        <v>1.583802E-3</v>
       </c>
       <c r="K2" s="4">
         <f t="shared" si="0"/>
-        <v>5.8028780082485321E-3</v>
+        <v>1.583802E-3</v>
       </c>
       <c r="L2" s="4">
         <f t="shared" si="0"/>
-        <v>5.8028780082485321E-3</v>
+        <v>1.583802E-3</v>
       </c>
       <c r="M2" s="4">
         <f t="shared" si="0"/>
-        <v>5.8028780082485321E-3</v>
+        <v>1.583802E-3</v>
       </c>
       <c r="N2" s="4">
         <f t="shared" si="0"/>
-        <v>5.8028780082485321E-3</v>
+        <v>1.583802E-3</v>
       </c>
       <c r="O2" s="4">
         <f t="shared" si="0"/>
-        <v>5.8028780082485321E-3</v>
+        <v>1.583802E-3</v>
       </c>
       <c r="P2" s="4">
         <f t="shared" si="0"/>
-        <v>5.8028780082485321E-3</v>
+        <v>1.583802E-3</v>
       </c>
       <c r="Q2" s="4">
         <f t="shared" si="0"/>
-        <v>5.8028780082485321E-3</v>
+        <v>1.583802E-3</v>
       </c>
       <c r="R2" s="4">
         <f t="shared" si="0"/>
-        <v>5.8028780082485321E-3</v>
+        <v>1.583802E-3</v>
       </c>
       <c r="S2" s="4">
         <f t="shared" si="0"/>
-        <v>5.8028780082485321E-3</v>
+        <v>1.583802E-3</v>
       </c>
       <c r="T2" s="4">
         <f t="shared" si="0"/>
-        <v>5.8028780082485321E-3</v>
+        <v>1.583802E-3</v>
       </c>
       <c r="U2" s="4">
         <f t="shared" si="0"/>
-        <v>5.8028780082485321E-3</v>
+        <v>1.583802E-3</v>
       </c>
       <c r="V2" s="4">
         <f t="shared" si="0"/>
-        <v>5.8028780082485321E-3</v>
+        <v>1.583802E-3</v>
       </c>
       <c r="W2" s="4">
         <f t="shared" si="0"/>
-        <v>5.8028780082485321E-3</v>
+        <v>1.583802E-3</v>
       </c>
       <c r="X2" s="4">
         <f t="shared" si="0"/>
-        <v>5.8028780082485321E-3</v>
+        <v>1.583802E-3</v>
       </c>
       <c r="Y2" s="4">
         <f t="shared" si="0"/>
-        <v>5.8028780082485321E-3</v>
+        <v>1.583802E-3</v>
       </c>
       <c r="Z2" s="4">
         <f t="shared" si="0"/>
-        <v>5.8028780082485321E-3</v>
+        <v>1.583802E-3</v>
       </c>
       <c r="AA2" s="4">
         <f t="shared" si="0"/>
-        <v>5.8028780082485321E-3</v>
+        <v>1.583802E-3</v>
       </c>
       <c r="AB2" s="4">
         <f t="shared" si="0"/>
-        <v>5.8028780082485321E-3</v>
+        <v>1.583802E-3</v>
       </c>
       <c r="AC2" s="4">
         <f t="shared" si="0"/>
-        <v>5.8028780082485321E-3</v>
+        <v>1.583802E-3</v>
       </c>
       <c r="AD2" s="4">
         <f t="shared" si="0"/>
-        <v>5.8028780082485321E-3</v>
+        <v>1.583802E-3</v>
       </c>
       <c r="AE2" s="4">
         <f t="shared" si="0"/>
-        <v>5.8028780082485321E-3</v>
+        <v>1.583802E-3</v>
       </c>
       <c r="AG2" s="4"/>
       <c r="AH2" s="4"/>
@@ -14613,123 +14670,123 @@
         <v>3</v>
       </c>
       <c r="B3" s="4">
-        <v>1.8223914406069774E-3</v>
+        <v>4.9739300000000005E-4</v>
       </c>
       <c r="C3" s="4">
         <f t="shared" ref="C3:C8" si="1">B3</f>
-        <v>1.8223914406069774E-3</v>
+        <v>4.9739300000000005E-4</v>
       </c>
       <c r="D3" s="4">
         <f t="shared" ref="D3:Q3" si="2">C3</f>
-        <v>1.8223914406069774E-3</v>
+        <v>4.9739300000000005E-4</v>
       </c>
       <c r="E3" s="4">
         <f t="shared" si="2"/>
-        <v>1.8223914406069774E-3</v>
+        <v>4.9739300000000005E-4</v>
       </c>
       <c r="F3" s="4">
         <f t="shared" si="2"/>
-        <v>1.8223914406069774E-3</v>
+        <v>4.9739300000000005E-4</v>
       </c>
       <c r="G3" s="4">
         <f t="shared" si="2"/>
-        <v>1.8223914406069774E-3</v>
+        <v>4.9739300000000005E-4</v>
       </c>
       <c r="H3" s="4">
         <f t="shared" si="2"/>
-        <v>1.8223914406069774E-3</v>
+        <v>4.9739300000000005E-4</v>
       </c>
       <c r="I3" s="4">
         <f t="shared" si="2"/>
-        <v>1.8223914406069774E-3</v>
+        <v>4.9739300000000005E-4</v>
       </c>
       <c r="J3" s="4">
         <f t="shared" si="2"/>
-        <v>1.8223914406069774E-3</v>
+        <v>4.9739300000000005E-4</v>
       </c>
       <c r="K3" s="4">
         <f t="shared" si="2"/>
-        <v>1.8223914406069774E-3</v>
+        <v>4.9739300000000005E-4</v>
       </c>
       <c r="L3" s="4">
         <f t="shared" si="2"/>
-        <v>1.8223914406069774E-3</v>
+        <v>4.9739300000000005E-4</v>
       </c>
       <c r="M3" s="4">
         <f t="shared" si="2"/>
-        <v>1.8223914406069774E-3</v>
+        <v>4.9739300000000005E-4</v>
       </c>
       <c r="N3" s="4">
         <f t="shared" si="2"/>
-        <v>1.8223914406069774E-3</v>
+        <v>4.9739300000000005E-4</v>
       </c>
       <c r="O3" s="4">
         <f t="shared" si="2"/>
-        <v>1.8223914406069774E-3</v>
+        <v>4.9739300000000005E-4</v>
       </c>
       <c r="P3" s="4">
         <f t="shared" si="2"/>
-        <v>1.8223914406069774E-3</v>
+        <v>4.9739300000000005E-4</v>
       </c>
       <c r="Q3" s="4">
         <f t="shared" si="2"/>
-        <v>1.8223914406069774E-3</v>
+        <v>4.9739300000000005E-4</v>
       </c>
       <c r="R3" s="4">
         <f t="shared" si="0"/>
-        <v>1.8223914406069774E-3</v>
+        <v>4.9739300000000005E-4</v>
       </c>
       <c r="S3" s="4">
         <f t="shared" si="0"/>
-        <v>1.8223914406069774E-3</v>
+        <v>4.9739300000000005E-4</v>
       </c>
       <c r="T3" s="4">
         <f t="shared" si="0"/>
-        <v>1.8223914406069774E-3</v>
+        <v>4.9739300000000005E-4</v>
       </c>
       <c r="U3" s="4">
         <f t="shared" si="0"/>
-        <v>1.8223914406069774E-3</v>
+        <v>4.9739300000000005E-4</v>
       </c>
       <c r="V3" s="4">
         <f t="shared" si="0"/>
-        <v>1.8223914406069774E-3</v>
+        <v>4.9739300000000005E-4</v>
       </c>
       <c r="W3" s="4">
         <f t="shared" si="0"/>
-        <v>1.8223914406069774E-3</v>
+        <v>4.9739300000000005E-4</v>
       </c>
       <c r="X3" s="4">
         <f t="shared" si="0"/>
-        <v>1.8223914406069774E-3</v>
+        <v>4.9739300000000005E-4</v>
       </c>
       <c r="Y3" s="4">
         <f t="shared" si="0"/>
-        <v>1.8223914406069774E-3</v>
+        <v>4.9739300000000005E-4</v>
       </c>
       <c r="Z3" s="4">
         <f t="shared" si="0"/>
-        <v>1.8223914406069774E-3</v>
+        <v>4.9739300000000005E-4</v>
       </c>
       <c r="AA3" s="4">
         <f t="shared" si="0"/>
-        <v>1.8223914406069774E-3</v>
+        <v>4.9739300000000005E-4</v>
       </c>
       <c r="AB3" s="4">
         <f t="shared" si="0"/>
-        <v>1.8223914406069774E-3</v>
+        <v>4.9739300000000005E-4</v>
       </c>
       <c r="AC3" s="4">
         <f t="shared" si="0"/>
-        <v>1.8223914406069774E-3</v>
+        <v>4.9739300000000005E-4</v>
       </c>
       <c r="AD3" s="4">
         <f t="shared" si="0"/>
-        <v>1.8223914406069774E-3</v>
+        <v>4.9739300000000005E-4</v>
       </c>
       <c r="AE3" s="4">
         <f t="shared" si="0"/>
-        <v>1.8223914406069774E-3</v>
+        <v>4.9739300000000005E-4</v>
       </c>
       <c r="AG3" s="4"/>
       <c r="AH3" s="4"/>
@@ -14739,123 +14796,123 @@
         <v>4</v>
       </c>
       <c r="B4" s="4">
-        <v>1.8223914406069774E-3</v>
+        <v>4.9739300000000005E-4</v>
       </c>
       <c r="C4" s="4">
         <f t="shared" si="1"/>
-        <v>1.8223914406069774E-3</v>
+        <v>4.9739300000000005E-4</v>
       </c>
       <c r="D4" s="4">
         <f t="shared" si="0"/>
-        <v>1.8223914406069774E-3</v>
+        <v>4.9739300000000005E-4</v>
       </c>
       <c r="E4" s="4">
         <f t="shared" si="0"/>
-        <v>1.8223914406069774E-3</v>
+        <v>4.9739300000000005E-4</v>
       </c>
       <c r="F4" s="4">
         <f t="shared" si="0"/>
-        <v>1.8223914406069774E-3</v>
+        <v>4.9739300000000005E-4</v>
       </c>
       <c r="G4" s="4">
         <f t="shared" si="0"/>
-        <v>1.8223914406069774E-3</v>
+        <v>4.9739300000000005E-4</v>
       </c>
       <c r="H4" s="4">
         <f t="shared" si="0"/>
-        <v>1.8223914406069774E-3</v>
+        <v>4.9739300000000005E-4</v>
       </c>
       <c r="I4" s="4">
         <f t="shared" si="0"/>
-        <v>1.8223914406069774E-3</v>
+        <v>4.9739300000000005E-4</v>
       </c>
       <c r="J4" s="4">
         <f t="shared" si="0"/>
-        <v>1.8223914406069774E-3</v>
+        <v>4.9739300000000005E-4</v>
       </c>
       <c r="K4" s="4">
         <f t="shared" si="0"/>
-        <v>1.8223914406069774E-3</v>
+        <v>4.9739300000000005E-4</v>
       </c>
       <c r="L4" s="4">
         <f t="shared" si="0"/>
-        <v>1.8223914406069774E-3</v>
+        <v>4.9739300000000005E-4</v>
       </c>
       <c r="M4" s="4">
         <f t="shared" si="0"/>
-        <v>1.8223914406069774E-3</v>
+        <v>4.9739300000000005E-4</v>
       </c>
       <c r="N4" s="4">
         <f t="shared" si="0"/>
-        <v>1.8223914406069774E-3</v>
+        <v>4.9739300000000005E-4</v>
       </c>
       <c r="O4" s="4">
         <f t="shared" si="0"/>
-        <v>1.8223914406069774E-3</v>
+        <v>4.9739300000000005E-4</v>
       </c>
       <c r="P4" s="4">
         <f t="shared" si="0"/>
-        <v>1.8223914406069774E-3</v>
+        <v>4.9739300000000005E-4</v>
       </c>
       <c r="Q4" s="4">
         <f t="shared" si="0"/>
-        <v>1.8223914406069774E-3</v>
+        <v>4.9739300000000005E-4</v>
       </c>
       <c r="R4" s="4">
         <f t="shared" si="0"/>
-        <v>1.8223914406069774E-3</v>
+        <v>4.9739300000000005E-4</v>
       </c>
       <c r="S4" s="4">
         <f t="shared" si="0"/>
-        <v>1.8223914406069774E-3</v>
+        <v>4.9739300000000005E-4</v>
       </c>
       <c r="T4" s="4">
         <f t="shared" si="0"/>
-        <v>1.8223914406069774E-3</v>
+        <v>4.9739300000000005E-4</v>
       </c>
       <c r="U4" s="4">
         <f t="shared" si="0"/>
-        <v>1.8223914406069774E-3</v>
+        <v>4.9739300000000005E-4</v>
       </c>
       <c r="V4" s="4">
         <f t="shared" si="0"/>
-        <v>1.8223914406069774E-3</v>
+        <v>4.9739300000000005E-4</v>
       </c>
       <c r="W4" s="4">
         <f t="shared" si="0"/>
-        <v>1.8223914406069774E-3</v>
+        <v>4.9739300000000005E-4</v>
       </c>
       <c r="X4" s="4">
         <f t="shared" si="0"/>
-        <v>1.8223914406069774E-3</v>
+        <v>4.9739300000000005E-4</v>
       </c>
       <c r="Y4" s="4">
         <f t="shared" si="0"/>
-        <v>1.8223914406069774E-3</v>
+        <v>4.9739300000000005E-4</v>
       </c>
       <c r="Z4" s="4">
         <f t="shared" si="0"/>
-        <v>1.8223914406069774E-3</v>
+        <v>4.9739300000000005E-4</v>
       </c>
       <c r="AA4" s="4">
         <f t="shared" si="0"/>
-        <v>1.8223914406069774E-3</v>
+        <v>4.9739300000000005E-4</v>
       </c>
       <c r="AB4" s="4">
         <f t="shared" si="0"/>
-        <v>1.8223914406069774E-3</v>
+        <v>4.9739300000000005E-4</v>
       </c>
       <c r="AC4" s="4">
         <f t="shared" si="0"/>
-        <v>1.8223914406069774E-3</v>
+        <v>4.9739300000000005E-4</v>
       </c>
       <c r="AD4" s="4">
         <f t="shared" si="0"/>
-        <v>1.8223914406069774E-3</v>
+        <v>4.9739300000000005E-4</v>
       </c>
       <c r="AE4" s="4">
         <f t="shared" si="0"/>
-        <v>1.8223914406069774E-3</v>
+        <v>4.9739300000000005E-4</v>
       </c>
       <c r="AG4" s="4"/>
       <c r="AH4" s="4"/>
@@ -14865,123 +14922,123 @@
         <v>5</v>
       </c>
       <c r="B5" s="4">
-        <v>1.8223914406069774E-3</v>
+        <v>4.9739300000000005E-4</v>
       </c>
       <c r="C5" s="4">
         <f t="shared" si="1"/>
-        <v>1.8223914406069774E-3</v>
+        <v>4.9739300000000005E-4</v>
       </c>
       <c r="D5" s="4">
         <f t="shared" si="0"/>
-        <v>1.8223914406069774E-3</v>
+        <v>4.9739300000000005E-4</v>
       </c>
       <c r="E5" s="4">
         <f t="shared" si="0"/>
-        <v>1.8223914406069774E-3</v>
+        <v>4.9739300000000005E-4</v>
       </c>
       <c r="F5" s="4">
         <f t="shared" si="0"/>
-        <v>1.8223914406069774E-3</v>
+        <v>4.9739300000000005E-4</v>
       </c>
       <c r="G5" s="4">
         <f t="shared" si="0"/>
-        <v>1.8223914406069774E-3</v>
+        <v>4.9739300000000005E-4</v>
       </c>
       <c r="H5" s="4">
         <f t="shared" si="0"/>
-        <v>1.8223914406069774E-3</v>
+        <v>4.9739300000000005E-4</v>
       </c>
       <c r="I5" s="4">
         <f t="shared" si="0"/>
-        <v>1.8223914406069774E-3</v>
+        <v>4.9739300000000005E-4</v>
       </c>
       <c r="J5" s="4">
         <f t="shared" si="0"/>
-        <v>1.8223914406069774E-3</v>
+        <v>4.9739300000000005E-4</v>
       </c>
       <c r="K5" s="4">
         <f t="shared" si="0"/>
-        <v>1.8223914406069774E-3</v>
+        <v>4.9739300000000005E-4</v>
       </c>
       <c r="L5" s="4">
         <f t="shared" si="0"/>
-        <v>1.8223914406069774E-3</v>
+        <v>4.9739300000000005E-4</v>
       </c>
       <c r="M5" s="4">
         <f t="shared" si="0"/>
-        <v>1.8223914406069774E-3</v>
+        <v>4.9739300000000005E-4</v>
       </c>
       <c r="N5" s="4">
         <f t="shared" si="0"/>
-        <v>1.8223914406069774E-3</v>
+        <v>4.9739300000000005E-4</v>
       </c>
       <c r="O5" s="4">
         <f t="shared" si="0"/>
-        <v>1.8223914406069774E-3</v>
+        <v>4.9739300000000005E-4</v>
       </c>
       <c r="P5" s="4">
         <f t="shared" si="0"/>
-        <v>1.8223914406069774E-3</v>
+        <v>4.9739300000000005E-4</v>
       </c>
       <c r="Q5" s="4">
         <f t="shared" si="0"/>
-        <v>1.8223914406069774E-3</v>
+        <v>4.9739300000000005E-4</v>
       </c>
       <c r="R5" s="4">
         <f t="shared" si="0"/>
-        <v>1.8223914406069774E-3</v>
+        <v>4.9739300000000005E-4</v>
       </c>
       <c r="S5" s="4">
         <f t="shared" si="0"/>
-        <v>1.8223914406069774E-3</v>
+        <v>4.9739300000000005E-4</v>
       </c>
       <c r="T5" s="4">
         <f t="shared" si="0"/>
-        <v>1.8223914406069774E-3</v>
+        <v>4.9739300000000005E-4</v>
       </c>
       <c r="U5" s="4">
         <f t="shared" si="0"/>
-        <v>1.8223914406069774E-3</v>
+        <v>4.9739300000000005E-4</v>
       </c>
       <c r="V5" s="4">
         <f t="shared" si="0"/>
-        <v>1.8223914406069774E-3</v>
+        <v>4.9739300000000005E-4</v>
       </c>
       <c r="W5" s="4">
         <f t="shared" si="0"/>
-        <v>1.8223914406069774E-3</v>
+        <v>4.9739300000000005E-4</v>
       </c>
       <c r="X5" s="4">
         <f t="shared" si="0"/>
-        <v>1.8223914406069774E-3</v>
+        <v>4.9739300000000005E-4</v>
       </c>
       <c r="Y5" s="4">
         <f t="shared" si="0"/>
-        <v>1.8223914406069774E-3</v>
+        <v>4.9739300000000005E-4</v>
       </c>
       <c r="Z5" s="4">
         <f t="shared" si="0"/>
-        <v>1.8223914406069774E-3</v>
+        <v>4.9739300000000005E-4</v>
       </c>
       <c r="AA5" s="4">
         <f t="shared" si="0"/>
-        <v>1.8223914406069774E-3</v>
+        <v>4.9739300000000005E-4</v>
       </c>
       <c r="AB5" s="4">
         <f t="shared" si="0"/>
-        <v>1.8223914406069774E-3</v>
+        <v>4.9739300000000005E-4</v>
       </c>
       <c r="AC5" s="4">
         <f t="shared" si="0"/>
-        <v>1.8223914406069774E-3</v>
+        <v>4.9739300000000005E-4</v>
       </c>
       <c r="AD5" s="4">
         <f t="shared" si="0"/>
-        <v>1.8223914406069774E-3</v>
+        <v>4.9739300000000005E-4</v>
       </c>
       <c r="AE5" s="4">
         <f t="shared" si="0"/>
-        <v>1.8223914406069774E-3</v>
+        <v>4.9739300000000005E-4</v>
       </c>
       <c r="AG5" s="4"/>
       <c r="AH5" s="4"/>
@@ -14991,123 +15048,123 @@
         <v>6</v>
       </c>
       <c r="B6" s="4">
-        <v>4.0116590528098328E-3</v>
+        <v>1.0949180000000001E-3</v>
       </c>
       <c r="C6" s="4">
         <f t="shared" si="1"/>
-        <v>4.0116590528098328E-3</v>
+        <v>1.0949180000000001E-3</v>
       </c>
       <c r="D6" s="4">
         <f t="shared" si="0"/>
-        <v>4.0116590528098328E-3</v>
+        <v>1.0949180000000001E-3</v>
       </c>
       <c r="E6" s="4">
         <f t="shared" si="0"/>
-        <v>4.0116590528098328E-3</v>
+        <v>1.0949180000000001E-3</v>
       </c>
       <c r="F6" s="4">
         <f t="shared" si="0"/>
-        <v>4.0116590528098328E-3</v>
+        <v>1.0949180000000001E-3</v>
       </c>
       <c r="G6" s="4">
         <f t="shared" si="0"/>
-        <v>4.0116590528098328E-3</v>
+        <v>1.0949180000000001E-3</v>
       </c>
       <c r="H6" s="4">
         <f t="shared" si="0"/>
-        <v>4.0116590528098328E-3</v>
+        <v>1.0949180000000001E-3</v>
       </c>
       <c r="I6" s="4">
         <f t="shared" si="0"/>
-        <v>4.0116590528098328E-3</v>
+        <v>1.0949180000000001E-3</v>
       </c>
       <c r="J6" s="4">
         <f t="shared" si="0"/>
-        <v>4.0116590528098328E-3</v>
+        <v>1.0949180000000001E-3</v>
       </c>
       <c r="K6" s="4">
         <f t="shared" si="0"/>
-        <v>4.0116590528098328E-3</v>
+        <v>1.0949180000000001E-3</v>
       </c>
       <c r="L6" s="4">
         <f t="shared" si="0"/>
-        <v>4.0116590528098328E-3</v>
+        <v>1.0949180000000001E-3</v>
       </c>
       <c r="M6" s="4">
         <f t="shared" si="0"/>
-        <v>4.0116590528098328E-3</v>
+        <v>1.0949180000000001E-3</v>
       </c>
       <c r="N6" s="4">
         <f t="shared" si="0"/>
-        <v>4.0116590528098328E-3</v>
+        <v>1.0949180000000001E-3</v>
       </c>
       <c r="O6" s="4">
         <f t="shared" si="0"/>
-        <v>4.0116590528098328E-3</v>
+        <v>1.0949180000000001E-3</v>
       </c>
       <c r="P6" s="4">
         <f t="shared" si="0"/>
-        <v>4.0116590528098328E-3</v>
+        <v>1.0949180000000001E-3</v>
       </c>
       <c r="Q6" s="4">
         <f t="shared" si="0"/>
-        <v>4.0116590528098328E-3</v>
+        <v>1.0949180000000001E-3</v>
       </c>
       <c r="R6" s="4">
         <f t="shared" si="0"/>
-        <v>4.0116590528098328E-3</v>
+        <v>1.0949180000000001E-3</v>
       </c>
       <c r="S6" s="4">
         <f t="shared" si="0"/>
-        <v>4.0116590528098328E-3</v>
+        <v>1.0949180000000001E-3</v>
       </c>
       <c r="T6" s="4">
         <f t="shared" si="0"/>
-        <v>4.0116590528098328E-3</v>
+        <v>1.0949180000000001E-3</v>
       </c>
       <c r="U6" s="4">
         <f t="shared" si="0"/>
-        <v>4.0116590528098328E-3</v>
+        <v>1.0949180000000001E-3</v>
       </c>
       <c r="V6" s="4">
         <f t="shared" si="0"/>
-        <v>4.0116590528098328E-3</v>
+        <v>1.0949180000000001E-3</v>
       </c>
       <c r="W6" s="4">
         <f t="shared" si="0"/>
-        <v>4.0116590528098328E-3</v>
+        <v>1.0949180000000001E-3</v>
       </c>
       <c r="X6" s="4">
         <f t="shared" si="0"/>
-        <v>4.0116590528098328E-3</v>
+        <v>1.0949180000000001E-3</v>
       </c>
       <c r="Y6" s="4">
         <f t="shared" si="0"/>
-        <v>4.0116590528098328E-3</v>
+        <v>1.0949180000000001E-3</v>
       </c>
       <c r="Z6" s="4">
         <f t="shared" si="0"/>
-        <v>4.0116590528098328E-3</v>
+        <v>1.0949180000000001E-3</v>
       </c>
       <c r="AA6" s="4">
         <f t="shared" si="0"/>
-        <v>4.0116590528098328E-3</v>
+        <v>1.0949180000000001E-3</v>
       </c>
       <c r="AB6" s="4">
         <f t="shared" si="0"/>
-        <v>4.0116590528098328E-3</v>
+        <v>1.0949180000000001E-3</v>
       </c>
       <c r="AC6" s="4">
         <f t="shared" si="0"/>
-        <v>4.0116590528098328E-3</v>
+        <v>1.0949180000000001E-3</v>
       </c>
       <c r="AD6" s="4">
         <f t="shared" si="0"/>
-        <v>4.0116590528098328E-3</v>
+        <v>1.0949180000000001E-3</v>
       </c>
       <c r="AE6" s="4">
         <f t="shared" si="0"/>
-        <v>4.0116590528098328E-3</v>
+        <v>1.0949180000000001E-3</v>
       </c>
       <c r="AG6" s="4"/>
       <c r="AH6" s="4"/>
@@ -15117,123 +15174,123 @@
         <v>84</v>
       </c>
       <c r="B7" s="4">
-        <v>1.4123533664704075E-3</v>
+        <v>3.8547899999999999E-4</v>
       </c>
       <c r="C7" s="4">
         <f t="shared" si="1"/>
-        <v>1.4123533664704075E-3</v>
+        <v>3.8547899999999999E-4</v>
       </c>
       <c r="D7" s="4">
         <f t="shared" si="0"/>
-        <v>1.4123533664704075E-3</v>
+        <v>3.8547899999999999E-4</v>
       </c>
       <c r="E7" s="4">
         <f t="shared" si="0"/>
-        <v>1.4123533664704075E-3</v>
+        <v>3.8547899999999999E-4</v>
       </c>
       <c r="F7" s="4">
         <f t="shared" si="0"/>
-        <v>1.4123533664704075E-3</v>
+        <v>3.8547899999999999E-4</v>
       </c>
       <c r="G7" s="4">
         <f t="shared" si="0"/>
-        <v>1.4123533664704075E-3</v>
+        <v>3.8547899999999999E-4</v>
       </c>
       <c r="H7" s="4">
         <f t="shared" si="0"/>
-        <v>1.4123533664704075E-3</v>
+        <v>3.8547899999999999E-4</v>
       </c>
       <c r="I7" s="4">
         <f t="shared" si="0"/>
-        <v>1.4123533664704075E-3</v>
+        <v>3.8547899999999999E-4</v>
       </c>
       <c r="J7" s="4">
         <f t="shared" si="0"/>
-        <v>1.4123533664704075E-3</v>
+        <v>3.8547899999999999E-4</v>
       </c>
       <c r="K7" s="4">
         <f t="shared" si="0"/>
-        <v>1.4123533664704075E-3</v>
+        <v>3.8547899999999999E-4</v>
       </c>
       <c r="L7" s="4">
         <f t="shared" si="0"/>
-        <v>1.4123533664704075E-3</v>
+        <v>3.8547899999999999E-4</v>
       </c>
       <c r="M7" s="4">
         <f t="shared" si="0"/>
-        <v>1.4123533664704075E-3</v>
+        <v>3.8547899999999999E-4</v>
       </c>
       <c r="N7" s="4">
         <f t="shared" si="0"/>
-        <v>1.4123533664704075E-3</v>
+        <v>3.8547899999999999E-4</v>
       </c>
       <c r="O7" s="4">
         <f t="shared" si="0"/>
-        <v>1.4123533664704075E-3</v>
+        <v>3.8547899999999999E-4</v>
       </c>
       <c r="P7" s="4">
         <f t="shared" si="0"/>
-        <v>1.4123533664704075E-3</v>
+        <v>3.8547899999999999E-4</v>
       </c>
       <c r="Q7" s="4">
         <f t="shared" si="0"/>
-        <v>1.4123533664704075E-3</v>
+        <v>3.8547899999999999E-4</v>
       </c>
       <c r="R7" s="4">
         <f t="shared" si="0"/>
-        <v>1.4123533664704075E-3</v>
+        <v>3.8547899999999999E-4</v>
       </c>
       <c r="S7" s="4">
         <f t="shared" si="0"/>
-        <v>1.4123533664704075E-3</v>
+        <v>3.8547899999999999E-4</v>
       </c>
       <c r="T7" s="4">
         <f t="shared" si="0"/>
-        <v>1.4123533664704075E-3</v>
+        <v>3.8547899999999999E-4</v>
       </c>
       <c r="U7" s="4">
         <f t="shared" si="0"/>
-        <v>1.4123533664704075E-3</v>
+        <v>3.8547899999999999E-4</v>
       </c>
       <c r="V7" s="4">
         <f t="shared" si="0"/>
-        <v>1.4123533664704075E-3</v>
+        <v>3.8547899999999999E-4</v>
       </c>
       <c r="W7" s="4">
         <f t="shared" si="0"/>
-        <v>1.4123533664704075E-3</v>
+        <v>3.8547899999999999E-4</v>
       </c>
       <c r="X7" s="4">
         <f t="shared" si="0"/>
-        <v>1.4123533664704075E-3</v>
+        <v>3.8547899999999999E-4</v>
       </c>
       <c r="Y7" s="4">
         <f t="shared" si="0"/>
-        <v>1.4123533664704075E-3</v>
+        <v>3.8547899999999999E-4</v>
       </c>
       <c r="Z7" s="4">
         <f t="shared" si="0"/>
-        <v>1.4123533664704075E-3</v>
+        <v>3.8547899999999999E-4</v>
       </c>
       <c r="AA7" s="4">
         <f t="shared" si="0"/>
-        <v>1.4123533664704075E-3</v>
+        <v>3.8547899999999999E-4</v>
       </c>
       <c r="AB7" s="4">
         <f t="shared" si="0"/>
-        <v>1.4123533664704075E-3</v>
+        <v>3.8547899999999999E-4</v>
       </c>
       <c r="AC7" s="4">
         <f t="shared" si="0"/>
-        <v>1.4123533664704075E-3</v>
+        <v>3.8547899999999999E-4</v>
       </c>
       <c r="AD7" s="4">
         <f t="shared" si="0"/>
-        <v>1.4123533664704075E-3</v>
+        <v>3.8547899999999999E-4</v>
       </c>
       <c r="AE7" s="4">
         <f t="shared" si="0"/>
-        <v>1.4123533664704075E-3</v>
+        <v>3.8547899999999999E-4</v>
       </c>
       <c r="AG7" s="4"/>
       <c r="AH7" s="4"/>
@@ -15243,123 +15300,123 @@
         <v>85</v>
       </c>
       <c r="B8" s="4">
-        <v>5.467174321820931E-3</v>
+        <v>1.492178E-3</v>
       </c>
       <c r="C8" s="4">
         <f t="shared" si="1"/>
-        <v>5.467174321820931E-3</v>
+        <v>1.492178E-3</v>
       </c>
       <c r="D8" s="4">
         <f t="shared" si="0"/>
-        <v>5.467174321820931E-3</v>
+        <v>1.492178E-3</v>
       </c>
       <c r="E8" s="4">
         <f t="shared" si="0"/>
-        <v>5.467174321820931E-3</v>
+        <v>1.492178E-3</v>
       </c>
       <c r="F8" s="4">
         <f t="shared" si="0"/>
-        <v>5.467174321820931E-3</v>
+        <v>1.492178E-3</v>
       </c>
       <c r="G8" s="4">
         <f t="shared" si="0"/>
-        <v>5.467174321820931E-3</v>
+        <v>1.492178E-3</v>
       </c>
       <c r="H8" s="4">
         <f t="shared" si="0"/>
-        <v>5.467174321820931E-3</v>
+        <v>1.492178E-3</v>
       </c>
       <c r="I8" s="4">
         <f t="shared" si="0"/>
-        <v>5.467174321820931E-3</v>
+        <v>1.492178E-3</v>
       </c>
       <c r="J8" s="4">
         <f t="shared" si="0"/>
-        <v>5.467174321820931E-3</v>
+        <v>1.492178E-3</v>
       </c>
       <c r="K8" s="4">
         <f t="shared" si="0"/>
-        <v>5.467174321820931E-3</v>
+        <v>1.492178E-3</v>
       </c>
       <c r="L8" s="4">
         <f t="shared" si="0"/>
-        <v>5.467174321820931E-3</v>
+        <v>1.492178E-3</v>
       </c>
       <c r="M8" s="4">
         <f t="shared" si="0"/>
-        <v>5.467174321820931E-3</v>
+        <v>1.492178E-3</v>
       </c>
       <c r="N8" s="4">
         <f t="shared" si="0"/>
-        <v>5.467174321820931E-3</v>
+        <v>1.492178E-3</v>
       </c>
       <c r="O8" s="4">
         <f t="shared" si="0"/>
-        <v>5.467174321820931E-3</v>
+        <v>1.492178E-3</v>
       </c>
       <c r="P8" s="4">
         <f t="shared" si="0"/>
-        <v>5.467174321820931E-3</v>
+        <v>1.492178E-3</v>
       </c>
       <c r="Q8" s="4">
         <f t="shared" si="0"/>
-        <v>5.467174321820931E-3</v>
+        <v>1.492178E-3</v>
       </c>
       <c r="R8" s="4">
         <f t="shared" si="0"/>
-        <v>5.467174321820931E-3</v>
+        <v>1.492178E-3</v>
       </c>
       <c r="S8" s="4">
         <f t="shared" si="0"/>
-        <v>5.467174321820931E-3</v>
+        <v>1.492178E-3</v>
       </c>
       <c r="T8" s="4">
         <f t="shared" si="0"/>
-        <v>5.467174321820931E-3</v>
+        <v>1.492178E-3</v>
       </c>
       <c r="U8" s="4">
         <f t="shared" si="0"/>
-        <v>5.467174321820931E-3</v>
+        <v>1.492178E-3</v>
       </c>
       <c r="V8" s="4">
         <f t="shared" si="0"/>
-        <v>5.467174321820931E-3</v>
+        <v>1.492178E-3</v>
       </c>
       <c r="W8" s="4">
         <f t="shared" si="0"/>
-        <v>5.467174321820931E-3</v>
+        <v>1.492178E-3</v>
       </c>
       <c r="X8" s="4">
         <f t="shared" si="0"/>
-        <v>5.467174321820931E-3</v>
+        <v>1.492178E-3</v>
       </c>
       <c r="Y8" s="4">
         <f t="shared" si="0"/>
-        <v>5.467174321820931E-3</v>
+        <v>1.492178E-3</v>
       </c>
       <c r="Z8" s="4">
         <f t="shared" si="0"/>
-        <v>5.467174321820931E-3</v>
+        <v>1.492178E-3</v>
       </c>
       <c r="AA8" s="4">
         <f t="shared" si="0"/>
-        <v>5.467174321820931E-3</v>
+        <v>1.492178E-3</v>
       </c>
       <c r="AB8" s="4">
         <f t="shared" si="0"/>
-        <v>5.467174321820931E-3</v>
+        <v>1.492178E-3</v>
       </c>
       <c r="AC8" s="4">
         <f t="shared" si="0"/>
-        <v>5.467174321820931E-3</v>
+        <v>1.492178E-3</v>
       </c>
       <c r="AD8" s="4">
         <f t="shared" si="0"/>
-        <v>5.467174321820931E-3</v>
+        <v>1.492178E-3</v>
       </c>
       <c r="AE8" s="4">
         <f t="shared" si="0"/>
-        <v>5.467174321820931E-3</v>
+        <v>1.492178E-3</v>
       </c>
       <c r="AG8" s="4"/>
       <c r="AH8" s="4"/>
@@ -15375,12 +15432,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AE8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="31.140625" customWidth="1"/>
+    <col min="1" max="1" width="31.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="30">
+    <row r="1" spans="1:31">
       <c r="A1" s="14" t="s">
         <v>87</v>
       </c>
@@ -16148,11 +16205,11 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AK30"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="18.42578125" customWidth="1"/>
-    <col min="2" max="2" width="16.42578125" customWidth="1"/>
-    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="1" max="1" width="18.453125" customWidth="1"/>
+    <col min="2" max="2" width="16.453125" customWidth="1"/>
+    <col min="3" max="3" width="30.7265625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:37">
@@ -18445,7 +18502,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:H15"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" t="s">
@@ -18608,25 +18665,25 @@
         <v>18</v>
       </c>
       <c r="B7">
-        <v>5.8028780082485321E-3</v>
+        <v>1.583802E-3</v>
       </c>
       <c r="C7">
-        <v>1.8223914406069774E-3</v>
+        <v>4.9739300000000005E-4</v>
       </c>
       <c r="D7">
-        <v>1.8223914406069774E-3</v>
+        <v>4.9739300000000005E-4</v>
       </c>
       <c r="E7">
-        <v>1.8223914406069774E-3</v>
+        <v>4.9739300000000005E-4</v>
       </c>
       <c r="F7">
-        <v>4.0116590528098328E-3</v>
+        <v>1.0949180000000001E-3</v>
       </c>
       <c r="G7">
-        <v>1.4123533664704075E-3</v>
+        <v>3.8547899999999999E-4</v>
       </c>
       <c r="H7">
-        <v>5.467174321820931E-3</v>
+        <v>1.492178E-3</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -18819,9 +18876,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:B14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="50.42578125" customWidth="1"/>
+    <col min="1" max="1" width="50.453125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -18923,11 +18980,11 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:AL31"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="42.140625" customWidth="1"/>
-    <col min="2" max="2" width="26.42578125" customWidth="1"/>
-    <col min="3" max="3" width="42.85546875" customWidth="1"/>
+    <col min="1" max="1" width="42.1796875" customWidth="1"/>
+    <col min="2" max="2" width="26.453125" customWidth="1"/>
+    <col min="3" max="3" width="42.81640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:38">
@@ -19097,7 +19154,7 @@
         <v>5.76</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="30">
+    <row r="20" spans="1:4" ht="29">
       <c r="A20" s="9" t="s">
         <v>68</v>
       </c>
@@ -19115,7 +19172,7 @@
         <v>6.7042622950819668</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="30">
+    <row r="22" spans="1:4" ht="29">
       <c r="A22" s="9" t="s">
         <v>70</v>
       </c>
@@ -19201,10 +19258,10 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:BT15"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="15" max="15" width="11.42578125" customWidth="1"/>
+    <col min="15" max="15" width="11.453125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:72">
@@ -22648,12 +22705,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AH10"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="31.140625" customWidth="1"/>
+    <col min="1" max="1" width="31.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" ht="30">
+    <row r="1" spans="1:34">
       <c r="A1" s="14" t="s">
         <v>87</v>
       </c>
@@ -23682,12 +23739,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AH8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="31.140625" customWidth="1"/>
+    <col min="1" max="1" width="31.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" ht="30">
+    <row r="1" spans="1:34">
       <c r="A1" s="14" t="s">
         <v>87</v>
       </c>
@@ -24676,12 +24733,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AH8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="31.140625" customWidth="1"/>
+    <col min="1" max="1" width="31.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" ht="30">
+    <row r="1" spans="1:34">
       <c r="A1" s="14" t="s">
         <v>87</v>
       </c>
